--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>IFERROR(IF(D16&gt;=10,"Très rentable",IF(D16&gt;=5,"Rentable",IF(D16&gt;=2,"Faiblement rentable","Très faible"))),"—")</f>
+        <f>IFERROR(IF(D16&gt;=10,"Tres rentable",IF(D16&gt;=5,"Rentable",IF(D16&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v/>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>IFERROR(IF(D17&gt;=10,"Très rentable",IF(D17&gt;=5,"Rentable",IF(D17&gt;=2,"Faiblement rentable","Très faible"))),"—")</f>
+        <f>IFERROR(IF(D17&gt;=10,"Tres rentable",IF(D17&gt;=5,"Rentable",IF(D17&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v/>
       </c>
       <c r="F17" s="13" t="n"/>
@@ -1062,7 +1062,7 @@
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>IFERROR(IF(D18&gt;=10,"Très rentable",IF(D18&gt;=5,"Rentable",IF(D18&gt;=2,"Faiblement rentable","Très faible"))),"—")</f>
+        <f>IFERROR(IF(D18&gt;=10,"Tres rentable",IF(D18&gt;=5,"Rentable",IF(D18&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v/>
       </c>
       <c r="F18" s="13" t="n"/>
@@ -1081,7 +1081,7 @@
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>IFERROR(IF(D19&gt;=10,"Très rentable",IF(D19&gt;=5,"Rentable",IF(D19&gt;=2,"Faiblement rentable","Très faible"))),"—")</f>
+        <f>IFERROR(IF(D19&gt;=10,"Tres rentable",IF(D19&gt;=5,"Rentable",IF(D19&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v/>
       </c>
       <c r="F19" s="13" t="n"/>
@@ -1100,7 +1100,7 @@
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>IFERROR(IF(D20&gt;=10,"Très rentable",IF(D20&gt;=5,"Rentable",IF(D20&gt;=2,"Faiblement rentable","Très faible"))),"—")</f>
+        <f>IFERROR(IF(D20&gt;=10,"Tres rentable",IF(D20&gt;=5,"Rentable",IF(D20&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v/>
       </c>
       <c r="F20" s="13" t="n"/>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="E30" s="10">
-        <f>IFERROR(IF(C30&gt;15,"Surévalué",IF(C30&lt;9,"Sous-évalué","Zone normale")),"—")</f>
+        <f>IFERROR(IF(C30&gt;15,"Surevalue",IF(C30&lt;9,"Sous-evalue","Zone normale")),"-")</f>
         <v/>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="E31" s="10">
-        <f>IFERROR(IF(B24&gt;C30,"Action surévaluée","Action sous-évaluée"),"—")</f>
+        <f>IFERROR(IF(B24&gt;C30,"Action surevaluee","Action sous-evaluee"),"-")</f>
         <v/>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="E32" s="10">
-        <f>IFERROR(IF(C30&lt;1,"Décote comptable",IF(C30&lt;2,"Normal","Prime élevée")),"—")</f>
+        <f>IFERROR(IF(C30&lt;1,"Decote comptable",IF(C30&lt;2,"Normal","Prime elevee")),"-")</f>
         <v/>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="E33" s="10">
-        <f>IFERROR(IF(C30&gt;=15,"Excellent",IF(C30&gt;=10,"Bon",IF(C30&gt;=5,"Moyen","Faible"))),"—")</f>
+        <f>IFERROR(IF(C30&gt;=15,"Excellent",IF(C30&gt;=10,"Bon",IF(C30&gt;=5,"Moyen","Faible"))),"-")</f>
         <v/>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="E34" s="10">
-        <f>IFERROR(IF(C30&lt;22,"Décote (achat possible)","Surévaluation"),"—")</f>
+        <f>IFERROR(IF(C30&lt;22,"Decote (achat possible)","Surevaluation"),"-")</f>
         <v/>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B74" s="32">
-        <f>IFERROR(IF(B73&gt;C73,"✅ MARCHÉ BOURSIER","✅ ÉPARGNE"),"Saisir les données")</f>
+        <f>IFERROR(IF(B73&gt;C73,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v/>
       </c>
       <c r="C74" s="33" t="inlineStr">
@@ -2039,7 +2039,7 @@
         <v/>
       </c>
       <c r="E90" s="39">
-        <f>IFERROR(IF(D90&gt;0,"Zone SURVENTE ➜ Achat possible",IF(D90&lt;0,"Zone SURACHAT ➜ Vente possible","NEUTRE")),"—")</f>
+        <f>IFERROR(IF(D90&gt;0,"Zone SURVENTE - Achat possible",IF(D90&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
         <v/>
       </c>
       <c r="E94" s="10">
-        <f>IFERROR(IF(B24&lt;D94,"EN DESSOUS du PM ➜ Survente","AU-DESSUS du PM ➜ Surachat"),"—")</f>
+        <f>IFERROR(IF(B24&lt;D94,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v/>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
         <v/>
       </c>
       <c r="E95" s="10">
-        <f>IFERROR(IF(B24&lt;D95,"EN DESSOUS du PM ➜ Survente","AU-DESSUS du PM ➜ Surachat"),"—")</f>
+        <f>IFERROR(IF(B24&lt;D95,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v/>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
         <v/>
       </c>
       <c r="C102" s="27">
-        <f> BNPA × (1 + évol%)</f>
+        <f> BNPA x (1 + evol%)</f>
         <v/>
       </c>
       <c r="D102" s="13" t="n"/>
@@ -2217,11 +2217,11 @@
         <v/>
       </c>
       <c r="C103" s="27">
-        <f> Prix / BNPA actualisé</f>
+        <f> Prix / BNPA actualise</f>
         <v/>
       </c>
       <c r="D103" s="10">
-        <f>IFERROR(IF(B103&gt;15,"Surévalué — Surachat",IF(B103&lt;9,"Sous-évalué — Survente","Normal (9–15)")),"—")</f>
+        <f>IFERROR(IF(B103&gt;15,"Surevalue - Surachat",IF(B103&lt;9,"Sous-evalue - Survente","Normal (9-15)")),"-")</f>
         <v/>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
         <v/>
       </c>
       <c r="C110" s="27">
-        <f> DVD × (1 + évol%)</f>
+        <f> DVD x (1 + evol%)</f>
         <v/>
       </c>
       <c r="D110" s="13" t="n"/>
@@ -2333,7 +2333,7 @@
         <v/>
       </c>
       <c r="C112" s="27">
-        <f> 100 × Dprev / Rend%</f>
+        <f> 100 x Dprev / Rend%</f>
         <v/>
       </c>
       <c r="D112" s="13" t="n"/>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
       <c r="C113" s="27">
-        <f> PCD × 0.95</f>
+        <f> PCD x 0.95</f>
         <v/>
       </c>
       <c r="D113" s="13" t="n"/>
@@ -2365,7 +2365,7 @@
         <v/>
       </c>
       <c r="C114" s="27">
-        <f> PCD × 1.05</f>
+        <f> PCD x 1.05</f>
         <v/>
       </c>
       <c r="D114" s="13" t="n"/>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B115" s="44">
-        <f>IFERROR(IF(NOT(ISNUMBER(B112)),"PCD N/A (pas de dividende)",IF(B24&lt;B113,"EN DESSOUS zone cible ➜ Survente",IF(B24&gt;B114,"AU-DESSUS zone cible ➜ Surachat","DANS LA ZONE"))),"")</f>
+        <f>IFERROR(IF(NOT(ISNUMBER(B112)),"PCD N/A (pas de dividende)",IF(B24&lt;B113,"EN DESSOUS zone cible - Survente",IF(B24&gt;B114,"AU-DESSUS zone cible - Surachat","DANS LA ZONE"))),"")</f>
         <v/>
       </c>
       <c r="C115" s="27" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B123" s="46">
-        <f>IFERROR(IF(B120=0,"D₁ non renseigné",B120/((B121/100)-(B122/100))),"")</f>
+        <f>IFERROR(IF(B120=0,"D1 non renseigne",B120/((B121/100)-(B122/100))),"")</f>
         <v/>
       </c>
       <c r="C123" s="27" t="inlineStr">
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="B124" s="47">
-        <f>IFERROR(IF(NOT(ISNUMBER(B123)),"Renseigner D₁",IF(B24&lt;B123*0.95,"Prix sous P₀ ➜ Opportunité d'achat",IF(B24&gt;B123*1.05,"Prix sur P₀ ➜ Surévalué","Dans la zone"))),"")</f>
+        <f>IFERROR(IF(NOT(ISNUMBER(B123)),"Renseigner D1",IF(B24&lt;B123*0.95,"Prix sous P0 - Opportunite achat",IF(B24&gt;B123*1.05,"Prix sur P0 - Surevalue","Dans la zone"))),"")</f>
         <v/>
       </c>
       <c r="C124" s="27" t="inlineStr">
@@ -2565,7 +2565,7 @@
         <v/>
       </c>
       <c r="C129" s="27">
-        <f> Prix × 0.90</f>
+        <f> Prix x 0.90</f>
         <v/>
       </c>
       <c r="D129" s="13" t="n"/>
@@ -2597,7 +2597,7 @@
         <v/>
       </c>
       <c r="C131" s="27">
-        <f> Prix − Stop</f>
+        <f> Prix - Stop</f>
         <v/>
       </c>
       <c r="D131" s="13" t="n"/>
@@ -2614,7 +2614,7 @@
         <v/>
       </c>
       <c r="C132" s="27">
-        <f> Objectif − Prix</f>
+        <f> Objectif - Prix</f>
         <v/>
       </c>
       <c r="D132" s="13" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D133" s="13" t="n"/>
       <c r="E133" s="47">
-        <f>IFERROR(IF(B133&gt;=2,"✅ Bon (≥ 2:1)",IF(B133&gt;=1,"⚠ Acceptable (1:1)","🚫 Mauvais")),"")</f>
+        <f>IFERROR(IF(B133&gt;=2,"Bon (&gt;= 2:1)",IF(B133&gt;=1,"Acceptable (1:1)","Mauvais")),"")</f>
         <v/>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
         <v/>
       </c>
       <c r="E27" s="26">
-        <f>IFERROR(IF(E14/24&gt;=0.7,"✅ Solide",IF(E14/24&gt;=0.5,"⚠ Moyen","🚫 Faible")),"—")</f>
+        <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v/>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         <v/>
       </c>
       <c r="E28" s="26">
-        <f>IFERROR(IF(E23/15&gt;=0.7,"✅ Solide",IF(E23/15&gt;=0.5,"⚠ Moyen","🚫 Faible")),"—")</f>
+        <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v/>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
         <v/>
       </c>
       <c r="E29" s="58">
-        <f>IFERROR(IF(B29/39&gt;=0.7,"✅ ACHETER",IF(B29/39&gt;=0.5,"⚠ SURVEILLER","🚫 ÉVITER")),"—")</f>
+        <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v/>
       </c>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="328">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -94,811 +94,802 @@
     <t>A4 — INDICATEURS DE VALORISATION</t>
   </si>
   <si>
+    <t>Indicateur [formule]</t>
+  </si>
+  <si>
+    <t>Valeur calculee</t>
+  </si>
+  <si>
+    <t>Zone reference</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Prix actuel de l'action (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir le prix actuel</t>
+  </si>
+  <si>
+    <t>BNPA — Benefice Net Par Action (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- RN / Nb titres (rapport annuel)</t>
+  </si>
+  <si>
+    <t>Capitaux Propres (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan comptable</t>
+  </si>
+  <si>
+    <t>Capitalisation boursiere (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Prix x Nb titres</t>
+  </si>
+  <si>
+    <t>Nombre de titres en circulation</t>
+  </si>
+  <si>
+    <t>&lt;-- BRVM.org</t>
+  </si>
+  <si>
+    <t>PER — Price Earning Ratio  [= Prix / BNPA]</t>
+  </si>
+  <si>
+    <t>Zone : 9-15</t>
+  </si>
+  <si>
+    <t>VMC — Valeur Mathematique Comptable  [= Capitaux Propres / Nb titres]</t>
+  </si>
+  <si>
+    <t>Prix &lt; VMC = bon</t>
+  </si>
+  <si>
+    <t>PBR — Price to Book Ratio  [= Capitalisation / Capitaux Propres]</t>
+  </si>
+  <si>
+    <t>&lt; 1 = decote</t>
+  </si>
+  <si>
+    <t>ROE — Return on Equity (%)  [= RN / Capitaux Propres x 100]</t>
+  </si>
+  <si>
+    <t>&gt; 10% = bon</t>
+  </si>
+  <si>
+    <t>RVC — PER x PBR (Lynch)  [= PER x PBR]</t>
+  </si>
+  <si>
+    <t>&lt; 22 = decote</t>
+  </si>
+  <si>
+    <t>A5 — DIVIDENDES &amp; TAUX DE DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>Dividende BRUT (FCFA)</t>
+  </si>
+  <si>
+    <t>Dividende NET (FCFA)</t>
+  </si>
+  <si>
+    <t>BNPA (FCFA)</t>
+  </si>
+  <si>
+    <t>Taux distrib. %</t>
+  </si>
+  <si>
+    <t>Rendement %</t>
+  </si>
+  <si>
+    <t>Progression %</t>
+  </si>
+  <si>
+    <t>TOTAL / MOYENNE</t>
+  </si>
+  <si>
+    <t>A6 — FONDS PROPRES (FCFA)</t>
+  </si>
+  <si>
+    <t>Composante</t>
+  </si>
+  <si>
+    <t>Annee N-1</t>
+  </si>
+  <si>
+    <t>Annee N</t>
+  </si>
+  <si>
+    <t>Variation %</t>
+  </si>
+  <si>
+    <t>Capital souscrit</t>
+  </si>
+  <si>
+    <t>Reserves</t>
+  </si>
+  <si>
+    <t>Report a nouveau</t>
+  </si>
+  <si>
+    <t>Dividendes verses</t>
+  </si>
+  <si>
+    <t>TOTAL FONDS PROPRES</t>
+  </si>
+  <si>
+    <t>A7 — NOTATION FINANCIERE &amp; ACTIVITES RECENTES</t>
+  </si>
+  <si>
     <t>Indicateur</t>
   </si>
   <si>
     <t>Valeur</t>
   </si>
   <si>
-    <t>Description formule</t>
-  </si>
-  <si>
-    <t>Valeur calculee</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Prix actuel de l'action (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir le prix actuel</t>
-  </si>
-  <si>
-    <t>BNPA — Benefice Net Par Action (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- RN / Nb titres (rapport annuel)</t>
-  </si>
-  <si>
-    <t>Capitaux Propres (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Bilan comptable</t>
-  </si>
-  <si>
-    <t>Capitalisation boursiere (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Prix x Nb titres</t>
-  </si>
-  <si>
-    <t>Nombre de titres en circulation</t>
-  </si>
-  <si>
-    <t>&lt;-- BRVM.org</t>
-  </si>
-  <si>
-    <t>PER — Price Earning Ratio</t>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Date rapport</t>
+  </si>
+  <si>
+    <t>Notation court terme</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Agence de notation</t>
+  </si>
+  <si>
+    <t>Notation long terme</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Variation CA/PNB (dernier trimestre)</t>
+  </si>
+  <si>
+    <t>RichBourse</t>
+  </si>
+  <si>
+    <t>Variation Resultat Net (dernier trimestre)</t>
+  </si>
+  <si>
+    <t>A8 — COMPARAISON MARCHE BOURSIER VS EPARGNE</t>
+  </si>
+  <si>
+    <t>Parametre</t>
+  </si>
+  <si>
+    <t>Marche Boursier</t>
+  </si>
+  <si>
+    <t>Epargne (saisir rendement %)</t>
+  </si>
+  <si>
+    <t>Montant investi (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix d'achat historique (FCFA)</t>
+  </si>
+  <si>
+    <t>CMP = Prix x 1,014 (frais 1,4%)</t>
+  </si>
+  <si>
+    <t>Nombre de titres acquis</t>
+  </si>
+  <si>
+    <t>Prix actuel du titre (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix net apres taxe cession 1,4% (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus-value unitaire (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus-value totale (FCFA)</t>
+  </si>
+  <si>
+    <t>Total dividendes recus par titre (FCFA)</t>
+  </si>
+  <si>
+    <t>Rendement dividendes total (FCFA)</t>
+  </si>
+  <si>
+    <t>RENDEMENT TOTAL (FCFA)</t>
+  </si>
+  <si>
+    <t>PERFORMANCE (%)</t>
+  </si>
+  <si>
+    <t>VERDICT</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir rendement epargne % ici</t>
+  </si>
+  <si>
+    <t>A9 — CONCLUSION ANALYSE FONDAMENTALE (texte libre)</t>
+  </si>
+  <si>
+    <t>B — ANALYSE TECHNIQUE</t>
+  </si>
+  <si>
+    <t>B1 — INDICATEURS TECHNIQUES (saisie depuis graphique)</t>
+  </si>
+  <si>
+    <t>Signal observe</t>
+  </si>
+  <si>
+    <t>Valeur / Niveau</t>
+  </si>
+  <si>
+    <t>Score auto</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Moyenne Mobile 20 jours (MM20)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir signal</t>
+  </si>
+  <si>
+    <t>Zone de survente : cours EN DESSOUS de la MM20</t>
+  </si>
+  <si>
+    <t>Bandes de Bollinger</t>
+  </si>
+  <si>
+    <t>Zone de survente : cours touche la bande inferieure</t>
+  </si>
+  <si>
+    <t>MACD</t>
+  </si>
+  <si>
+    <t>Zone de survente : MACD croise Signal a la hausse</t>
+  </si>
+  <si>
+    <t>RSI (saisir valeur en col C)</t>
+  </si>
+  <si>
+    <t>&lt; 30 survente | 30-70 neutre | &gt; 70 surachat</t>
+  </si>
+  <si>
+    <t>Volume (tendance recente)</t>
+  </si>
+  <si>
+    <t>Volume croissant sur baisse = accumulation = survente</t>
+  </si>
+  <si>
+    <t>SCORE TECHNIQUE (max +5 / min -5)</t>
+  </si>
+  <si>
+    <t>B2 — PRIX MEDIANS (PM)</t>
+  </si>
+  <si>
+    <t>Horizon</t>
+  </si>
+  <si>
+    <t>Plus Haut (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus Bas (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix Median</t>
+  </si>
+  <si>
+    <t>Signal (vs prix actuel B24)</t>
+  </si>
+  <si>
+    <t>52 semaines (1 an)</t>
+  </si>
+  <si>
+    <t>2 ans</t>
+  </si>
+  <si>
+    <t>B3 — PER ACTUALISE (integre la derniere evolution du RN)</t>
+  </si>
+  <si>
+    <t>Source / Formule</t>
+  </si>
+  <si>
+    <t>Prix actuel (FCFA)</t>
+  </si>
+  <si>
+    <t>Lie a B24</t>
+  </si>
+  <si>
+    <t>BNPA N (FCFA)</t>
+  </si>
+  <si>
+    <t>Lie a B25</t>
+  </si>
+  <si>
+    <t>Evolution RN dernier trimestre (%)</t>
+  </si>
+  <si>
+    <t>RichBourse / Rapport trimestriel</t>
+  </si>
+  <si>
+    <t>BNPA actualise (FCFA)</t>
+  </si>
+  <si>
+    <t>= BNPA x (1 + evol%)</t>
+  </si>
+  <si>
+    <t>PER actualise</t>
+  </si>
+  <si>
+    <t>= Prix / BNPA actualise</t>
+  </si>
+  <si>
+    <t>B4 — PRIX CIBLE AUX DIVIDENDES (PCD)</t>
+  </si>
+  <si>
+    <t>Note : Le PCD n'est pertinent que si l'entreprise verse des dividendes. Si dividende = 0, utiliser B5 (Gordon-Shapiro).</t>
+  </si>
+  <si>
+    <t>Formule</t>
+  </si>
+  <si>
+    <t>Evolution RN (%)</t>
+  </si>
+  <si>
+    <t>Meme valeur qu'en B3</t>
+  </si>
+  <si>
+    <t>Dividende brut N (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir le dernier dividende verse</t>
+  </si>
+  <si>
+    <t>Dividende previsionnel (FCFA)</t>
+  </si>
+  <si>
+    <t>= Dividende x (1 + evol%)</t>
+  </si>
+  <si>
+    <t>Rendement sectoriel BRVM (%)</t>
+  </si>
+  <si>
+    <t>Reference : 5-8% (modifiable)</t>
+  </si>
+  <si>
+    <t>PCD = 100 x DVD_prev / Rendement</t>
+  </si>
+  <si>
+    <t>= 100 x Dprev / Rendement%</t>
+  </si>
+  <si>
+    <t>Zone cible basse (-5%)</t>
+  </si>
+  <si>
+    <t>= PCD x 0.95</t>
+  </si>
+  <si>
+    <t>Zone cible haute (+5%)</t>
+  </si>
+  <si>
+    <t>= PCD x 1.05</t>
+  </si>
+  <si>
+    <t>Signal (prix B24 vs zone cible)</t>
+  </si>
+  <si>
+    <t>Calcul automatique</t>
+  </si>
+  <si>
+    <t>B5 — MODELE DE GORDON-SHAPIRO   P0 = D1 / (r - g)</t>
+  </si>
+  <si>
+    <t>D1 = dividende attendu l'an prochain | r = taux exige | g = taux croissance dividendes</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>D1 - Dividende attendu (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Hypothese ou dernier DVD x (1+g)</t>
+  </si>
+  <si>
+    <t>r - Taux de rentabilite exige (%)</t>
+  </si>
+  <si>
+    <t>Cout du capital / rendement cible (ex: 8%)</t>
+  </si>
+  <si>
+    <t>g - Taux de croissance DVD (%)</t>
+  </si>
+  <si>
+    <t>Croissance annuelle supposee (ex: 2%)</t>
+  </si>
+  <si>
+    <t>P0 = D1 / (r - g)  [FCFA]</t>
+  </si>
+  <si>
+    <t>Prix theorique calcule automatiquement</t>
+  </si>
+  <si>
+    <t>Signal prix actuel vs P0</t>
+  </si>
+  <si>
+    <t>B6 — GESTION DU RISQUE : STOP-LOSS &amp; RISK/REWARD</t>
+  </si>
+  <si>
+    <t>Formule/Note</t>
+  </si>
+  <si>
+    <t>Prix d'achat vise (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir prix entree prevue</t>
+  </si>
+  <si>
+    <t>Stop-Loss = Prix x 0,90 (FCFA)</t>
+  </si>
+  <si>
+    <t>= Prix x 0.90 (perte max 10%)</t>
+  </si>
+  <si>
+    <t>Objectif Take Profit (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir objectif de prix</t>
+  </si>
+  <si>
+    <t>Perte potentielle / titre (FCFA)</t>
+  </si>
+  <si>
+    <t>= Prix - Stop</t>
+  </si>
+  <si>
+    <t>Gain potentiel / titre (FCFA)</t>
+  </si>
+  <si>
+    <t>= Objectif - Prix</t>
+  </si>
+  <si>
+    <t>Ratio Risk / Reward</t>
+  </si>
+  <si>
+    <t>= Gain / Perte  (objectif &gt;= 2)</t>
+  </si>
+  <si>
+    <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
+  </si>
+  <si>
+    <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
+  </si>
+  <si>
+    <t>Societe : [NOM]   |   Date : [JJ/MM/AAAA]   |   Prix analyse : [FCFA]</t>
+  </si>
+  <si>
+    <t>SCORECARD FONDAMENTALE</t>
+  </si>
+  <si>
+    <t>Critere</t>
+  </si>
+  <si>
+    <t>Valeur (depuis ETUDE)</t>
+  </si>
+  <si>
+    <t>Zone normale</t>
+  </si>
+  <si>
+    <t>Score (0-3)</t>
+  </si>
+  <si>
+    <t>Croissance CA (N/N-4 %)</t>
+  </si>
+  <si>
+    <t>&lt;-- depuis ETUDE</t>
+  </si>
+  <si>
+    <t>&gt; 10%</t>
+  </si>
+  <si>
+    <t>&lt;-- saisir signal</t>
+  </si>
+  <si>
+    <t>Croissance RN (N/N-4 %)</t>
+  </si>
+  <si>
+    <t>Marge nette moyenne (%)</t>
+  </si>
+  <si>
+    <t>&gt; 5%</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>9 - 15</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>&lt; 1 ideal</t>
+  </si>
+  <si>
+    <t>ROE (%)</t>
+  </si>
+  <si>
+    <t>Rendement dividende (%)</t>
+  </si>
+  <si>
+    <t>&gt; 3%</t>
+  </si>
+  <si>
+    <t>RVC (PER x PBR)</t>
+  </si>
+  <si>
+    <t>&lt; 22</t>
+  </si>
+  <si>
+    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
+  </si>
+  <si>
+    <t>SCORECARD TECHNIQUE</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
+  </si>
+  <si>
+    <t>-5 a +5</t>
+  </si>
+  <si>
+    <t>Prix Medians PM1 et PM2 (B2)</t>
+  </si>
+  <si>
+    <t>&lt; PM = survente</t>
+  </si>
+  <si>
+    <t>PER actualise (B3)</t>
+  </si>
+  <si>
+    <t>9-15 = normal</t>
+  </si>
+  <si>
+    <t>PCD / Gordon-Shapiro (B4/B5)</t>
+  </si>
+  <si>
+    <t>&lt; PCD = survente</t>
+  </si>
+  <si>
+    <t>Risk/Reward (B6)</t>
+  </si>
+  <si>
+    <t>&gt;= 2 = bon</t>
+  </si>
+  <si>
+    <t>SCORE TECHNIQUE TOTAL (/15)</t>
+  </si>
+  <si>
+    <t>VERDICT GLOBAL</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>% atteint</t>
+  </si>
+  <si>
+    <t>Appreciation</t>
+  </si>
+  <si>
+    <t>Score Fondamental</t>
+  </si>
+  <si>
+    <t>Score Technique</t>
+  </si>
+  <si>
+    <t>SCORE TOTAL</t>
+  </si>
+  <si>
+    <t>RECOMMANDATION FINALE (texte libre)</t>
+  </si>
+  <si>
+    <t>PROFIL DE LA SOCIETE</t>
+  </si>
+  <si>
+    <t>IDENTIFICATION</t>
+  </si>
+  <si>
+    <t>Nom de la societe</t>
+  </si>
+  <si>
+    <t>Ticker BRVM</t>
+  </si>
+  <si>
+    <t>Secteur d'activite</t>
+  </si>
+  <si>
+    <t>Pays d'origine</t>
+  </si>
+  <si>
+    <t>Date d'introduction en bourse</t>
+  </si>
+  <si>
+    <t>CAPITAL &amp; ACTIONNARIAT</t>
+  </si>
+  <si>
+    <t>Capital social (FCFA)</t>
+  </si>
+  <si>
+    <t>Nombre de titres</t>
+  </si>
+  <si>
+    <t>Flottant (%)</t>
+  </si>
+  <si>
+    <t>Principaux actionnaires</t>
+  </si>
+  <si>
+    <t>LIQUIDITE DU TITRE (critique sur BRVM)</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (titres)</t>
+  </si>
+  <si>
+    <t>&lt;-- Source : BRVM.org</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (FCFA)</t>
+  </si>
+  <si>
+    <t>Frequence de cotation (%)</t>
+  </si>
+  <si>
+    <t>&lt;-- % seances avec transaction</t>
+  </si>
+  <si>
+    <t>Appreciation liquidite</t>
+  </si>
+  <si>
+    <t>&lt;-- Forte / Moyenne / Faible</t>
+  </si>
+  <si>
+    <t>NOTATION &amp; CONFORMITE</t>
+  </si>
+  <si>
+    <t>Note court terme</t>
+  </si>
+  <si>
+    <t>Note long terme</t>
+  </si>
+  <si>
+    <t>Dividende verse regulierement ?</t>
+  </si>
+  <si>
+    <t>&lt;-- Oui / Non</t>
+  </si>
+  <si>
+    <t>SOURCES D'INFORMATION</t>
+  </si>
+  <si>
+    <t>Rapport annuel</t>
+  </si>
+  <si>
+    <t>&lt;-- Lien ou date</t>
+  </si>
+  <si>
+    <t>Site de la societe</t>
+  </si>
+  <si>
+    <t>Profil RichBourse</t>
+  </si>
+  <si>
+    <t>&lt;-- richbourse.com</t>
+  </si>
+  <si>
+    <t>Profil BRVM</t>
+  </si>
+  <si>
+    <t>&lt;-- brvm.org</t>
+  </si>
+  <si>
+    <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
+  </si>
+  <si>
+    <t>Expression mathematique</t>
+  </si>
+  <si>
+    <t>Unite</t>
+  </si>
+  <si>
+    <t>Interpretation / Seuils BRVM</t>
+  </si>
+  <si>
+    <t>ANALYSE FONDAMENTALE</t>
+  </si>
+  <si>
+    <t>Croissance N/N-4</t>
+  </si>
+  <si>
+    <t>(N - N-4) / |N-4| x 100</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Positif = croissance. Negatif = contraction. Seuil : &gt; 10%/an = excellent</t>
+  </si>
+  <si>
+    <t>TCAM (CAGR)</t>
+  </si>
+  <si>
+    <t>(N / N-4)^(1/4) - 1</t>
+  </si>
+  <si>
+    <t>Taux de Croissance Annuel Moyen sur 4 ans</t>
+  </si>
+  <si>
+    <t>Marge Nette</t>
+  </si>
+  <si>
+    <t>RN / CA x 100</t>
+  </si>
+  <si>
+    <t>&lt; 2% = faible | 2-5% = moyen | &gt; 5% = bon | &gt; 10% = tres bon</t>
   </si>
   <si>
     <t>Prix / BNPA</t>
   </si>
   <si>
-    <t>=B24/B25</t>
-  </si>
-  <si>
-    <t>Zone : 9-15</t>
-  </si>
-  <si>
-    <t>VMC — Valeur Mathematique Comptable (FCFA)</t>
+    <t>fois</t>
+  </si>
+  <si>
+    <t>Zone normale BRVM : 9-15. &gt; 15 = surevalue, &lt; 9 = sous-evalue</t>
+  </si>
+  <si>
+    <t>VMC</t>
   </si>
   <si>
     <t>Capitaux Propres / Nb titres</t>
   </si>
   <si>
-    <t>=B26/B28</t>
-  </si>
-  <si>
-    <t>Prix &lt; VMC = bon</t>
-  </si>
-  <si>
-    <t>PBR — Price to Book Ratio</t>
+    <t>FCFA</t>
+  </si>
+  <si>
+    <t>Prix &lt; VMC = action decotee (achat potentiellement interessant)</t>
   </si>
   <si>
     <t>Capitalisation / Capitaux Propres</t>
   </si>
   <si>
-    <t>=B27/B26</t>
-  </si>
-  <si>
-    <t>&lt; 1 = decote</t>
-  </si>
-  <si>
-    <t>ROE — Return on Equity (%)</t>
+    <t>&lt; 1 = decote sur actif net | &gt; 2 = prime significative</t>
+  </si>
+  <si>
+    <t>ROE</t>
   </si>
   <si>
     <t>RN / Capitaux Propres x 100</t>
   </si>
   <si>
-    <t>=F12*1000000/B26*100</t>
-  </si>
-  <si>
-    <t>&gt; 10% = bon</t>
-  </si>
-  <si>
-    <t>RVC — PER x PBR (Lynch)</t>
+    <t>&lt; 5% = faible | 5-10% = moyen | 10-15% = bon | &gt; 15% = excellent</t>
+  </si>
+  <si>
+    <t>RVC (Lynch)</t>
   </si>
   <si>
     <t>PER x PBR</t>
-  </si>
-  <si>
-    <t>=D30*D32</t>
-  </si>
-  <si>
-    <t>&lt; 22 = decote</t>
-  </si>
-  <si>
-    <t>A5 — DIVIDENDES &amp; TAUX DE DISTRIBUTION</t>
-  </si>
-  <si>
-    <t>Dividende brut (FCFA)</t>
-  </si>
-  <si>
-    <t>BNPA (FCFA)</t>
-  </si>
-  <si>
-    <t>Taux distrib. %</t>
-  </si>
-  <si>
-    <t>Rendement %</t>
-  </si>
-  <si>
-    <t>Progression %</t>
-  </si>
-  <si>
-    <t>TOTAL / MOYENNE</t>
-  </si>
-  <si>
-    <t>A6 — FONDS PROPRES (FCFA)</t>
-  </si>
-  <si>
-    <t>Composante</t>
-  </si>
-  <si>
-    <t>Annee N-1</t>
-  </si>
-  <si>
-    <t>Annee N</t>
-  </si>
-  <si>
-    <t>Variation %</t>
-  </si>
-  <si>
-    <t>Capital souscrit</t>
-  </si>
-  <si>
-    <t>Reserves</t>
-  </si>
-  <si>
-    <t>Report a nouveau</t>
-  </si>
-  <si>
-    <t>Dividendes verses</t>
-  </si>
-  <si>
-    <t>TOTAL FONDS PROPRES</t>
-  </si>
-  <si>
-    <t>A7 — NOTATION FINANCIERE &amp; ACTIVITES RECENTES</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Date rapport</t>
-  </si>
-  <si>
-    <t>Notation court terme</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>Agence de notation</t>
-  </si>
-  <si>
-    <t>Notation long terme</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Variation CA/PNB (dernier trimestre)</t>
-  </si>
-  <si>
-    <t>RichBourse</t>
-  </si>
-  <si>
-    <t>Variation Resultat Net (dernier trimestre)</t>
-  </si>
-  <si>
-    <t>A8 — COMPARAISON MARCHE BOURSIER VS EPARGNE</t>
-  </si>
-  <si>
-    <t>Parametre</t>
-  </si>
-  <si>
-    <t>Marche Boursier</t>
-  </si>
-  <si>
-    <t>Epargne (saisir rendement %)</t>
-  </si>
-  <si>
-    <t>Montant investi (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix d'achat historique (FCFA)</t>
-  </si>
-  <si>
-    <t>CMP = Prix x 1,014 (frais 1,4%)</t>
-  </si>
-  <si>
-    <t>Nombre de titres acquis</t>
-  </si>
-  <si>
-    <t>Prix actuel du titre (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix net apres taxe cession 1,4% (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus-value unitaire (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus-value totale (FCFA)</t>
-  </si>
-  <si>
-    <t>Total dividendes recus par titre (FCFA)</t>
-  </si>
-  <si>
-    <t>Rendement dividendes total (FCFA)</t>
-  </si>
-  <si>
-    <t>RENDEMENT TOTAL (FCFA)</t>
-  </si>
-  <si>
-    <t>PERFORMANCE (%)</t>
-  </si>
-  <si>
-    <t>VERDICT</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir rendement epargne % ici</t>
-  </si>
-  <si>
-    <t>A9 — CONCLUSION ANALYSE FONDAMENTALE (texte libre)</t>
-  </si>
-  <si>
-    <t>B — ANALYSE TECHNIQUE</t>
-  </si>
-  <si>
-    <t>B1 — INDICATEURS TECHNIQUES (saisie depuis graphique)</t>
-  </si>
-  <si>
-    <t>Signal observe</t>
-  </si>
-  <si>
-    <t>Valeur / Niveau</t>
-  </si>
-  <si>
-    <t>Score auto</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>Moyenne Mobile 20 jours (MM20)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir signal</t>
-  </si>
-  <si>
-    <t>Zone de survente : cours EN DESSOUS de la MM20</t>
-  </si>
-  <si>
-    <t>Bandes de Bollinger</t>
-  </si>
-  <si>
-    <t>Zone de survente : cours touche la bande inferieure</t>
-  </si>
-  <si>
-    <t>MACD</t>
-  </si>
-  <si>
-    <t>Zone de survente : MACD croise Signal a la hausse</t>
-  </si>
-  <si>
-    <t>RSI (saisir valeur en col C)</t>
-  </si>
-  <si>
-    <t>&lt; 30 survente | 30-70 neutre | &gt; 70 surachat</t>
-  </si>
-  <si>
-    <t>Volume (tendance recente)</t>
-  </si>
-  <si>
-    <t>Volume croissant sur baisse = accumulation = survente</t>
-  </si>
-  <si>
-    <t>SCORE TECHNIQUE (max +5 / min -5)</t>
-  </si>
-  <si>
-    <t>B2 — PRIX MEDIANS (PM)</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Plus Haut (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus Bas (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix Median</t>
-  </si>
-  <si>
-    <t>Signal (vs prix actuel B24)</t>
-  </si>
-  <si>
-    <t>52 semaines (1 an)</t>
-  </si>
-  <si>
-    <t>2 ans</t>
-  </si>
-  <si>
-    <t>B3 — PER ACTUALISE (integre la derniere evolution du RN)</t>
-  </si>
-  <si>
-    <t>Source / Formule</t>
-  </si>
-  <si>
-    <t>Prix actuel (FCFA)</t>
-  </si>
-  <si>
-    <t>Lie a B24</t>
-  </si>
-  <si>
-    <t>BNPA N (FCFA)</t>
-  </si>
-  <si>
-    <t>Lie a B25</t>
-  </si>
-  <si>
-    <t>Evolution RN dernier trimestre (%)</t>
-  </si>
-  <si>
-    <t>RichBourse / Rapport trimestriel</t>
-  </si>
-  <si>
-    <t>BNPA actualise (FCFA)</t>
-  </si>
-  <si>
-    <t>= BNPA x (1 + evol%)</t>
-  </si>
-  <si>
-    <t>PER actualise</t>
-  </si>
-  <si>
-    <t>= Prix / BNPA actualise</t>
-  </si>
-  <si>
-    <t>B4 — PRIX CIBLE AUX DIVIDENDES (PCD)</t>
-  </si>
-  <si>
-    <t>Note : Le PCD n'est pertinent que si l'entreprise verse des dividendes. Si dividende = 0, utiliser B5 (Gordon-Shapiro).</t>
-  </si>
-  <si>
-    <t>Formule</t>
-  </si>
-  <si>
-    <t>Evolution RN (%)</t>
-  </si>
-  <si>
-    <t>Meme valeur qu'en B3</t>
-  </si>
-  <si>
-    <t>Dividende brut N (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir le dernier dividende verse</t>
-  </si>
-  <si>
-    <t>Dividende previsionnel (FCFA)</t>
-  </si>
-  <si>
-    <t>= Dividende x (1 + evol%)</t>
-  </si>
-  <si>
-    <t>Rendement sectoriel BRVM (%)</t>
-  </si>
-  <si>
-    <t>Reference : 5-8% (modifiable)</t>
-  </si>
-  <si>
-    <t>PCD = 100 x DVD_prev / Rendement</t>
-  </si>
-  <si>
-    <t>= 100 x Dprev / Rendement%</t>
-  </si>
-  <si>
-    <t>Zone cible basse (-5%)</t>
-  </si>
-  <si>
-    <t>= PCD x 0.95</t>
-  </si>
-  <si>
-    <t>Zone cible haute (+5%)</t>
-  </si>
-  <si>
-    <t>= PCD x 1.05</t>
-  </si>
-  <si>
-    <t>Signal (prix B24 vs zone cible)</t>
-  </si>
-  <si>
-    <t>Calcul automatique</t>
-  </si>
-  <si>
-    <t>B5 — MODELE DE GORDON-SHAPIRO   P0 = D1 / (r - g)</t>
-  </si>
-  <si>
-    <t>D1 = dividende attendu l'an prochain | r = taux exige | g = taux croissance dividendes</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>D1 - Dividende attendu (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Hypothese ou dernier DVD x (1+g)</t>
-  </si>
-  <si>
-    <t>r - Taux de rentabilite exige (%)</t>
-  </si>
-  <si>
-    <t>Cout du capital / rendement cible (ex: 8%)</t>
-  </si>
-  <si>
-    <t>g - Taux de croissance DVD (%)</t>
-  </si>
-  <si>
-    <t>Croissance annuelle supposee (ex: 2%)</t>
-  </si>
-  <si>
-    <t>P0 = D1 / (r - g)  [FCFA]</t>
-  </si>
-  <si>
-    <t>Prix theorique calcule automatiquement</t>
-  </si>
-  <si>
-    <t>Signal prix actuel vs P0</t>
-  </si>
-  <si>
-    <t>B6 — GESTION DU RISQUE : STOP-LOSS &amp; RISK/REWARD</t>
-  </si>
-  <si>
-    <t>Formule/Note</t>
-  </si>
-  <si>
-    <t>Prix d'achat vise (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir prix entree prevue</t>
-  </si>
-  <si>
-    <t>Stop-Loss = Prix x 0,90 (FCFA)</t>
-  </si>
-  <si>
-    <t>= Prix x 0.90 (perte max 10%)</t>
-  </si>
-  <si>
-    <t>Objectif Take Profit (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir objectif de prix</t>
-  </si>
-  <si>
-    <t>Perte potentielle / titre (FCFA)</t>
-  </si>
-  <si>
-    <t>= Prix - Stop</t>
-  </si>
-  <si>
-    <t>Gain potentiel / titre (FCFA)</t>
-  </si>
-  <si>
-    <t>= Objectif - Prix</t>
-  </si>
-  <si>
-    <t>Ratio Risk / Reward</t>
-  </si>
-  <si>
-    <t>= Gain / Perte  (objectif &gt;= 2)</t>
-  </si>
-  <si>
-    <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
-  </si>
-  <si>
-    <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
-  </si>
-  <si>
-    <t>Societe : [NOM]   |   Date : [JJ/MM/AAAA]   |   Prix analyse : [FCFA]</t>
-  </si>
-  <si>
-    <t>SCORECARD FONDAMENTALE</t>
-  </si>
-  <si>
-    <t>Critere</t>
-  </si>
-  <si>
-    <t>Valeur (depuis ETUDE)</t>
-  </si>
-  <si>
-    <t>Zone normale</t>
-  </si>
-  <si>
-    <t>Score (0-3)</t>
-  </si>
-  <si>
-    <t>Croissance CA (N/N-4 %)</t>
-  </si>
-  <si>
-    <t>&lt;-- depuis ETUDE</t>
-  </si>
-  <si>
-    <t>&gt; 10%</t>
-  </si>
-  <si>
-    <t>&lt;-- saisir signal</t>
-  </si>
-  <si>
-    <t>Croissance RN (N/N-4 %)</t>
-  </si>
-  <si>
-    <t>Marge nette moyenne (%)</t>
-  </si>
-  <si>
-    <t>&gt; 5%</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>9 - 15</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>&lt; 1 ideal</t>
-  </si>
-  <si>
-    <t>ROE (%)</t>
-  </si>
-  <si>
-    <t>Rendement dividende (%)</t>
-  </si>
-  <si>
-    <t>&gt; 3%</t>
-  </si>
-  <si>
-    <t>RVC (PER x PBR)</t>
-  </si>
-  <si>
-    <t>&lt; 22</t>
-  </si>
-  <si>
-    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
-  </si>
-  <si>
-    <t>SCORECARD TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
-  </si>
-  <si>
-    <t>-5 a +5</t>
-  </si>
-  <si>
-    <t>Prix Medians PM1 et PM2 (B2)</t>
-  </si>
-  <si>
-    <t>&lt; PM = survente</t>
-  </si>
-  <si>
-    <t>PER actualise (B3)</t>
-  </si>
-  <si>
-    <t>9-15 = normal</t>
-  </si>
-  <si>
-    <t>PCD / Gordon-Shapiro (B4/B5)</t>
-  </si>
-  <si>
-    <t>&lt; PCD = survente</t>
-  </si>
-  <si>
-    <t>Risk/Reward (B6)</t>
-  </si>
-  <si>
-    <t>&gt;= 2 = bon</t>
-  </si>
-  <si>
-    <t>SCORE TECHNIQUE TOTAL (/15)</t>
-  </si>
-  <si>
-    <t>VERDICT GLOBAL</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>% atteint</t>
-  </si>
-  <si>
-    <t>Appreciation</t>
-  </si>
-  <si>
-    <t>Score Fondamental</t>
-  </si>
-  <si>
-    <t>Score Technique</t>
-  </si>
-  <si>
-    <t>SCORE TOTAL</t>
-  </si>
-  <si>
-    <t>RECOMMANDATION FINALE (texte libre)</t>
-  </si>
-  <si>
-    <t>PROFIL DE LA SOCIETE</t>
-  </si>
-  <si>
-    <t>IDENTIFICATION</t>
-  </si>
-  <si>
-    <t>Nom de la societe</t>
-  </si>
-  <si>
-    <t>Ticker BRVM</t>
-  </si>
-  <si>
-    <t>Secteur d'activite</t>
-  </si>
-  <si>
-    <t>Pays d'origine</t>
-  </si>
-  <si>
-    <t>Date d'introduction en bourse</t>
-  </si>
-  <si>
-    <t>CAPITAL &amp; ACTIONNARIAT</t>
-  </si>
-  <si>
-    <t>Capital social (FCFA)</t>
-  </si>
-  <si>
-    <t>Nombre de titres</t>
-  </si>
-  <si>
-    <t>Flottant (%)</t>
-  </si>
-  <si>
-    <t>Principaux actionnaires</t>
-  </si>
-  <si>
-    <t>LIQUIDITE DU TITRE (critique sur BRVM)</t>
-  </si>
-  <si>
-    <t>Volume moyen journalier (titres)</t>
-  </si>
-  <si>
-    <t>&lt;-- Source : BRVM.org</t>
-  </si>
-  <si>
-    <t>Volume moyen journalier (FCFA)</t>
-  </si>
-  <si>
-    <t>Frequence de cotation (%)</t>
-  </si>
-  <si>
-    <t>&lt;-- % seances avec transaction</t>
-  </si>
-  <si>
-    <t>Appreciation liquidite</t>
-  </si>
-  <si>
-    <t>&lt;-- Forte / Moyenne / Faible</t>
-  </si>
-  <si>
-    <t>NOTATION &amp; CONFORMITE</t>
-  </si>
-  <si>
-    <t>Note court terme</t>
-  </si>
-  <si>
-    <t>Note long terme</t>
-  </si>
-  <si>
-    <t>Dividende verse regulierement ?</t>
-  </si>
-  <si>
-    <t>&lt;-- Oui / Non</t>
-  </si>
-  <si>
-    <t>SOURCES D'INFORMATION</t>
-  </si>
-  <si>
-    <t>Rapport annuel</t>
-  </si>
-  <si>
-    <t>&lt;-- Lien ou date</t>
-  </si>
-  <si>
-    <t>Site de la societe</t>
-  </si>
-  <si>
-    <t>Profil RichBourse</t>
-  </si>
-  <si>
-    <t>&lt;-- richbourse.com</t>
-  </si>
-  <si>
-    <t>Profil BRVM</t>
-  </si>
-  <si>
-    <t>&lt;-- brvm.org</t>
-  </si>
-  <si>
-    <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
-  </si>
-  <si>
-    <t>Expression mathematique</t>
-  </si>
-  <si>
-    <t>Unite</t>
-  </si>
-  <si>
-    <t>Interpretation / Seuils BRVM</t>
-  </si>
-  <si>
-    <t>ANALYSE FONDAMENTALE</t>
-  </si>
-  <si>
-    <t>Croissance N/N-4</t>
-  </si>
-  <si>
-    <t>(N - N-4) / |N-4| x 100</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Positif = croissance. Negatif = contraction. Seuil : &gt; 10%/an = excellent</t>
-  </si>
-  <si>
-    <t>TCAM (CAGR)</t>
-  </si>
-  <si>
-    <t>(N / N-4)^(1/4) - 1</t>
-  </si>
-  <si>
-    <t>Taux de Croissance Annuel Moyen sur 4 ans</t>
-  </si>
-  <si>
-    <t>Marge Nette</t>
-  </si>
-  <si>
-    <t>RN / CA x 100</t>
-  </si>
-  <si>
-    <t>&lt; 2% = faible | 2-5% = moyen | &gt; 5% = bon | &gt; 10% = tres bon</t>
-  </si>
-  <si>
-    <t>fois</t>
-  </si>
-  <si>
-    <t>Zone normale BRVM : 9-15. &gt; 15 = surevalue, &lt; 9 = sous-evalue</t>
-  </si>
-  <si>
-    <t>VMC</t>
-  </si>
-  <si>
-    <t>FCFA</t>
-  </si>
-  <si>
-    <t>Prix &lt; VMC = action decotee (achat potentiellement interessant)</t>
-  </si>
-  <si>
-    <t>&lt; 1 = decote sur actif net | &gt; 2 = prime significative</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>&lt; 5% = faible | 5-10% = moyen | 10-15% = bon | &gt; 15% = excellent</t>
-  </si>
-  <si>
-    <t>RVC (Lynch)</t>
   </si>
   <si>
     <t>&lt; 22 = decote globale. Indicateur de sous-valorisation composite</t>
@@ -1276,6 +1267,9 @@
     <xf numFmtId="166" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1302,9 +1296,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1876,17 +1867,23 @@
       <c r="A16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="9">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <f>B8</f>
+        <v>0</v>
+      </c>
       <c r="D16" s="7">
         <f>IFERROR(B16/C16*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f>IFERROR(IF(D16&gt;=10,"Tres rentable",IF(D16&gt;=5,"Rentable",IF(D16&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="7">
@@ -1898,69 +1895,93 @@
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <f>C8</f>
+        <v>0</v>
+      </c>
       <c r="D17" s="7">
         <f>IFERROR(B17/C17*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>IFERROR(IF(D17&gt;=10,"Tres rentable",IF(D17&gt;=5,"Rentable",IF(D17&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="9">
+        <f>D12</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <f>D8</f>
+        <v>0</v>
+      </c>
       <c r="D18" s="7">
         <f>IFERROR(B18/C18*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>IFERROR(IF(D18&gt;=10,"Tres rentable",IF(D18&gt;=5,"Rentable",IF(D18&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="9">
+        <f>E12</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <f>E8</f>
+        <v>0</v>
+      </c>
       <c r="D19" s="7">
         <f>IFERROR(B19/C19*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>IFERROR(IF(D19&gt;=10,"Tres rentable",IF(D19&gt;=5,"Rentable",IF(D19&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="9">
+        <f>F12</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <f>F8</f>
+        <v>0</v>
+      </c>
       <c r="D20" s="7">
         <f>IFERROR(B20/C20*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f>IFERROR(IF(D20&gt;=10,"Tres rentable",IF(D20&gt;=5,"Rentable",IF(D20&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
     <row r="22" spans="1:8" ht="18" customHeight="1">
@@ -1988,193 +2009,161 @@
       <c r="D23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:8" ht="5" customHeight="1"/>
     <row r="30" spans="1:8">
       <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="7">
+        <f>IFERROR(B24/B25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="7">
-        <f>IFERROR(B24/B25,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
-        <f>IFERROR(IF(D30&gt;15,"Surevalue",IF(D30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>43</v>
+      <c r="D30" s="10">
+        <f>IFERROR(IF(B30&gt;15,"Surevalue",IF(B30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="15">
+        <v>41</v>
+      </c>
+      <c r="B31" s="16">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="9">
-        <f>IFERROR(IF(B24&gt;D31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>47</v>
+      <c r="C31" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="10">
+        <f>IFERROR(IF(B24&gt;B31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="7">
+        <v>43</v>
+      </c>
+      <c r="B32" s="7">
         <f>IFERROR(B27/B26,"")</f>
         <v>0</v>
       </c>
-      <c r="E32" s="9">
-        <f>IFERROR(IF(D32&lt;1,"Decote comptable",IF(D32&lt;2,"Normal","Prime elevee")),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>51</v>
+      <c r="C32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="10">
+        <f>IFERROR(IF(B32&lt;1,"Decote comptable",IF(B32&lt;2,"Normal","Prime elevee")),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="7">
+        <v>45</v>
+      </c>
+      <c r="B33" s="7">
         <f>IFERROR(F12*1000000/B26*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="9">
-        <f>IFERROR(IF(D33&gt;=15,"Excellent",IF(D33&gt;=10,"Bon",IF(D33&gt;=5,"Moyen","Faible"))),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>55</v>
+      <c r="C33" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="10">
+        <f>IFERROR(IF(B33&gt;=15,"Excellent",IF(B33&gt;=10,"Bon",IF(B33&gt;=5,"Moyen","Faible"))),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="7">
-        <f>IFERROR(D30*D32,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="9">
-        <f>IFERROR(IF(D34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
+      </c>
+      <c r="B34" s="7">
+        <f>IFERROR(B30*B32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="10">
+        <f>IFERROR(IF(B34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
     <row r="36" spans="1:8" ht="18" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2189,52 +2178,63 @@
         <v>15</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="7">
-        <f>IFERROR(B38/(C38*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="16">
+        <f>IFERROR(B38*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="17"/>
       <c r="E38" s="7">
+        <f>IFERROR(B38/D38*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
         <f>IFERROR(B38/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F38" s="11"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="7">
-        <f>IFERROR(B39/(C39*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="16">
+        <f>IFERROR(B39*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="17"/>
       <c r="E39" s="7">
+        <f>IFERROR(B39/D39*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
         <f>IFERROR(B39/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F39" s="7">
+      <c r="G39" s="7">
         <f>IFERROR((B39-B38)/ABS(B38)*100,"")</f>
         <v>0</v>
       </c>
@@ -2243,17 +2243,21 @@
       <c r="A40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="7">
-        <f>IFERROR(B40/(C40*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="16">
+        <f>IFERROR(B40*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="17"/>
       <c r="E40" s="7">
+        <f>IFERROR(B40/D40*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
         <f>IFERROR(B40/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F40" s="7">
+      <c r="G40" s="7">
         <f>IFERROR((B40-B39)/ABS(B39)*100,"")</f>
         <v>0</v>
       </c>
@@ -2262,17 +2266,21 @@
       <c r="A41" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="7">
-        <f>IFERROR(B41/(C41*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="16">
+        <f>IFERROR(B41*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="17"/>
       <c r="E41" s="7">
+        <f>IFERROR(B41/D41*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="7">
         <f>IFERROR(B41/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="7">
+      <c r="G41" s="7">
         <f>IFERROR((B41-B40)/ABS(B40)*100,"")</f>
         <v>0</v>
       </c>
@@ -2281,44 +2289,52 @@
       <c r="A42" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="7">
-        <f>IFERROR(B42/(C42*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="16">
+        <f>IFERROR(B42*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="17"/>
       <c r="E42" s="7">
+        <f>IFERROR(B42/D42*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
         <f>IFERROR(B42/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="7">
+      <c r="G42" s="7">
         <f>IFERROR((B42-B41)/ABS(B41)*100,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="16">
         <f>SUM(B38:B42)</f>
         <v>0</v>
       </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="7">
-        <f>IFERROR(AVERAGE(D38:D42),"")</f>
-        <v>0</v>
-      </c>
+      <c r="C43" s="16">
+        <f>IFERROR(B43*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="12"/>
       <c r="E43" s="7">
         <f>IFERROR(AVERAGE(E38:E42),"")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="11"/>
+      <c r="F43" s="7">
+        <f>IFERROR(AVERAGE(F38:F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:8" ht="5" customHeight="1"/>
     <row r="45" spans="1:8" ht="18" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2330,21 +2346,21 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2355,7 +2371,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2366,7 +2382,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2388,7 +2404,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2398,14 +2414,14 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="18">
+      <c r="A52" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="9">
         <f>SUM(B47:B51)</f>
         <v>0</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="9">
         <f>SUM(C47:C51)</f>
         <v>0</v>
       </c>
@@ -2417,7 +2433,7 @@
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
     <row r="54" spans="1:8" ht="18" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2429,66 +2445,66 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D56" s="20"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D57" s="20"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="18" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2500,153 +2516,153 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="21"/>
-      <c r="D63" s="11"/>
+      <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="21"/>
-      <c r="D64" s="11"/>
+      <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" s="15">
+        <v>86</v>
+      </c>
+      <c r="B65" s="16">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
       <c r="C65" s="21"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B66" s="15">
+        <v>87</v>
+      </c>
+      <c r="B66" s="16">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
       <c r="C66" s="21"/>
-      <c r="D66" s="11"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="21"/>
-      <c r="D67" s="11"/>
+      <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="15">
+        <v>89</v>
+      </c>
+      <c r="B68" s="16">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="11"/>
+      <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="15">
+        <v>90</v>
+      </c>
+      <c r="B69" s="16">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="11"/>
+      <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="18">
+        <v>91</v>
+      </c>
+      <c r="B70" s="9">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="11"/>
+      <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="B71" s="17"/>
       <c r="C71" s="21"/>
-      <c r="D71" s="11"/>
+      <c r="D71" s="12"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B72" s="18">
+        <v>93</v>
+      </c>
+      <c r="B72" s="9">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B73" s="18">
+      <c r="A73" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="9">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="11"/>
+      <c r="D73" s="12"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="17" t="s">
-        <v>103</v>
+      <c r="A74" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="B74" s="7">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
       <c r="C74" s="21"/>
-      <c r="D74" s="11"/>
+      <c r="D74" s="12"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="17" t="s">
-        <v>104</v>
+      <c r="A75" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="B75" s="22">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="11"/>
+      <c r="C75" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
     <row r="77" spans="1:8" ht="18" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2688,7 +2704,7 @@
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2701,7 +2717,7 @@
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
     <row r="84" spans="1:8" ht="18" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2713,27 +2729,27 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>114</v>
+        <v>105</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C86" s="21"/>
       <c r="D86" s="24">
@@ -2741,15 +2757,15 @@
         <v>0</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C87" s="21"/>
       <c r="D87" s="24">
@@ -2757,15 +2773,15 @@
         <v>0</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C88" s="21"/>
       <c r="D88" s="24">
@@ -2773,15 +2789,15 @@
         <v>0</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C89" s="21"/>
       <c r="D89" s="24">
@@ -2789,15 +2805,15 @@
         <v>0</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B90" s="13" t="s">
         <v>114</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C90" s="21"/>
       <c r="D90" s="24">
@@ -2805,15 +2821,15 @@
         <v>0</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
+      <c r="A91" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
       <c r="D91" s="26">
         <f>SUM(D86:D90)</f>
         <v>0</v>
@@ -2826,7 +2842,7 @@
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
     <row r="93" spans="1:8" ht="18" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2838,47 +2854,47 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="15">
+      <c r="D95" s="16">
         <f>IFERROR((B95+C95)/2,"")</f>
         <v>0</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="10">
         <f>IFERROR(IF(B24&lt;D95,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="15">
+      <c r="D96" s="16">
         <f>IFERROR((B96+C96)/2,"")</f>
         <v>0</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="10">
         <f>IFERROR(IF(B24&lt;D96,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v>0</v>
       </c>
@@ -2886,7 +2902,7 @@
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
     <row r="98" spans="1:8" ht="18" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2898,79 +2914,79 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B100" s="18">
+        <v>127</v>
+      </c>
+      <c r="B100" s="9">
         <f>B24</f>
         <v>0</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="D100" s="12"/>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B101" s="15">
+        <v>129</v>
+      </c>
+      <c r="B101" s="16">
         <f>B25</f>
         <v>0</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D101" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="D101" s="12"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="5" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B102" s="28"/>
       <c r="C102" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D102" s="11"/>
+        <v>132</v>
+      </c>
+      <c r="D102" s="12"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B103" s="15">
+        <v>133</v>
+      </c>
+      <c r="B103" s="16">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D103" s="11"/>
+        <v>134</v>
+      </c>
+      <c r="D103" s="12"/>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B104" s="7">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="D104" s="9">
+        <v>136</v>
+      </c>
+      <c r="D104" s="10">
         <f>IFERROR(IF(B104&gt;15,"Surevalue - Surachat",IF(B104&lt;9,"Sous-evalue - Survente","Normal (9-15)")),"-")</f>
         <v>0</v>
       </c>
@@ -2978,7 +2994,7 @@
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
     <row r="106" spans="1:8" ht="18" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2990,7 +3006,7 @@
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B107" s="29"/>
       <c r="C107" s="29"/>
@@ -3002,119 +3018,119 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="D109" s="11"/>
+        <v>141</v>
+      </c>
+      <c r="D109" s="12"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B110" s="16"/>
+        <v>142</v>
+      </c>
+      <c r="B110" s="17"/>
       <c r="C110" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D110" s="11"/>
+        <v>143</v>
+      </c>
+      <c r="D110" s="12"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B111" s="15">
+        <v>144</v>
+      </c>
+      <c r="B111" s="16">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D111" s="11"/>
+        <v>145</v>
+      </c>
+      <c r="D111" s="12"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="5" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B112" s="28">
         <v>6.5</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D112" s="11"/>
+        <v>147</v>
+      </c>
+      <c r="D112" s="12"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B113" s="15">
+        <v>148</v>
+      </c>
+      <c r="B113" s="16">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D113" s="11"/>
+        <v>149</v>
+      </c>
+      <c r="D113" s="12"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B114" s="15">
+        <v>150</v>
+      </c>
+      <c r="B114" s="16">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D114" s="11"/>
+        <v>151</v>
+      </c>
+      <c r="D114" s="12"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B115" s="15">
+        <v>152</v>
+      </c>
+      <c r="B115" s="16">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="D115" s="11"/>
+        <v>153</v>
+      </c>
+      <c r="D115" s="12"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B116" s="27">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D116" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="D116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
     <row r="118" spans="1:8" ht="18" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3126,7 +3142,7 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="30" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B119" s="30"/>
       <c r="C119" s="30"/>
@@ -3138,82 +3154,82 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B121" s="16"/>
+        <v>159</v>
+      </c>
+      <c r="B121" s="17"/>
       <c r="C121" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D121" s="11"/>
+        <v>160</v>
+      </c>
+      <c r="D121" s="12"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B122" s="28">
         <v>8</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D122" s="11"/>
+        <v>162</v>
+      </c>
+      <c r="D122" s="12"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B123" s="28">
         <v>2</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D123" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="D123" s="12"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B124" s="31">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="D124" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="D124" s="12"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B125" s="27">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D125" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="D125" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
     <row r="128" spans="1:8" ht="18" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3225,89 +3241,89 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="5" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B130" s="6"/>
       <c r="C130" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D130" s="11"/>
+        <v>171</v>
+      </c>
+      <c r="D130" s="12"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B131" s="15">
+        <v>172</v>
+      </c>
+      <c r="B131" s="16">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D131" s="11"/>
+        <v>173</v>
+      </c>
+      <c r="D131" s="12"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B132" s="6"/>
       <c r="C132" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D132" s="11"/>
+        <v>175</v>
+      </c>
+      <c r="D132" s="12"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B133" s="15">
+        <v>176</v>
+      </c>
+      <c r="B133" s="16">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D133" s="11"/>
+        <v>177</v>
+      </c>
+      <c r="D133" s="12"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B134" s="15">
+        <v>178</v>
+      </c>
+      <c r="B134" s="16">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D134" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="D134" s="12"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B135" s="7">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D135" s="9">
+        <v>181</v>
+      </c>
+      <c r="D135" s="10">
         <f>IFERROR(IF(B135&gt;=2,"Bon (&gt;= 2:1)",IF(B135&gt;=1,"Acceptable (1:1)","Mauvais")),"")</f>
         <v>0</v>
       </c>
@@ -3315,7 +3331,7 @@
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
     <row r="137" spans="1:8" ht="18" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3405,7 +3421,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3414,7 +3430,7 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="32" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
@@ -3424,7 +3440,7 @@
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3433,144 +3449,144 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>200</v>
+        <v>190</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E6" s="34"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E7" s="34"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>204</v>
+        <v>195</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E8" s="34"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>206</v>
+        <v>197</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E9" s="34"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>208</v>
+      <c r="B10" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>211</v>
+        <v>202</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>203</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E12" s="34"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>213</v>
+        <v>204</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E13" s="34"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17" t="s">
-        <v>214</v>
+      <c r="A14" s="18" t="s">
+        <v>206</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -3583,7 +3599,7 @@
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3592,99 +3608,99 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>219</v>
+        <v>193</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>211</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>221</v>
+        <v>193</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>213</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>223</v>
+        <v>193</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E20" s="34"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>225</v>
+        <v>193</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>217</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E21" s="34"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>227</v>
+        <v>193</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E22" s="34"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="17" t="s">
-        <v>228</v>
+      <c r="A23" s="18" t="s">
+        <v>220</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3697,7 +3713,7 @@
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="36" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B25" s="36"/>
       <c r="C25" s="36"/>
@@ -3706,24 +3722,24 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B27" s="37">
         <f>E14</f>
@@ -3743,7 +3759,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="B28" s="37">
         <f>E23</f>
@@ -3762,8 +3778,8 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="17" t="s">
-        <v>235</v>
+      <c r="A29" s="18" t="s">
+        <v>227</v>
       </c>
       <c r="B29" s="40">
         <f>IFERROR(E14+E23,"")</f>
@@ -3784,7 +3800,7 @@
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3846,7 +3862,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3854,7 +3870,7 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3862,48 +3878,48 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+        <v>231</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+        <v>232</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+        <v>233</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+        <v>234</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+        <v>235</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" ht="5" customHeight="1"/>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3911,40 +3927,40 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+        <v>237</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+        <v>238</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+        <v>239</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="18" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3952,46 +3968,46 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+        <v>242</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+        <v>244</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+        <v>245</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+        <v>247</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3999,42 +4015,42 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+        <v>74</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+        <v>250</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+        <v>251</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+        <v>252</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="18" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -4042,41 +4058,41 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
+        <v>257</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+        <v>258</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+        <v>260</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
@@ -4105,7 +4121,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4113,314 +4129,314 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="43" t="s">
         <v>275</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="C6" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="38" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="28" customHeight="1">
+      <c r="A7" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="C7" s="38" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="28" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="D7" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="43" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="28" customHeight="1">
+      <c r="A8" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D5" s="44" t="s">
+      <c r="B8" s="43" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="28" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="C8" s="38" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="D8" s="44" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" s="44" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="28" customHeight="1">
+      <c r="A9" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="43" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="38" t="s">
+      <c r="C9" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="D7" s="44" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="28" customHeight="1">
+      <c r="A10" s="18" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="28" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="B10" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="C10" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="44" t="s">
         <v>288</v>
       </c>
-      <c r="D8" s="44" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="28" customHeight="1">
+      <c r="A11" s="18" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="28" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="D9" s="44" t="s">
+      <c r="B11" s="43" t="s">
         <v>290</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="28" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="28" customHeight="1">
-      <c r="A11" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>57</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28" customHeight="1">
+      <c r="A12" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="44" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28" customHeight="1">
-      <c r="A12" s="17" t="s">
+    <row r="13" spans="1:4" ht="28" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B13" s="43" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="44" t="s">
+      <c r="C13" s="38" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="44" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="28" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B16" s="43" t="s">
         <v>303</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="28" customHeight="1">
-      <c r="A16" s="17" t="s">
-        <v>305</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>306</v>
       </c>
       <c r="C16" s="38"/>
       <c r="D16" s="44" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
-      <c r="A17" s="17" t="s">
-        <v>118</v>
+      <c r="A17" s="18" t="s">
+        <v>110</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C17" s="38"/>
       <c r="D17" s="44" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28" customHeight="1">
+      <c r="A19" s="18" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="28" customHeight="1">
-      <c r="A18" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="43" t="s">
+      <c r="B19" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="C18" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="D18" s="44" t="s">
+      <c r="C19" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D19" s="44" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28" customHeight="1">
-      <c r="A19" s="17" t="s">
+    <row r="20" spans="1:4" ht="28" customHeight="1">
+      <c r="A20" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B20" s="43" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="44" t="s">
+      <c r="C20" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="44" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28" customHeight="1">
-      <c r="A20" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>316</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28" customHeight="1">
+      <c r="A23" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B23" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D22" s="44" t="s">
+      <c r="C23" s="38" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="28" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="D23" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="B23" s="43" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="28" customHeight="1">
+      <c r="A24" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="B24" s="43" t="s">
         <v>323</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="C24" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D24" s="44" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28" customHeight="1">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:4" ht="28" customHeight="1">
+      <c r="A25" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B25" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="C24" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D24" s="44" t="s">
+      <c r="C25" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D25" s="44" t="s">
         <v>327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="28" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="328">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -580,76 +580,76 @@
     <t>Critere</t>
   </si>
   <si>
-    <t>Valeur (depuis ETUDE)</t>
+    <t>Valeur (auto depuis ETUDE)</t>
   </si>
   <si>
     <t>Zone normale</t>
   </si>
   <si>
+    <t>Signal (auto)</t>
+  </si>
+  <si>
     <t>Score (0-3)</t>
   </si>
   <si>
     <t>Croissance CA (N/N-4 %)</t>
   </si>
   <si>
-    <t>&lt;-- depuis ETUDE</t>
-  </si>
-  <si>
     <t>&gt; 10%</t>
   </si>
   <si>
+    <t>Croissance RN (N/N-4 %)</t>
+  </si>
+  <si>
+    <t>Marge nette moyenne (%)</t>
+  </si>
+  <si>
+    <t>&gt; 5%</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>9 - 15</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>&lt; 1 ideal</t>
+  </si>
+  <si>
+    <t>ROE (%)</t>
+  </si>
+  <si>
+    <t>Rendement dividende (%)</t>
+  </si>
+  <si>
+    <t>&gt; 3%</t>
+  </si>
+  <si>
+    <t>RVC (PER x PBR)</t>
+  </si>
+  <si>
+    <t>&lt; 22</t>
+  </si>
+  <si>
+    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
+  </si>
+  <si>
+    <t>SCORECARD TECHNIQUE</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
+  </si>
+  <si>
     <t>&lt;-- saisir signal</t>
-  </si>
-  <si>
-    <t>Croissance RN (N/N-4 %)</t>
-  </si>
-  <si>
-    <t>Marge nette moyenne (%)</t>
-  </si>
-  <si>
-    <t>&gt; 5%</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>9 - 15</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>&lt; 1 ideal</t>
-  </si>
-  <si>
-    <t>ROE (%)</t>
-  </si>
-  <si>
-    <t>Rendement dividende (%)</t>
-  </si>
-  <si>
-    <t>&gt; 3%</t>
-  </si>
-  <si>
-    <t>RVC (PER x PBR)</t>
-  </si>
-  <si>
-    <t>&lt; 22</t>
-  </si>
-  <si>
-    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
-  </si>
-  <si>
-    <t>SCORECARD TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
   </si>
   <si>
     <t>-5 a +5</t>
@@ -1014,7 +1014,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1118,6 +1118,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -1149,15 +1164,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1206,6 +1214,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1241,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1339,19 +1359,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1360,16 +1389,16 @@
     <xf numFmtId="168" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3458,140 +3487,156 @@
         <v>188</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>28</v>
+        <v>189</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B6" s="14" t="s">
         <v>191</v>
+      </c>
+      <c r="B6" s="33">
+        <f>IFERROR(ETUDE!G8,"")</f>
+        <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E6" s="34"/>
+      <c r="D6" s="34">
+        <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="B7" s="33">
+        <f>IFERROR(ETUDE!G12,"")</f>
+        <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E7" s="34"/>
+      <c r="D7" s="34">
+        <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" s="33">
+        <f>IFERROR(ETUDE!G16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E8" s="34"/>
+      <c r="D8" s="34">
+        <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="33">
+        <f>IFERROR(ETUDE!B30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E9" s="34"/>
+      <c r="D9" s="34">
+        <f>IFERROR(ETUDE!D30,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="35"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="33">
+        <f>IFERROR(ETUDE!B32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E10" s="34"/>
+      <c r="D10" s="34">
+        <f>IFERROR(ETUDE!D32,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="35"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>191</v>
+        <v>200</v>
+      </c>
+      <c r="B11" s="33">
+        <f>IFERROR(ETUDE!B33,"")</f>
+        <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="34"/>
+      <c r="D11" s="34">
+        <f>IFERROR(ETUDE!D33,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="33">
+        <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E12" s="34"/>
+      <c r="D12" s="34">
+        <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="33">
+        <f>IFERROR(ETUDE!B34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="34"/>
+      <c r="D13" s="34">
+        <f>IFERROR(ETUDE!D34,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="35"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
@@ -3599,7 +3644,7 @@
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3614,89 +3659,89 @@
         <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="37" t="s">
         <v>210</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>193</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E18" s="34"/>
+      <c r="D18" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="33" t="s">
-        <v>193</v>
+      <c r="B19" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E19" s="34"/>
+      <c r="D19" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="33" t="s">
-        <v>193</v>
+      <c r="B20" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E20" s="34"/>
+      <c r="D20" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="B21" s="33" t="s">
-        <v>193</v>
+      <c r="B21" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E21" s="34"/>
+      <c r="D21" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B22" s="33" t="s">
-        <v>193</v>
+      <c r="B22" s="37" t="s">
+        <v>210</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D22" s="33" t="s">
-        <v>193</v>
-      </c>
-      <c r="E22" s="34"/>
+      <c r="D22" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
@@ -3705,27 +3750,27 @@
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="35">
+      <c r="E23" s="36">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>222</v>
@@ -3741,14 +3786,14 @@
       <c r="A27" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B27" s="37">
+      <c r="B27" s="40">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="41">
         <v>24</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="42">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
@@ -3761,14 +3806,14 @@
       <c r="A28" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="40">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="41">
         <v>15</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="42">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
@@ -3781,18 +3826,18 @@
       <c r="A29" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="43">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="44">
         <v>39</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="42">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="45">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
@@ -4153,13 +4198,13 @@
       <c r="A4" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="46" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="47" t="s">
         <v>270</v>
       </c>
     </row>
@@ -4167,13 +4212,13 @@
       <c r="A5" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="47" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4181,27 +4226,27 @@
       <c r="A6" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="47" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="B7" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="47" t="s">
         <v>279</v>
       </c>
     </row>
@@ -4209,27 +4254,27 @@
       <c r="A8" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="47" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="47" t="s">
         <v>285</v>
       </c>
     </row>
@@ -4237,13 +4282,13 @@
       <c r="A10" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="47" t="s">
         <v>288</v>
       </c>
     </row>
@@ -4251,11 +4296,11 @@
       <c r="A11" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="44" t="s">
+      <c r="C11" s="41"/>
+      <c r="D11" s="47" t="s">
         <v>291</v>
       </c>
     </row>
@@ -4263,13 +4308,13 @@
       <c r="A12" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="47" t="s">
         <v>294</v>
       </c>
     </row>
@@ -4277,13 +4322,13 @@
       <c r="A13" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="47" t="s">
         <v>297</v>
       </c>
     </row>
@@ -4299,13 +4344,13 @@
       <c r="A15" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="47" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4313,11 +4358,11 @@
       <c r="A16" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="44" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="47" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4325,11 +4370,11 @@
       <c r="A17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="44" t="s">
+      <c r="C17" s="41"/>
+      <c r="D17" s="47" t="s">
         <v>305</v>
       </c>
     </row>
@@ -4337,13 +4382,13 @@
       <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="47" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4351,13 +4396,13 @@
       <c r="A19" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="47" t="s">
         <v>310</v>
       </c>
     </row>
@@ -4365,13 +4410,13 @@
       <c r="A20" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="47" t="s">
         <v>313</v>
       </c>
     </row>
@@ -4387,13 +4432,13 @@
       <c r="A22" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="47" t="s">
         <v>317</v>
       </c>
     </row>
@@ -4401,13 +4446,13 @@
       <c r="A23" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="41" t="s">
         <v>320</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="47" t="s">
         <v>321</v>
       </c>
     </row>
@@ -4415,13 +4460,13 @@
       <c r="A24" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="47" t="s">
         <v>324</v>
       </c>
     </row>
@@ -4429,13 +4474,13 @@
       <c r="A25" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="47" t="s">
         <v>327</v>
       </c>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="328">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -94,811 +94,802 @@
     <t>A4 — INDICATEURS DE VALORISATION</t>
   </si>
   <si>
+    <t>Indicateur [formule]</t>
+  </si>
+  <si>
+    <t>Valeur calculee</t>
+  </si>
+  <si>
+    <t>Zone reference</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Prix actuel de l'action (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir le prix actuel</t>
+  </si>
+  <si>
+    <t>BNPA — Benefice Net Par Action (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- RN / Nb titres (rapport annuel)</t>
+  </si>
+  <si>
+    <t>Capitaux Propres (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan comptable</t>
+  </si>
+  <si>
+    <t>Capitalisation boursiere (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Prix x Nb titres</t>
+  </si>
+  <si>
+    <t>Nombre de titres en circulation</t>
+  </si>
+  <si>
+    <t>&lt;-- BRVM.org</t>
+  </si>
+  <si>
+    <t>PER — Price Earning Ratio  [= Prix / BNPA]</t>
+  </si>
+  <si>
+    <t>Zone : 9-15</t>
+  </si>
+  <si>
+    <t>VMC — Valeur Mathematique Comptable  [= Capitaux Propres / Nb titres]</t>
+  </si>
+  <si>
+    <t>Prix &lt; VMC = bon</t>
+  </si>
+  <si>
+    <t>PBR — Price to Book Ratio  [= Capitalisation / Capitaux Propres]</t>
+  </si>
+  <si>
+    <t>&lt; 1 = decote</t>
+  </si>
+  <si>
+    <t>ROE — Return on Equity (%)  [= RN / Capitaux Propres x 100]</t>
+  </si>
+  <si>
+    <t>&gt; 10% = bon</t>
+  </si>
+  <si>
+    <t>RVC — PER x PBR (Lynch)  [= PER x PBR]</t>
+  </si>
+  <si>
+    <t>&lt; 22 = decote</t>
+  </si>
+  <si>
+    <t>A5 — DIVIDENDES &amp; TAUX DE DISTRIBUTION</t>
+  </si>
+  <si>
+    <t>Dividende BRUT (FCFA)</t>
+  </si>
+  <si>
+    <t>Dividende NET (FCFA)</t>
+  </si>
+  <si>
+    <t>BNPA (FCFA)</t>
+  </si>
+  <si>
+    <t>Taux distrib. %</t>
+  </si>
+  <si>
+    <t>Rendement %</t>
+  </si>
+  <si>
+    <t>Progression %</t>
+  </si>
+  <si>
+    <t>TOTAL / MOYENNE</t>
+  </si>
+  <si>
+    <t>A6 — FONDS PROPRES (FCFA)</t>
+  </si>
+  <si>
+    <t>Composante</t>
+  </si>
+  <si>
+    <t>Annee N-1</t>
+  </si>
+  <si>
+    <t>Annee N</t>
+  </si>
+  <si>
+    <t>Variation %</t>
+  </si>
+  <si>
+    <t>Capital souscrit</t>
+  </si>
+  <si>
+    <t>Reserves</t>
+  </si>
+  <si>
+    <t>Report a nouveau</t>
+  </si>
+  <si>
+    <t>Dividendes verses</t>
+  </si>
+  <si>
+    <t>TOTAL FONDS PROPRES</t>
+  </si>
+  <si>
+    <t>A7 — NOTATION FINANCIERE &amp; ACTIVITES RECENTES</t>
+  </si>
+  <si>
     <t>Indicateur</t>
   </si>
   <si>
     <t>Valeur</t>
   </si>
   <si>
-    <t>Description formule</t>
-  </si>
-  <si>
-    <t>Valeur calculee</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Prix actuel de l'action (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir le prix actuel</t>
-  </si>
-  <si>
-    <t>BNPA — Benefice Net Par Action (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- RN / Nb titres (rapport annuel)</t>
-  </si>
-  <si>
-    <t>Capitaux Propres (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Bilan comptable</t>
-  </si>
-  <si>
-    <t>Capitalisation boursiere (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Prix x Nb titres</t>
-  </si>
-  <si>
-    <t>Nombre de titres en circulation</t>
-  </si>
-  <si>
-    <t>&lt;-- BRVM.org</t>
-  </si>
-  <si>
-    <t>PER — Price Earning Ratio</t>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Date rapport</t>
+  </si>
+  <si>
+    <t>Notation court terme</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Agence de notation</t>
+  </si>
+  <si>
+    <t>Notation long terme</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Variation CA/PNB (dernier trimestre)</t>
+  </si>
+  <si>
+    <t>RichBourse</t>
+  </si>
+  <si>
+    <t>Variation Resultat Net (dernier trimestre)</t>
+  </si>
+  <si>
+    <t>A8 — COMPARAISON MARCHE BOURSIER VS EPARGNE</t>
+  </si>
+  <si>
+    <t>Parametre</t>
+  </si>
+  <si>
+    <t>Marche Boursier</t>
+  </si>
+  <si>
+    <t>Epargne (saisir rendement %)</t>
+  </si>
+  <si>
+    <t>Montant investi (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix d'achat historique (FCFA)</t>
+  </si>
+  <si>
+    <t>CMP = Prix x 1,014 (frais 1,4%)</t>
+  </si>
+  <si>
+    <t>Nombre de titres acquis</t>
+  </si>
+  <si>
+    <t>Prix actuel du titre (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix net apres taxe cession 1,4% (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus-value unitaire (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus-value totale (FCFA)</t>
+  </si>
+  <si>
+    <t>Total dividendes recus par titre (FCFA)</t>
+  </si>
+  <si>
+    <t>Rendement dividendes total (FCFA)</t>
+  </si>
+  <si>
+    <t>RENDEMENT TOTAL (FCFA)</t>
+  </si>
+  <si>
+    <t>PERFORMANCE (%)</t>
+  </si>
+  <si>
+    <t>VERDICT</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir rendement epargne % ici</t>
+  </si>
+  <si>
+    <t>A9 — CONCLUSION ANALYSE FONDAMENTALE (texte libre)</t>
+  </si>
+  <si>
+    <t>B — ANALYSE TECHNIQUE</t>
+  </si>
+  <si>
+    <t>B1 — INDICATEURS TECHNIQUES (saisie depuis graphique)</t>
+  </si>
+  <si>
+    <t>Signal observe</t>
+  </si>
+  <si>
+    <t>Valeur / Niveau</t>
+  </si>
+  <si>
+    <t>Score auto</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Moyenne Mobile 20 jours (MM20)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir signal</t>
+  </si>
+  <si>
+    <t>Zone de survente : cours EN DESSOUS de la MM20</t>
+  </si>
+  <si>
+    <t>Bandes de Bollinger</t>
+  </si>
+  <si>
+    <t>Zone de survente : cours touche la bande inferieure</t>
+  </si>
+  <si>
+    <t>MACD</t>
+  </si>
+  <si>
+    <t>Zone de survente : MACD croise Signal a la hausse</t>
+  </si>
+  <si>
+    <t>RSI (saisir valeur en col C)</t>
+  </si>
+  <si>
+    <t>&lt; 30 survente | 30-70 neutre | &gt; 70 surachat</t>
+  </si>
+  <si>
+    <t>Volume (tendance recente)</t>
+  </si>
+  <si>
+    <t>Volume croissant sur baisse = accumulation = survente</t>
+  </si>
+  <si>
+    <t>SCORE TECHNIQUE (max +5 / min -5)</t>
+  </si>
+  <si>
+    <t>B2 — PRIX MEDIANS (PM)</t>
+  </si>
+  <si>
+    <t>Horizon</t>
+  </si>
+  <si>
+    <t>Plus Haut (FCFA)</t>
+  </si>
+  <si>
+    <t>Plus Bas (FCFA)</t>
+  </si>
+  <si>
+    <t>Prix Median</t>
+  </si>
+  <si>
+    <t>Signal (vs prix actuel B24)</t>
+  </si>
+  <si>
+    <t>52 semaines (1 an)</t>
+  </si>
+  <si>
+    <t>2 ans</t>
+  </si>
+  <si>
+    <t>B3 — PER ACTUALISE (integre la derniere evolution du RN)</t>
+  </si>
+  <si>
+    <t>Source / Formule</t>
+  </si>
+  <si>
+    <t>Prix actuel (FCFA)</t>
+  </si>
+  <si>
+    <t>Lie a B24</t>
+  </si>
+  <si>
+    <t>BNPA N (FCFA)</t>
+  </si>
+  <si>
+    <t>Lie a B25</t>
+  </si>
+  <si>
+    <t>Evolution RN dernier trimestre (%)</t>
+  </si>
+  <si>
+    <t>RichBourse / Rapport trimestriel</t>
+  </si>
+  <si>
+    <t>BNPA actualise (FCFA)</t>
+  </si>
+  <si>
+    <t>= BNPA x (1 + evol%)</t>
+  </si>
+  <si>
+    <t>PER actualise</t>
+  </si>
+  <si>
+    <t>= Prix / BNPA actualise</t>
+  </si>
+  <si>
+    <t>B4 — PRIX CIBLE AUX DIVIDENDES (PCD)</t>
+  </si>
+  <si>
+    <t>Note : Le PCD n'est pertinent que si l'entreprise verse des dividendes. Si dividende = 0, utiliser B5 (Gordon-Shapiro).</t>
+  </si>
+  <si>
+    <t>Formule</t>
+  </si>
+  <si>
+    <t>Evolution RN (%)</t>
+  </si>
+  <si>
+    <t>Meme valeur qu'en B3</t>
+  </si>
+  <si>
+    <t>Dividende brut N (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir le dernier dividende verse</t>
+  </si>
+  <si>
+    <t>Dividende previsionnel (FCFA)</t>
+  </si>
+  <si>
+    <t>= Dividende x (1 + evol%)</t>
+  </si>
+  <si>
+    <t>Rendement sectoriel BRVM (%)</t>
+  </si>
+  <si>
+    <t>Reference : 5-8% (modifiable)</t>
+  </si>
+  <si>
+    <t>PCD = 100 x DVD_prev / Rendement</t>
+  </si>
+  <si>
+    <t>= 100 x Dprev / Rendement%</t>
+  </si>
+  <si>
+    <t>Zone cible basse (-5%)</t>
+  </si>
+  <si>
+    <t>= PCD x 0.95</t>
+  </si>
+  <si>
+    <t>Zone cible haute (+5%)</t>
+  </si>
+  <si>
+    <t>= PCD x 1.05</t>
+  </si>
+  <si>
+    <t>Signal (prix B24 vs zone cible)</t>
+  </si>
+  <si>
+    <t>Calcul automatique</t>
+  </si>
+  <si>
+    <t>B5 — MODELE DE GORDON-SHAPIRO   P0 = D1 / (r - g)</t>
+  </si>
+  <si>
+    <t>D1 = dividende attendu l'an prochain | r = taux exige | g = taux croissance dividendes</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>D1 - Dividende attendu (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Hypothese ou dernier DVD x (1+g)</t>
+  </si>
+  <si>
+    <t>r - Taux de rentabilite exige (%)</t>
+  </si>
+  <si>
+    <t>Cout du capital / rendement cible (ex: 8%)</t>
+  </si>
+  <si>
+    <t>g - Taux de croissance DVD (%)</t>
+  </si>
+  <si>
+    <t>Croissance annuelle supposee (ex: 2%)</t>
+  </si>
+  <si>
+    <t>P0 = D1 / (r - g)  [FCFA]</t>
+  </si>
+  <si>
+    <t>Prix theorique calcule automatiquement</t>
+  </si>
+  <si>
+    <t>Signal prix actuel vs P0</t>
+  </si>
+  <si>
+    <t>B6 — GESTION DU RISQUE : STOP-LOSS &amp; RISK/REWARD</t>
+  </si>
+  <si>
+    <t>Formule/Note</t>
+  </si>
+  <si>
+    <t>Prix d'achat vise (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir prix entree prevue</t>
+  </si>
+  <si>
+    <t>Stop-Loss = Prix x 0,90 (FCFA)</t>
+  </si>
+  <si>
+    <t>= Prix x 0.90 (perte max 10%)</t>
+  </si>
+  <si>
+    <t>Objectif Take Profit (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Saisir objectif de prix</t>
+  </si>
+  <si>
+    <t>Perte potentielle / titre (FCFA)</t>
+  </si>
+  <si>
+    <t>= Prix - Stop</t>
+  </si>
+  <si>
+    <t>Gain potentiel / titre (FCFA)</t>
+  </si>
+  <si>
+    <t>= Objectif - Prix</t>
+  </si>
+  <si>
+    <t>Ratio Risk / Reward</t>
+  </si>
+  <si>
+    <t>= Gain / Perte  (objectif &gt;= 2)</t>
+  </si>
+  <si>
+    <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
+  </si>
+  <si>
+    <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
+  </si>
+  <si>
+    <t>Societe : [NOM]   |   Date : [JJ/MM/AAAA]   |   Prix analyse : [FCFA]</t>
+  </si>
+  <si>
+    <t>SCORECARD FONDAMENTALE</t>
+  </si>
+  <si>
+    <t>Critere</t>
+  </si>
+  <si>
+    <t>Valeur (auto depuis ETUDE)</t>
+  </si>
+  <si>
+    <t>Zone normale</t>
+  </si>
+  <si>
+    <t>Signal (auto)</t>
+  </si>
+  <si>
+    <t>Score (0-3)</t>
+  </si>
+  <si>
+    <t>Croissance CA (N/N-4 %)</t>
+  </si>
+  <si>
+    <t>&gt; 10%</t>
+  </si>
+  <si>
+    <t>Croissance RN (N/N-4 %)</t>
+  </si>
+  <si>
+    <t>Marge nette moyenne (%)</t>
+  </si>
+  <si>
+    <t>&gt; 5%</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>9 - 15</t>
+  </si>
+  <si>
+    <t>PBR</t>
+  </si>
+  <si>
+    <t>&lt; 1 ideal</t>
+  </si>
+  <si>
+    <t>ROE (%)</t>
+  </si>
+  <si>
+    <t>Rendement dividende (%)</t>
+  </si>
+  <si>
+    <t>&gt; 3%</t>
+  </si>
+  <si>
+    <t>RVC (PER x PBR)</t>
+  </si>
+  <si>
+    <t>&lt; 22</t>
+  </si>
+  <si>
+    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
+  </si>
+  <si>
+    <t>SCORECARD TECHNIQUE</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
+  </si>
+  <si>
+    <t>&lt;-- saisir signal</t>
+  </si>
+  <si>
+    <t>-5 a +5</t>
+  </si>
+  <si>
+    <t>Prix Medians PM1 et PM2 (B2)</t>
+  </si>
+  <si>
+    <t>&lt; PM = survente</t>
+  </si>
+  <si>
+    <t>PER actualise (B3)</t>
+  </si>
+  <si>
+    <t>9-15 = normal</t>
+  </si>
+  <si>
+    <t>PCD / Gordon-Shapiro (B4/B5)</t>
+  </si>
+  <si>
+    <t>&lt; PCD = survente</t>
+  </si>
+  <si>
+    <t>Risk/Reward (B6)</t>
+  </si>
+  <si>
+    <t>&gt;= 2 = bon</t>
+  </si>
+  <si>
+    <t>SCORE TECHNIQUE TOTAL (/15)</t>
+  </si>
+  <si>
+    <t>VERDICT GLOBAL</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>% atteint</t>
+  </si>
+  <si>
+    <t>Appreciation</t>
+  </si>
+  <si>
+    <t>Score Fondamental</t>
+  </si>
+  <si>
+    <t>Score Technique</t>
+  </si>
+  <si>
+    <t>SCORE TOTAL</t>
+  </si>
+  <si>
+    <t>RECOMMANDATION FINALE (texte libre)</t>
+  </si>
+  <si>
+    <t>PROFIL DE LA SOCIETE</t>
+  </si>
+  <si>
+    <t>IDENTIFICATION</t>
+  </si>
+  <si>
+    <t>Nom de la societe</t>
+  </si>
+  <si>
+    <t>Ticker BRVM</t>
+  </si>
+  <si>
+    <t>Secteur d'activite</t>
+  </si>
+  <si>
+    <t>Pays d'origine</t>
+  </si>
+  <si>
+    <t>Date d'introduction en bourse</t>
+  </si>
+  <si>
+    <t>CAPITAL &amp; ACTIONNARIAT</t>
+  </si>
+  <si>
+    <t>Capital social (FCFA)</t>
+  </si>
+  <si>
+    <t>Nombre de titres</t>
+  </si>
+  <si>
+    <t>Flottant (%)</t>
+  </si>
+  <si>
+    <t>Principaux actionnaires</t>
+  </si>
+  <si>
+    <t>LIQUIDITE DU TITRE (critique sur BRVM)</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (titres)</t>
+  </si>
+  <si>
+    <t>&lt;-- Source : BRVM.org</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (FCFA)</t>
+  </si>
+  <si>
+    <t>Frequence de cotation (%)</t>
+  </si>
+  <si>
+    <t>&lt;-- % seances avec transaction</t>
+  </si>
+  <si>
+    <t>Appreciation liquidite</t>
+  </si>
+  <si>
+    <t>&lt;-- Forte / Moyenne / Faible</t>
+  </si>
+  <si>
+    <t>NOTATION &amp; CONFORMITE</t>
+  </si>
+  <si>
+    <t>Note court terme</t>
+  </si>
+  <si>
+    <t>Note long terme</t>
+  </si>
+  <si>
+    <t>Dividende verse regulierement ?</t>
+  </si>
+  <si>
+    <t>&lt;-- Oui / Non</t>
+  </si>
+  <si>
+    <t>SOURCES D'INFORMATION</t>
+  </si>
+  <si>
+    <t>Rapport annuel</t>
+  </si>
+  <si>
+    <t>&lt;-- Lien ou date</t>
+  </si>
+  <si>
+    <t>Site de la societe</t>
+  </si>
+  <si>
+    <t>Profil RichBourse</t>
+  </si>
+  <si>
+    <t>&lt;-- richbourse.com</t>
+  </si>
+  <si>
+    <t>Profil BRVM</t>
+  </si>
+  <si>
+    <t>&lt;-- brvm.org</t>
+  </si>
+  <si>
+    <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
+  </si>
+  <si>
+    <t>Expression mathematique</t>
+  </si>
+  <si>
+    <t>Unite</t>
+  </si>
+  <si>
+    <t>Interpretation / Seuils BRVM</t>
+  </si>
+  <si>
+    <t>ANALYSE FONDAMENTALE</t>
+  </si>
+  <si>
+    <t>Croissance N/N-4</t>
+  </si>
+  <si>
+    <t>(N - N-4) / |N-4| x 100</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Positif = croissance. Negatif = contraction. Seuil : &gt; 10%/an = excellent</t>
+  </si>
+  <si>
+    <t>TCAM (CAGR)</t>
+  </si>
+  <si>
+    <t>(N / N-4)^(1/4) - 1</t>
+  </si>
+  <si>
+    <t>Taux de Croissance Annuel Moyen sur 4 ans</t>
+  </si>
+  <si>
+    <t>Marge Nette</t>
+  </si>
+  <si>
+    <t>RN / CA x 100</t>
+  </si>
+  <si>
+    <t>&lt; 2% = faible | 2-5% = moyen | &gt; 5% = bon | &gt; 10% = tres bon</t>
   </si>
   <si>
     <t>Prix / BNPA</t>
   </si>
   <si>
-    <t>=B24/B25</t>
-  </si>
-  <si>
-    <t>Zone : 9-15</t>
-  </si>
-  <si>
-    <t>VMC — Valeur Mathematique Comptable (FCFA)</t>
+    <t>fois</t>
+  </si>
+  <si>
+    <t>Zone normale BRVM : 9-15. &gt; 15 = surevalue, &lt; 9 = sous-evalue</t>
+  </si>
+  <si>
+    <t>VMC</t>
   </si>
   <si>
     <t>Capitaux Propres / Nb titres</t>
   </si>
   <si>
-    <t>=B26/B28</t>
-  </si>
-  <si>
-    <t>Prix &lt; VMC = bon</t>
-  </si>
-  <si>
-    <t>PBR — Price to Book Ratio</t>
+    <t>FCFA</t>
+  </si>
+  <si>
+    <t>Prix &lt; VMC = action decotee (achat potentiellement interessant)</t>
   </si>
   <si>
     <t>Capitalisation / Capitaux Propres</t>
   </si>
   <si>
-    <t>=B27/B26</t>
-  </si>
-  <si>
-    <t>&lt; 1 = decote</t>
-  </si>
-  <si>
-    <t>ROE — Return on Equity (%)</t>
+    <t>&lt; 1 = decote sur actif net | &gt; 2 = prime significative</t>
+  </si>
+  <si>
+    <t>ROE</t>
   </si>
   <si>
     <t>RN / Capitaux Propres x 100</t>
   </si>
   <si>
-    <t>=F12*1000000/B26*100</t>
-  </si>
-  <si>
-    <t>&gt; 10% = bon</t>
-  </si>
-  <si>
-    <t>RVC — PER x PBR (Lynch)</t>
+    <t>&lt; 5% = faible | 5-10% = moyen | 10-15% = bon | &gt; 15% = excellent</t>
+  </si>
+  <si>
+    <t>RVC (Lynch)</t>
   </si>
   <si>
     <t>PER x PBR</t>
-  </si>
-  <si>
-    <t>=D30*D32</t>
-  </si>
-  <si>
-    <t>&lt; 22 = decote</t>
-  </si>
-  <si>
-    <t>A5 — DIVIDENDES &amp; TAUX DE DISTRIBUTION</t>
-  </si>
-  <si>
-    <t>Dividende brut (FCFA)</t>
-  </si>
-  <si>
-    <t>BNPA (FCFA)</t>
-  </si>
-  <si>
-    <t>Taux distrib. %</t>
-  </si>
-  <si>
-    <t>Rendement %</t>
-  </si>
-  <si>
-    <t>Progression %</t>
-  </si>
-  <si>
-    <t>TOTAL / MOYENNE</t>
-  </si>
-  <si>
-    <t>A6 — FONDS PROPRES (FCFA)</t>
-  </si>
-  <si>
-    <t>Composante</t>
-  </si>
-  <si>
-    <t>Annee N-1</t>
-  </si>
-  <si>
-    <t>Annee N</t>
-  </si>
-  <si>
-    <t>Variation %</t>
-  </si>
-  <si>
-    <t>Capital souscrit</t>
-  </si>
-  <si>
-    <t>Reserves</t>
-  </si>
-  <si>
-    <t>Report a nouveau</t>
-  </si>
-  <si>
-    <t>Dividendes verses</t>
-  </si>
-  <si>
-    <t>TOTAL FONDS PROPRES</t>
-  </si>
-  <si>
-    <t>A7 — NOTATION FINANCIERE &amp; ACTIVITES RECENTES</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Date rapport</t>
-  </si>
-  <si>
-    <t>Notation court terme</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>Agence de notation</t>
-  </si>
-  <si>
-    <t>Notation long terme</t>
-  </si>
-  <si>
-    <t>A+</t>
-  </si>
-  <si>
-    <t>Variation CA/PNB (dernier trimestre)</t>
-  </si>
-  <si>
-    <t>RichBourse</t>
-  </si>
-  <si>
-    <t>Variation Resultat Net (dernier trimestre)</t>
-  </si>
-  <si>
-    <t>A8 — COMPARAISON MARCHE BOURSIER VS EPARGNE</t>
-  </si>
-  <si>
-    <t>Parametre</t>
-  </si>
-  <si>
-    <t>Marche Boursier</t>
-  </si>
-  <si>
-    <t>Epargne (saisir rendement %)</t>
-  </si>
-  <si>
-    <t>Montant investi (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix d'achat historique (FCFA)</t>
-  </si>
-  <si>
-    <t>CMP = Prix x 1,014 (frais 1,4%)</t>
-  </si>
-  <si>
-    <t>Nombre de titres acquis</t>
-  </si>
-  <si>
-    <t>Prix actuel du titre (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix net apres taxe cession 1,4% (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus-value unitaire (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus-value totale (FCFA)</t>
-  </si>
-  <si>
-    <t>Total dividendes recus par titre (FCFA)</t>
-  </si>
-  <si>
-    <t>Rendement dividendes total (FCFA)</t>
-  </si>
-  <si>
-    <t>RENDEMENT TOTAL (FCFA)</t>
-  </si>
-  <si>
-    <t>PERFORMANCE (%)</t>
-  </si>
-  <si>
-    <t>VERDICT</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir rendement epargne % ici</t>
-  </si>
-  <si>
-    <t>A9 — CONCLUSION ANALYSE FONDAMENTALE (texte libre)</t>
-  </si>
-  <si>
-    <t>B — ANALYSE TECHNIQUE</t>
-  </si>
-  <si>
-    <t>B1 — INDICATEURS TECHNIQUES (saisie depuis graphique)</t>
-  </si>
-  <si>
-    <t>Signal observe</t>
-  </si>
-  <si>
-    <t>Valeur / Niveau</t>
-  </si>
-  <si>
-    <t>Score auto</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>Moyenne Mobile 20 jours (MM20)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir signal</t>
-  </si>
-  <si>
-    <t>Zone de survente : cours EN DESSOUS de la MM20</t>
-  </si>
-  <si>
-    <t>Bandes de Bollinger</t>
-  </si>
-  <si>
-    <t>Zone de survente : cours touche la bande inferieure</t>
-  </si>
-  <si>
-    <t>MACD</t>
-  </si>
-  <si>
-    <t>Zone de survente : MACD croise Signal a la hausse</t>
-  </si>
-  <si>
-    <t>RSI (saisir valeur en col C)</t>
-  </si>
-  <si>
-    <t>&lt; 30 survente | 30-70 neutre | &gt; 70 surachat</t>
-  </si>
-  <si>
-    <t>Volume (tendance recente)</t>
-  </si>
-  <si>
-    <t>Volume croissant sur baisse = accumulation = survente</t>
-  </si>
-  <si>
-    <t>SCORE TECHNIQUE (max +5 / min -5)</t>
-  </si>
-  <si>
-    <t>B2 — PRIX MEDIANS (PM)</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Plus Haut (FCFA)</t>
-  </si>
-  <si>
-    <t>Plus Bas (FCFA)</t>
-  </si>
-  <si>
-    <t>Prix Median</t>
-  </si>
-  <si>
-    <t>Signal (vs prix actuel B24)</t>
-  </si>
-  <si>
-    <t>52 semaines (1 an)</t>
-  </si>
-  <si>
-    <t>2 ans</t>
-  </si>
-  <si>
-    <t>B3 — PER ACTUALISE (integre la derniere evolution du RN)</t>
-  </si>
-  <si>
-    <t>Source / Formule</t>
-  </si>
-  <si>
-    <t>Prix actuel (FCFA)</t>
-  </si>
-  <si>
-    <t>Lie a B24</t>
-  </si>
-  <si>
-    <t>BNPA N (FCFA)</t>
-  </si>
-  <si>
-    <t>Lie a B25</t>
-  </si>
-  <si>
-    <t>Evolution RN dernier trimestre (%)</t>
-  </si>
-  <si>
-    <t>RichBourse / Rapport trimestriel</t>
-  </si>
-  <si>
-    <t>BNPA actualise (FCFA)</t>
-  </si>
-  <si>
-    <t>= BNPA x (1 + evol%)</t>
-  </si>
-  <si>
-    <t>PER actualise</t>
-  </si>
-  <si>
-    <t>= Prix / BNPA actualise</t>
-  </si>
-  <si>
-    <t>B4 — PRIX CIBLE AUX DIVIDENDES (PCD)</t>
-  </si>
-  <si>
-    <t>Note : Le PCD n'est pertinent que si l'entreprise verse des dividendes. Si dividende = 0, utiliser B5 (Gordon-Shapiro).</t>
-  </si>
-  <si>
-    <t>Formule</t>
-  </si>
-  <si>
-    <t>Evolution RN (%)</t>
-  </si>
-  <si>
-    <t>Meme valeur qu'en B3</t>
-  </si>
-  <si>
-    <t>Dividende brut N (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir le dernier dividende verse</t>
-  </si>
-  <si>
-    <t>Dividende previsionnel (FCFA)</t>
-  </si>
-  <si>
-    <t>= Dividende x (1 + evol%)</t>
-  </si>
-  <si>
-    <t>Rendement sectoriel BRVM (%)</t>
-  </si>
-  <si>
-    <t>Reference : 5-8% (modifiable)</t>
-  </si>
-  <si>
-    <t>PCD = 100 x DVD_prev / Rendement</t>
-  </si>
-  <si>
-    <t>= 100 x Dprev / Rendement%</t>
-  </si>
-  <si>
-    <t>Zone cible basse (-5%)</t>
-  </si>
-  <si>
-    <t>= PCD x 0.95</t>
-  </si>
-  <si>
-    <t>Zone cible haute (+5%)</t>
-  </si>
-  <si>
-    <t>= PCD x 1.05</t>
-  </si>
-  <si>
-    <t>Signal (prix B24 vs zone cible)</t>
-  </si>
-  <si>
-    <t>Calcul automatique</t>
-  </si>
-  <si>
-    <t>B5 — MODELE DE GORDON-SHAPIRO   P0 = D1 / (r - g)</t>
-  </si>
-  <si>
-    <t>D1 = dividende attendu l'an prochain | r = taux exige | g = taux croissance dividendes</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>D1 - Dividende attendu (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Hypothese ou dernier DVD x (1+g)</t>
-  </si>
-  <si>
-    <t>r - Taux de rentabilite exige (%)</t>
-  </si>
-  <si>
-    <t>Cout du capital / rendement cible (ex: 8%)</t>
-  </si>
-  <si>
-    <t>g - Taux de croissance DVD (%)</t>
-  </si>
-  <si>
-    <t>Croissance annuelle supposee (ex: 2%)</t>
-  </si>
-  <si>
-    <t>P0 = D1 / (r - g)  [FCFA]</t>
-  </si>
-  <si>
-    <t>Prix theorique calcule automatiquement</t>
-  </si>
-  <si>
-    <t>Signal prix actuel vs P0</t>
-  </si>
-  <si>
-    <t>B6 — GESTION DU RISQUE : STOP-LOSS &amp; RISK/REWARD</t>
-  </si>
-  <si>
-    <t>Formule/Note</t>
-  </si>
-  <si>
-    <t>Prix d'achat vise (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir prix entree prevue</t>
-  </si>
-  <si>
-    <t>Stop-Loss = Prix x 0,90 (FCFA)</t>
-  </si>
-  <si>
-    <t>= Prix x 0.90 (perte max 10%)</t>
-  </si>
-  <si>
-    <t>Objectif Take Profit (FCFA)</t>
-  </si>
-  <si>
-    <t>&lt;-- Saisir objectif de prix</t>
-  </si>
-  <si>
-    <t>Perte potentielle / titre (FCFA)</t>
-  </si>
-  <si>
-    <t>= Prix - Stop</t>
-  </si>
-  <si>
-    <t>Gain potentiel / titre (FCFA)</t>
-  </si>
-  <si>
-    <t>= Objectif - Prix</t>
-  </si>
-  <si>
-    <t>Ratio Risk / Reward</t>
-  </si>
-  <si>
-    <t>= Gain / Perte  (objectif &gt;= 2)</t>
-  </si>
-  <si>
-    <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
-  </si>
-  <si>
-    <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
-  </si>
-  <si>
-    <t>Societe : [NOM]   |   Date : [JJ/MM/AAAA]   |   Prix analyse : [FCFA]</t>
-  </si>
-  <si>
-    <t>SCORECARD FONDAMENTALE</t>
-  </si>
-  <si>
-    <t>Critere</t>
-  </si>
-  <si>
-    <t>Valeur (depuis ETUDE)</t>
-  </si>
-  <si>
-    <t>Zone normale</t>
-  </si>
-  <si>
-    <t>Score (0-3)</t>
-  </si>
-  <si>
-    <t>Croissance CA (N/N-4 %)</t>
-  </si>
-  <si>
-    <t>&lt;-- depuis ETUDE</t>
-  </si>
-  <si>
-    <t>&gt; 10%</t>
-  </si>
-  <si>
-    <t>&lt;-- saisir signal</t>
-  </si>
-  <si>
-    <t>Croissance RN (N/N-4 %)</t>
-  </si>
-  <si>
-    <t>Marge nette moyenne (%)</t>
-  </si>
-  <si>
-    <t>&gt; 5%</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>9 - 15</t>
-  </si>
-  <si>
-    <t>PBR</t>
-  </si>
-  <si>
-    <t>&lt; 1 ideal</t>
-  </si>
-  <si>
-    <t>ROE (%)</t>
-  </si>
-  <si>
-    <t>Rendement dividende (%)</t>
-  </si>
-  <si>
-    <t>&gt; 3%</t>
-  </si>
-  <si>
-    <t>RVC (PER x PBR)</t>
-  </si>
-  <si>
-    <t>&lt; 22</t>
-  </si>
-  <si>
-    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
-  </si>
-  <si>
-    <t>SCORECARD TECHNIQUE</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
-  </si>
-  <si>
-    <t>-5 a +5</t>
-  </si>
-  <si>
-    <t>Prix Medians PM1 et PM2 (B2)</t>
-  </si>
-  <si>
-    <t>&lt; PM = survente</t>
-  </si>
-  <si>
-    <t>PER actualise (B3)</t>
-  </si>
-  <si>
-    <t>9-15 = normal</t>
-  </si>
-  <si>
-    <t>PCD / Gordon-Shapiro (B4/B5)</t>
-  </si>
-  <si>
-    <t>&lt; PCD = survente</t>
-  </si>
-  <si>
-    <t>Risk/Reward (B6)</t>
-  </si>
-  <si>
-    <t>&gt;= 2 = bon</t>
-  </si>
-  <si>
-    <t>SCORE TECHNIQUE TOTAL (/15)</t>
-  </si>
-  <si>
-    <t>VERDICT GLOBAL</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>% atteint</t>
-  </si>
-  <si>
-    <t>Appreciation</t>
-  </si>
-  <si>
-    <t>Score Fondamental</t>
-  </si>
-  <si>
-    <t>Score Technique</t>
-  </si>
-  <si>
-    <t>SCORE TOTAL</t>
-  </si>
-  <si>
-    <t>RECOMMANDATION FINALE (texte libre)</t>
-  </si>
-  <si>
-    <t>PROFIL DE LA SOCIETE</t>
-  </si>
-  <si>
-    <t>IDENTIFICATION</t>
-  </si>
-  <si>
-    <t>Nom de la societe</t>
-  </si>
-  <si>
-    <t>Ticker BRVM</t>
-  </si>
-  <si>
-    <t>Secteur d'activite</t>
-  </si>
-  <si>
-    <t>Pays d'origine</t>
-  </si>
-  <si>
-    <t>Date d'introduction en bourse</t>
-  </si>
-  <si>
-    <t>CAPITAL &amp; ACTIONNARIAT</t>
-  </si>
-  <si>
-    <t>Capital social (FCFA)</t>
-  </si>
-  <si>
-    <t>Nombre de titres</t>
-  </si>
-  <si>
-    <t>Flottant (%)</t>
-  </si>
-  <si>
-    <t>Principaux actionnaires</t>
-  </si>
-  <si>
-    <t>LIQUIDITE DU TITRE (critique sur BRVM)</t>
-  </si>
-  <si>
-    <t>Volume moyen journalier (titres)</t>
-  </si>
-  <si>
-    <t>&lt;-- Source : BRVM.org</t>
-  </si>
-  <si>
-    <t>Volume moyen journalier (FCFA)</t>
-  </si>
-  <si>
-    <t>Frequence de cotation (%)</t>
-  </si>
-  <si>
-    <t>&lt;-- % seances avec transaction</t>
-  </si>
-  <si>
-    <t>Appreciation liquidite</t>
-  </si>
-  <si>
-    <t>&lt;-- Forte / Moyenne / Faible</t>
-  </si>
-  <si>
-    <t>NOTATION &amp; CONFORMITE</t>
-  </si>
-  <si>
-    <t>Note court terme</t>
-  </si>
-  <si>
-    <t>Note long terme</t>
-  </si>
-  <si>
-    <t>Dividende verse regulierement ?</t>
-  </si>
-  <si>
-    <t>&lt;-- Oui / Non</t>
-  </si>
-  <si>
-    <t>SOURCES D'INFORMATION</t>
-  </si>
-  <si>
-    <t>Rapport annuel</t>
-  </si>
-  <si>
-    <t>&lt;-- Lien ou date</t>
-  </si>
-  <si>
-    <t>Site de la societe</t>
-  </si>
-  <si>
-    <t>Profil RichBourse</t>
-  </si>
-  <si>
-    <t>&lt;-- richbourse.com</t>
-  </si>
-  <si>
-    <t>Profil BRVM</t>
-  </si>
-  <si>
-    <t>&lt;-- brvm.org</t>
-  </si>
-  <si>
-    <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
-  </si>
-  <si>
-    <t>Expression mathematique</t>
-  </si>
-  <si>
-    <t>Unite</t>
-  </si>
-  <si>
-    <t>Interpretation / Seuils BRVM</t>
-  </si>
-  <si>
-    <t>ANALYSE FONDAMENTALE</t>
-  </si>
-  <si>
-    <t>Croissance N/N-4</t>
-  </si>
-  <si>
-    <t>(N - N-4) / |N-4| x 100</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>Positif = croissance. Negatif = contraction. Seuil : &gt; 10%/an = excellent</t>
-  </si>
-  <si>
-    <t>TCAM (CAGR)</t>
-  </si>
-  <si>
-    <t>(N / N-4)^(1/4) - 1</t>
-  </si>
-  <si>
-    <t>Taux de Croissance Annuel Moyen sur 4 ans</t>
-  </si>
-  <si>
-    <t>Marge Nette</t>
-  </si>
-  <si>
-    <t>RN / CA x 100</t>
-  </si>
-  <si>
-    <t>&lt; 2% = faible | 2-5% = moyen | &gt; 5% = bon | &gt; 10% = tres bon</t>
-  </si>
-  <si>
-    <t>fois</t>
-  </si>
-  <si>
-    <t>Zone normale BRVM : 9-15. &gt; 15 = surevalue, &lt; 9 = sous-evalue</t>
-  </si>
-  <si>
-    <t>VMC</t>
-  </si>
-  <si>
-    <t>FCFA</t>
-  </si>
-  <si>
-    <t>Prix &lt; VMC = action decotee (achat potentiellement interessant)</t>
-  </si>
-  <si>
-    <t>&lt; 1 = decote sur actif net | &gt; 2 = prime significative</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>&lt; 5% = faible | 5-10% = moyen | 10-15% = bon | &gt; 15% = excellent</t>
-  </si>
-  <si>
-    <t>RVC (Lynch)</t>
   </si>
   <si>
     <t>&lt; 22 = decote globale. Indicateur de sous-valorisation composite</t>
@@ -1023,7 +1014,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1127,6 +1118,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
@@ -1158,15 +1164,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1215,6 +1214,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1250,7 +1261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1276,6 +1287,9 @@
     <xf numFmtId="166" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1303,9 +1317,6 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1348,19 +1359,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1369,16 +1389,16 @@
     <xf numFmtId="168" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1876,17 +1896,23 @@
       <c r="A16" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="9">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="9">
+        <f>B8</f>
+        <v>0</v>
+      </c>
       <c r="D16" s="7">
         <f>IFERROR(B16/C16*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <f>IFERROR(IF(D16&gt;=10,"Tres rentable",IF(D16&gt;=5,"Rentable",IF(D16&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="7">
@@ -1898,69 +1924,93 @@
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="9">
+        <f>C8</f>
+        <v>0</v>
+      </c>
       <c r="D17" s="7">
         <f>IFERROR(B17/C17*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <f>IFERROR(IF(D17&gt;=10,"Tres rentable",IF(D17&gt;=5,"Rentable",IF(D17&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="9">
+        <f>D12</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="9">
+        <f>D8</f>
+        <v>0</v>
+      </c>
       <c r="D18" s="7">
         <f>IFERROR(B18/C18*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <f>IFERROR(IF(D18&gt;=10,"Tres rentable",IF(D18&gt;=5,"Rentable",IF(D18&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="B19" s="9">
+        <f>E12</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="9">
+        <f>E8</f>
+        <v>0</v>
+      </c>
       <c r="D19" s="7">
         <f>IFERROR(B19/C19*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <f>IFERROR(IF(D19&gt;=10,"Tres rentable",IF(D19&gt;=5,"Rentable",IF(D19&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="B20" s="9">
+        <f>F12</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="9">
+        <f>F8</f>
+        <v>0</v>
+      </c>
       <c r="D20" s="7">
         <f>IFERROR(B20/C20*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <f>IFERROR(IF(D20&gt;=10,"Tres rentable",IF(D20&gt;=5,"Rentable",IF(D20&gt;=2,"Faiblement rentable","Tres faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
     <row r="22" spans="1:8" ht="18" customHeight="1">
@@ -1988,193 +2038,161 @@
       <c r="D23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="13"/>
+      <c r="C26" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row r="29" spans="1:8" ht="5" customHeight="1"/>
     <row r="30" spans="1:8">
       <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="7">
+        <f>IFERROR(B24/B25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="7">
-        <f>IFERROR(B24/B25,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="9">
-        <f>IFERROR(IF(D30&gt;15,"Surevalue",IF(D30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>43</v>
+      <c r="D30" s="10">
+        <f>IFERROR(IF(B30&gt;15,"Surevalue",IF(B30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="15">
+        <v>41</v>
+      </c>
+      <c r="B31" s="16">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="9">
-        <f>IFERROR(IF(B24&gt;D31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="10" t="s">
-        <v>47</v>
+      <c r="C31" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="10">
+        <f>IFERROR(IF(B24&gt;B31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="7">
+        <v>43</v>
+      </c>
+      <c r="B32" s="7">
         <f>IFERROR(B27/B26,"")</f>
         <v>0</v>
       </c>
-      <c r="E32" s="9">
-        <f>IFERROR(IF(D32&lt;1,"Decote comptable",IF(D32&lt;2,"Normal","Prime elevee")),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>51</v>
+      <c r="C32" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="10">
+        <f>IFERROR(IF(B32&lt;1,"Decote comptable",IF(B32&lt;2,"Normal","Prime elevee")),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="7">
+        <v>45</v>
+      </c>
+      <c r="B33" s="7">
         <f>IFERROR(F12*1000000/B26*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="9">
-        <f>IFERROR(IF(D33&gt;=15,"Excellent",IF(D33&gt;=10,"Bon",IF(D33&gt;=5,"Moyen","Faible"))),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>55</v>
+      <c r="C33" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="10">
+        <f>IFERROR(IF(B33&gt;=15,"Excellent",IF(B33&gt;=10,"Bon",IF(B33&gt;=5,"Moyen","Faible"))),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D34" s="7">
-        <f>IFERROR(D30*D32,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="9">
-        <f>IFERROR(IF(D34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
+      </c>
+      <c r="B34" s="7">
+        <f>IFERROR(B30*B32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="10">
+        <f>IFERROR(IF(B34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
     <row r="36" spans="1:8" ht="18" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2189,52 +2207,63 @@
         <v>15</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="7">
-        <f>IFERROR(B38/(C38*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B38" s="17"/>
+      <c r="C38" s="16">
+        <f>IFERROR(B38*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="17"/>
       <c r="E38" s="7">
+        <f>IFERROR(B38/D38*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="7">
         <f>IFERROR(B38/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F38" s="11"/>
+      <c r="G38" s="12"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="7">
-        <f>IFERROR(B39/(C39*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B39" s="17"/>
+      <c r="C39" s="16">
+        <f>IFERROR(B39*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="17"/>
       <c r="E39" s="7">
+        <f>IFERROR(B39/D39*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="7">
         <f>IFERROR(B39/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F39" s="7">
+      <c r="G39" s="7">
         <f>IFERROR((B39-B38)/ABS(B38)*100,"")</f>
         <v>0</v>
       </c>
@@ -2243,17 +2272,21 @@
       <c r="A40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="7">
-        <f>IFERROR(B40/(C40*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="16">
+        <f>IFERROR(B40*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="17"/>
       <c r="E40" s="7">
+        <f>IFERROR(B40/D40*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="7">
         <f>IFERROR(B40/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F40" s="7">
+      <c r="G40" s="7">
         <f>IFERROR((B40-B39)/ABS(B39)*100,"")</f>
         <v>0</v>
       </c>
@@ -2262,17 +2295,21 @@
       <c r="A41" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="7">
-        <f>IFERROR(B41/(C41*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="16">
+        <f>IFERROR(B41*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="17"/>
       <c r="E41" s="7">
+        <f>IFERROR(B41/D41*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="7">
         <f>IFERROR(B41/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F41" s="7">
+      <c r="G41" s="7">
         <f>IFERROR((B41-B40)/ABS(B40)*100,"")</f>
         <v>0</v>
       </c>
@@ -2281,44 +2318,52 @@
       <c r="A42" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="7">
-        <f>IFERROR(B42/(C42*0.85)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="16">
+        <f>IFERROR(B42*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="17"/>
       <c r="E42" s="7">
+        <f>IFERROR(B42/D42*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="7">
         <f>IFERROR(B42/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="F42" s="7">
+      <c r="G42" s="7">
         <f>IFERROR((B42-B41)/ABS(B41)*100,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="15">
+      <c r="A43" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="16">
         <f>SUM(B38:B42)</f>
         <v>0</v>
       </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="7">
-        <f>IFERROR(AVERAGE(D38:D42),"")</f>
-        <v>0</v>
-      </c>
+      <c r="C43" s="16">
+        <f>IFERROR(B43*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="12"/>
       <c r="E43" s="7">
         <f>IFERROR(AVERAGE(E38:E42),"")</f>
         <v>0</v>
       </c>
-      <c r="F43" s="11"/>
+      <c r="F43" s="7">
+        <f>IFERROR(AVERAGE(F38:F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:8" ht="5" customHeight="1"/>
     <row r="45" spans="1:8" ht="18" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2330,21 +2375,21 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2355,7 +2400,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="5" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2366,7 +2411,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="5" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2388,7 +2433,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2398,14 +2443,14 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="18">
+      <c r="A52" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="9">
         <f>SUM(B47:B51)</f>
         <v>0</v>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="9">
         <f>SUM(C47:C51)</f>
         <v>0</v>
       </c>
@@ -2417,7 +2462,7 @@
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
     <row r="54" spans="1:8" ht="18" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2429,66 +2474,66 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D56" s="20"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D57" s="20"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D58" s="20"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="20" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="18" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2500,153 +2545,153 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="21"/>
-      <c r="D63" s="11"/>
+      <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="21"/>
-      <c r="D64" s="11"/>
+      <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B65" s="15">
+        <v>86</v>
+      </c>
+      <c r="B65" s="16">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
       <c r="C65" s="21"/>
-      <c r="D65" s="11"/>
+      <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B66" s="15">
+        <v>87</v>
+      </c>
+      <c r="B66" s="16">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
       <c r="C66" s="21"/>
-      <c r="D66" s="11"/>
+      <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="21"/>
-      <c r="D67" s="11"/>
+      <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="15">
+        <v>89</v>
+      </c>
+      <c r="B68" s="16">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
       <c r="C68" s="21"/>
-      <c r="D68" s="11"/>
+      <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B69" s="15">
+        <v>90</v>
+      </c>
+      <c r="B69" s="16">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
       <c r="C69" s="21"/>
-      <c r="D69" s="11"/>
+      <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B70" s="18">
+        <v>91</v>
+      </c>
+      <c r="B70" s="9">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
       <c r="C70" s="21"/>
-      <c r="D70" s="11"/>
+      <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B71" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="B71" s="17"/>
       <c r="C71" s="21"/>
-      <c r="D71" s="11"/>
+      <c r="D71" s="12"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B72" s="18">
+        <v>93</v>
+      </c>
+      <c r="B72" s="9">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
       <c r="C72" s="21"/>
-      <c r="D72" s="11"/>
+      <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B73" s="18">
+      <c r="A73" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B73" s="9">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
       <c r="C73" s="21"/>
-      <c r="D73" s="11"/>
+      <c r="D73" s="12"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="17" t="s">
-        <v>103</v>
+      <c r="A74" s="18" t="s">
+        <v>95</v>
       </c>
       <c r="B74" s="7">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
       <c r="C74" s="21"/>
-      <c r="D74" s="11"/>
+      <c r="D74" s="12"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="17" t="s">
-        <v>104</v>
+      <c r="A75" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="B75" s="22">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
-      <c r="C75" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="11"/>
+      <c r="C75" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
     <row r="77" spans="1:8" ht="18" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2688,7 +2733,7 @@
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -2701,7 +2746,7 @@
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
     <row r="84" spans="1:8" ht="18" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2713,27 +2758,27 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>114</v>
+        <v>105</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C86" s="21"/>
       <c r="D86" s="24">
@@ -2741,15 +2786,15 @@
         <v>0</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>114</v>
+        <v>108</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C87" s="21"/>
       <c r="D87" s="24">
@@ -2757,15 +2802,15 @@
         <v>0</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C88" s="21"/>
       <c r="D88" s="24">
@@ -2773,15 +2818,15 @@
         <v>0</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C89" s="21"/>
       <c r="D89" s="24">
@@ -2789,15 +2834,15 @@
         <v>0</v>
       </c>
       <c r="E89" s="25" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B90" s="13" t="s">
         <v>114</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="C90" s="21"/>
       <c r="D90" s="24">
@@ -2805,15 +2850,15 @@
         <v>0</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
+      <c r="A91" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
       <c r="D91" s="26">
         <f>SUM(D86:D90)</f>
         <v>0</v>
@@ -2826,7 +2871,7 @@
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
     <row r="93" spans="1:8" ht="18" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2838,47 +2883,47 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="15">
+      <c r="D95" s="16">
         <f>IFERROR((B95+C95)/2,"")</f>
         <v>0</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="10">
         <f>IFERROR(IF(B24&lt;D95,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="15">
+      <c r="D96" s="16">
         <f>IFERROR((B96+C96)/2,"")</f>
         <v>0</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="10">
         <f>IFERROR(IF(B24&lt;D96,"EN DESSOUS du PM - Survente","AU-DESSUS du PM - Surachat"),"-")</f>
         <v>0</v>
       </c>
@@ -2886,7 +2931,7 @@
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
     <row r="98" spans="1:8" ht="18" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2898,79 +2943,79 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B100" s="18">
+        <v>127</v>
+      </c>
+      <c r="B100" s="9">
         <f>B24</f>
         <v>0</v>
       </c>
       <c r="C100" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D100" s="11"/>
+        <v>128</v>
+      </c>
+      <c r="D100" s="12"/>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B101" s="15">
+        <v>129</v>
+      </c>
+      <c r="B101" s="16">
         <f>B25</f>
         <v>0</v>
       </c>
       <c r="C101" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="D101" s="11"/>
+        <v>130</v>
+      </c>
+      <c r="D101" s="12"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="5" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B102" s="28"/>
       <c r="C102" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D102" s="11"/>
+        <v>132</v>
+      </c>
+      <c r="D102" s="12"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B103" s="15">
+        <v>133</v>
+      </c>
+      <c r="B103" s="16">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
       <c r="C103" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D103" s="11"/>
+        <v>134</v>
+      </c>
+      <c r="D103" s="12"/>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="5" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B104" s="7">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
       <c r="C104" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="D104" s="9">
+        <v>136</v>
+      </c>
+      <c r="D104" s="10">
         <f>IFERROR(IF(B104&gt;15,"Surevalue - Surachat",IF(B104&lt;9,"Sous-evalue - Survente","Normal (9-15)")),"-")</f>
         <v>0</v>
       </c>
@@ -2978,7 +3023,7 @@
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
     <row r="106" spans="1:8" ht="18" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2990,7 +3035,7 @@
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
       <c r="A107" s="29" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B107" s="29"/>
       <c r="C107" s="29"/>
@@ -3002,119 +3047,119 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="5" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B109" s="28"/>
       <c r="C109" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="D109" s="11"/>
+        <v>141</v>
+      </c>
+      <c r="D109" s="12"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B110" s="16"/>
+        <v>142</v>
+      </c>
+      <c r="B110" s="17"/>
       <c r="C110" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D110" s="11"/>
+        <v>143</v>
+      </c>
+      <c r="D110" s="12"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B111" s="15">
+        <v>144</v>
+      </c>
+      <c r="B111" s="16">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
       <c r="C111" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D111" s="11"/>
+        <v>145</v>
+      </c>
+      <c r="D111" s="12"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="5" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B112" s="28">
         <v>6.5</v>
       </c>
       <c r="C112" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="D112" s="11"/>
+        <v>147</v>
+      </c>
+      <c r="D112" s="12"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B113" s="15">
+        <v>148</v>
+      </c>
+      <c r="B113" s="16">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
       <c r="C113" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="D113" s="11"/>
+        <v>149</v>
+      </c>
+      <c r="D113" s="12"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B114" s="15">
+        <v>150</v>
+      </c>
+      <c r="B114" s="16">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C114" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D114" s="11"/>
+        <v>151</v>
+      </c>
+      <c r="D114" s="12"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B115" s="15">
+        <v>152</v>
+      </c>
+      <c r="B115" s="16">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C115" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="D115" s="11"/>
+        <v>153</v>
+      </c>
+      <c r="D115" s="12"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B116" s="27">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
       <c r="C116" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D116" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="D116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
     <row r="118" spans="1:8" ht="18" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3126,7 +3171,7 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="30" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B119" s="30"/>
       <c r="C119" s="30"/>
@@ -3138,82 +3183,82 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B121" s="16"/>
+        <v>159</v>
+      </c>
+      <c r="B121" s="17"/>
       <c r="C121" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D121" s="11"/>
+        <v>160</v>
+      </c>
+      <c r="D121" s="12"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B122" s="28">
         <v>8</v>
       </c>
       <c r="C122" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="D122" s="11"/>
+        <v>162</v>
+      </c>
+      <c r="D122" s="12"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="5" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B123" s="28">
         <v>2</v>
       </c>
       <c r="C123" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="D123" s="11"/>
+        <v>164</v>
+      </c>
+      <c r="D123" s="12"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="5" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B124" s="31">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
       <c r="C124" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="D124" s="11"/>
+        <v>166</v>
+      </c>
+      <c r="D124" s="12"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="5" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B125" s="27">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
       <c r="C125" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D125" s="11"/>
+        <v>155</v>
+      </c>
+      <c r="D125" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
     <row r="128" spans="1:8" ht="18" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3225,89 +3270,89 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="5" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B130" s="6"/>
       <c r="C130" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D130" s="11"/>
+        <v>171</v>
+      </c>
+      <c r="D130" s="12"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B131" s="15">
+        <v>172</v>
+      </c>
+      <c r="B131" s="16">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
       <c r="C131" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="D131" s="11"/>
+        <v>173</v>
+      </c>
+      <c r="D131" s="12"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="5" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B132" s="6"/>
       <c r="C132" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="D132" s="11"/>
+        <v>175</v>
+      </c>
+      <c r="D132" s="12"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B133" s="15">
+        <v>176</v>
+      </c>
+      <c r="B133" s="16">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
       <c r="C133" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="D133" s="11"/>
+        <v>177</v>
+      </c>
+      <c r="D133" s="12"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B134" s="15">
+        <v>178</v>
+      </c>
+      <c r="B134" s="16">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
       <c r="C134" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="D134" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="D134" s="12"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="5" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B135" s="7">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
       <c r="C135" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="D135" s="9">
+        <v>181</v>
+      </c>
+      <c r="D135" s="10">
         <f>IFERROR(IF(B135&gt;=2,"Bon (&gt;= 2:1)",IF(B135&gt;=1,"Acceptable (1:1)","Mauvais")),"")</f>
         <v>0</v>
       </c>
@@ -3315,7 +3360,7 @@
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
     <row r="137" spans="1:8" ht="18" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3405,7 +3450,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3414,7 +3459,7 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="32" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
@@ -3424,7 +3469,7 @@
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -3433,149 +3478,165 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E6" s="34"/>
+        <v>191</v>
+      </c>
+      <c r="B6" s="33">
+        <f>IFERROR(ETUDE!G8,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D6" s="34">
+        <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E7" s="34"/>
+        <v>193</v>
+      </c>
+      <c r="B7" s="33">
+        <f>IFERROR(ETUDE!G12,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="34">
+        <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" s="34"/>
+        <v>194</v>
+      </c>
+      <c r="B8" s="33">
+        <f>IFERROR(ETUDE!G16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="34">
+        <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="35"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E9" s="34"/>
+        <v>196</v>
+      </c>
+      <c r="B9" s="33">
+        <f>IFERROR(ETUDE!B30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="34">
+        <f>IFERROR(ETUDE!D30,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="35"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B10" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="33">
+        <f>IFERROR(ETUDE!B32,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E10" s="34"/>
+      <c r="D10" s="34">
+        <f>IFERROR(ETUDE!D32,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="35"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="D11" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="34"/>
+      <c r="B11" s="33">
+        <f>IFERROR(ETUDE!B33,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="34">
+        <f>IFERROR(ETUDE!D33,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="35"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="34"/>
+      <c r="B12" s="33">
+        <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="34">
+        <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E13" s="34"/>
+        <v>203</v>
+      </c>
+      <c r="B13" s="33">
+        <f>IFERROR(ETUDE!B34,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="34">
+        <f>IFERROR(ETUDE!D34,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="35"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="17" t="s">
-        <v>214</v>
+      <c r="A14" s="18" t="s">
+        <v>205</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
@@ -3583,7 +3644,7 @@
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -3592,147 +3653,147 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E18" s="34"/>
+        <v>209</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E18" s="38"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E19" s="34"/>
+        <v>212</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="38"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E20" s="34"/>
+        <v>214</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="38"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B21" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E21" s="34"/>
+        <v>216</v>
+      </c>
+      <c r="B21" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="38"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="E22" s="34"/>
+        <v>218</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="17" t="s">
-        <v>228</v>
+      <c r="A23" s="18" t="s">
+        <v>220</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="35">
+      <c r="E23" s="36">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
+      <c r="A25" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B27" s="37">
+        <v>225</v>
+      </c>
+      <c r="B27" s="40">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="41">
         <v>24</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="42">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
@@ -3743,16 +3804,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B28" s="37">
+        <v>226</v>
+      </c>
+      <c r="B28" s="40">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="41">
         <v>15</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="42">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
@@ -3762,21 +3823,21 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="B29" s="40">
+      <c r="A29" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B29" s="43">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="44">
         <v>39</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="42">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="42">
+      <c r="E29" s="45">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
@@ -3784,7 +3845,7 @@
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -3846,7 +3907,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3854,7 +3915,7 @@
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3862,48 +3923,48 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+        <v>231</v>
+      </c>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+        <v>232</v>
+      </c>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+        <v>233</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+        <v>234</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+        <v>235</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" ht="5" customHeight="1"/>
     <row r="9" spans="1:4" ht="18" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -3911,40 +3972,40 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+        <v>237</v>
+      </c>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+        <v>238</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+        <v>239</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+        <v>240</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="18" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -3952,46 +4013,46 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+        <v>242</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+        <v>244</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+        <v>245</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+        <v>247</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3999,42 +4060,42 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+        <v>74</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+        <v>250</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+        <v>251</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+        <v>252</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="18" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -4042,41 +4103,41 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
+        <v>257</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
+        <v>258</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
+        <v>260</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
@@ -4105,7 +4166,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4113,314 +4174,314 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28" customHeight="1">
+      <c r="A5" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28" customHeight="1">
+      <c r="A6" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B6" s="46" t="s">
         <v>275</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="C6" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="38" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="28" customHeight="1">
+      <c r="A7" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="46" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="C7" s="41" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="28" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="D7" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="43" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="28" customHeight="1">
+      <c r="A8" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="C5" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D5" s="44" t="s">
+      <c r="B8" s="46" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="28" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="C8" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="D8" s="47" t="s">
         <v>283</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D6" s="44" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="28" customHeight="1">
+      <c r="A9" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="46" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28" customHeight="1">
-      <c r="A7" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="38" t="s">
+      <c r="C9" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="D7" s="44" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="28" customHeight="1">
+      <c r="A10" s="18" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="28" customHeight="1">
-      <c r="A8" s="17" t="s">
+      <c r="B10" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="C10" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="D8" s="44" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="28" customHeight="1">
+      <c r="A11" s="18" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="28" customHeight="1">
-      <c r="A9" s="17" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="D9" s="44" t="s">
+      <c r="B11" s="46" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="28" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="C11" s="41"/>
+      <c r="D11" s="47" t="s">
         <v>291</v>
       </c>
-      <c r="B10" s="43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" s="44" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="28" customHeight="1">
+      <c r="A12" s="18" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="28" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="B12" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="44" t="s">
+      <c r="C12" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="47" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28" customHeight="1">
-      <c r="A12" s="17" t="s">
+    <row r="13" spans="1:4" ht="28" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B13" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="C12" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" s="44" t="s">
+      <c r="C13" s="41" t="s">
+        <v>269</v>
+      </c>
+      <c r="D13" s="47" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="28" customHeight="1">
-      <c r="A13" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" s="44" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28" customHeight="1">
+      <c r="A16" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B16" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="C15" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D15" s="44" t="s">
+      <c r="C16" s="41"/>
+      <c r="D16" s="47" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="28" customHeight="1">
-      <c r="A16" s="17" t="s">
+    <row r="17" spans="1:4" ht="28" customHeight="1">
+      <c r="A17" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C17" s="41"/>
+      <c r="D17" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="B16" s="43" t="s">
+    </row>
+    <row r="18" spans="1:4" ht="28" customHeight="1">
+      <c r="A18" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="44" t="s">
+      <c r="C18" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="D18" s="47" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28" customHeight="1">
-      <c r="A17" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>306</v>
-      </c>
-      <c r="C17" s="38"/>
-      <c r="D17" s="44" t="s">
+    <row r="19" spans="1:4" ht="28" customHeight="1">
+      <c r="A19" s="18" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="28" customHeight="1">
-      <c r="A18" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="43" t="s">
+      <c r="B19" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="C18" s="38" t="s">
-        <v>285</v>
-      </c>
-      <c r="D18" s="44" t="s">
+      <c r="C19" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D19" s="47" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28" customHeight="1">
-      <c r="A19" s="17" t="s">
+    <row r="20" spans="1:4" ht="28" customHeight="1">
+      <c r="A20" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B20" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D19" s="44" t="s">
+      <c r="C20" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="47" t="s">
         <v>313</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28" customHeight="1">
-      <c r="A20" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="B20" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D20" s="44" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="28" customHeight="1">
+      <c r="A23" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B23" s="46" t="s">
         <v>319</v>
       </c>
-      <c r="C22" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D22" s="44" t="s">
+      <c r="C23" s="41" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="28" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="D23" s="47" t="s">
         <v>321</v>
       </c>
-      <c r="B23" s="43" t="s">
+    </row>
+    <row r="24" spans="1:4" ht="28" customHeight="1">
+      <c r="A24" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="B24" s="46" t="s">
         <v>323</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="C24" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D24" s="47" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="28" customHeight="1">
-      <c r="A24" s="17" t="s">
+    <row r="25" spans="1:4" ht="28" customHeight="1">
+      <c r="A25" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B25" s="46" t="s">
         <v>326</v>
       </c>
-      <c r="C24" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D24" s="44" t="s">
+      <c r="C25" s="41" t="s">
+        <v>282</v>
+      </c>
+      <c r="D25" s="47" t="s">
         <v>327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="28" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="B25" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>288</v>
-      </c>
-      <c r="D25" s="44" t="s">
-        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="327">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -647,9 +647,6 @@
   </si>
   <si>
     <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
-  </si>
-  <si>
-    <t>&lt;-- saisir signal</t>
   </si>
   <si>
     <t>-5 a +5</t>
@@ -1014,7 +1011,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1024,7 +1021,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1033,14 +1030,14 @@
     <font>
       <i/>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFDC2626"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1049,7 +1046,14 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1080,7 +1084,7 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1102,9 +1106,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="8"/>
-      <color rgb="FFFF6600"/>
+      <color rgb="FFD97706"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1113,6 +1125,14 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1141,6 +1161,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1E3A5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF404040"/>
@@ -1158,6 +1185,14 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
@@ -1165,7 +1200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,7 +1209,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF0D1B2A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1186,7 +1221,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
+        <fgColor rgb="FF1E3A5F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFDF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1198,19 +1269,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FF2F5496"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1223,6 +1282,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDE7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1261,7 +1332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,7 +1349,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1293,31 +1364,31 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1326,89 +1397,270 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="21" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF065F46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF065F46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -1698,6 +1950,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF0EA5E9"/>
+  </sheetPr>
   <dimension ref="A1:H140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1747,7 +2002,7 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="5" customHeight="1"/>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
+    <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1802,7 +2057,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="5" customHeight="1"/>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
+    <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1857,7 +2112,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="5" customHeight="1"/>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
+    <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
@@ -2013,7 +2268,7 @@
       <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
+    <row r="22" spans="1:8" ht="20" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2190,7 +2445,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
-    <row r="36" spans="1:8" ht="18" customHeight="1">
+    <row r="36" spans="1:8" ht="20" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
@@ -2361,7 +2616,7 @@
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:8" ht="5" customHeight="1"/>
-    <row r="45" spans="1:8" ht="18" customHeight="1">
+    <row r="45" spans="1:8" ht="20" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>57</v>
       </c>
@@ -2460,7 +2715,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
-    <row r="54" spans="1:8" ht="18" customHeight="1">
+    <row r="54" spans="1:8" ht="20" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>67</v>
       </c>
@@ -2531,7 +2786,7 @@
       <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
-    <row r="61" spans="1:8" ht="18" customHeight="1">
+    <row r="61" spans="1:8" ht="20" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -2575,7 +2830,7 @@
       <c r="A65" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="22">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
@@ -2586,7 +2841,7 @@
       <c r="A66" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="22">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
@@ -2597,7 +2852,10 @@
       <c r="A67" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B67" s="6"/>
+      <c r="B67" s="23">
+        <f>IFERROR(B24,"")</f>
+        <v>0</v>
+      </c>
       <c r="C67" s="21"/>
       <c r="D67" s="12"/>
     </row>
@@ -2605,7 +2863,7 @@
       <c r="A68" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="22">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
@@ -2616,7 +2874,7 @@
       <c r="A69" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="22">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
@@ -2627,7 +2885,7 @@
       <c r="A70" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="23">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
@@ -2646,7 +2904,7 @@
       <c r="A72" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="23">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
@@ -2657,7 +2915,7 @@
       <c r="A73" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="23">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
@@ -2668,7 +2926,7 @@
       <c r="A74" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="24">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
@@ -2679,7 +2937,7 @@
       <c r="A75" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="25">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
@@ -2689,7 +2947,7 @@
       <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
-    <row r="77" spans="1:8" ht="18" customHeight="1">
+    <row r="77" spans="1:8" ht="20" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>98</v>
       </c>
@@ -2702,34 +2960,34 @@
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="40" customHeight="1">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
+      <c r="A78" s="26"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
+      <c r="A79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
+      <c r="A80" s="26"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
@@ -2744,7 +3002,7 @@
       <c r="H81" s="1"/>
     </row>
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
-    <row r="84" spans="1:8" ht="18" customHeight="1">
+    <row r="84" spans="1:8" ht="20" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>100</v>
       </c>
@@ -2781,11 +3039,11 @@
         <v>106</v>
       </c>
       <c r="C86" s="21"/>
-      <c r="D86" s="24">
+      <c r="D86" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E86" s="25" t="s">
+      <c r="E86" s="28" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2797,11 +3055,11 @@
         <v>106</v>
       </c>
       <c r="C87" s="21"/>
-      <c r="D87" s="24">
+      <c r="D87" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B87)),1,IF(ISNUMBER(SEARCH("surachat",B87)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E87" s="25" t="s">
+      <c r="E87" s="28" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2813,11 +3071,11 @@
         <v>106</v>
       </c>
       <c r="C88" s="21"/>
-      <c r="D88" s="24">
+      <c r="D88" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B88)),1,IF(ISNUMBER(SEARCH("surachat",B88)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="25" t="s">
+      <c r="E88" s="28" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2829,11 +3087,11 @@
         <v>106</v>
       </c>
       <c r="C89" s="21"/>
-      <c r="D89" s="24">
+      <c r="D89" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B89)),1,IF(ISNUMBER(SEARCH("surachat",B89)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="28" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2845,11 +3103,11 @@
         <v>106</v>
       </c>
       <c r="C90" s="21"/>
-      <c r="D90" s="24">
+      <c r="D90" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E90" s="25" t="s">
+      <c r="E90" s="28" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2859,17 +3117,17 @@
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
-      <c r="D91" s="26">
+      <c r="D91" s="29">
         <f>SUM(D86:D90)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="27">
+      <c r="E91" s="30">
         <f>IFERROR(IF(D91&gt;0,"Zone SURVENTE - Achat possible",IF(D91&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
-    <row r="93" spans="1:8" ht="18" customHeight="1">
+    <row r="93" spans="1:8" ht="20" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>117</v>
       </c>
@@ -2929,7 +3187,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
-    <row r="98" spans="1:8" ht="18" customHeight="1">
+    <row r="98" spans="1:8" ht="20" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>125</v>
       </c>
@@ -2959,7 +3217,7 @@
       <c r="A100" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="23">
         <f>B24</f>
         <v>0</v>
       </c>
@@ -2972,7 +3230,7 @@
       <c r="A101" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="22">
         <f>B25</f>
         <v>0</v>
       </c>
@@ -2985,7 +3243,7 @@
       <c r="A102" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B102" s="28"/>
+      <c r="B102" s="31"/>
       <c r="C102" s="20" t="s">
         <v>132</v>
       </c>
@@ -2995,7 +3253,7 @@
       <c r="A103" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="22">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
@@ -3008,7 +3266,7 @@
       <c r="A104" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="24">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
@@ -3021,7 +3279,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
-    <row r="106" spans="1:8" ht="18" customHeight="1">
+    <row r="106" spans="1:8" ht="20" customHeight="1">
       <c r="A106" s="3" t="s">
         <v>137</v>
       </c>
@@ -3034,16 +3292,16 @@
       <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
-      <c r="A107" s="29" t="s">
+      <c r="A107" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="29"/>
-      <c r="F107" s="29"/>
-      <c r="G107" s="29"/>
-      <c r="H107" s="29"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="32"/>
+      <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
@@ -3063,7 +3321,7 @@
       <c r="A109" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B109" s="28"/>
+      <c r="B109" s="31"/>
       <c r="C109" s="20" t="s">
         <v>141</v>
       </c>
@@ -3083,7 +3341,7 @@
       <c r="A111" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="22">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
@@ -3096,7 +3354,7 @@
       <c r="A112" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B112" s="28">
+      <c r="B112" s="31">
         <v>6.5</v>
       </c>
       <c r="C112" s="20" t="s">
@@ -3108,7 +3366,7 @@
       <c r="A113" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="22">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
@@ -3121,7 +3379,7 @@
       <c r="A114" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="22">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
@@ -3134,7 +3392,7 @@
       <c r="A115" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="22">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
@@ -3147,7 +3405,7 @@
       <c r="A116" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B116" s="27">
+      <c r="B116" s="30">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
@@ -3157,7 +3415,7 @@
       <c r="D116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
-    <row r="118" spans="1:8" ht="18" customHeight="1">
+    <row r="118" spans="1:8" ht="20" customHeight="1">
       <c r="A118" s="3" t="s">
         <v>156</v>
       </c>
@@ -3170,16 +3428,16 @@
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="30" t="s">
+      <c r="A119" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="B119" s="30"/>
-      <c r="C119" s="30"/>
-      <c r="D119" s="30"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="30"/>
-      <c r="H119" s="30"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="33"/>
+      <c r="F119" s="33"/>
+      <c r="G119" s="33"/>
+      <c r="H119" s="33"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
@@ -3209,7 +3467,7 @@
       <c r="A122" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="28">
+      <c r="B122" s="31">
         <v>8</v>
       </c>
       <c r="C122" s="20" t="s">
@@ -3221,7 +3479,7 @@
       <c r="A123" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B123" s="28">
+      <c r="B123" s="31">
         <v>2</v>
       </c>
       <c r="C123" s="20" t="s">
@@ -3233,7 +3491,7 @@
       <c r="A124" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B124" s="31">
+      <c r="B124" s="34">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
@@ -3246,7 +3504,7 @@
       <c r="A125" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B125" s="27">
+      <c r="B125" s="30">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
@@ -3256,7 +3514,7 @@
       <c r="D125" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
-    <row r="128" spans="1:8" ht="18" customHeight="1">
+    <row r="128" spans="1:8" ht="20" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>168</v>
       </c>
@@ -3296,7 +3554,7 @@
       <c r="A131" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="22">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
@@ -3319,7 +3577,7 @@
       <c r="A133" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="22">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
@@ -3332,7 +3590,7 @@
       <c r="A134" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="22">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
@@ -3345,7 +3603,7 @@
       <c r="A135" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="24">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
@@ -3358,7 +3616,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
-    <row r="137" spans="1:8" ht="18" customHeight="1">
+    <row r="137" spans="1:8" ht="20" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>182</v>
       </c>
@@ -3371,34 +3629,34 @@
       <c r="H137" s="3"/>
     </row>
     <row r="138" spans="1:8" ht="40" customHeight="1">
-      <c r="A138" s="23"/>
-      <c r="B138" s="23"/>
-      <c r="C138" s="23"/>
-      <c r="D138" s="23"/>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="23"/>
+      <c r="A138" s="26"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
+      <c r="H138" s="26"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="23"/>
-      <c r="B139" s="23"/>
-      <c r="C139" s="23"/>
-      <c r="D139" s="23"/>
-      <c r="E139" s="23"/>
-      <c r="F139" s="23"/>
-      <c r="G139" s="23"/>
-      <c r="H139" s="23"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
+      <c r="H139" s="26"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="23"/>
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
-      <c r="D140" s="23"/>
-      <c r="E140" s="23"/>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="26"/>
+      <c r="F140" s="26"/>
+      <c r="G140" s="26"/>
+      <c r="H140" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3432,12 +3690,56 @@
     <mergeCell ref="A137:H137"/>
     <mergeCell ref="A138:H140"/>
   </mergeCells>
+  <conditionalFormatting sqref="D30:D34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="sous-evaluee">
+      <formula>NOT(ISERROR(SEARCH("sous-evaluee",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Excellent">
+      <formula>NOT(ISERROR(SEARCH("Excellent",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="surevaluee">
+      <formula>NOT(ISERROR(SEARCH("surevaluee",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="11" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="13" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF1E3A5F"/>
+  </sheetPr>
   <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3458,23 +3760,23 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
@@ -3497,159 +3799,159 @@
       <c r="A6" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="37">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="39">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="37">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="39">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="37">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="39">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="40"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="37">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="39">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="40"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="37">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="34">
+      <c r="D10" s="39">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35"/>
+      <c r="E10" s="40"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="37">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="34">
+      <c r="D11" s="39">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="40"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="37">
         <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="39">
         <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="37">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="34">
+      <c r="D13" s="39">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="40"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="36">
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -3672,98 +3974,108 @@
       <c r="A18" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="43">
+        <f>IFERROR(ETUDE!D91,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="38"/>
+      <c r="D18" s="39">
+        <f>IFERROR(ETUDE!E91,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="44"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="43">
+        <f>IFERROR(ETUDE!E95,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="B19" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="38"/>
+      <c r="D19" s="39">
+        <f>IFERROR(ETUDE!E96,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="44"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B20" s="43">
+        <f>IFERROR(ETUDE!B104,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="B20" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="38"/>
+      <c r="D20" s="39">
+        <f>IFERROR(ETUDE!D104,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="44"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="43">
+        <f>IFERROR(ETUDE!B116,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="B21" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="38"/>
+      <c r="D21" s="39">
+        <f>IFERROR(ETUDE!B125,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="44"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="43">
+        <f>IFERROR(ETUDE!B135,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="38"/>
+      <c r="D22" s="39">
+        <f>IFERROR(ETUDE!D135,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="44"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="36">
+        <v>219</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="42">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+      <c r="A25" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -3773,112 +4085,112 @@
         <v>208</v>
       </c>
       <c r="C26" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B27" s="40">
+        <v>224</v>
+      </c>
+      <c r="B27" s="46">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="47">
         <v>24</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="48">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="49">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B28" s="40">
+        <v>225</v>
+      </c>
+      <c r="B28" s="46">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="47">
         <v>15</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="48">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="49">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B29" s="43">
+        <v>226</v>
+      </c>
+      <c r="B29" s="50">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="51">
         <v>39</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="48">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29" s="52">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="A31" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
     </row>
     <row r="32" spans="1:5" ht="50" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3890,12 +4202,109 @@
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A32:E35"/>
   </mergeCells>
+  <conditionalFormatting sqref="D18:D22">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="rentable">
+      <formula>NOT(ISERROR(SEARCH("rentable",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="Opportunite">
+      <formula>NOT(ISERROR(SEARCH("Opportunite",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="12" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="14" operator="containsText" text="ACHETER">
+      <formula>NOT(ISERROR(SEARCH("ACHETER",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="20" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="22" operator="containsText" text="Negatif">
+      <formula>NOT(ISERROR(SEARCH("Negatif",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="24" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="26" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="28" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="NEUTRE">
+      <formula>NOT(ISERROR(SEARCH("NEUTRE",D18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D13">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="rentable">
+      <formula>NOT(ISERROR(SEARCH("rentable",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Opportunite">
+      <formula>NOT(ISERROR(SEARCH("Opportunite",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="ACHETER">
+      <formula>NOT(ISERROR(SEARCH("ACHETER",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="15" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="17" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="19" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="21" operator="containsText" text="Negatif">
+      <formula>NOT(ISERROR(SEARCH("Negatif",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="23" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="25" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="27" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="29" operator="containsText" text="NEUTRE">
+      <formula>NOT(ISERROR(SEARCH("NEUTRE",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF6B7280"/>
+  </sheetPr>
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3907,23 +4316,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -3931,7 +4340,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -3939,7 +4348,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -3947,7 +4356,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -3955,7 +4364,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -3963,16 +4372,16 @@
     </row>
     <row r="8" spans="1:4" ht="5" customHeight="1"/>
     <row r="9" spans="1:4" ht="18" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -3980,7 +4389,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -3988,7 +4397,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -3996,7 +4405,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -4004,26 +4413,26 @@
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="18" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="A15" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="14" t="s">
         <v>242</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -4031,32 +4440,32 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>245</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>246</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>247</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>248</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="A21" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
@@ -4068,7 +4477,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -4076,7 +4485,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -4084,36 +4493,36 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B25" s="14" t="s">
         <v>252</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>253</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="18" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="A27" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>256</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4121,20 +4530,20 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B30" s="14" t="s">
         <v>258</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>259</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>260</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>261</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -4155,6 +4564,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF374151"/>
+  </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4166,322 +4578,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="D2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="C4" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="D4" s="55" t="s">
         <v>269</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="C5" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="55" t="s">
         <v>272</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="C6" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" s="55" t="s">
         <v>275</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="47" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="D7" s="55" t="s">
         <v>278</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="54" t="s">
         <v>280</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="C8" s="47" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="D8" s="55" t="s">
         <v>282</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="54" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" s="55" t="s">
         <v>284</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="54" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="C10" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="55" t="s">
         <v>287</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="C11" s="47"/>
+      <c r="D11" s="55" t="s">
         <v>290</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="47" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="C12" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="55" t="s">
         <v>293</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B13" s="54" t="s">
         <v>295</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="C13" s="47" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="55" t="s">
         <v>296</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="47" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="18" customHeight="1">
+      <c r="A14" s="36" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="C15" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" s="55" t="s">
         <v>300</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="54" t="s">
         <v>302</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="55" t="s">
         <v>303</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="47" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="47" t="s">
-        <v>305</v>
+      <c r="B17" s="54" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="47"/>
+      <c r="D17" s="55" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="54" t="s">
+        <v>305</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" s="55" t="s">
         <v>306</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B19" s="54" t="s">
         <v>308</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="C19" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="55" t="s">
         <v>309</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="C20" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="55" t="s">
         <v>312</v>
       </c>
-      <c r="C20" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D20" s="47" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="18" customHeight="1">
+      <c r="A21" s="36" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" s="54" t="s">
         <v>315</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="C22" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="55" t="s">
         <v>316</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="B23" s="54" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="C23" s="47" t="s">
         <v>319</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="D23" s="55" t="s">
         <v>320</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="B24" s="54" t="s">
         <v>322</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="C24" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" s="55" t="s">
         <v>323</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="54" t="s">
         <v>325</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="C25" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="D25" s="55" t="s">
         <v>326</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1059,16 +1059,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF404040"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF6600"/>
+      <color rgb="FFD97706"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1085,6 +1078,13 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1200,7 +1200,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1239,19 +1239,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFFFFBEB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECFDF5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1332,7 +1326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1349,8 +1343,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1364,32 +1359,37 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1397,106 +1397,103 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="21" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3659,6 +3656,7 @@
       <c r="H140" s="26"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="29">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -3803,14 +3801,14 @@
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="40"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
@@ -3820,14 +3818,14 @@
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="40"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
@@ -3837,14 +3835,14 @@
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="40"/>
+      <c r="E8" s="39"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
@@ -3854,14 +3852,14 @@
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="40"/>
+      <c r="E9" s="39"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
@@ -3871,14 +3869,14 @@
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="40"/>
+      <c r="E10" s="39"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
@@ -3888,14 +3886,14 @@
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="40"/>
+      <c r="E11" s="39"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
@@ -3905,14 +3903,14 @@
         <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
         <v>0</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="38">
         <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="40"/>
+      <c r="E12" s="39"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
@@ -3922,23 +3920,23 @@
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="38">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="40"/>
+      <c r="E13" s="39"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
@@ -3974,108 +3972,108 @@
       <c r="A18" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="42">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="38">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="44"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="42">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="38">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="44"/>
+      <c r="E19" s="39"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="42">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="38">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="44"/>
+      <c r="E20" s="39"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="42">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="38">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="44"/>
+      <c r="E21" s="39"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B22" s="43">
+      <c r="B22" s="42">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="38">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="44"/>
+      <c r="E22" s="39"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="42">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="41">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="43" t="s">
         <v>220</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -4098,18 +4096,18 @@
       <c r="A27" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B27" s="46">
+      <c r="B27" s="44">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="47">
+      <c r="C27" s="45">
         <v>24</v>
       </c>
-      <c r="D27" s="48">
+      <c r="D27" s="46">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="49">
+      <c r="E27" s="47">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
@@ -4118,18 +4116,18 @@
       <c r="A28" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B28" s="46">
+      <c r="B28" s="44">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="45">
         <v>15</v>
       </c>
-      <c r="D28" s="48">
+      <c r="D28" s="46">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="49">
+      <c r="E28" s="47">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
@@ -4138,18 +4136,18 @@
       <c r="A29" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="B29" s="50">
+      <c r="B29" s="48">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="49">
         <v>39</v>
       </c>
-      <c r="D29" s="48">
+      <c r="D29" s="46">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="52">
+      <c r="E29" s="50">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
@@ -4193,6 +4191,7 @@
       <c r="E35" s="26"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="7">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -4550,6 +4549,7 @@
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -4585,16 +4585,16 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="51" t="s">
         <v>264</v>
       </c>
     </row>
@@ -4610,13 +4610,13 @@
       <c r="A4" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="52" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="53" t="s">
         <v>269</v>
       </c>
     </row>
@@ -4624,13 +4624,13 @@
       <c r="A5" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="52" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="53" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4638,13 +4638,13 @@
       <c r="A6" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="53" t="s">
         <v>275</v>
       </c>
     </row>
@@ -4652,13 +4652,13 @@
       <c r="A7" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="53" t="s">
         <v>278</v>
       </c>
     </row>
@@ -4666,13 +4666,13 @@
       <c r="A8" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="52" t="s">
         <v>280</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="53" t="s">
         <v>282</v>
       </c>
     </row>
@@ -4680,13 +4680,13 @@
       <c r="A9" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="53" t="s">
         <v>284</v>
       </c>
     </row>
@@ -4694,13 +4694,13 @@
       <c r="A10" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="52" t="s">
         <v>286</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="53" t="s">
         <v>287</v>
       </c>
     </row>
@@ -4708,11 +4708,11 @@
       <c r="A11" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="52" t="s">
         <v>289</v>
       </c>
-      <c r="C11" s="47"/>
-      <c r="D11" s="55" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="53" t="s">
         <v>290</v>
       </c>
     </row>
@@ -4720,13 +4720,13 @@
       <c r="A12" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="52" t="s">
         <v>292</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="53" t="s">
         <v>293</v>
       </c>
     </row>
@@ -4734,13 +4734,13 @@
       <c r="A13" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="B13" s="54" t="s">
+      <c r="B13" s="52" t="s">
         <v>295</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="45" t="s">
         <v>268</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="53" t="s">
         <v>296</v>
       </c>
     </row>
@@ -4756,13 +4756,13 @@
       <c r="A15" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="53" t="s">
         <v>300</v>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       <c r="A16" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="55" t="s">
+      <c r="C16" s="45"/>
+      <c r="D16" s="53" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4782,11 +4782,11 @@
       <c r="A17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="52" t="s">
         <v>302</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="55" t="s">
+      <c r="C17" s="45"/>
+      <c r="D17" s="53" t="s">
         <v>304</v>
       </c>
     </row>
@@ -4794,13 +4794,13 @@
       <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="52" t="s">
         <v>305</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="45" t="s">
         <v>277</v>
       </c>
-      <c r="D18" s="55" t="s">
+      <c r="D18" s="53" t="s">
         <v>306</v>
       </c>
     </row>
@@ -4808,13 +4808,13 @@
       <c r="A19" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="52" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="53" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4822,13 +4822,13 @@
       <c r="A20" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="52" t="s">
         <v>311</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="53" t="s">
         <v>312</v>
       </c>
     </row>
@@ -4844,13 +4844,13 @@
       <c r="A22" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="52" t="s">
         <v>315</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D22" s="53" t="s">
         <v>316</v>
       </c>
     </row>
@@ -4858,13 +4858,13 @@
       <c r="A23" s="18" t="s">
         <v>317</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="52" t="s">
         <v>318</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="45" t="s">
         <v>319</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D23" s="53" t="s">
         <v>320</v>
       </c>
     </row>
@@ -4872,13 +4872,13 @@
       <c r="A24" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="53" t="s">
         <v>323</v>
       </c>
     </row>
@@ -4886,17 +4886,18 @@
       <c r="A25" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="52" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="45" t="s">
         <v>281</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D25" s="53" t="s">
         <v>326</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="368">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -568,6 +568,120 @@
     <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
   </si>
   <si>
+    <t>C — ANALYSE CONTRARIAN &amp; OPPORTUNITES DE MARCHE</t>
+  </si>
+  <si>
+    <t>C1 — NORMALISATION DU RESULTAT NET  (recurrent vs exceptionnel)</t>
+  </si>
+  <si>
+    <t>Saisir les elements exceptionnels (positifs = booste le RN, negatifs = penalise le RN). Un mauvais RN publie mais un RN recurrent positif = opportunite contrarian.</t>
+  </si>
+  <si>
+    <t>RN Publie (M FCFA)</t>
+  </si>
+  <si>
+    <t>Dont Exceptionnel (M FCFA)</t>
+  </si>
+  <si>
+    <t>RN Recurrent (M FCFA)</t>
+  </si>
+  <si>
+    <t>Marge Recurrente %</t>
+  </si>
+  <si>
+    <t>BNPA Recurrent N (FCFA)</t>
+  </si>
+  <si>
+    <t>PER Normalise</t>
+  </si>
+  <si>
+    <t>Signal Normalisation RN</t>
+  </si>
+  <si>
+    <t>C2 — COMPARAISON SECTORIELLE BRVM</t>
+  </si>
+  <si>
+    <t>Reference marche</t>
+  </si>
+  <si>
+    <t>Ecart %</t>
+  </si>
+  <si>
+    <t>PER sectoriel moyen BRVM (reference)</t>
+  </si>
+  <si>
+    <t>&lt;-- Banques ~10 | Industrie ~12-14 | Distribution ~15 | Telecom ~8</t>
+  </si>
+  <si>
+    <t>Rendement dividende sectoriel BRVM (%)</t>
+  </si>
+  <si>
+    <t>&lt;-- Marche BRVM: 4 - 6% en moyenne</t>
+  </si>
+  <si>
+    <t>PER action vs sectoriel</t>
+  </si>
+  <si>
+    <t>Rendement div. action vs sectoriel</t>
+  </si>
+  <si>
+    <t>C3 — FIABILITE DU DIVIDENDE (5 ANS)</t>
+  </si>
+  <si>
+    <t>Score /3</t>
+  </si>
+  <si>
+    <t>Nb annees avec dividende verse (sur 5)</t>
+  </si>
+  <si>
+    <t>CAGR dividende 5 ans (croissance annuelle)</t>
+  </si>
+  <si>
+    <t>SCORE FIABILITE DIVIDENDE</t>
+  </si>
+  <si>
+    <t>/3</t>
+  </si>
+  <si>
+    <t>C4 — SCORE CONTRARIAN BRVM  (detecteur : fondamentaux OK + titre boude par le marche)</t>
+  </si>
+  <si>
+    <t>Critere</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>PER action &lt; PER sectoriel (action moins chere que le marche)</t>
+  </si>
+  <si>
+    <t>Prix actuel &lt; VMC (decote sur valeur comptable)</t>
+  </si>
+  <si>
+    <t>ROE &gt;= 10% (rentabilite correcte malgre sentiment negatif)</t>
+  </si>
+  <si>
+    <t>Dividende fiable &gt;= 4 ans sur 5</t>
+  </si>
+  <si>
+    <t>Cours &lt; Prix Median 1 an (survente technique)</t>
+  </si>
+  <si>
+    <t>Marge nette moyenne &gt; 5% (profitabilite structurelle)</t>
+  </si>
+  <si>
+    <t>SCORE CONTRARIAN TOTAL (/10)</t>
+  </si>
+  <si>
+    <t>/10</t>
+  </si>
+  <si>
+    <t>VERDICT CONTRARIAN</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -577,9 +691,6 @@
     <t>SCORECARD FONDAMENTALE</t>
   </si>
   <si>
-    <t>Critere</t>
-  </si>
-  <si>
     <t>Valeur (auto depuis ETUDE)</t>
   </si>
   <si>
@@ -643,9 +754,6 @@
     <t>Zone</t>
   </si>
   <si>
-    <t>Score</t>
-  </si>
-  <si>
     <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
   </si>
   <si>
@@ -698,6 +806,21 @@
   </si>
   <si>
     <t>SCORE TOTAL</t>
+  </si>
+  <si>
+    <t>C — SIGNAL CONTRARIAN BRVM  (depuis ETUDE C4)</t>
+  </si>
+  <si>
+    <t>Score /10</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>PER vs Sectoriel</t>
+  </si>
+  <si>
+    <t>Decote VMC</t>
   </si>
   <si>
     <t>RECOMMANDATION FINALE (texte libre)</t>
@@ -1011,7 +1134,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1130,9 +1253,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFECFDF5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1199,8 +1354,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1263,6 +1441,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF064E3B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF2F5496"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1292,7 +1476,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1322,11 +1506,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1438,38 +1637,60 @@
     <xf numFmtId="167" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="9" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,19 +1699,32 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="25" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1950,7 +2184,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -3655,9 +3889,518 @@
       <c r="G140" s="26"/>
       <c r="H140" s="26"/>
     </row>
+    <row r="141" spans="1:8" ht="26" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+    </row>
+    <row r="143" spans="1:8" ht="5" customHeight="1"/>
+    <row r="144" spans="1:8" ht="20" customHeight="1">
+      <c r="A144" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8" ht="30" customHeight="1">
+      <c r="A145" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B145" s="35"/>
+      <c r="C145" s="35"/>
+      <c r="D145" s="35"/>
+      <c r="E145" s="35"/>
+      <c r="F145" s="35"/>
+      <c r="G145" s="35"/>
+      <c r="H145" s="35"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="9">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+      <c r="C147" s="6"/>
+      <c r="D147" s="9">
+        <f>IFERROR(B147-C147,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E147" s="7">
+        <f>IFERROR(D147/B8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C148" s="6"/>
+      <c r="D148" s="9">
+        <f>IFERROR(B148-C148,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E148" s="7">
+        <f>IFERROR(D148/C8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="9">
+        <f>D12</f>
+        <v>0</v>
+      </c>
+      <c r="C149" s="6"/>
+      <c r="D149" s="9">
+        <f>IFERROR(B149-C149,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E149" s="7">
+        <f>IFERROR(D149/D8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="9">
+        <f>E12</f>
+        <v>0</v>
+      </c>
+      <c r="C150" s="6"/>
+      <c r="D150" s="9">
+        <f>IFERROR(B150-C150,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E150" s="7">
+        <f>IFERROR(D150/E8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B151" s="9">
+        <f>F12</f>
+        <v>0</v>
+      </c>
+      <c r="C151" s="6"/>
+      <c r="D151" s="9">
+        <f>IFERROR(B151-C151,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E151" s="7">
+        <f>IFERROR(D151/F8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="5" customHeight="1"/>
+    <row r="153" spans="1:8">
+      <c r="A153" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B153" s="16">
+        <f>IFERROR(D151*1000000/B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D153" s="7">
+        <f>IFERROR(B24/B153,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E153" s="10">
+        <f>IFERROR(IF(D153&gt;15,"PER normalise eleve",IF(D153&lt;9,"Sous-evalue normalise","Normal (9-15)")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B154" s="10">
+        <f>IFERROR(IF(C151&lt;0,"Mauvais resultat PONCTUEL — RN recurrent &gt; RN publie — opportunite contrarian potentielle",IF(C151&gt;0,"Resultat FLATTE par elements exceptionnels — prudence sur la valorisation","Pas d'element exceptionnel detecte — RN publie = RN recurrent")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="5" customHeight="1"/>
+    <row r="156" spans="1:8" ht="20" customHeight="1">
+      <c r="A156" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B158" s="36">
+        <v>12</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D158" s="14"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="14"/>
+      <c r="G158" s="14"/>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B159" s="36">
+        <v>5</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D159" s="14"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="14"/>
+    </row>
+    <row r="160" spans="1:8" ht="5" customHeight="1"/>
+    <row r="161" spans="1:8">
+      <c r="A161" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B161" s="7">
+        <f>IFERROR(B30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C161" s="21">
+        <f>B158</f>
+        <v>0</v>
+      </c>
+      <c r="D161" s="7">
+        <f>IFERROR((B30/B158-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E161" s="10">
+        <f>IFERROR(IF((B30/B158-1)*100&lt;=-20,"Forte decote sectorielle — opportunite",IF((B30/B158-1)*100&lt;=-5,"Legere decote sectorielle",IF((B30/B158-1)*100&lt;=15,"Dans la norme sectorielle","Prime elevee vs secteur — prudence"))),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" s="7">
+        <f>IFERROR(AVERAGE(F38:F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C162" s="21">
+        <f>B159</f>
+        <v>0</v>
+      </c>
+      <c r="D162" s="7">
+        <f>IFERROR((AVERAGE(F38:F42)/B159-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E162" s="10">
+        <f>IFERROR(IF(AVERAGE(F38:F42)&gt;=B159*1.2,"Rendement superieur au marche — attractif",IF(AVERAGE(F38:F42)&gt;=B159,"Dans la moyenne du marche","Rendement inferieur au marche")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="5" customHeight="1"/>
+    <row r="164" spans="1:8" ht="20" customHeight="1">
+      <c r="A164" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B166" s="37">
+        <f>COUNTIF(B38:B42,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="C166" s="10">
+        <f>IFERROR(IF(B166=5,"Regulier 5/5 — fiable",IF(B166&gt;=4,"Quasi-regulier 4/5",IF(B166&gt;=3,"Irregulier 3/5","Tres irregulier — risque dividende"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D166" s="37">
+        <f>IF(B166=5,2,IF(B166&gt;=4,1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B167" s="8">
+        <f>IFERROR(IF(OR(B38&lt;=0,B42&lt;=0),"N/A",(B42/B38)^(1/4)-1),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="C167" s="10">
+        <f>IFERROR(IF(NOT(ISNUMBER(B167)),"Dividende absent",IF(B167&gt;0.05,"Forte croissance dividende",IF(B167&gt;0,"Croissance modeste","Dividende en baisse"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D167" s="37">
+        <f>IFERROR(IF(ISNUMBER(B167),IF(B167&gt;0,1,0),0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B168" s="38">
+        <f>IFERROR(D166+D167,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C168" s="10">
+        <f>IFERROR(IF(D166+D167&gt;=3,"Dividende tres fiable",IF(D166+D167&gt;=2,"Dividende assez fiable","Dividende peu fiable — risque")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D168" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="5" customHeight="1"/>
+    <row r="170" spans="1:8" ht="20" customHeight="1">
+      <c r="A170" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B172" s="10">
+        <f>IFERROR(IF(B30&lt;B158,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C172" s="10">
+        <f>IFERROR("PER="&amp;ROUND(B30,1)&amp;" vs sectoriel="&amp;B158,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D172" s="37">
+        <f>IFERROR(IF(B30&lt;B158*0.85,2,IF(B30&lt;B158,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B173" s="10">
+        <f>IFERROR(IF(B24&lt;B31,"OUI — decote comptable","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C173" s="10">
+        <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs VMC="&amp;ROUND(B31,0)&amp;" FCFA","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D173" s="37">
+        <f>IFERROR(IF(B24&lt;B31*0.85,2,IF(B24&lt;B31,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B174" s="10">
+        <f>IFERROR(IF(B33&gt;=10,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C174" s="10">
+        <f>IFERROR("ROE="&amp;ROUND(B33,1)&amp;"%","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D174" s="37">
+        <f>IFERROR(IF(B33&gt;=15,2,IF(B33&gt;=10,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B175" s="10">
+        <f>IFERROR(IF(B168&gt;=2,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C175" s="10">
+        <f>IFERROR(C168,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D175" s="37">
+        <f>IFERROR(MIN(B168,2),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B176" s="10">
+        <f>IFERROR(IF(B24&lt;D95,"OUI — survente","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C176" s="10">
+        <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs PM1an="&amp;ROUND(D95,0)&amp;" FCFA","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D176" s="37">
+        <f>IFERROR(IF(B24&lt;D95,1,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B177" s="10">
+        <f>IFERROR(IF(G16&gt;=5,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C177" s="10">
+        <f>IFERROR("Marge moy="&amp;ROUND(G16,1)&amp;"%","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D177" s="37">
+        <f>IFERROR(IF(G16&gt;=10,2,IF(G16&gt;=5,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B178" s="12"/>
+      <c r="C178" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D178" s="39">
+        <f>IFERROR(SUM(D172:D177),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="30" customHeight="1">
+      <c r="A179" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B179" s="40"/>
+      <c r="C179" s="40"/>
+      <c r="D179" s="40"/>
+      <c r="E179" s="41"/>
+      <c r="F179" s="41"/>
+      <c r="G179" s="41"/>
+      <c r="H179" s="41"/>
+    </row>
+    <row r="180" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="29">
+  <mergeCells count="39">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -3687,7 +4430,25 @@
     <mergeCell ref="A128:H128"/>
     <mergeCell ref="A137:H137"/>
     <mergeCell ref="A138:H140"/>
+    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="C158:G158"/>
+    <mergeCell ref="C159:G159"/>
+    <mergeCell ref="A164:H164"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="E179:H179"/>
   </mergeCells>
+  <conditionalFormatting sqref="B172:B177">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
+      <formula>NOT(ISERROR(SEARCH("OUI",B172)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="NON">
+      <formula>NOT(ISERROR(SEARCH("NON",B172)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D30:D34">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sous-evalue">
       <formula>NOT(ISERROR(SEARCH("Sous-evalue",D30)))</formula>
@@ -3738,7 +4499,7 @@
   <sheetPr>
     <tabColor rgb="FF1E3A5F"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3750,7 +4511,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3758,448 +4519,505 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
+      <c r="A2" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
+      <c r="A4" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="37">
+        <v>228</v>
+      </c>
+      <c r="B6" s="44">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="38">
+        <v>229</v>
+      </c>
+      <c r="D6" s="45">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="39"/>
+      <c r="E6" s="46"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="37">
+        <v>230</v>
+      </c>
+      <c r="B7" s="44">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="38">
+        <v>229</v>
+      </c>
+      <c r="D7" s="45">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="39"/>
+      <c r="E7" s="46"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="37">
+        <v>231</v>
+      </c>
+      <c r="B8" s="44">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="38">
+        <v>232</v>
+      </c>
+      <c r="D8" s="45">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="39"/>
+      <c r="E8" s="46"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="37">
+        <v>233</v>
+      </c>
+      <c r="B9" s="44">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="38">
+        <v>234</v>
+      </c>
+      <c r="D9" s="45">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="39"/>
+      <c r="E9" s="46"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="37">
+        <v>235</v>
+      </c>
+      <c r="B10" s="44">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="38">
+        <v>236</v>
+      </c>
+      <c r="D10" s="45">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="39"/>
+      <c r="E10" s="46"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B11" s="37">
+        <v>237</v>
+      </c>
+      <c r="B11" s="44">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="38">
+        <v>229</v>
+      </c>
+      <c r="D11" s="45">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="39"/>
+      <c r="E11" s="46"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" s="37">
+        <v>238</v>
+      </c>
+      <c r="B12" s="44">
         <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D12" s="38">
+        <v>239</v>
+      </c>
+      <c r="D12" s="45">
         <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="39"/>
+      <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="37">
+        <v>240</v>
+      </c>
+      <c r="B13" s="44">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" s="38">
+        <v>241</v>
+      </c>
+      <c r="D13" s="45">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="39"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="41">
+        <v>242</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="A16" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="42">
+        <v>245</v>
+      </c>
+      <c r="B18" s="49">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="38">
+        <v>246</v>
+      </c>
+      <c r="D18" s="45">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="39"/>
+      <c r="E18" s="46"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B19" s="42">
+        <v>247</v>
+      </c>
+      <c r="B19" s="49">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="38">
+        <v>248</v>
+      </c>
+      <c r="D19" s="45">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="39"/>
+      <c r="E19" s="46"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="42">
+        <v>249</v>
+      </c>
+      <c r="B20" s="49">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="38">
+        <v>250</v>
+      </c>
+      <c r="D20" s="45">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="39"/>
+      <c r="E20" s="46"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B21" s="42">
+        <v>251</v>
+      </c>
+      <c r="B21" s="49">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D21" s="38">
+        <v>252</v>
+      </c>
+      <c r="D21" s="45">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="39"/>
+      <c r="E21" s="46"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="42">
+        <v>253</v>
+      </c>
+      <c r="B22" s="49">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="D22" s="38">
+        <v>254</v>
+      </c>
+      <c r="D22" s="45">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="39"/>
+      <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="41">
+        <v>255</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
+      <c r="A25" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B27" s="44">
+        <v>260</v>
+      </c>
+      <c r="B27" s="51">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="45">
+      <c r="C27" s="52">
         <v>24</v>
       </c>
-      <c r="D27" s="46">
+      <c r="D27" s="53">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="54">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B28" s="44">
+        <v>261</v>
+      </c>
+      <c r="B28" s="51">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="45">
+      <c r="C28" s="52">
         <v>15</v>
       </c>
-      <c r="D28" s="46">
+      <c r="D28" s="53">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="47">
+      <c r="E28" s="54">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B29" s="48">
+        <v>262</v>
+      </c>
+      <c r="B29" s="55">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="49">
+      <c r="C29" s="56">
         <v>39</v>
       </c>
-      <c r="D29" s="46">
+      <c r="D29" s="53">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="50">
+      <c r="E29" s="57">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-    </row>
-    <row r="32" spans="1:5" ht="50" customHeight="1">
-      <c r="A32" s="26"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="26"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
+      <c r="A31" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" customHeight="1">
+      <c r="A33" s="58">
+        <f>IFERROR(ETUDE!D178,"")</f>
+        <v>0</v>
+      </c>
+      <c r="B33" s="59">
+        <f>IFERROR(ETUDE!E179,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="60">
+        <f>IFERROR(ETUDE!D153,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="60">
+        <f>IFERROR(ETUDE!D161,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="61">
+        <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="5" customHeight="1"/>
+    <row r="35" spans="1:5" ht="18" customHeight="1">
+      <c r="A35" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+    </row>
+    <row r="36" spans="1:5" ht="50" customHeight="1">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E35"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E40"/>
   </mergeCells>
   <conditionalFormatting sqref="D18:D22">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
@@ -4315,23 +5133,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
-      <c r="A2" s="36" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
+      <c r="A2" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -4339,7 +5157,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -4347,7 +5165,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -4355,7 +5173,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -4363,7 +5181,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -4371,16 +5189,16 @@
     </row>
     <row r="8" spans="1:4" ht="5" customHeight="1"/>
     <row r="9" spans="1:4" ht="18" customHeight="1">
-      <c r="A9" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="A9" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -4388,7 +5206,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -4396,7 +5214,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -4404,7 +5222,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -4412,26 +5230,26 @@
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="18" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
+      <c r="A15" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -4439,32 +5257,32 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="36" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="A21" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
@@ -4476,7 +5294,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -4484,7 +5302,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -4492,36 +5310,36 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="18" customHeight="1">
-      <c r="A27" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
+      <c r="A27" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4529,20 +5347,20 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -4578,322 +5396,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>264</v>
+      <c r="B2" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="A3" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>267</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D4" s="53" t="s">
-        <v>269</v>
+        <v>307</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>271</v>
-      </c>
-      <c r="C5" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D5" s="53" t="s">
-        <v>272</v>
+        <v>311</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="B6" s="52" t="s">
-        <v>274</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D6" s="53" t="s">
-        <v>275</v>
+        <v>314</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>278</v>
+        <v>233</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="52" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="53" t="s">
-        <v>282</v>
+        <v>320</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="52" t="s">
-        <v>283</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>284</v>
+        <v>235</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>286</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D10" s="53" t="s">
-        <v>287</v>
+        <v>326</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="45"/>
-      <c r="D11" s="53" t="s">
-        <v>290</v>
+        <v>329</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="64" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="52" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>293</v>
+        <v>332</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>295</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="53" t="s">
-        <v>296</v>
+        <v>335</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
+      <c r="A14" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" s="53" t="s">
-        <v>300</v>
+        <v>339</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>302</v>
-      </c>
-      <c r="C16" s="45"/>
-      <c r="D16" s="53" t="s">
-        <v>303</v>
+        <v>342</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="64" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="52" t="s">
-        <v>302</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="53" t="s">
-        <v>304</v>
+      <c r="B17" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="64" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="52" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" s="53" t="s">
-        <v>306</v>
+      <c r="B18" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>308</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" s="53" t="s">
-        <v>309</v>
+        <v>348</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>310</v>
-      </c>
-      <c r="B20" s="52" t="s">
-        <v>311</v>
-      </c>
-      <c r="C20" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D20" s="53" t="s">
-        <v>312</v>
+        <v>351</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
+      <c r="A21" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B22" s="52" t="s">
-        <v>315</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D22" s="53" t="s">
-        <v>316</v>
+        <v>355</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>318</v>
-      </c>
-      <c r="C23" s="45" t="s">
-        <v>319</v>
-      </c>
-      <c r="D23" s="53" t="s">
-        <v>320</v>
+        <v>358</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="B24" s="52" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="C24" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D24" s="53" t="s">
-        <v>323</v>
+      <c r="D24" s="64" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="52" t="s">
-        <v>325</v>
-      </c>
-      <c r="C25" s="45" t="s">
-        <v>281</v>
-      </c>
-      <c r="D25" s="53" t="s">
-        <v>326</v>
+        <v>365</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -4392,7 +4392,10 @@
       <c r="B179" s="40"/>
       <c r="C179" s="40"/>
       <c r="D179" s="40"/>
-      <c r="E179" s="41"/>
+      <c r="E179" s="41">
+        <f>IFERROR(IF(D178&gt;=7,"FORTE OPPORTUNITE CONTRARIAN — fondamentaux sains, titre boude",IF(D178&gt;=5,"A SURVEILLER — signaux contrarians partiels","PAS DE SIGNAL CONTRARIAN — attendre")),"-")</f>
+        <v>0</v>
+      </c>
       <c r="F179" s="41"/>
       <c r="G179" s="41"/>
       <c r="H179" s="41"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="368">
   <si>
     <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
   </si>
@@ -568,6 +568,120 @@
     <t>B7 — CONCLUSION ANALYSE TECHNIQUE (texte libre)</t>
   </si>
   <si>
+    <t>C — ANALYSE CONTRARIAN &amp; OPPORTUNITES DE MARCHE</t>
+  </si>
+  <si>
+    <t>C1 — NORMALISATION DU RESULTAT NET  (recurrent vs exceptionnel)</t>
+  </si>
+  <si>
+    <t>Saisir les elements exceptionnels (positifs = booste le RN, negatifs = penalise le RN). Un mauvais RN publie mais un RN recurrent positif = opportunite contrarian.</t>
+  </si>
+  <si>
+    <t>RN Publie (M FCFA)</t>
+  </si>
+  <si>
+    <t>Dont Exceptionnel (M FCFA)</t>
+  </si>
+  <si>
+    <t>RN Recurrent (M FCFA)</t>
+  </si>
+  <si>
+    <t>Marge Recurrente %</t>
+  </si>
+  <si>
+    <t>BNPA Recurrent N (FCFA)</t>
+  </si>
+  <si>
+    <t>PER Normalise</t>
+  </si>
+  <si>
+    <t>Signal Normalisation RN</t>
+  </si>
+  <si>
+    <t>C2 — COMPARAISON SECTORIELLE BRVM</t>
+  </si>
+  <si>
+    <t>Reference marche</t>
+  </si>
+  <si>
+    <t>Ecart %</t>
+  </si>
+  <si>
+    <t>PER sectoriel moyen BRVM (reference)</t>
+  </si>
+  <si>
+    <t>&lt;-- Banques ~10 | Industrie ~12-14 | Distribution ~15 | Telecom ~8</t>
+  </si>
+  <si>
+    <t>Rendement dividende sectoriel BRVM (%)</t>
+  </si>
+  <si>
+    <t>&lt;-- Marche BRVM: 4 - 6% en moyenne</t>
+  </si>
+  <si>
+    <t>PER action vs sectoriel</t>
+  </si>
+  <si>
+    <t>Rendement div. action vs sectoriel</t>
+  </si>
+  <si>
+    <t>C3 — FIABILITE DU DIVIDENDE (5 ANS)</t>
+  </si>
+  <si>
+    <t>Score /3</t>
+  </si>
+  <si>
+    <t>Nb annees avec dividende verse (sur 5)</t>
+  </si>
+  <si>
+    <t>CAGR dividende 5 ans (croissance annuelle)</t>
+  </si>
+  <si>
+    <t>SCORE FIABILITE DIVIDENDE</t>
+  </si>
+  <si>
+    <t>/3</t>
+  </si>
+  <si>
+    <t>C4 — SCORE CONTRARIAN BRVM  (detecteur : fondamentaux OK + titre boude par le marche)</t>
+  </si>
+  <si>
+    <t>Critere</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>PER action &lt; PER sectoriel (action moins chere que le marche)</t>
+  </si>
+  <si>
+    <t>Prix actuel &lt; VMC (decote sur valeur comptable)</t>
+  </si>
+  <si>
+    <t>ROE &gt;= 10% (rentabilite correcte malgre sentiment negatif)</t>
+  </si>
+  <si>
+    <t>Dividende fiable &gt;= 4 ans sur 5</t>
+  </si>
+  <si>
+    <t>Cours &lt; Prix Median 1 an (survente technique)</t>
+  </si>
+  <si>
+    <t>Marge nette moyenne &gt; 5% (profitabilite structurelle)</t>
+  </si>
+  <si>
+    <t>SCORE CONTRARIAN TOTAL (/10)</t>
+  </si>
+  <si>
+    <t>/10</t>
+  </si>
+  <si>
+    <t>VERDICT CONTRARIAN</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -577,9 +691,6 @@
     <t>SCORECARD FONDAMENTALE</t>
   </si>
   <si>
-    <t>Critere</t>
-  </si>
-  <si>
     <t>Valeur (auto depuis ETUDE)</t>
   </si>
   <si>
@@ -643,15 +754,9 @@
     <t>Zone</t>
   </si>
   <si>
-    <t>Score</t>
-  </si>
-  <si>
     <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
   </si>
   <si>
-    <t>&lt;-- saisir signal</t>
-  </si>
-  <si>
     <t>-5 a +5</t>
   </si>
   <si>
@@ -701,6 +806,21 @@
   </si>
   <si>
     <t>SCORE TOTAL</t>
+  </si>
+  <si>
+    <t>C — SIGNAL CONTRARIAN BRVM  (depuis ETUDE C4)</t>
+  </si>
+  <si>
+    <t>Score /10</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>PER vs Sectoriel</t>
+  </si>
+  <si>
+    <t>Decote VMC</t>
   </si>
   <si>
     <t>RECOMMANDATION FINALE (texte libre)</t>
@@ -1014,7 +1134,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1024,7 +1144,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1033,14 +1153,14 @@
     <font>
       <i/>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFDC2626"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1049,14 +1169,14 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF1F3864"/>
+      <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF404040"/>
+      <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1064,7 +1184,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF6600"/>
+      <color rgb="FFD97706"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1079,6 +1199,13 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
@@ -1102,9 +1229,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="8"/>
-      <color rgb="FFFF6600"/>
+      <color rgb="FFD97706"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1113,6 +1248,46 @@
       <i/>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFECFDF5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1141,6 +1316,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF1E3A5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF404040"/>
@@ -1158,14 +1340,45 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,7 +1387,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="FF0D1B2A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1186,7 +1399,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5496"/>
+        <fgColor rgb="FF1E3A5F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE8F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFBEB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFDF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1198,19 +1441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FF064E3B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FF2F5496"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1226,8 +1463,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1257,11 +1506,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1278,8 +1542,9 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1293,32 +1558,37 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1326,89 +1596,302 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="15" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="25" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="30" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF065F46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF065F46"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD1FAE5"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -1698,7 +2181,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H140"/>
+  <sheetPr>
+    <tabColor rgb="FF0EA5E9"/>
+  </sheetPr>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -1747,7 +2233,7 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="5" customHeight="1"/>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
+    <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>3</v>
       </c>
@@ -1802,7 +2288,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="5" customHeight="1"/>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
+    <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1857,7 +2343,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="5" customHeight="1"/>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
+    <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
@@ -2013,7 +2499,7 @@
       <c r="G20" s="12"/>
     </row>
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
-    <row r="22" spans="1:8" ht="18" customHeight="1">
+    <row r="22" spans="1:8" ht="20" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
@@ -2190,7 +2676,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
-    <row r="36" spans="1:8" ht="18" customHeight="1">
+    <row r="36" spans="1:8" ht="20" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>49</v>
       </c>
@@ -2361,7 +2847,7 @@
       <c r="G43" s="12"/>
     </row>
     <row r="44" spans="1:8" ht="5" customHeight="1"/>
-    <row r="45" spans="1:8" ht="18" customHeight="1">
+    <row r="45" spans="1:8" ht="20" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>57</v>
       </c>
@@ -2460,7 +2946,7 @@
       </c>
     </row>
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
-    <row r="54" spans="1:8" ht="18" customHeight="1">
+    <row r="54" spans="1:8" ht="20" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>67</v>
       </c>
@@ -2531,7 +3017,7 @@
       <c r="D59" s="20"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
-    <row r="61" spans="1:8" ht="18" customHeight="1">
+    <row r="61" spans="1:8" ht="20" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -2575,7 +3061,7 @@
       <c r="A65" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="22">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
@@ -2586,7 +3072,7 @@
       <c r="A66" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="22">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
@@ -2597,7 +3083,10 @@
       <c r="A67" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B67" s="6"/>
+      <c r="B67" s="23">
+        <f>IFERROR(B24,"")</f>
+        <v>0</v>
+      </c>
       <c r="C67" s="21"/>
       <c r="D67" s="12"/>
     </row>
@@ -2605,7 +3094,7 @@
       <c r="A68" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="22">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
@@ -2616,7 +3105,7 @@
       <c r="A69" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="22">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
@@ -2627,7 +3116,7 @@
       <c r="A70" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="23">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
@@ -2646,7 +3135,7 @@
       <c r="A72" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="23">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
@@ -2657,7 +3146,7 @@
       <c r="A73" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="23">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
@@ -2668,7 +3157,7 @@
       <c r="A74" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="24">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
@@ -2679,7 +3168,7 @@
       <c r="A75" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B75" s="22">
+      <c r="B75" s="25">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
@@ -2689,7 +3178,7 @@
       <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
-    <row r="77" spans="1:8" ht="18" customHeight="1">
+    <row r="77" spans="1:8" ht="20" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>98</v>
       </c>
@@ -2702,34 +3191,34 @@
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="40" customHeight="1">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-      <c r="D78" s="23"/>
-      <c r="E78" s="23"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="23"/>
-      <c r="H78" s="23"/>
+      <c r="A78" s="26"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
+      <c r="A79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="23"/>
-      <c r="H80" s="23"/>
+      <c r="A80" s="26"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
@@ -2744,7 +3233,7 @@
       <c r="H81" s="1"/>
     </row>
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
-    <row r="84" spans="1:8" ht="18" customHeight="1">
+    <row r="84" spans="1:8" ht="20" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>100</v>
       </c>
@@ -2781,11 +3270,11 @@
         <v>106</v>
       </c>
       <c r="C86" s="21"/>
-      <c r="D86" s="24">
+      <c r="D86" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E86" s="25" t="s">
+      <c r="E86" s="28" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2797,11 +3286,11 @@
         <v>106</v>
       </c>
       <c r="C87" s="21"/>
-      <c r="D87" s="24">
+      <c r="D87" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B87)),1,IF(ISNUMBER(SEARCH("surachat",B87)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E87" s="25" t="s">
+      <c r="E87" s="28" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2813,11 +3302,11 @@
         <v>106</v>
       </c>
       <c r="C88" s="21"/>
-      <c r="D88" s="24">
+      <c r="D88" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B88)),1,IF(ISNUMBER(SEARCH("surachat",B88)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="25" t="s">
+      <c r="E88" s="28" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2829,11 +3318,11 @@
         <v>106</v>
       </c>
       <c r="C89" s="21"/>
-      <c r="D89" s="24">
+      <c r="D89" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B89)),1,IF(ISNUMBER(SEARCH("surachat",B89)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="25" t="s">
+      <c r="E89" s="28" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2845,11 +3334,11 @@
         <v>106</v>
       </c>
       <c r="C90" s="21"/>
-      <c r="D90" s="24">
+      <c r="D90" s="27">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E90" s="25" t="s">
+      <c r="E90" s="28" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2859,17 +3348,17 @@
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
-      <c r="D91" s="26">
+      <c r="D91" s="29">
         <f>SUM(D86:D90)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="27">
+      <c r="E91" s="30">
         <f>IFERROR(IF(D91&gt;0,"Zone SURVENTE - Achat possible",IF(D91&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
-    <row r="93" spans="1:8" ht="18" customHeight="1">
+    <row r="93" spans="1:8" ht="20" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>117</v>
       </c>
@@ -2929,7 +3418,7 @@
       </c>
     </row>
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
-    <row r="98" spans="1:8" ht="18" customHeight="1">
+    <row r="98" spans="1:8" ht="20" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>125</v>
       </c>
@@ -2959,7 +3448,7 @@
       <c r="A100" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="23">
         <f>B24</f>
         <v>0</v>
       </c>
@@ -2972,7 +3461,7 @@
       <c r="A101" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B101" s="22">
         <f>B25</f>
         <v>0</v>
       </c>
@@ -2985,7 +3474,7 @@
       <c r="A102" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B102" s="28"/>
+      <c r="B102" s="31"/>
       <c r="C102" s="20" t="s">
         <v>132</v>
       </c>
@@ -2995,7 +3484,7 @@
       <c r="A103" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B103" s="22">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
@@ -3008,7 +3497,7 @@
       <c r="A104" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="24">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
@@ -3021,7 +3510,7 @@
       </c>
     </row>
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
-    <row r="106" spans="1:8" ht="18" customHeight="1">
+    <row r="106" spans="1:8" ht="20" customHeight="1">
       <c r="A106" s="3" t="s">
         <v>137</v>
       </c>
@@ -3034,16 +3523,16 @@
       <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
-      <c r="A107" s="29" t="s">
+      <c r="A107" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="29"/>
-      <c r="F107" s="29"/>
-      <c r="G107" s="29"/>
-      <c r="H107" s="29"/>
+      <c r="B107" s="32"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="32"/>
+      <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
@@ -3063,7 +3552,7 @@
       <c r="A109" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B109" s="28"/>
+      <c r="B109" s="31"/>
       <c r="C109" s="20" t="s">
         <v>141</v>
       </c>
@@ -3083,7 +3572,7 @@
       <c r="A111" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B111" s="22">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
@@ -3096,7 +3585,7 @@
       <c r="A112" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B112" s="28">
+      <c r="B112" s="31">
         <v>6.5</v>
       </c>
       <c r="C112" s="20" t="s">
@@ -3108,7 +3597,7 @@
       <c r="A113" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B113" s="22">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
@@ -3121,7 +3610,7 @@
       <c r="A114" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B114" s="22">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
@@ -3134,7 +3623,7 @@
       <c r="A115" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="22">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
@@ -3147,7 +3636,7 @@
       <c r="A116" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B116" s="27">
+      <c r="B116" s="30">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
@@ -3157,7 +3646,7 @@
       <c r="D116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
-    <row r="118" spans="1:8" ht="18" customHeight="1">
+    <row r="118" spans="1:8" ht="20" customHeight="1">
       <c r="A118" s="3" t="s">
         <v>156</v>
       </c>
@@ -3170,16 +3659,16 @@
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="30" t="s">
+      <c r="A119" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="B119" s="30"/>
-      <c r="C119" s="30"/>
-      <c r="D119" s="30"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="30"/>
-      <c r="H119" s="30"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="33"/>
+      <c r="E119" s="33"/>
+      <c r="F119" s="33"/>
+      <c r="G119" s="33"/>
+      <c r="H119" s="33"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
@@ -3209,7 +3698,7 @@
       <c r="A122" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B122" s="28">
+      <c r="B122" s="31">
         <v>8</v>
       </c>
       <c r="C122" s="20" t="s">
@@ -3221,7 +3710,7 @@
       <c r="A123" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B123" s="28">
+      <c r="B123" s="31">
         <v>2</v>
       </c>
       <c r="C123" s="20" t="s">
@@ -3233,7 +3722,7 @@
       <c r="A124" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B124" s="31">
+      <c r="B124" s="34">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
@@ -3246,7 +3735,7 @@
       <c r="A125" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B125" s="27">
+      <c r="B125" s="30">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
@@ -3256,7 +3745,7 @@
       <c r="D125" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
-    <row r="128" spans="1:8" ht="18" customHeight="1">
+    <row r="128" spans="1:8" ht="20" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>168</v>
       </c>
@@ -3296,7 +3785,7 @@
       <c r="A131" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B131" s="16">
+      <c r="B131" s="22">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
@@ -3319,7 +3808,7 @@
       <c r="A133" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B133" s="16">
+      <c r="B133" s="22">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
@@ -3332,7 +3821,7 @@
       <c r="A134" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B134" s="16">
+      <c r="B134" s="22">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
@@ -3345,7 +3834,7 @@
       <c r="A135" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="24">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
@@ -3358,7 +3847,7 @@
       </c>
     </row>
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
-    <row r="137" spans="1:8" ht="18" customHeight="1">
+    <row r="137" spans="1:8" ht="20" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>182</v>
       </c>
@@ -3371,37 +3860,550 @@
       <c r="H137" s="3"/>
     </row>
     <row r="138" spans="1:8" ht="40" customHeight="1">
-      <c r="A138" s="23"/>
-      <c r="B138" s="23"/>
-      <c r="C138" s="23"/>
-      <c r="D138" s="23"/>
-      <c r="E138" s="23"/>
-      <c r="F138" s="23"/>
-      <c r="G138" s="23"/>
-      <c r="H138" s="23"/>
+      <c r="A138" s="26"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
+      <c r="D138" s="26"/>
+      <c r="E138" s="26"/>
+      <c r="F138" s="26"/>
+      <c r="G138" s="26"/>
+      <c r="H138" s="26"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="23"/>
-      <c r="B139" s="23"/>
-      <c r="C139" s="23"/>
-      <c r="D139" s="23"/>
-      <c r="E139" s="23"/>
-      <c r="F139" s="23"/>
-      <c r="G139" s="23"/>
-      <c r="H139" s="23"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
+      <c r="D139" s="26"/>
+      <c r="E139" s="26"/>
+      <c r="F139" s="26"/>
+      <c r="G139" s="26"/>
+      <c r="H139" s="26"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="23"/>
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
-      <c r="D140" s="23"/>
-      <c r="E140" s="23"/>
-      <c r="F140" s="23"/>
-      <c r="G140" s="23"/>
-      <c r="H140" s="23"/>
-    </row>
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
+      <c r="D140" s="26"/>
+      <c r="E140" s="26"/>
+      <c r="F140" s="26"/>
+      <c r="G140" s="26"/>
+      <c r="H140" s="26"/>
+    </row>
+    <row r="141" spans="1:8" ht="26" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+      <c r="E141" s="1"/>
+      <c r="F141" s="1"/>
+      <c r="G141" s="1"/>
+      <c r="H141" s="1"/>
+    </row>
+    <row r="143" spans="1:8" ht="5" customHeight="1"/>
+    <row r="144" spans="1:8" ht="20" customHeight="1">
+      <c r="A144" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="3"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+      <c r="H144" s="3"/>
+    </row>
+    <row r="145" spans="1:8" ht="30" customHeight="1">
+      <c r="A145" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B145" s="35"/>
+      <c r="C145" s="35"/>
+      <c r="D145" s="35"/>
+      <c r="E145" s="35"/>
+      <c r="F145" s="35"/>
+      <c r="G145" s="35"/>
+      <c r="H145" s="35"/>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D146" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B147" s="9">
+        <f>B12</f>
+        <v>0</v>
+      </c>
+      <c r="C147" s="6"/>
+      <c r="D147" s="9">
+        <f>IFERROR(B147-C147,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E147" s="7">
+        <f>IFERROR(D147/B8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" s="9">
+        <f>C12</f>
+        <v>0</v>
+      </c>
+      <c r="C148" s="6"/>
+      <c r="D148" s="9">
+        <f>IFERROR(B148-C148,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E148" s="7">
+        <f>IFERROR(D148/C8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="9">
+        <f>D12</f>
+        <v>0</v>
+      </c>
+      <c r="C149" s="6"/>
+      <c r="D149" s="9">
+        <f>IFERROR(B149-C149,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E149" s="7">
+        <f>IFERROR(D149/D8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="9">
+        <f>E12</f>
+        <v>0</v>
+      </c>
+      <c r="C150" s="6"/>
+      <c r="D150" s="9">
+        <f>IFERROR(B150-C150,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E150" s="7">
+        <f>IFERROR(D150/E8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B151" s="9">
+        <f>F12</f>
+        <v>0</v>
+      </c>
+      <c r="C151" s="6"/>
+      <c r="D151" s="9">
+        <f>IFERROR(B151-C151,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E151" s="7">
+        <f>IFERROR(D151/F8*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="5" customHeight="1"/>
+    <row r="153" spans="1:8">
+      <c r="A153" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B153" s="16">
+        <f>IFERROR(D151*1000000/B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D153" s="7">
+        <f>IFERROR(B24/B153,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E153" s="10">
+        <f>IFERROR(IF(D153&gt;15,"PER normalise eleve",IF(D153&lt;9,"Sous-evalue normalise","Normal (9-15)")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B154" s="10">
+        <f>IFERROR(IF(C151&lt;0,"Mauvais resultat PONCTUEL — RN recurrent &gt; RN publie — opportunite contrarian potentielle",IF(C151&gt;0,"Resultat FLATTE par elements exceptionnels — prudence sur la valorisation","Pas d'element exceptionnel detecte — RN publie = RN recurrent")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="5" customHeight="1"/>
+    <row r="156" spans="1:8" ht="20" customHeight="1">
+      <c r="A156" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="3"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3"/>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B158" s="36">
+        <v>12</v>
+      </c>
+      <c r="C158" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D158" s="14"/>
+      <c r="E158" s="14"/>
+      <c r="F158" s="14"/>
+      <c r="G158" s="14"/>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B159" s="36">
+        <v>5</v>
+      </c>
+      <c r="C159" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="D159" s="14"/>
+      <c r="E159" s="14"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="14"/>
+    </row>
+    <row r="160" spans="1:8" ht="5" customHeight="1"/>
+    <row r="161" spans="1:8">
+      <c r="A161" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B161" s="7">
+        <f>IFERROR(B30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C161" s="21">
+        <f>B158</f>
+        <v>0</v>
+      </c>
+      <c r="D161" s="7">
+        <f>IFERROR((B30/B158-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E161" s="10">
+        <f>IFERROR(IF((B30/B158-1)*100&lt;=-20,"Forte decote sectorielle — opportunite",IF((B30/B158-1)*100&lt;=-5,"Legere decote sectorielle",IF((B30/B158-1)*100&lt;=15,"Dans la norme sectorielle","Prime elevee vs secteur — prudence"))),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
+      <c r="A162" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" s="7">
+        <f>IFERROR(AVERAGE(F38:F42),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C162" s="21">
+        <f>B159</f>
+        <v>0</v>
+      </c>
+      <c r="D162" s="7">
+        <f>IFERROR((AVERAGE(F38:F42)/B159-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E162" s="10">
+        <f>IFERROR(IF(AVERAGE(F38:F42)&gt;=B159*1.2,"Rendement superieur au marche — attractif",IF(AVERAGE(F38:F42)&gt;=B159,"Dans la moyenne du marche","Rendement inferieur au marche")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="5" customHeight="1"/>
+    <row r="164" spans="1:8" ht="20" customHeight="1">
+      <c r="A164" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+      <c r="H164" s="3"/>
+    </row>
+    <row r="165" spans="1:8">
+      <c r="A165" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
+      <c r="A166" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B166" s="37">
+        <f>COUNTIF(B38:B42,"&gt;0")</f>
+        <v>0</v>
+      </c>
+      <c r="C166" s="10">
+        <f>IFERROR(IF(B166=5,"Regulier 5/5 — fiable",IF(B166&gt;=4,"Quasi-regulier 4/5",IF(B166&gt;=3,"Irregulier 3/5","Tres irregulier — risque dividende"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D166" s="37">
+        <f>IF(B166=5,2,IF(B166&gt;=4,1,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
+      <c r="A167" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B167" s="8">
+        <f>IFERROR(IF(OR(B38&lt;=0,B42&lt;=0),"N/A",(B42/B38)^(1/4)-1),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="C167" s="10">
+        <f>IFERROR(IF(NOT(ISNUMBER(B167)),"Dividende absent",IF(B167&gt;0.05,"Forte croissance dividende",IF(B167&gt;0,"Croissance modeste","Dividende en baisse"))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D167" s="37">
+        <f>IFERROR(IF(ISNUMBER(B167),IF(B167&gt;0,1,0),0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
+      <c r="A168" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B168" s="38">
+        <f>IFERROR(D166+D167,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C168" s="10">
+        <f>IFERROR(IF(D166+D167&gt;=3,"Dividende tres fiable",IF(D166+D167&gt;=2,"Dividende assez fiable","Dividende peu fiable — risque")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D168" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="5" customHeight="1"/>
+    <row r="170" spans="1:8" ht="20" customHeight="1">
+      <c r="A170" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+      <c r="H170" s="3"/>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B172" s="10">
+        <f>IFERROR(IF(B30&lt;B158,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C172" s="10">
+        <f>IFERROR("PER="&amp;ROUND(B30,1)&amp;" vs sectoriel="&amp;B158,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D172" s="37">
+        <f>IFERROR(IF(B30&lt;B158*0.85,2,IF(B30&lt;B158,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B173" s="10">
+        <f>IFERROR(IF(B24&lt;B31,"OUI — decote comptable","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C173" s="10">
+        <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs VMC="&amp;ROUND(B31,0)&amp;" FCFA","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D173" s="37">
+        <f>IFERROR(IF(B24&lt;B31*0.85,2,IF(B24&lt;B31,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B174" s="10">
+        <f>IFERROR(IF(B33&gt;=10,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C174" s="10">
+        <f>IFERROR("ROE="&amp;ROUND(B33,1)&amp;"%","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D174" s="37">
+        <f>IFERROR(IF(B33&gt;=15,2,IF(B33&gt;=10,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B175" s="10">
+        <f>IFERROR(IF(B168&gt;=2,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C175" s="10">
+        <f>IFERROR(C168,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="D175" s="37">
+        <f>IFERROR(MIN(B168,2),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B176" s="10">
+        <f>IFERROR(IF(B24&lt;D95,"OUI — survente","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C176" s="10">
+        <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs PM1an="&amp;ROUND(D95,0)&amp;" FCFA","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D176" s="37">
+        <f>IFERROR(IF(B24&lt;D95,1,0),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B177" s="10">
+        <f>IFERROR(IF(G16&gt;=5,"OUI","NON"),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C177" s="10">
+        <f>IFERROR("Marge moy="&amp;ROUND(G16,1)&amp;"%","-")</f>
+        <v>0</v>
+      </c>
+      <c r="D177" s="37">
+        <f>IFERROR(IF(G16&gt;=10,2,IF(G16&gt;=5,1,0)),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="B178" s="12"/>
+      <c r="C178" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D178" s="39">
+        <f>IFERROR(SUM(D172:D177),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="30" customHeight="1">
+      <c r="A179" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="B179" s="40"/>
+      <c r="C179" s="40"/>
+      <c r="D179" s="40"/>
+      <c r="E179" s="41">
+        <f>IFERROR(IF(D178&gt;=7,"FORTE OPPORTUNITE CONTRARIAN — fondamentaux sains, titre boude",IF(D178&gt;=5,"A SURVEILLER — signaux contrarians partiels","PAS DE SIGNAL CONTRARIAN — attendre")),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="F179" s="41"/>
+      <c r="G179" s="41"/>
+      <c r="H179" s="41"/>
+    </row>
+    <row r="180" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
-  <mergeCells count="29">
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
+  <mergeCells count="39">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -3431,14 +4433,76 @@
     <mergeCell ref="A128:H128"/>
     <mergeCell ref="A137:H137"/>
     <mergeCell ref="A138:H140"/>
+    <mergeCell ref="A141:H141"/>
+    <mergeCell ref="A144:H144"/>
+    <mergeCell ref="A145:H145"/>
+    <mergeCell ref="A156:H156"/>
+    <mergeCell ref="C158:G158"/>
+    <mergeCell ref="C159:G159"/>
+    <mergeCell ref="A164:H164"/>
+    <mergeCell ref="A170:H170"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="E179:H179"/>
   </mergeCells>
+  <conditionalFormatting sqref="B172:B177">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
+      <formula>NOT(ISERROR(SEARCH("OUI",B172)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="15" operator="containsText" text="NON">
+      <formula>NOT(ISERROR(SEARCH("NON",B172)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D34">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="sous-evaluee">
+      <formula>NOT(ISERROR(SEARCH("sous-evaluee",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Excellent">
+      <formula>NOT(ISERROR(SEARCH("Excellent",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="8" operator="containsText" text="surevaluee">
+      <formula>NOT(ISERROR(SEARCH("surevaluee",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="9" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="11" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="12" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="13" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E35"/>
+  <sheetPr>
+    <tabColor rgb="FF1E3A5F"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3450,7 +4514,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3458,444 +4522,609 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+      <c r="A2" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="A4" s="43" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="33">
+        <v>228</v>
+      </c>
+      <c r="B6" s="44">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="34">
+        <v>229</v>
+      </c>
+      <c r="D6" s="45">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35"/>
+      <c r="E6" s="46"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B7" s="33">
+        <v>230</v>
+      </c>
+      <c r="B7" s="44">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="34">
+        <v>229</v>
+      </c>
+      <c r="D7" s="45">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35"/>
+      <c r="E7" s="46"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B8" s="33">
+        <v>231</v>
+      </c>
+      <c r="B8" s="44">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="34">
+        <v>232</v>
+      </c>
+      <c r="D8" s="45">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35"/>
+      <c r="E8" s="46"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="33">
+        <v>233</v>
+      </c>
+      <c r="B9" s="44">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="34">
+        <v>234</v>
+      </c>
+      <c r="D9" s="45">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="35"/>
+      <c r="E9" s="46"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B10" s="33">
+        <v>235</v>
+      </c>
+      <c r="B10" s="44">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D10" s="34">
+        <v>236</v>
+      </c>
+      <c r="D10" s="45">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35"/>
+      <c r="E10" s="46"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B11" s="33">
+        <v>237</v>
+      </c>
+      <c r="B11" s="44">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="34">
+        <v>229</v>
+      </c>
+      <c r="D11" s="45">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35"/>
+      <c r="E11" s="46"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B12" s="33">
+        <v>238</v>
+      </c>
+      <c r="B12" s="44">
         <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D12" s="34">
+        <v>239</v>
+      </c>
+      <c r="D12" s="45">
         <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35"/>
+      <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="33">
+        <v>240</v>
+      </c>
+      <c r="B13" s="44">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="D13" s="34">
+        <v>241</v>
+      </c>
+      <c r="D13" s="45">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="36">
+        <v>242</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="A16" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>207</v>
+        <v>244</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>210</v>
+        <v>245</v>
+      </c>
+      <c r="B18" s="49">
+        <f>IFERROR(ETUDE!D91,"")</f>
+        <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E18" s="38"/>
+        <v>246</v>
+      </c>
+      <c r="D18" s="45">
+        <f>IFERROR(ETUDE!E91,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="46"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="37" t="s">
-        <v>210</v>
+        <v>247</v>
+      </c>
+      <c r="B19" s="49">
+        <f>IFERROR(ETUDE!E95,"")</f>
+        <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E19" s="38"/>
+        <v>248</v>
+      </c>
+      <c r="D19" s="45">
+        <f>IFERROR(ETUDE!E96,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="46"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>210</v>
+        <v>249</v>
+      </c>
+      <c r="B20" s="49">
+        <f>IFERROR(ETUDE!B104,"")</f>
+        <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E20" s="38"/>
+        <v>250</v>
+      </c>
+      <c r="D20" s="45">
+        <f>IFERROR(ETUDE!D104,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="46"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>210</v>
+        <v>251</v>
+      </c>
+      <c r="B21" s="49">
+        <f>IFERROR(ETUDE!B116,"")</f>
+        <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="38"/>
+        <v>252</v>
+      </c>
+      <c r="D21" s="45">
+        <f>IFERROR(ETUDE!B125,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="46"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B22" s="37" t="s">
-        <v>210</v>
+        <v>253</v>
+      </c>
+      <c r="B22" s="49">
+        <f>IFERROR(ETUDE!B135,"")</f>
+        <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="E22" s="38"/>
+        <v>254</v>
+      </c>
+      <c r="D22" s="45">
+        <f>IFERROR(ETUDE!D135,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="18" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="36">
+        <v>255</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
+      <c r="A25" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B27" s="40">
+        <v>260</v>
+      </c>
+      <c r="B27" s="51">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="52">
         <v>24</v>
       </c>
-      <c r="D27" s="42">
+      <c r="D27" s="53">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="54">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B28" s="40">
+        <v>261</v>
+      </c>
+      <c r="B28" s="51">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="52">
         <v>15</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D28" s="53">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="54">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B29" s="43">
+        <v>262</v>
+      </c>
+      <c r="B29" s="55">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="56">
         <v>39</v>
       </c>
-      <c r="D29" s="42">
+      <c r="D29" s="53">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29" s="57">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" ht="50" customHeight="1">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
+      <c r="A31" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" customHeight="1">
+      <c r="A33" s="58">
+        <f>IFERROR(ETUDE!D178,"")</f>
+        <v>0</v>
+      </c>
+      <c r="B33" s="59">
+        <f>IFERROR(ETUDE!E179,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="60">
+        <f>IFERROR(ETUDE!D153,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="60">
+        <f>IFERROR(ETUDE!D161,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="61">
+        <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="5" customHeight="1"/>
+    <row r="35" spans="1:5" ht="18" customHeight="1">
+      <c r="A35" s="43" t="s">
+        <v>268</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+    </row>
+    <row r="36" spans="1:5" ht="50" customHeight="1">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
+  <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A32:E35"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:E40"/>
   </mergeCells>
+  <conditionalFormatting sqref="D18:D22">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="rentable">
+      <formula>NOT(ISERROR(SEARCH("rentable",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="Opportunite">
+      <formula>NOT(ISERROR(SEARCH("Opportunite",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="12" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="14" operator="containsText" text="ACHETER">
+      <formula>NOT(ISERROR(SEARCH("ACHETER",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="20" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="22" operator="containsText" text="Negatif">
+      <formula>NOT(ISERROR(SEARCH("Negatif",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="24" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="26" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="28" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="NEUTRE">
+      <formula>NOT(ISERROR(SEARCH("NEUTRE",D18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D13">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Bon">
+      <formula>NOT(ISERROR(SEARCH("Bon",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="rentable">
+      <formula>NOT(ISERROR(SEARCH("rentable",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Sous-evalue">
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="Decote">
+      <formula>NOT(ISERROR(SEARCH("Decote",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Opportunite">
+      <formula>NOT(ISERROR(SEARCH("Opportunite",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="11" operator="containsText" text="SURVENTE">
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="13" operator="containsText" text="ACHETER">
+      <formula>NOT(ISERROR(SEARCH("ACHETER",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="15" operator="containsText" text="Surevalue">
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="17" operator="containsText" text="SURACHAT">
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="19" operator="containsText" text="Prime">
+      <formula>NOT(ISERROR(SEARCH("Prime",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="21" operator="containsText" text="Negatif">
+      <formula>NOT(ISERROR(SEARCH("Negatif",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="23" operator="containsText" text="Normal">
+      <formula>NOT(ISERROR(SEARCH("Normal",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="25" operator="containsText" text="Faible">
+      <formula>NOT(ISERROR(SEARCH("Faible",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="27" operator="containsText" text="Moyen">
+      <formula>NOT(ISERROR(SEARCH("Moyen",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="29" operator="containsText" text="NEUTRE">
+      <formula>NOT(ISERROR(SEARCH("NEUTRE",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF6B7280"/>
+  </sheetPr>
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3907,23 +5136,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>269</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>231</v>
+        <v>271</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -3931,7 +5160,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -3939,7 +5168,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>233</v>
+        <v>273</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -3947,7 +5176,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>234</v>
+        <v>274</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -3955,7 +5184,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>235</v>
+        <v>275</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -3963,16 +5192,16 @@
     </row>
     <row r="8" spans="1:4" ht="5" customHeight="1"/>
     <row r="9" spans="1:4" ht="18" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="A9" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>237</v>
+        <v>277</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -3980,7 +5209,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -3988,7 +5217,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>239</v>
+        <v>279</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -3996,7 +5225,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -4004,26 +5233,26 @@
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="18" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="A15" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>242</v>
+        <v>282</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>243</v>
+        <v>283</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>244</v>
+        <v>284</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
@@ -4031,32 +5260,32 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>246</v>
+        <v>286</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="A21" s="43" t="s">
+        <v>289</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
@@ -4068,7 +5297,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -4076,7 +5305,7 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>251</v>
+        <v>291</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -4084,36 +5313,36 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>253</v>
+        <v>293</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="18" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="A27" s="43" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>257</v>
+        <v>297</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -4121,26 +5350,27 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -4155,6 +5385,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF374151"/>
+  </sheetPr>
   <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4166,325 +5399,326 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>265</v>
+      <c r="B2" s="62" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>304</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="A3" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>268</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>270</v>
+        <v>307</v>
+      </c>
+      <c r="B4" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D4" s="64" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>273</v>
+        <v>311</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="64" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>276</v>
+        <v>314</v>
+      </c>
+      <c r="B6" s="63" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" s="64" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>279</v>
+        <v>233</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>317</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" s="64" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>283</v>
+        <v>320</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="64" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>284</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>285</v>
+        <v>235</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="64" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>288</v>
+        <v>326</v>
+      </c>
+      <c r="B10" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D10" s="64" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>290</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="47" t="s">
-        <v>291</v>
+        <v>329</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="64" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>293</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>294</v>
+        <v>332</v>
+      </c>
+      <c r="B12" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" s="64" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>269</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>297</v>
+        <v>335</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>309</v>
+      </c>
+      <c r="D13" s="64" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="A14" s="43" t="s">
+        <v>338</v>
+      </c>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>301</v>
+        <v>339</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="C15" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15" s="64" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="47" t="s">
-        <v>304</v>
+        <v>342</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="52"/>
+      <c r="D16" s="64" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="47" t="s">
-        <v>305</v>
+      <c r="B17" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="64" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>307</v>
+      <c r="B18" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>318</v>
+      </c>
+      <c r="D18" s="64" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>310</v>
+        <v>348</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D19" s="64" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B20" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>313</v>
+        <v>351</v>
+      </c>
+      <c r="B20" s="63" t="s">
+        <v>352</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="A21" s="43" t="s">
+        <v>354</v>
+      </c>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>316</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>317</v>
+        <v>355</v>
+      </c>
+      <c r="B22" s="63" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>321</v>
+        <v>358</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="B24" s="63" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="B24" s="46" t="s">
-        <v>323</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>324</v>
+      <c r="D24" s="64" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="B25" s="46" t="s">
-        <v>326</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>282</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>327</v>
+        <v>365</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>366</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>322</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,13 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="368">
-  <si>
-    <t>FICHE D'ANALYSE BRVM — [NOM SOCIETE]   |   Date : [JJ/MM/AAAA]</t>
-  </si>
-  <si>
-    <t>Remplacer [NOM SOCIETE] et [JJ/MM/AAAA] dans la cellule A1 avant utilisation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="373">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -169,10 +163,7 @@
     <t>A5 — DIVIDENDES &amp; TAUX DE DISTRIBUTION</t>
   </si>
   <si>
-    <t>Dividende BRUT (FCFA)</t>
-  </si>
-  <si>
-    <t>Dividende NET (FCFA)</t>
+    <t>Dividende NET recu (FCFA)</t>
   </si>
   <si>
     <t>BNPA (FCFA)</t>
@@ -187,6 +178,9 @@
     <t>Progression %</t>
   </si>
   <si>
+    <t>Dividende NET = montant effectivement recu apres prelevement 15% a la source. Taux distribution = (Div NET / 0,85) / BNPA x 100  (reconstitution du brut)</t>
+  </si>
+  <si>
     <t>TOTAL / MOYENNE</t>
   </si>
   <si>
@@ -610,7 +604,7 @@
     <t>PER sectoriel moyen BRVM (reference)</t>
   </si>
   <si>
-    <t>&lt;-- Banques ~10 | Industrie ~12-14 | Distribution ~15 | Telecom ~8</t>
+    <t>&lt;-- Auto depuis PROFIL!B5 | Banque~10, Industrie~13, Distribution~14, Telecom~8</t>
   </si>
   <si>
     <t>Rendement dividende sectoriel BRVM (%)</t>
@@ -685,9 +679,6 @@
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
-    <t>Societe : [NOM]   |   Date : [JJ/MM/AAAA]   |   Prix analyse : [FCFA]</t>
-  </si>
-  <si>
     <t>SCORECARD FONDAMENTALE</t>
   </si>
   <si>
@@ -829,13 +820,37 @@
     <t>PROFIL DE LA SOCIETE</t>
   </si>
   <si>
-    <t>IDENTIFICATION</t>
+    <t>DONNEES CLES — liees automatiquement a ETUDE et SYNTHESE</t>
   </si>
   <si>
     <t>Nom de la societe</t>
   </si>
   <si>
+    <t>PROFIL!B3 -&gt; titre de ETUDE et SYNTHESE</t>
+  </si>
+  <si>
     <t>Ticker BRVM</t>
+  </si>
+  <si>
+    <t>ex: BIDC, ETIT, SNTS, ONTBF...</t>
+  </si>
+  <si>
+    <t>Secteur d activite</t>
+  </si>
+  <si>
+    <t>Banque | Assurance | Industrie | Distribution | Telecom | Autre</t>
+  </si>
+  <si>
+    <t>Date d analyse</t>
+  </si>
+  <si>
+    <t>ex: 14/05/2026  (texte libre)</t>
+  </si>
+  <si>
+    <t>IDENTIFICATION COMPLETE</t>
+  </si>
+  <si>
+    <t>Nom complet</t>
   </si>
   <si>
     <t>Secteur d'activite</t>
@@ -1134,7 +1149,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1151,9 +1166,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FFDC2626"/>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1168,14 +1183,14 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1198,15 +1213,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF0D1B2A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1230,7 +1253,7 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1246,7 +1269,7 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1254,7 +1277,7 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1278,14 +1301,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFECFDF5"/>
       <name val="Calibri"/>
@@ -1293,7 +1308,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1301,22 +1316,14 @@
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color rgb="FF1E3A5F"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1340,7 +1347,7 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF404040"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1377,6 +1384,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -1388,12 +1411,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0D1B2A"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1429,13 +1446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6E4F7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1525,209 +1548,227 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="17" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="17" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="25" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2195,8 +2236,9 @@
     <col min="8" max="8" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="26" customHeight="1">
+      <c r="A1" s="1">
+        <f>IFERROR("FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"   ("&amp;PROFIL!B4&amp;")   |   "&amp;PROFIL!B5&amp;"   |   "&amp;PROFIL!B6,"FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]")</f>
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -2208,8 +2250,9 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" s="2">
+        <f>IFERROR("Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date analyse : "&amp;PROFIL!B6,"Completer le PROFIL : nom, ticker, secteur, date")</f>
+        <v>0</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2222,7 +2265,7 @@
     <row r="3" spans="1:8" ht="5" customHeight="1"/>
     <row r="4" spans="1:8" ht="22" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2235,7 +2278,7 @@
     <row r="5" spans="1:8" ht="5" customHeight="1"/>
     <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -2248,30 +2291,30 @@
     <row r="7" spans="1:8">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -2290,7 +2333,7 @@
     <row r="9" spans="1:8" ht="5" customHeight="1"/>
     <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2303,30 +2346,30 @@
     <row r="11" spans="1:8">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2345,7 +2388,7 @@
     <row r="13" spans="1:8" ht="5" customHeight="1"/>
     <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2357,30 +2400,30 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B16" s="9">
         <f>B12</f>
@@ -2399,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G16" s="7">
         <f>IFERROR(AVERAGE(D16:D20),"")</f>
@@ -2408,7 +2451,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B17" s="9">
         <f>C12</f>
@@ -2431,7 +2474,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B18" s="9">
         <f>D12</f>
@@ -2454,7 +2497,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B19" s="9">
         <f>E12</f>
@@ -2477,7 +2520,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" s="9">
         <f>F12</f>
@@ -2501,7 +2544,7 @@
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
     <row r="22" spans="1:8" ht="20" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2513,16 +2556,16 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -2531,11 +2574,11 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
@@ -2544,11 +2587,11 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -2557,11 +2600,11 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
@@ -2570,11 +2613,11 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
@@ -2583,11 +2626,11 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
@@ -2597,14 +2640,14 @@
     <row r="29" spans="1:8" ht="5" customHeight="1"/>
     <row r="30" spans="1:8">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B30" s="7">
         <f>IFERROR(B24/B25,"")</f>
         <v>0</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D30" s="10">
         <f>IFERROR(IF(B30&gt;15,"Surevalue",IF(B30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
@@ -2613,14 +2656,14 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31" s="16">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D31" s="10">
         <f>IFERROR(IF(B24&gt;B31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
@@ -2629,14 +2672,14 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="7">
         <f>IFERROR(B27/B26,"")</f>
         <v>0</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D32" s="10">
         <f>IFERROR(IF(B32&lt;1,"Decote comptable",IF(B32&lt;2,"Normal","Prime elevee")),"-")</f>
@@ -2645,14 +2688,14 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B33" s="7">
         <f>IFERROR(F12*1000000/B26*100,"")</f>
         <v>0</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D33" s="10">
         <f>IFERROR(IF(B33&gt;=15,"Excellent",IF(B33&gt;=10,"Bon",IF(B33&gt;=5,"Moyen","Faible"))),"-")</f>
@@ -2661,14 +2704,14 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B34" s="7">
         <f>IFERROR(B30*B32,"")</f>
         <v>0</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D34" s="10">
         <f>IFERROR(IF(B34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
@@ -2678,7 +2721,7 @@
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
     <row r="36" spans="1:8" ht="20" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2690,166 +2733,148 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="E37" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="F37" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="4" t="s">
+    </row>
+    <row r="38" spans="1:8" ht="25" customHeight="1">
+      <c r="A38" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="5" t="s">
-        <v>4</v>
-      </c>
       <c r="B38" s="17"/>
-      <c r="C38" s="16">
-        <f>IFERROR(B38*0.85,"")</f>
-        <v>0</v>
-      </c>
+      <c r="C38" s="17"/>
       <c r="D38" s="17"/>
-      <c r="E38" s="7">
-        <f>IFERROR(B38/D38*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="7">
-        <f>IFERROR(B38/B24*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G38" s="12"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="16">
-        <f>IFERROR(B39*0.85,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="7">
+        <f>IFERROR((B39/0.85)/C39*100,"")</f>
+        <v>0</v>
+      </c>
       <c r="E39" s="7">
-        <f>IFERROR(B39/D39*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="7">
         <f>IFERROR(B39/B24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="G39" s="7">
-        <f>IFERROR((B39-B38)/ABS(B38)*100,"")</f>
-        <v>0</v>
-      </c>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="16">
-        <f>IFERROR(B40*0.85,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="17"/>
+        <v>3</v>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="7">
+        <f>IFERROR((B40/0.85)/C40*100,"")</f>
+        <v>0</v>
+      </c>
       <c r="E40" s="7">
-        <f>IFERROR(B40/D40*100,"")</f>
+        <f>IFERROR(B40/B24*100,"")</f>
         <v>0</v>
       </c>
       <c r="F40" s="7">
-        <f>IFERROR(B40/B24*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G40" s="7">
         <f>IFERROR((B40-B39)/ABS(B39)*100,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="16">
-        <f>IFERROR(B41*0.85,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="17"/>
+        <v>4</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="7">
+        <f>IFERROR((B41/0.85)/C41*100,"")</f>
+        <v>0</v>
+      </c>
       <c r="E41" s="7">
-        <f>IFERROR(B41/D41*100,"")</f>
+        <f>IFERROR(B41/B24*100,"")</f>
         <v>0</v>
       </c>
       <c r="F41" s="7">
-        <f>IFERROR(B41/B24*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="7">
         <f>IFERROR((B41-B40)/ABS(B40)*100,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="16">
-        <f>IFERROR(B42*0.85,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="7">
+        <f>IFERROR((B42/0.85)/C42*100,"")</f>
+        <v>0</v>
+      </c>
       <c r="E42" s="7">
-        <f>IFERROR(B42/D42*100,"")</f>
+        <f>IFERROR(B42/B24*100,"")</f>
         <v>0</v>
       </c>
       <c r="F42" s="7">
-        <f>IFERROR(B42/B24*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="7">
         <f>IFERROR((B42-B41)/ABS(B41)*100,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="16">
-        <f>SUM(B38:B42)</f>
-        <v>0</v>
-      </c>
-      <c r="C43" s="16">
-        <f>IFERROR(B43*0.85,"")</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="12"/>
+      <c r="A43" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="7">
+        <f>IFERROR((B43/0.85)/C43*100,"")</f>
+        <v>0</v>
+      </c>
       <c r="E43" s="7">
-        <f>IFERROR(AVERAGE(E38:E42),"")</f>
+        <f>IFERROR(B43/B24*100,"")</f>
         <v>0</v>
       </c>
       <c r="F43" s="7">
-        <f>IFERROR(AVERAGE(F38:F42),"")</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="12"/>
-    </row>
-    <row r="44" spans="1:8" ht="5" customHeight="1"/>
+        <f>IFERROR((B43-B42)/ABS(B42)*100,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="16">
+        <f>SUM(B39:B43)</f>
+        <v>0</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="7">
+        <f>IFERROR(AVERAGE(D39:D43),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="7">
+        <f>IFERROR(AVERAGE(E39:E43),"")</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="12"/>
+    </row>
     <row r="45" spans="1:8" ht="20" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2861,21 +2886,21 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -2886,7 +2911,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -2897,7 +2922,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -2908,7 +2933,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -2919,7 +2944,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -2929,8 +2954,8 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="18" t="s">
-        <v>66</v>
+      <c r="A52" s="19" t="s">
+        <v>64</v>
       </c>
       <c r="B52" s="9">
         <f>SUM(B47:B51)</f>
@@ -2948,7 +2973,7 @@
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
     <row r="54" spans="1:8" ht="20" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2960,66 +2985,66 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C56" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="B56" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="D56" s="20"/>
+      <c r="D56" s="21"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B57" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="20"/>
+      <c r="C57" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="21"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D58" s="20"/>
+        <v>75</v>
+      </c>
+      <c r="B58" s="20"/>
+      <c r="C58" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58" s="21"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D59" s="20"/>
+        <v>77</v>
+      </c>
+      <c r="B59" s="20"/>
+      <c r="C59" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59" s="21"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="20" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3031,156 +3056,156 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="D62" s="4"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B63" s="6"/>
-      <c r="C63" s="21"/>
+      <c r="C63" s="22"/>
       <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B64" s="6"/>
-      <c r="C64" s="21"/>
+      <c r="C64" s="22"/>
       <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B65" s="22">
+        <v>84</v>
+      </c>
+      <c r="B65" s="23">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
-      <c r="C65" s="21"/>
+      <c r="C65" s="22"/>
       <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B66" s="22">
+        <v>85</v>
+      </c>
+      <c r="B66" s="23">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C66" s="21"/>
+      <c r="C66" s="22"/>
       <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B67" s="23">
+        <v>86</v>
+      </c>
+      <c r="B67" s="24">
         <f>IFERROR(B24,"")</f>
         <v>0</v>
       </c>
-      <c r="C67" s="21"/>
+      <c r="C67" s="22"/>
       <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B68" s="22">
+        <v>87</v>
+      </c>
+      <c r="B68" s="23">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
-      <c r="C68" s="21"/>
+      <c r="C68" s="22"/>
       <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B69" s="22">
+        <v>88</v>
+      </c>
+      <c r="B69" s="23">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C69" s="21"/>
+      <c r="C69" s="22"/>
       <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="23">
+        <v>89</v>
+      </c>
+      <c r="B70" s="24">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
-      <c r="C70" s="21"/>
+      <c r="C70" s="22"/>
       <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="21"/>
+        <v>90</v>
+      </c>
+      <c r="B71" s="18"/>
+      <c r="C71" s="22"/>
       <c r="D71" s="12"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" s="24">
+        <f>IFERROR(B71*B66,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C72" s="22"/>
+      <c r="D72" s="12"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="24">
+        <f>IFERROR(B70+B72,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="22"/>
+      <c r="D73" s="12"/>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B72" s="23">
-        <f>IFERROR(B71*B66,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="12"/>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="18" t="s">
+      <c r="B74" s="25">
+        <f>IFERROR(B73/B63*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="22"/>
+      <c r="D74" s="12"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B73" s="23">
-        <f>IFERROR(B70+B72,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="12"/>
-    </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="18" t="s">
+      <c r="B75" s="26">
+        <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="14" t="s">
         <v>95</v>
-      </c>
-      <c r="B74" s="24">
-        <f>IFERROR(B73/B63*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="12"/>
-    </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="25">
-        <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="D75" s="12"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
     <row r="77" spans="1:8" ht="20" customHeight="1">
       <c r="A77" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3191,38 +3216,38 @@
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="40" customHeight="1">
-      <c r="A78" s="26"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
-      <c r="D78" s="26"/>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
+      <c r="A78" s="27"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="26"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26"/>
+      <c r="A79" s="27"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="26"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
+      <c r="A80" s="27"/>
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3235,7 +3260,7 @@
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
     <row r="84" spans="1:8" ht="20" customHeight="1">
       <c r="A84" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3247,112 +3272,112 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="E85" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C86" s="22"/>
+      <c r="D86" s="28">
+        <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E86" s="29" t="s">
         <v>105</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C86" s="21"/>
-      <c r="D86" s="27">
-        <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E86" s="28" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C87" s="21"/>
-      <c r="D87" s="27">
+        <v>104</v>
+      </c>
+      <c r="C87" s="22"/>
+      <c r="D87" s="28">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B87)),1,IF(ISNUMBER(SEARCH("surachat",B87)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E87" s="28" t="s">
-        <v>109</v>
+      <c r="E87" s="29" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C88" s="21"/>
-      <c r="D88" s="27">
+        <v>104</v>
+      </c>
+      <c r="C88" s="22"/>
+      <c r="D88" s="28">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B88)),1,IF(ISNUMBER(SEARCH("surachat",B88)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="28" t="s">
-        <v>111</v>
+      <c r="E88" s="29" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C89" s="21"/>
-      <c r="D89" s="27">
+        <v>104</v>
+      </c>
+      <c r="C89" s="22"/>
+      <c r="D89" s="28">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B89)),1,IF(ISNUMBER(SEARCH("surachat",B89)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="28" t="s">
-        <v>113</v>
+      <c r="E89" s="29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="22"/>
+      <c r="D90" s="28">
+        <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="19" t="s">
         <v>114</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C90" s="21"/>
-      <c r="D90" s="27">
-        <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="28" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="18" t="s">
-        <v>116</v>
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
-      <c r="D91" s="29">
+      <c r="D91" s="30">
         <f>SUM(D86:D90)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="30">
+      <c r="E91" s="31">
         <f>IFERROR(IF(D91&gt;0,"Zone SURVENTE - Achat possible",IF(D91&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v>0</v>
       </c>
@@ -3360,7 +3385,7 @@
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
     <row r="93" spans="1:8" ht="20" customHeight="1">
       <c r="A93" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3372,24 +3397,24 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="D94" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="E94" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -3404,7 +3429,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -3420,7 +3445,7 @@
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
     <row r="98" spans="1:8" ht="20" customHeight="1">
       <c r="A98" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3432,77 +3457,77 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B100" s="23">
+        <v>125</v>
+      </c>
+      <c r="B100" s="24">
         <f>B24</f>
         <v>0</v>
       </c>
-      <c r="C100" s="20" t="s">
-        <v>128</v>
+      <c r="C100" s="21" t="s">
+        <v>126</v>
       </c>
       <c r="D100" s="12"/>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B101" s="22">
+        <v>127</v>
+      </c>
+      <c r="B101" s="23">
         <f>B25</f>
         <v>0</v>
       </c>
-      <c r="C101" s="20" t="s">
-        <v>130</v>
+      <c r="C101" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="D101" s="12"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B102" s="31"/>
-      <c r="C102" s="20" t="s">
-        <v>132</v>
+        <v>129</v>
+      </c>
+      <c r="B102" s="32"/>
+      <c r="C102" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="D102" s="12"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B103" s="22">
+        <v>131</v>
+      </c>
+      <c r="B103" s="23">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
-      <c r="C103" s="20" t="s">
-        <v>134</v>
+      <c r="C103" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="D103" s="12"/>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B104" s="24">
+        <v>133</v>
+      </c>
+      <c r="B104" s="25">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
-      <c r="C104" s="20" t="s">
-        <v>136</v>
+      <c r="C104" s="21" t="s">
+        <v>134</v>
       </c>
       <c r="D104" s="10">
         <f>IFERROR(IF(B104&gt;15,"Surevalue - Surachat",IF(B104&lt;9,"Sous-evalue - Survente","Normal (9-15)")),"-")</f>
@@ -3512,7 +3537,7 @@
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
     <row r="106" spans="1:8" ht="20" customHeight="1">
       <c r="A106" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3523,132 +3548,132 @@
       <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
-      <c r="A107" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="B107" s="32"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="32"/>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32"/>
-      <c r="H107" s="32"/>
+      <c r="A107" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="B107" s="33"/>
+      <c r="C107" s="33"/>
+      <c r="D107" s="33"/>
+      <c r="E107" s="33"/>
+      <c r="F107" s="33"/>
+      <c r="G107" s="33"/>
+      <c r="H107" s="33"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="B109" s="31"/>
-      <c r="C109" s="20" t="s">
-        <v>141</v>
+        <v>138</v>
+      </c>
+      <c r="B109" s="32"/>
+      <c r="C109" s="21" t="s">
+        <v>139</v>
       </c>
       <c r="D109" s="12"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B110" s="17"/>
-      <c r="C110" s="20" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="B110" s="18"/>
+      <c r="C110" s="21" t="s">
+        <v>141</v>
       </c>
       <c r="D110" s="12"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B111" s="22">
+        <v>142</v>
+      </c>
+      <c r="B111" s="23">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
-      <c r="C111" s="20" t="s">
-        <v>145</v>
+      <c r="C111" s="21" t="s">
+        <v>143</v>
       </c>
       <c r="D111" s="12"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B112" s="31">
+        <v>144</v>
+      </c>
+      <c r="B112" s="32">
         <v>6.5</v>
       </c>
-      <c r="C112" s="20" t="s">
-        <v>147</v>
+      <c r="C112" s="21" t="s">
+        <v>145</v>
       </c>
       <c r="D112" s="12"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B113" s="22">
+        <v>146</v>
+      </c>
+      <c r="B113" s="23">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
-      <c r="C113" s="20" t="s">
-        <v>149</v>
+      <c r="C113" s="21" t="s">
+        <v>147</v>
       </c>
       <c r="D113" s="12"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B114" s="22">
+        <v>148</v>
+      </c>
+      <c r="B114" s="23">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C114" s="20" t="s">
-        <v>151</v>
+      <c r="C114" s="21" t="s">
+        <v>149</v>
       </c>
       <c r="D114" s="12"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B115" s="22">
+        <v>150</v>
+      </c>
+      <c r="B115" s="23">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C115" s="20" t="s">
-        <v>153</v>
+      <c r="C115" s="21" t="s">
+        <v>151</v>
       </c>
       <c r="D115" s="12"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B116" s="30">
+        <v>152</v>
+      </c>
+      <c r="B116" s="31">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C116" s="20" t="s">
-        <v>155</v>
+      <c r="C116" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="D116" s="12"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
     <row r="118" spans="1:8" ht="20" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3659,95 +3684,95 @@
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="B119" s="33"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="33"/>
-      <c r="E119" s="33"/>
-      <c r="F119" s="33"/>
-      <c r="G119" s="33"/>
-      <c r="H119" s="33"/>
+      <c r="A119" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B119" s="34"/>
+      <c r="C119" s="34"/>
+      <c r="D119" s="34"/>
+      <c r="E119" s="34"/>
+      <c r="F119" s="34"/>
+      <c r="G119" s="34"/>
+      <c r="H119" s="34"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B121" s="17"/>
-      <c r="C121" s="20" t="s">
-        <v>160</v>
+        <v>157</v>
+      </c>
+      <c r="B121" s="18"/>
+      <c r="C121" s="21" t="s">
+        <v>158</v>
       </c>
       <c r="D121" s="12"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B122" s="31">
+        <v>159</v>
+      </c>
+      <c r="B122" s="32">
         <v>8</v>
       </c>
-      <c r="C122" s="20" t="s">
-        <v>162</v>
+      <c r="C122" s="21" t="s">
+        <v>160</v>
       </c>
       <c r="D122" s="12"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B123" s="31">
+        <v>161</v>
+      </c>
+      <c r="B123" s="32">
         <v>2</v>
       </c>
-      <c r="C123" s="20" t="s">
-        <v>164</v>
+      <c r="C123" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="D123" s="12"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B124" s="34">
+        <v>163</v>
+      </c>
+      <c r="B124" s="35">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
-      <c r="C124" s="20" t="s">
-        <v>166</v>
+      <c r="C124" s="21" t="s">
+        <v>164</v>
       </c>
       <c r="D124" s="12"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B125" s="30">
+        <v>165</v>
+      </c>
+      <c r="B125" s="31">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C125" s="20" t="s">
-        <v>155</v>
+      <c r="C125" s="21" t="s">
+        <v>153</v>
       </c>
       <c r="D125" s="12"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
     <row r="128" spans="1:8" ht="20" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3759,87 +3784,87 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B130" s="6"/>
-      <c r="C130" s="20" t="s">
-        <v>171</v>
+      <c r="C130" s="21" t="s">
+        <v>169</v>
       </c>
       <c r="D130" s="12"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B131" s="22">
+        <v>170</v>
+      </c>
+      <c r="B131" s="23">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
-      <c r="C131" s="20" t="s">
-        <v>173</v>
+      <c r="C131" s="21" t="s">
+        <v>171</v>
       </c>
       <c r="D131" s="12"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B132" s="6"/>
-      <c r="C132" s="20" t="s">
-        <v>175</v>
+      <c r="C132" s="21" t="s">
+        <v>173</v>
       </c>
       <c r="D132" s="12"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B133" s="22">
+        <v>174</v>
+      </c>
+      <c r="B133" s="23">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
-      <c r="C133" s="20" t="s">
-        <v>177</v>
+      <c r="C133" s="21" t="s">
+        <v>175</v>
       </c>
       <c r="D133" s="12"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B134" s="22">
+        <v>176</v>
+      </c>
+      <c r="B134" s="23">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
-      <c r="C134" s="20" t="s">
-        <v>179</v>
+      <c r="C134" s="21" t="s">
+        <v>177</v>
       </c>
       <c r="D134" s="12"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B135" s="24">
+        <v>178</v>
+      </c>
+      <c r="B135" s="25">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
-      <c r="C135" s="20" t="s">
-        <v>181</v>
+      <c r="C135" s="21" t="s">
+        <v>179</v>
       </c>
       <c r="D135" s="10">
         <f>IFERROR(IF(B135&gt;=2,"Bon (&gt;= 2:1)",IF(B135&gt;=1,"Acceptable (1:1)","Mauvais")),"")</f>
@@ -3849,7 +3874,7 @@
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
     <row r="137" spans="1:8" ht="20" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3860,38 +3885,38 @@
       <c r="H137" s="3"/>
     </row>
     <row r="138" spans="1:8" ht="40" customHeight="1">
-      <c r="A138" s="26"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
-      <c r="D138" s="26"/>
-      <c r="E138" s="26"/>
-      <c r="F138" s="26"/>
-      <c r="G138" s="26"/>
-      <c r="H138" s="26"/>
+      <c r="A138" s="27"/>
+      <c r="B138" s="27"/>
+      <c r="C138" s="27"/>
+      <c r="D138" s="27"/>
+      <c r="E138" s="27"/>
+      <c r="F138" s="27"/>
+      <c r="G138" s="27"/>
+      <c r="H138" s="27"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="26"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
-      <c r="D139" s="26"/>
-      <c r="E139" s="26"/>
-      <c r="F139" s="26"/>
-      <c r="G139" s="26"/>
-      <c r="H139" s="26"/>
+      <c r="A139" s="27"/>
+      <c r="B139" s="27"/>
+      <c r="C139" s="27"/>
+      <c r="D139" s="27"/>
+      <c r="E139" s="27"/>
+      <c r="F139" s="27"/>
+      <c r="G139" s="27"/>
+      <c r="H139" s="27"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="26"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
-      <c r="D140" s="26"/>
-      <c r="E140" s="26"/>
-      <c r="F140" s="26"/>
-      <c r="G140" s="26"/>
-      <c r="H140" s="26"/>
+      <c r="A140" s="27"/>
+      <c r="B140" s="27"/>
+      <c r="C140" s="27"/>
+      <c r="D140" s="27"/>
+      <c r="E140" s="27"/>
+      <c r="F140" s="27"/>
+      <c r="G140" s="27"/>
+      <c r="H140" s="27"/>
     </row>
     <row r="141" spans="1:8" ht="26" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -3904,7 +3929,7 @@
     <row r="143" spans="1:8" ht="5" customHeight="1"/>
     <row r="144" spans="1:8" ht="20" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -3915,37 +3940,37 @@
       <c r="H144" s="3"/>
     </row>
     <row r="145" spans="1:8" ht="30" customHeight="1">
-      <c r="A145" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="B145" s="35"/>
-      <c r="C145" s="35"/>
-      <c r="D145" s="35"/>
-      <c r="E145" s="35"/>
-      <c r="F145" s="35"/>
-      <c r="G145" s="35"/>
-      <c r="H145" s="35"/>
+      <c r="A145" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="B145" s="36"/>
+      <c r="C145" s="36"/>
+      <c r="D145" s="36"/>
+      <c r="E145" s="36"/>
+      <c r="F145" s="36"/>
+      <c r="G145" s="36"/>
+      <c r="H145" s="36"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B146" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D146" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="E146" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="D146" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="E146" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B147" s="9">
         <f>B12</f>
@@ -3963,7 +3988,7 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B148" s="9">
         <f>C12</f>
@@ -3981,7 +4006,7 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B149" s="9">
         <f>D12</f>
@@ -3999,7 +4024,7 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B150" s="9">
         <f>E12</f>
@@ -4017,7 +4042,7 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B151" s="9">
         <f>F12</f>
@@ -4036,14 +4061,14 @@
     <row r="152" spans="1:8" ht="5" customHeight="1"/>
     <row r="153" spans="1:8">
       <c r="A153" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B153" s="16">
         <f>IFERROR(D151*1000000/B28,"")</f>
         <v>0</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D153" s="7">
         <f>IFERROR(B24/B153,"")</f>
@@ -4056,7 +4081,7 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B154" s="10">
         <f>IFERROR(IF(C151&lt;0,"Mauvais resultat PONCTUEL — RN recurrent &gt; RN publie — opportunite contrarian potentielle",IF(C151&gt;0,"Resultat FLATTE par elements exceptionnels — prudence sur la valorisation","Pas d'element exceptionnel detecte — RN publie = RN recurrent")),"-")</f>
@@ -4066,7 +4091,7 @@
     <row r="155" spans="1:8" ht="5" customHeight="1"/>
     <row r="156" spans="1:8" ht="20" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4078,30 +4103,31 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B158" s="36">
-        <v>12</v>
+        <v>194</v>
+      </c>
+      <c r="B158" s="7">
+        <f>IFERROR(CHOOSE(MATCH(PROFIL!B5,{"Banque","Assurance","Industrie","Distribution","Telecom","Autre"},0),10,12,13,14,8,12),12)</f>
+        <v>0</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D158" s="14"/>
       <c r="E158" s="14"/>
@@ -4110,13 +4136,13 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B159" s="36">
+        <v>196</v>
+      </c>
+      <c r="B159" s="37">
         <v>5</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D159" s="14"/>
       <c r="E159" s="14"/>
@@ -4126,13 +4152,13 @@
     <row r="160" spans="1:8" ht="5" customHeight="1"/>
     <row r="161" spans="1:8">
       <c r="A161" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B161" s="7">
         <f>IFERROR(B30,"")</f>
         <v>0</v>
       </c>
-      <c r="C161" s="21">
+      <c r="C161" s="22">
         <f>B158</f>
         <v>0</v>
       </c>
@@ -4147,29 +4173,29 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B162" s="7">
-        <f>IFERROR(AVERAGE(F38:F42),"")</f>
-        <v>0</v>
-      </c>
-      <c r="C162" s="21">
+        <f>IFERROR(AVERAGE(E39:E43),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C162" s="22">
         <f>B159</f>
         <v>0</v>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR((AVERAGE(F38:F42)/B159-1)*100,"")</f>
+        <f>IFERROR((AVERAGE(E39:E43)/B159-1)*100,"")</f>
         <v>0</v>
       </c>
       <c r="E162" s="10">
-        <f>IFERROR(IF(AVERAGE(F38:F42)&gt;=B159*1.2,"Rendement superieur au marche — attractif",IF(AVERAGE(F38:F42)&gt;=B159,"Dans la moyenne du marche","Rendement inferieur au marche")),"-")</f>
+        <f>IFERROR(IF(AVERAGE(E39:E43)&gt;=B159*1.2,"Rendement superieur au marche — attractif",IF(AVERAGE(E39:E43)&gt;=B159,"Dans la moyenne du marche","Rendement inferieur au marche")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="5" customHeight="1"/>
     <row r="164" spans="1:8" ht="20" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -4181,57 +4207,57 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B166" s="37">
-        <f>COUNTIF(B38:B42,"&gt;0")</f>
+        <v>202</v>
+      </c>
+      <c r="B166" s="38">
+        <f>COUNTIF(B39:B43,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="C166" s="10">
         <f>IFERROR(IF(B166=5,"Regulier 5/5 — fiable",IF(B166&gt;=4,"Quasi-regulier 4/5",IF(B166&gt;=3,"Irregulier 3/5","Tres irregulier — risque dividende"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D166" s="37">
+      <c r="D166" s="38">
         <f>IF(B166=5,2,IF(B166&gt;=4,1,0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B167" s="8">
-        <f>IFERROR(IF(OR(B38&lt;=0,B42&lt;=0),"N/A",(B42/B38)^(1/4)-1),"N/A")</f>
+        <f>IFERROR(IF(OR(B39&lt;=0,B43&lt;=0),"N/A",(B43/B39)^(1/4)-1),"N/A")</f>
         <v>0</v>
       </c>
       <c r="C167" s="10">
         <f>IFERROR(IF(NOT(ISNUMBER(B167)),"Dividende absent",IF(B167&gt;0.05,"Forte croissance dividende",IF(B167&gt;0,"Croissance modeste","Dividende en baisse"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D167" s="37">
+      <c r="D167" s="38">
         <f>IFERROR(IF(ISNUMBER(B167),IF(B167&gt;0,1,0),0),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B168" s="38">
+      <c r="A168" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="B168" s="39">
         <f>IFERROR(D166+D167,0)</f>
         <v>0</v>
       </c>
@@ -4239,14 +4265,14 @@
         <f>IFERROR(IF(D166+D167&gt;=3,"Dividende tres fiable",IF(D166+D167&gt;=2,"Dividende assez fiable","Dividende peu fiable — risque")),"-")</f>
         <v>0</v>
       </c>
-      <c r="D168" s="20" t="s">
-        <v>207</v>
+      <c r="D168" s="21" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="5" customHeight="1"/>
     <row r="170" spans="1:8" ht="20" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -4258,21 +4284,21 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B172" s="10">
         <f>IFERROR(IF(B30&lt;B158,"OUI","NON"),"-")</f>
@@ -4282,14 +4308,14 @@
         <f>IFERROR("PER="&amp;ROUND(B30,1)&amp;" vs sectoriel="&amp;B158,"-")</f>
         <v>0</v>
       </c>
-      <c r="D172" s="37">
+      <c r="D172" s="38">
         <f>IFERROR(IF(B30&lt;B158*0.85,2,IF(B30&lt;B158,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B173" s="10">
         <f>IFERROR(IF(B24&lt;B31,"OUI — decote comptable","NON"),"-")</f>
@@ -4299,14 +4325,14 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs VMC="&amp;ROUND(B31,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D173" s="37">
+      <c r="D173" s="38">
         <f>IFERROR(IF(B24&lt;B31*0.85,2,IF(B24&lt;B31,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B174" s="10">
         <f>IFERROR(IF(B33&gt;=10,"OUI","NON"),"-")</f>
@@ -4316,14 +4342,14 @@
         <f>IFERROR("ROE="&amp;ROUND(B33,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D174" s="37">
+      <c r="D174" s="38">
         <f>IFERROR(IF(B33&gt;=15,2,IF(B33&gt;=10,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B175" s="10">
         <f>IFERROR(IF(B168&gt;=2,"OUI","NON"),"-")</f>
@@ -4333,14 +4359,14 @@
         <f>IFERROR(C168,"-")</f>
         <v>0</v>
       </c>
-      <c r="D175" s="37">
+      <c r="D175" s="38">
         <f>IFERROR(MIN(B168,2),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B176" s="10">
         <f>IFERROR(IF(B24&lt;D95,"OUI — survente","NON"),"-")</f>
@@ -4350,14 +4376,14 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs PM1an="&amp;ROUND(D95,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D176" s="37">
+      <c r="D176" s="38">
         <f>IFERROR(IF(B24&lt;D95,1,0),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B177" s="10">
         <f>IFERROR(IF(G16&gt;=5,"OUI","NON"),"-")</f>
@@ -4367,43 +4393,43 @@
         <f>IFERROR("Marge moy="&amp;ROUND(G16,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D177" s="37">
+      <c r="D177" s="38">
         <f>IFERROR(IF(G16&gt;=10,2,IF(G16&gt;=5,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="18" t="s">
+      <c r="A178" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="B178" s="12"/>
+      <c r="C178" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D178" s="40">
+        <f>IFERROR(SUM(D172:D177),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="30" customHeight="1">
+      <c r="A179" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="B178" s="12"/>
-      <c r="C178" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="D178" s="39">
-        <f>IFERROR(SUM(D172:D177),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" ht="30" customHeight="1">
-      <c r="A179" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="B179" s="40"/>
-      <c r="C179" s="40"/>
-      <c r="D179" s="40"/>
-      <c r="E179" s="41">
+      <c r="B179" s="41"/>
+      <c r="C179" s="41"/>
+      <c r="D179" s="41"/>
+      <c r="E179" s="42">
         <f>IFERROR(IF(D178&gt;=7,"FORTE OPPORTUNITE CONTRARIAN — fondamentaux sains, titre boude",IF(D178&gt;=5,"A SURVEILLER — signaux contrarians partiels","PAS DE SIGNAL CONTRARIAN — attendre")),"-")</f>
         <v>0</v>
       </c>
-      <c r="F179" s="41"/>
-      <c r="G179" s="41"/>
-      <c r="H179" s="41"/>
+      <c r="F179" s="42"/>
+      <c r="G179" s="42"/>
+      <c r="H179" s="42"/>
     </row>
     <row r="180" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -4417,6 +4443,7 @@
     <mergeCell ref="C27:G27"/>
     <mergeCell ref="C28:G28"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A54:H54"/>
     <mergeCell ref="A61:H61"/>
@@ -4514,7 +4541,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4522,18 +4549,19 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
-      <c r="A2" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="A2" s="2">
+        <f>IFERROR(PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;TEXT(ETUDE!B24,"#,##0")&amp;" FCFA  |  Date : "&amp;PROFIL!B6,"Completer le PROFIL")</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
       <c r="A4" s="43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -4542,31 +4570,31 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B6" s="44">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D6" s="45">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
@@ -4576,14 +4604,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B7" s="44">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D7" s="45">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
@@ -4593,14 +4621,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B8" s="44">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D8" s="45">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
@@ -4610,14 +4638,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B9" s="44">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D9" s="45">
         <f>IFERROR(ETUDE!D30,"-")</f>
@@ -4627,14 +4655,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B10" s="44">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" s="45">
         <f>IFERROR(ETUDE!D32,"-")</f>
@@ -4644,14 +4672,14 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B11" s="44">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D11" s="45">
         <f>IFERROR(ETUDE!D33,"-")</f>
@@ -4661,31 +4689,31 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B12" s="44">
-        <f>IFERROR(AVERAGE(ETUDE!F38:ETUDE!F42),"")</f>
+        <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D12" s="45">
-        <f>IFERROR(IF(AVERAGE(ETUDE!F38:ETUDE!F42)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
+        <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
       <c r="E12" s="46"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B13" s="44">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D13" s="45">
         <f>IFERROR(ETUDE!D34,"-")</f>
@@ -4694,8 +4722,8 @@
       <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="18" t="s">
-        <v>242</v>
+      <c r="A14" s="19" t="s">
+        <v>239</v>
       </c>
       <c r="B14" s="47"/>
       <c r="C14" s="47"/>
@@ -4708,7 +4736,7 @@
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="43" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B16" s="43"/>
       <c r="C16" s="43"/>
@@ -4717,31 +4745,31 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>209</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B18" s="49">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D18" s="45">
         <f>IFERROR(ETUDE!E91,"-")</f>
@@ -4751,14 +4779,14 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B19" s="49">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D19" s="45">
         <f>IFERROR(ETUDE!E96,"-")</f>
@@ -4768,14 +4796,14 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B20" s="49">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D20" s="45">
         <f>IFERROR(ETUDE!D104,"-")</f>
@@ -4785,14 +4813,14 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B21" s="49">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D21" s="45">
         <f>IFERROR(ETUDE!B125,"-")</f>
@@ -4802,14 +4830,14 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B22" s="49">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D22" s="45">
         <f>IFERROR(ETUDE!D135,"-")</f>
@@ -4818,8 +4846,8 @@
       <c r="E22" s="46"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="18" t="s">
-        <v>255</v>
+      <c r="A23" s="19" t="s">
+        <v>252</v>
       </c>
       <c r="B23" s="47"/>
       <c r="C23" s="47"/>
@@ -4832,7 +4860,7 @@
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="50" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B25" s="50"/>
       <c r="C25" s="50"/>
@@ -4841,24 +4869,24 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B27" s="51">
         <f>E14</f>
@@ -4878,7 +4906,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B28" s="51">
         <f>E23</f>
@@ -4897,8 +4925,8 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="18" t="s">
-        <v>262</v>
+      <c r="A29" s="19" t="s">
+        <v>259</v>
       </c>
       <c r="B29" s="55">
         <f>IFERROR(E14+E23,"")</f>
@@ -4919,7 +4947,7 @@
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="43" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B31" s="43"/>
       <c r="C31" s="43"/>
@@ -4928,19 +4956,19 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
@@ -4968,7 +4996,7 @@
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
       <c r="A35" s="43" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B35" s="43"/>
       <c r="C35" s="43"/>
@@ -4976,39 +5004,39 @@
       <c r="E35" s="43"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
+      <c r="A36" s="27"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
+      <c r="A37" s="27"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
+      <c r="A39" s="27"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
+      <c r="A40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -5125,7 +5153,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -5136,180 +5164,186 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="18" customHeight="1">
-      <c r="A2" s="43" t="s">
+    <row r="2" spans="1:4" ht="20" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4" ht="22" customHeight="1">
+      <c r="A3" s="62" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="63"/>
+    </row>
+    <row r="4" spans="1:4" ht="22" customHeight="1">
+      <c r="A4" s="62" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="5" t="s">
+      <c r="B4" s="63"/>
+      <c r="C4" s="64" t="s">
         <v>271</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
+      <c r="D4" s="63"/>
+    </row>
+    <row r="5" spans="1:4" ht="22" customHeight="1">
+      <c r="A5" s="62" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="64" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
+      <c r="D5" s="63"/>
+    </row>
+    <row r="6" spans="1:4" ht="22" customHeight="1">
+      <c r="A6" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="63"/>
+      <c r="C6" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-    </row>
-    <row r="8" spans="1:4" ht="5" customHeight="1"/>
-    <row r="9" spans="1:4" ht="18" customHeight="1">
-      <c r="A9" s="43" t="s">
+      <c r="D6" s="63"/>
+    </row>
+    <row r="7" spans="1:4" ht="8" customHeight="1"/>
+    <row r="8" spans="1:4" ht="20" customHeight="1">
+      <c r="A8" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B9" s="65"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+        <v>270</v>
+      </c>
+      <c r="B10" s="65"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
-    <row r="15" spans="1:4" ht="18" customHeight="1">
-      <c r="A15" s="43" t="s">
+    <row r="15" spans="1:4" ht="20" customHeight="1">
+      <c r="A15" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="B16" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+        <v>283</v>
+      </c>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+        <v>284</v>
+      </c>
+      <c r="B18" s="65"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="66"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+        <v>285</v>
+      </c>
+      <c r="B19" s="65"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
-    <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="43" t="s">
-        <v>289</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
+    <row r="21" spans="1:4" ht="20" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+        <v>287</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+        <v>289</v>
+      </c>
+      <c r="B23" s="65"/>
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
@@ -5318,66 +5352,114 @@
       <c r="B25" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
-    <row r="27" spans="1:4" ht="18" customHeight="1">
-      <c r="A27" s="43" t="s">
+    <row r="27" spans="1:4" ht="20" customHeight="1">
+      <c r="A27" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+        <v>72</v>
+      </c>
+      <c r="B28" s="65"/>
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+        <v>295</v>
+      </c>
+      <c r="B29" s="65"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+        <v>296</v>
+      </c>
+      <c r="B30" s="65"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+    </row>
+    <row r="32" spans="1:4" ht="5" customHeight="1"/>
+    <row r="33" spans="1:4" ht="20" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B34" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-    </row>
-    <row r="32" spans="1:4" ht="5" customHeight="1"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="66"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B35" s="65"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="66"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="C36" s="66"/>
+      <c r="D36" s="66"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+    </row>
+    <row r="38" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="6">
+  <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5399,322 +5481,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>303</v>
-      </c>
-      <c r="C2" s="62" t="s">
-        <v>304</v>
-      </c>
-      <c r="D2" s="62" t="s">
-        <v>305</v>
+      <c r="A2" s="67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" s="67" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="43" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B3" s="43"/>
       <c r="C3" s="43"/>
       <c r="D3" s="43"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
-      <c r="A4" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="B4" s="63" t="s">
-        <v>308</v>
+      <c r="A4" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>313</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>310</v>
+        <v>314</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
-      <c r="A5" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>312</v>
+      <c r="A5" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>317</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D5" s="64" t="s">
-        <v>313</v>
+        <v>314</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="63" t="s">
-        <v>315</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D6" s="64" t="s">
-        <v>316</v>
+      <c r="D6" s="69" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
-      <c r="A7" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>317</v>
+      <c r="A7" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="68" t="s">
+        <v>322</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>318</v>
-      </c>
-      <c r="D7" s="64" t="s">
-        <v>319</v>
+        <v>323</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
-      <c r="A8" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>321</v>
+      <c r="A8" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>326</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" s="64" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28" customHeight="1">
+      <c r="A9" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="68" t="s">
+        <v>329</v>
+      </c>
+      <c r="C9" s="52" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="28" customHeight="1">
-      <c r="A9" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>324</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>318</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>325</v>
+      <c r="D9" s="69" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
-      <c r="A10" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>327</v>
+      <c r="A10" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>332</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>328</v>
+        <v>314</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
-      <c r="A11" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>330</v>
+      <c r="A11" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B11" s="68" t="s">
+        <v>335</v>
       </c>
       <c r="C11" s="52"/>
-      <c r="D11" s="64" t="s">
-        <v>331</v>
+      <c r="D11" s="69" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
-      <c r="A12" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B12" s="63" t="s">
-        <v>333</v>
+      <c r="A12" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>338</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D12" s="64" t="s">
-        <v>334</v>
+        <v>314</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
-      <c r="A13" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="B13" s="63" t="s">
-        <v>336</v>
+      <c r="A13" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B13" s="68" t="s">
+        <v>341</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>309</v>
-      </c>
-      <c r="D13" s="64" t="s">
-        <v>337</v>
+        <v>314</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="43" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B14" s="43"/>
       <c r="C14" s="43"/>
       <c r="D14" s="43"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
-      <c r="A15" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="B15" s="63" t="s">
-        <v>340</v>
+      <c r="A15" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B15" s="68" t="s">
+        <v>345</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D15" s="64" t="s">
-        <v>341</v>
+        <v>327</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
-      <c r="A16" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="B16" s="63" t="s">
-        <v>343</v>
+      <c r="A16" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>348</v>
       </c>
       <c r="C16" s="52"/>
-      <c r="D16" s="64" t="s">
-        <v>344</v>
+      <c r="D16" s="69" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
-      <c r="A17" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="63" t="s">
-        <v>343</v>
+      <c r="A17" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="68" t="s">
+        <v>348</v>
       </c>
       <c r="C17" s="52"/>
-      <c r="D17" s="64" t="s">
-        <v>345</v>
+      <c r="D17" s="69" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
-      <c r="A18" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="63" t="s">
-        <v>346</v>
+      <c r="A18" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>351</v>
       </c>
       <c r="C18" s="52" t="s">
-        <v>318</v>
-      </c>
-      <c r="D18" s="64" t="s">
-        <v>347</v>
+        <v>323</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
-      <c r="A19" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="B19" s="63" t="s">
-        <v>349</v>
+      <c r="A19" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" s="68" t="s">
+        <v>354</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D19" s="64" t="s">
-        <v>350</v>
+        <v>327</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
-      <c r="A20" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>352</v>
+      <c r="A20" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>357</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>353</v>
+        <v>327</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="43" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="B21" s="43"/>
       <c r="C21" s="43"/>
       <c r="D21" s="43"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
-      <c r="A22" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="B22" s="63" t="s">
-        <v>356</v>
+      <c r="A22" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="B22" s="68" t="s">
+        <v>361</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D22" s="64" t="s">
-        <v>357</v>
+        <v>327</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
-      <c r="A23" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="B23" s="63" t="s">
-        <v>359</v>
+      <c r="A23" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" s="68" t="s">
+        <v>364</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>360</v>
-      </c>
-      <c r="D23" s="64" t="s">
-        <v>361</v>
+        <v>365</v>
+      </c>
+      <c r="D23" s="69" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
-      <c r="A24" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="B24" s="63" t="s">
-        <v>363</v>
+      <c r="A24" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B24" s="68" t="s">
+        <v>368</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D24" s="64" t="s">
-        <v>364</v>
+        <v>327</v>
+      </c>
+      <c r="D24" s="69" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
-      <c r="A25" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>366</v>
+      <c r="A25" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="B25" s="68" t="s">
+        <v>371</v>
       </c>
       <c r="C25" s="52" t="s">
-        <v>322</v>
-      </c>
-      <c r="D25" s="64" t="s">
-        <v>367</v>
+        <v>327</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="380">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -127,7 +127,7 @@
     <t>Nombre de titres en circulation</t>
   </si>
   <si>
-    <t>&lt;-- BRVM.org</t>
+    <t>&lt;-- Auto depuis PROFIL onglet (Capital &amp; Actionnariat)</t>
   </si>
   <si>
     <t>PER — Price Earning Ratio  [= Prix / BNPA]</t>
@@ -676,6 +676,54 @@
     <t>VERDICT CONTRARIAN</t>
   </si>
   <si>
+    <t>D — DONNEES SOCIETE  (auto depuis onglet PROFIL — saisir dans PROFIL uniquement)</t>
+  </si>
+  <si>
+    <t>D1 — CAPITAL &amp; ACTIONNARIAT</t>
+  </si>
+  <si>
+    <t>Champ</t>
+  </si>
+  <si>
+    <t>Valeur (auto depuis PROFIL)</t>
+  </si>
+  <si>
+    <t>Capital social (FCFA)</t>
+  </si>
+  <si>
+    <t>Flottant (%)</t>
+  </si>
+  <si>
+    <t>Principaux actionnaires</t>
+  </si>
+  <si>
+    <t>D2 — LIQUIDITE DU TITRE  (critique sur BRVM)</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (titres)</t>
+  </si>
+  <si>
+    <t>Volume moyen journalier (FCFA)</t>
+  </si>
+  <si>
+    <t>Frequence de cotation (%)</t>
+  </si>
+  <si>
+    <t>Appreciation liquidite</t>
+  </si>
+  <si>
+    <t>D3 — NOTATION &amp; CONFORMITE</t>
+  </si>
+  <si>
+    <t>Note court terme</t>
+  </si>
+  <si>
+    <t>Note long terme</t>
+  </si>
+  <si>
+    <t>Dividende verse regulierement ?</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -853,6 +901,9 @@
     <t>Nom complet</t>
   </si>
   <si>
+    <t>&lt;-- Auto depuis cellules cles ci-dessus</t>
+  </si>
+  <si>
     <t>Secteur d'activite</t>
   </si>
   <si>
@@ -865,52 +916,22 @@
     <t>CAPITAL &amp; ACTIONNARIAT</t>
   </si>
   <si>
-    <t>Capital social (FCFA)</t>
-  </si>
-  <si>
     <t>Nombre de titres</t>
   </si>
   <si>
-    <t>Flottant (%)</t>
-  </si>
-  <si>
-    <t>Principaux actionnaires</t>
-  </si>
-  <si>
     <t>LIQUIDITE DU TITRE (critique sur BRVM)</t>
   </si>
   <si>
-    <t>Volume moyen journalier (titres)</t>
-  </si>
-  <si>
     <t>&lt;-- Source : BRVM.org</t>
   </si>
   <si>
-    <t>Volume moyen journalier (FCFA)</t>
-  </si>
-  <si>
-    <t>Frequence de cotation (%)</t>
-  </si>
-  <si>
     <t>&lt;-- % seances avec transaction</t>
   </si>
   <si>
-    <t>Appreciation liquidite</t>
-  </si>
-  <si>
     <t>&lt;-- Forte / Moyenne / Faible</t>
   </si>
   <si>
     <t>NOTATION &amp; CONFORMITE</t>
-  </si>
-  <si>
-    <t>Note court terme</t>
-  </si>
-  <si>
-    <t>Note long terme</t>
-  </si>
-  <si>
-    <t>Dividende verse regulierement ?</t>
   </si>
   <si>
     <t>&lt;-- Oui / Non</t>
@@ -1548,7 +1569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1685,6 +1706,9 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1754,11 +1778,11 @@
     <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2225,7 +2249,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -2238,7 +2262,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1">
       <c r="A1" s="1">
-        <f>IFERROR("FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"   ("&amp;PROFIL!B4&amp;")   |   "&amp;PROFIL!B5&amp;"   |   "&amp;PROFIL!B6,"FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]")</f>
+        <f>IFERROR("FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"   ("&amp;PROFIL!B4&amp;")   |   "&amp;PROFIL!B5&amp;"   |   "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]")</f>
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -2251,7 +2275,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2">
-        <f>IFERROR("Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date analyse : "&amp;PROFIL!B6,"Completer le PROFIL : nom, ticker, secteur, date")</f>
+        <f>IFERROR("Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date analyse : "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"Completer le PROFIL : nom, ticker, secteur, date")</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -2628,7 +2652,10 @@
       <c r="A28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="13"/>
+      <c r="B28" s="9">
+        <f>IFERROR(PROFIL!B17,"")</f>
+        <v>0</v>
+      </c>
       <c r="C28" s="14" t="s">
         <v>36</v>
       </c>
@@ -4427,9 +4454,284 @@
       <c r="H179" s="42"/>
     </row>
     <row r="180" spans="1:8" ht="5" customHeight="1"/>
+    <row r="181" spans="1:8" ht="5" customHeight="1"/>
+    <row r="182" spans="1:8" ht="22" customHeight="1">
+      <c r="A182" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+      <c r="E182" s="1"/>
+      <c r="F182" s="1"/>
+      <c r="G182" s="1"/>
+      <c r="H182" s="1"/>
+    </row>
+    <row r="183" spans="1:8" ht="5" customHeight="1"/>
+    <row r="184" spans="1:8" ht="20" customHeight="1">
+      <c r="A184" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="3"/>
+      <c r="G184" s="3"/>
+      <c r="H184" s="3"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B186" s="9">
+        <f>IFERROR(PROFIL!B16,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C186" s="12"/>
+      <c r="D186" s="12"/>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
+      <c r="G186" s="12"/>
+      <c r="H186" s="12"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B187" s="9">
+        <f>IFERROR(PROFIL!B17,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C187" s="12"/>
+      <c r="D187" s="12"/>
+      <c r="E187" s="12"/>
+      <c r="F187" s="12"/>
+      <c r="G187" s="12"/>
+      <c r="H187" s="12"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B188" s="43">
+        <f>IFERROR(PROFIL!B18,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C188" s="12"/>
+      <c r="D188" s="12"/>
+      <c r="E188" s="12"/>
+      <c r="F188" s="12"/>
+      <c r="G188" s="12"/>
+      <c r="H188" s="12"/>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B189" s="43">
+        <f>IFERROR(PROFIL!B19,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C189" s="12"/>
+      <c r="D189" s="12"/>
+      <c r="E189" s="12"/>
+      <c r="F189" s="12"/>
+      <c r="G189" s="12"/>
+      <c r="H189" s="12"/>
+    </row>
+    <row r="190" spans="1:8" ht="5" customHeight="1"/>
+    <row r="191" spans="1:8" ht="20" customHeight="1">
+      <c r="A191" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C192" s="4"/>
+      <c r="D192" s="4"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="4"/>
+      <c r="G192" s="4"/>
+      <c r="H192" s="4"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B193" s="9">
+        <f>IFERROR(PROFIL!B22,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C193" s="12"/>
+      <c r="D193" s="12"/>
+      <c r="E193" s="12"/>
+      <c r="F193" s="12"/>
+      <c r="G193" s="12"/>
+      <c r="H193" s="12"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B194" s="9">
+        <f>IFERROR(PROFIL!B23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C194" s="12"/>
+      <c r="D194" s="12"/>
+      <c r="E194" s="12"/>
+      <c r="F194" s="12"/>
+      <c r="G194" s="12"/>
+      <c r="H194" s="12"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B195" s="43">
+        <f>IFERROR(PROFIL!B24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C195" s="12"/>
+      <c r="D195" s="12"/>
+      <c r="E195" s="12"/>
+      <c r="F195" s="12"/>
+      <c r="G195" s="12"/>
+      <c r="H195" s="12"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B196" s="43">
+        <f>IFERROR(PROFIL!B25,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C196" s="12"/>
+      <c r="D196" s="12"/>
+      <c r="E196" s="12"/>
+      <c r="F196" s="12"/>
+      <c r="G196" s="12"/>
+      <c r="H196" s="12"/>
+    </row>
+    <row r="197" spans="1:8" ht="5" customHeight="1"/>
+    <row r="198" spans="1:8" ht="20" customHeight="1">
+      <c r="A198" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C199" s="4"/>
+      <c r="D199" s="4"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+      <c r="G199" s="4"/>
+      <c r="H199" s="4"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B200" s="43">
+        <f>IFERROR(PROFIL!B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C200" s="12"/>
+      <c r="D200" s="12"/>
+      <c r="E200" s="12"/>
+      <c r="F200" s="12"/>
+      <c r="G200" s="12"/>
+      <c r="H200" s="12"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B201" s="43">
+        <f>IFERROR(PROFIL!B29,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C201" s="12"/>
+      <c r="D201" s="12"/>
+      <c r="E201" s="12"/>
+      <c r="F201" s="12"/>
+      <c r="G201" s="12"/>
+      <c r="H201" s="12"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B202" s="43">
+        <f>IFERROR(PROFIL!B30,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C202" s="12"/>
+      <c r="D202" s="12"/>
+      <c r="E202" s="12"/>
+      <c r="F202" s="12"/>
+      <c r="G202" s="12"/>
+      <c r="H202" s="12"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B203" s="43">
+        <f>IFERROR(PROFIL!B31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C203" s="12"/>
+      <c r="D203" s="12"/>
+      <c r="E203" s="12"/>
+      <c r="F203" s="12"/>
+      <c r="G203" s="12"/>
+      <c r="H203" s="12"/>
+    </row>
+    <row r="204" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="40">
+  <mergeCells count="44">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -4470,6 +4772,10 @@
     <mergeCell ref="A170:H170"/>
     <mergeCell ref="A179:D179"/>
     <mergeCell ref="E179:H179"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A184:H184"/>
+    <mergeCell ref="A191:H191"/>
+    <mergeCell ref="A198:H198"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -4541,7 +4847,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4550,7 +4856,7 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="2">
-        <f>IFERROR(PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;TEXT(ETUDE!B24,"#,##0")&amp;" FCFA  |  Date : "&amp;PROFIL!B6,"Completer le PROFIL")</f>
+        <f>IFERROR(PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;TEXT(ETUDE!B24,"#,##0")&amp;" FCFA  |  Date : "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"Completer le PROFIL")</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -4560,188 +4866,188 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="43" t="s">
-        <v>220</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
+      <c r="A4" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
         <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="44">
+        <v>241</v>
+      </c>
+      <c r="B6" s="45">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D6" s="45">
+        <v>242</v>
+      </c>
+      <c r="D6" s="46">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="46"/>
+      <c r="E6" s="47"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="44">
+        <v>243</v>
+      </c>
+      <c r="B7" s="45">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D7" s="45">
+        <v>242</v>
+      </c>
+      <c r="D7" s="46">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="46"/>
+      <c r="E7" s="47"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="44">
+        <v>244</v>
+      </c>
+      <c r="B8" s="45">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" s="45">
+        <v>245</v>
+      </c>
+      <c r="D8" s="46">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="46"/>
+      <c r="E8" s="47"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="44">
+        <v>246</v>
+      </c>
+      <c r="B9" s="45">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" s="45">
+        <v>247</v>
+      </c>
+      <c r="D9" s="46">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="46"/>
+      <c r="E9" s="47"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="44">
+        <v>248</v>
+      </c>
+      <c r="B10" s="45">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="D10" s="45">
+        <v>249</v>
+      </c>
+      <c r="D10" s="46">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="46"/>
+      <c r="E10" s="47"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="44">
+        <v>250</v>
+      </c>
+      <c r="B11" s="45">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="45">
+        <v>242</v>
+      </c>
+      <c r="D11" s="46">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="46"/>
+      <c r="E11" s="47"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="44">
+        <v>251</v>
+      </c>
+      <c r="B12" s="45">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="D12" s="45">
+        <v>252</v>
+      </c>
+      <c r="D12" s="46">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="46"/>
+      <c r="E12" s="47"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B13" s="44">
+        <v>253</v>
+      </c>
+      <c r="B13" s="45">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="D13" s="45">
+        <v>254</v>
+      </c>
+      <c r="D13" s="46">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="46"/>
+      <c r="E13" s="47"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="19" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="48">
+        <v>255</v>
+      </c>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="49">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="43" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="A16" s="44" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -4751,7 +5057,7 @@
         <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>17</v>
@@ -4762,110 +5068,110 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" s="49">
+        <v>258</v>
+      </c>
+      <c r="B18" s="50">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="45">
+        <v>259</v>
+      </c>
+      <c r="D18" s="46">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="46"/>
+      <c r="E18" s="47"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B19" s="49">
+        <v>260</v>
+      </c>
+      <c r="B19" s="50">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D19" s="45">
+        <v>261</v>
+      </c>
+      <c r="D19" s="46">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="46"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" s="49">
+        <v>262</v>
+      </c>
+      <c r="B20" s="50">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="D20" s="45">
+        <v>263</v>
+      </c>
+      <c r="D20" s="46">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="46"/>
+      <c r="E20" s="47"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="49">
+        <v>264</v>
+      </c>
+      <c r="B21" s="50">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D21" s="45">
+        <v>265</v>
+      </c>
+      <c r="D21" s="46">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="46"/>
+      <c r="E21" s="47"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B22" s="49">
+        <v>266</v>
+      </c>
+      <c r="B22" s="50">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D22" s="45">
+        <v>267</v>
+      </c>
+      <c r="D22" s="46">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="46"/>
+      <c r="E22" s="47"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="48">
+        <v>268</v>
+      </c>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="49">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
+      <c r="A25" s="51" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -4875,133 +5181,133 @@
         <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B27" s="51">
+        <v>273</v>
+      </c>
+      <c r="B27" s="52">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="53">
         <v>24</v>
       </c>
-      <c r="D27" s="53">
+      <c r="D27" s="54">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="54">
+      <c r="E27" s="55">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="51">
+        <v>274</v>
+      </c>
+      <c r="B28" s="52">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="52">
+      <c r="C28" s="53">
         <v>15</v>
       </c>
-      <c r="D28" s="53">
+      <c r="D28" s="54">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="55">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="B29" s="55">
+        <v>275</v>
+      </c>
+      <c r="B29" s="56">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="57">
         <v>39</v>
       </c>
-      <c r="D29" s="53">
+      <c r="D29" s="54">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="58">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="43" t="s">
-        <v>260</v>
-      </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
+      <c r="A31" s="44" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="58">
+      <c r="A33" s="59">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="59">
+      <c r="B33" s="60">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="60">
+      <c r="C33" s="61">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="60">
+      <c r="D33" s="61">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="61">
+      <c r="E33" s="62">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="43" t="s">
-        <v>265</v>
-      </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
+      <c r="A35" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="B35" s="44"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="44"/>
+      <c r="E35" s="44"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
       <c r="A36" s="27"/>
@@ -5164,7 +5470,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5172,56 +5478,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="62" t="s">
-        <v>268</v>
-      </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64" t="s">
-        <v>269</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="A3" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="62" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="64" t="s">
-        <v>271</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="A4" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="65" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" s="64"/>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="62" t="s">
-        <v>272</v>
-      </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="64" t="s">
-        <v>273</v>
-      </c>
-      <c r="D5" s="63"/>
+      <c r="A5" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="64"/>
+      <c r="C5" s="65" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="64" t="s">
-        <v>275</v>
-      </c>
-      <c r="D6" s="63"/>
+      <c r="A6" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="B6" s="64"/>
+      <c r="C6" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5229,48 +5535,63 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B9" s="65"/>
-      <c r="C9" s="66"/>
+        <v>293</v>
+      </c>
+      <c r="B9" s="43">
+        <f>B3</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>294</v>
+      </c>
       <c r="D9" s="66"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="66"/>
+        <v>286</v>
+      </c>
+      <c r="B10" s="43">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>294</v>
+      </c>
       <c r="D10" s="66"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="66"/>
+        <v>295</v>
+      </c>
+      <c r="B11" s="43">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>294</v>
+      </c>
       <c r="D11" s="66"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B12" s="65"/>
+        <v>296</v>
+      </c>
+      <c r="B12" s="67"/>
       <c r="C12" s="66"/>
       <c r="D12" s="66"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B13" s="65"/>
+        <v>297</v>
+      </c>
+      <c r="B13" s="67"/>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5278,40 +5599,40 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" s="65"/>
+        <v>223</v>
+      </c>
+      <c r="B16" s="67"/>
       <c r="C16" s="66"/>
       <c r="D16" s="66"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" s="65"/>
+        <v>299</v>
+      </c>
+      <c r="B17" s="67"/>
       <c r="C17" s="66"/>
       <c r="D17" s="66"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B18" s="65"/>
+        <v>224</v>
+      </c>
+      <c r="B18" s="67"/>
       <c r="C18" s="66"/>
       <c r="D18" s="66"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B19" s="65"/>
+        <v>225</v>
+      </c>
+      <c r="B19" s="67"/>
       <c r="C19" s="66"/>
       <c r="D19" s="66"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5319,38 +5640,38 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="5" t="s">
-        <v>287</v>
+        <v>227</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C22" s="66"/>
       <c r="D22" s="66"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B23" s="65"/>
+        <v>228</v>
+      </c>
+      <c r="B23" s="67"/>
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
-        <v>292</v>
+        <v>230</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C25" s="66"/>
       <c r="D25" s="66"/>
@@ -5358,7 +5679,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -5368,32 +5689,32 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="65"/>
+      <c r="B28" s="67"/>
       <c r="C28" s="66"/>
       <c r="D28" s="66"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="B29" s="65"/>
+        <v>232</v>
+      </c>
+      <c r="B29" s="67"/>
       <c r="C29" s="66"/>
       <c r="D29" s="66"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B30" s="65"/>
+        <v>233</v>
+      </c>
+      <c r="B30" s="67"/>
       <c r="C30" s="66"/>
       <c r="D30" s="66"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C31" s="66"/>
       <c r="D31" s="66"/>
@@ -5401,7 +5722,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5409,38 +5730,38 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C34" s="66"/>
       <c r="D34" s="66"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B35" s="65"/>
+        <v>309</v>
+      </c>
+      <c r="B35" s="67"/>
       <c r="C35" s="66"/>
       <c r="D35" s="66"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C36" s="66"/>
       <c r="D36" s="66"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C37" s="66"/>
       <c r="D37" s="66"/>
@@ -5481,322 +5802,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="67" t="s">
-        <v>308</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>309</v>
-      </c>
-      <c r="D2" s="67" t="s">
-        <v>310</v>
+      <c r="B2" s="68" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>316</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="43" t="s">
-        <v>311</v>
-      </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
+      <c r="A3" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>313</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D4" s="69" t="s">
-        <v>315</v>
+        <v>319</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="70" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D5" s="69" t="s">
-        <v>318</v>
+        <v>323</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>324</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="70" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="B6" s="68" t="s">
-        <v>320</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D6" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="53" t="s">
         <v>321</v>
+      </c>
+      <c r="D6" s="70" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>322</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>324</v>
+        <v>246</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="70" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="B8" s="68" t="s">
-        <v>326</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D8" s="69" t="s">
-        <v>328</v>
+        <v>332</v>
+      </c>
+      <c r="B8" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" s="70" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="68" t="s">
-        <v>329</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>323</v>
-      </c>
-      <c r="D9" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="53" t="s">
         <v>330</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="B10" s="68" t="s">
-        <v>332</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D10" s="69" t="s">
-        <v>333</v>
+        <v>338</v>
+      </c>
+      <c r="B10" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="B11" s="68" t="s">
-        <v>335</v>
-      </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="69" t="s">
-        <v>336</v>
+        <v>341</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="53"/>
+      <c r="D11" s="70" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="B12" s="68" t="s">
-        <v>338</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D12" s="69" t="s">
-        <v>339</v>
+        <v>344</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="70" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="B13" s="68" t="s">
-        <v>341</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>314</v>
-      </c>
-      <c r="D13" s="69" t="s">
-        <v>342</v>
+        <v>347</v>
+      </c>
+      <c r="B13" s="69" t="s">
+        <v>348</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="43" t="s">
-        <v>343</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="A14" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B15" s="68" t="s">
-        <v>345</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D15" s="69" t="s">
-        <v>346</v>
+        <v>351</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="B16" s="68" t="s">
-        <v>348</v>
-      </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="69" t="s">
-        <v>349</v>
+        <v>354</v>
+      </c>
+      <c r="B16" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="C16" s="53"/>
+      <c r="D16" s="70" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="68" t="s">
-        <v>348</v>
-      </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="69" t="s">
-        <v>350</v>
+      <c r="B17" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="C17" s="53"/>
+      <c r="D17" s="70" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="68" t="s">
-        <v>351</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>323</v>
-      </c>
-      <c r="D18" s="69" t="s">
-        <v>352</v>
+      <c r="B18" s="69" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="D18" s="70" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="B19" s="68" t="s">
-        <v>354</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D19" s="69" t="s">
-        <v>355</v>
+        <v>360</v>
+      </c>
+      <c r="B19" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="B20" s="68" t="s">
-        <v>357</v>
-      </c>
-      <c r="C20" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D20" s="69" t="s">
-        <v>358</v>
+        <v>363</v>
+      </c>
+      <c r="B20" s="69" t="s">
+        <v>364</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="70" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="43" t="s">
-        <v>359</v>
-      </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
+      <c r="A21" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="B22" s="68" t="s">
-        <v>361</v>
-      </c>
-      <c r="C22" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D22" s="69" t="s">
-        <v>362</v>
+        <v>367</v>
+      </c>
+      <c r="B22" s="69" t="s">
+        <v>368</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D22" s="70" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="B23" s="68" t="s">
-        <v>364</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>365</v>
-      </c>
-      <c r="D23" s="69" t="s">
-        <v>366</v>
+        <v>370</v>
+      </c>
+      <c r="B23" s="69" t="s">
+        <v>371</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="D23" s="70" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="B24" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="C24" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D24" s="69" t="s">
-        <v>369</v>
+        <v>374</v>
+      </c>
+      <c r="B24" s="69" t="s">
+        <v>375</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D24" s="70" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="B25" s="68" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>327</v>
-      </c>
-      <c r="D25" s="69" t="s">
-        <v>372</v>
+        <v>377</v>
+      </c>
+      <c r="B25" s="69" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>334</v>
+      </c>
+      <c r="D25" s="70" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -5489,40 +5489,40 @@
         <v>284</v>
       </c>
       <c r="B3" s="64"/>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="65" t="s">
         <v>285</v>
       </c>
-      <c r="D3" s="64"/>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
       <c r="A4" s="63" t="s">
         <v>286</v>
       </c>
       <c r="B4" s="64"/>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="64"/>
+      <c r="D4" s="65" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="64"/>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
       <c r="A5" s="63" t="s">
         <v>288</v>
       </c>
       <c r="B5" s="64"/>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="64"/>
+      <c r="D5" s="65" t="s">
         <v>289</v>
       </c>
-      <c r="D5" s="64"/>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
       <c r="A6" s="63" t="s">
         <v>290</v>
       </c>
       <c r="B6" s="64"/>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="64"/>
+      <c r="D6" s="65" t="s">
         <v>291</v>
       </c>
-      <c r="D6" s="64"/>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
@@ -5772,10 +5772,10 @@
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A21:D21"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -4730,7 +4730,6 @@
     </row>
     <row r="204" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="44">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5345,7 +5344,6 @@
       <c r="E40" s="27"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -5768,7 +5766,6 @@
     </row>
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -6121,7 +6118,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1569,22 +1569,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1606,86 +1611,112 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1694,91 +1725,111 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1786,14 +1837,17 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2652,7 +2706,7 @@
       <c r="A28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="16">
         <f>IFERROR(PROFIL!B17,"")</f>
         <v>0</v>
       </c>
@@ -2685,7 +2739,7 @@
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
@@ -2779,21 +2833,21 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="25" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="7">
         <f>IFERROR((B39/0.85)/C39*100,"")</f>
         <v>0</v>
@@ -2808,8 +2862,8 @@
       <c r="A40" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
       <c r="D40" s="7">
         <f>IFERROR((B40/0.85)/C40*100,"")</f>
         <v>0</v>
@@ -2827,8 +2881,8 @@
       <c r="A41" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="7">
         <f>IFERROR((B41/0.85)/C41*100,"")</f>
         <v>0</v>
@@ -2846,8 +2900,8 @@
       <c r="A42" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="7">
         <f>IFERROR((B42/0.85)/C42*100,"")</f>
         <v>0</v>
@@ -2865,8 +2919,8 @@
       <c r="A43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="7">
         <f>IFERROR((B43/0.85)/C43*100,"")</f>
         <v>0</v>
@@ -2881,10 +2935,10 @@
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <f>SUM(B39:B43)</f>
         <v>0</v>
       </c>
@@ -2981,7 +3035,7 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="19" t="s">
+      <c r="A52" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B52" s="9">
@@ -3028,45 +3082,45 @@
       <c r="A56" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="21"/>
+      <c r="D56" s="22"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D57" s="21"/>
+      <c r="D57" s="22"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="21" t="s">
+      <c r="B58" s="21"/>
+      <c r="C58" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="21"/>
+      <c r="D58" s="22"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="21" t="s">
+      <c r="B59" s="21"/>
+      <c r="C59" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="21"/>
+      <c r="D59" s="22"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="20" customHeight="1">
@@ -3098,7 +3152,7 @@
         <v>82</v>
       </c>
       <c r="B63" s="6"/>
-      <c r="C63" s="22"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:8">
@@ -3106,121 +3160,121 @@
         <v>83</v>
       </c>
       <c r="B64" s="6"/>
-      <c r="C64" s="22"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="24">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
-      <c r="C65" s="22"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="24">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C66" s="22"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B67" s="25">
         <f>IFERROR(B24,"")</f>
         <v>0</v>
       </c>
-      <c r="C67" s="22"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B68" s="24">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
-      <c r="C68" s="22"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="24">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C69" s="22"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B70" s="25">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
-      <c r="C70" s="22"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="22"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="12"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B72" s="25">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
-      <c r="C72" s="22"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="19" t="s">
+      <c r="A73" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B73" s="25">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
-      <c r="C73" s="22"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="12"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="19" t="s">
+      <c r="A74" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="26">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
-      <c r="C74" s="22"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="12"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="19" t="s">
+      <c r="A75" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B75" s="26">
+      <c r="B75" s="27">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
@@ -3243,34 +3297,34 @@
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="40" customHeight="1">
-      <c r="A78" s="27"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="27"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="28"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="27"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
+      <c r="A80" s="28"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="28"/>
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
@@ -3321,12 +3375,12 @@
       <c r="B86" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C86" s="22"/>
-      <c r="D86" s="28">
+      <c r="C86" s="23"/>
+      <c r="D86" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="30" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3337,12 +3391,12 @@
       <c r="B87" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C87" s="22"/>
-      <c r="D87" s="28">
+      <c r="C87" s="23"/>
+      <c r="D87" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B87)),1,IF(ISNUMBER(SEARCH("surachat",B87)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="30" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3353,12 +3407,12 @@
       <c r="B88" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C88" s="22"/>
-      <c r="D88" s="28">
+      <c r="C88" s="23"/>
+      <c r="D88" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B88)),1,IF(ISNUMBER(SEARCH("surachat",B88)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="30" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3369,12 +3423,12 @@
       <c r="B89" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C89" s="22"/>
-      <c r="D89" s="28">
+      <c r="C89" s="23"/>
+      <c r="D89" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B89)),1,IF(ISNUMBER(SEARCH("surachat",B89)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="30" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3385,26 +3439,26 @@
       <c r="B90" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C90" s="22"/>
-      <c r="D90" s="28">
+      <c r="C90" s="23"/>
+      <c r="D90" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E90" s="29" t="s">
+      <c r="E90" s="30" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="19" t="s">
+      <c r="A91" s="20" t="s">
         <v>114</v>
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
-      <c r="D91" s="30">
+      <c r="D91" s="31">
         <f>SUM(D86:D90)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="31">
+      <c r="E91" s="32">
         <f>IFERROR(IF(D91&gt;0,"Zone SURVENTE - Achat possible",IF(D91&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v>0</v>
       </c>
@@ -3445,7 +3499,7 @@
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="16">
+      <c r="D95" s="17">
         <f>IFERROR((B95+C95)/2,"")</f>
         <v>0</v>
       </c>
@@ -3460,7 +3514,7 @@
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <f>IFERROR((B96+C96)/2,"")</f>
         <v>0</v>
       </c>
@@ -3500,11 +3554,11 @@
       <c r="A100" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B100" s="24">
+      <c r="B100" s="25">
         <f>B24</f>
         <v>0</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="22" t="s">
         <v>126</v>
       </c>
       <c r="D100" s="12"/>
@@ -3513,11 +3567,11 @@
       <c r="A101" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B101" s="24">
         <f>B25</f>
         <v>0</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" s="22" t="s">
         <v>128</v>
       </c>
       <c r="D101" s="12"/>
@@ -3526,8 +3580,8 @@
       <c r="A102" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B102" s="32"/>
-      <c r="C102" s="21" t="s">
+      <c r="B102" s="33"/>
+      <c r="C102" s="22" t="s">
         <v>130</v>
       </c>
       <c r="D102" s="12"/>
@@ -3536,11 +3590,11 @@
       <c r="A103" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B103" s="24">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
-      <c r="C103" s="21" t="s">
+      <c r="C103" s="22" t="s">
         <v>132</v>
       </c>
       <c r="D103" s="12"/>
@@ -3549,11 +3603,11 @@
       <c r="A104" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B104" s="25">
+      <c r="B104" s="26">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="22" t="s">
         <v>134</v>
       </c>
       <c r="D104" s="10">
@@ -3575,16 +3629,16 @@
       <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
-      <c r="A107" s="33" t="s">
+      <c r="A107" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B107" s="33"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="33"/>
-      <c r="H107" s="33"/>
+      <c r="B107" s="34"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="34"/>
+      <c r="H107" s="34"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
@@ -3604,8 +3658,8 @@
       <c r="A109" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B109" s="32"/>
-      <c r="C109" s="21" t="s">
+      <c r="B109" s="33"/>
+      <c r="C109" s="22" t="s">
         <v>139</v>
       </c>
       <c r="D109" s="12"/>
@@ -3614,8 +3668,8 @@
       <c r="A110" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B110" s="18"/>
-      <c r="C110" s="21" t="s">
+      <c r="B110" s="19"/>
+      <c r="C110" s="22" t="s">
         <v>141</v>
       </c>
       <c r="D110" s="12"/>
@@ -3624,11 +3678,11 @@
       <c r="A111" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B111" s="24">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="22" t="s">
         <v>143</v>
       </c>
       <c r="D111" s="12"/>
@@ -3637,10 +3691,10 @@
       <c r="A112" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B112" s="32">
+      <c r="B112" s="33">
         <v>6.5</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="22" t="s">
         <v>145</v>
       </c>
       <c r="D112" s="12"/>
@@ -3649,11 +3703,11 @@
       <c r="A113" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B113" s="23">
+      <c r="B113" s="24">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="22" t="s">
         <v>147</v>
       </c>
       <c r="D113" s="12"/>
@@ -3662,11 +3716,11 @@
       <c r="A114" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B114" s="23">
+      <c r="B114" s="24">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="22" t="s">
         <v>149</v>
       </c>
       <c r="D114" s="12"/>
@@ -3675,11 +3729,11 @@
       <c r="A115" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B115" s="23">
+      <c r="B115" s="24">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="22" t="s">
         <v>151</v>
       </c>
       <c r="D115" s="12"/>
@@ -3688,11 +3742,11 @@
       <c r="A116" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B116" s="31">
+      <c r="B116" s="32">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D116" s="12"/>
@@ -3711,16 +3765,16 @@
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="34" t="s">
+      <c r="A119" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="B119" s="34"/>
-      <c r="C119" s="34"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="34"/>
-      <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="34"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="35"/>
+      <c r="E119" s="35"/>
+      <c r="F119" s="35"/>
+      <c r="G119" s="35"/>
+      <c r="H119" s="35"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
@@ -3740,8 +3794,8 @@
       <c r="A121" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B121" s="18"/>
-      <c r="C121" s="21" t="s">
+      <c r="B121" s="19"/>
+      <c r="C121" s="22" t="s">
         <v>158</v>
       </c>
       <c r="D121" s="12"/>
@@ -3750,10 +3804,10 @@
       <c r="A122" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B122" s="32">
+      <c r="B122" s="33">
         <v>8</v>
       </c>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="22" t="s">
         <v>160</v>
       </c>
       <c r="D122" s="12"/>
@@ -3762,10 +3816,10 @@
       <c r="A123" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B123" s="32">
+      <c r="B123" s="33">
         <v>2</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" s="22" t="s">
         <v>162</v>
       </c>
       <c r="D123" s="12"/>
@@ -3774,11 +3828,11 @@
       <c r="A124" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B124" s="35">
+      <c r="B124" s="36">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
-      <c r="C124" s="21" t="s">
+      <c r="C124" s="22" t="s">
         <v>164</v>
       </c>
       <c r="D124" s="12"/>
@@ -3787,11 +3841,11 @@
       <c r="A125" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B125" s="31">
+      <c r="B125" s="32">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C125" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D125" s="12"/>
@@ -3828,7 +3882,7 @@
         <v>168</v>
       </c>
       <c r="B130" s="6"/>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="22" t="s">
         <v>169</v>
       </c>
       <c r="D130" s="12"/>
@@ -3837,11 +3891,11 @@
       <c r="A131" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B131" s="23">
+      <c r="B131" s="24">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C131" s="22" t="s">
         <v>171</v>
       </c>
       <c r="D131" s="12"/>
@@ -3851,7 +3905,7 @@
         <v>172</v>
       </c>
       <c r="B132" s="6"/>
-      <c r="C132" s="21" t="s">
+      <c r="C132" s="22" t="s">
         <v>173</v>
       </c>
       <c r="D132" s="12"/>
@@ -3860,11 +3914,11 @@
       <c r="A133" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B133" s="23">
+      <c r="B133" s="24">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C133" s="22" t="s">
         <v>175</v>
       </c>
       <c r="D133" s="12"/>
@@ -3873,11 +3927,11 @@
       <c r="A134" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B134" s="23">
+      <c r="B134" s="24">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C134" s="22" t="s">
         <v>177</v>
       </c>
       <c r="D134" s="12"/>
@@ -3886,11 +3940,11 @@
       <c r="A135" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B135" s="25">
+      <c r="B135" s="26">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C135" s="22" t="s">
         <v>179</v>
       </c>
       <c r="D135" s="10">
@@ -3912,34 +3966,34 @@
       <c r="H137" s="3"/>
     </row>
     <row r="138" spans="1:8" ht="40" customHeight="1">
-      <c r="A138" s="27"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
-      <c r="D138" s="27"/>
-      <c r="E138" s="27"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="27"/>
-      <c r="H138" s="27"/>
+      <c r="A138" s="28"/>
+      <c r="B138" s="28"/>
+      <c r="C138" s="28"/>
+      <c r="D138" s="28"/>
+      <c r="E138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="28"/>
+      <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="27"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="27"/>
-      <c r="H139" s="27"/>
+      <c r="A139" s="28"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="28"/>
+      <c r="D139" s="28"/>
+      <c r="E139" s="28"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="28"/>
+      <c r="H139" s="28"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="27"/>
-      <c r="B140" s="27"/>
-      <c r="C140" s="27"/>
-      <c r="D140" s="27"/>
-      <c r="E140" s="27"/>
-      <c r="F140" s="27"/>
-      <c r="G140" s="27"/>
-      <c r="H140" s="27"/>
+      <c r="A140" s="28"/>
+      <c r="B140" s="28"/>
+      <c r="C140" s="28"/>
+      <c r="D140" s="28"/>
+      <c r="E140" s="28"/>
+      <c r="F140" s="28"/>
+      <c r="G140" s="28"/>
+      <c r="H140" s="28"/>
     </row>
     <row r="141" spans="1:8" ht="26" customHeight="1">
       <c r="A141" s="1" t="s">
@@ -3967,16 +4021,16 @@
       <c r="H144" s="3"/>
     </row>
     <row r="145" spans="1:8" ht="30" customHeight="1">
-      <c r="A145" s="36" t="s">
+      <c r="A145" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B145" s="36"/>
-      <c r="C145" s="36"/>
-      <c r="D145" s="36"/>
-      <c r="E145" s="36"/>
-      <c r="F145" s="36"/>
-      <c r="G145" s="36"/>
-      <c r="H145" s="36"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37"/>
+      <c r="D145" s="37"/>
+      <c r="E145" s="37"/>
+      <c r="F145" s="37"/>
+      <c r="G145" s="37"/>
+      <c r="H145" s="37"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
@@ -4090,7 +4144,7 @@
       <c r="A153" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="17">
         <f>IFERROR(D151*1000000/B28,"")</f>
         <v>0</v>
       </c>
@@ -4149,7 +4203,7 @@
       <c r="A158" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="38">
         <f>IFERROR(CHOOSE(MATCH(PROFIL!B5,{"Banque","Assurance","Industrie","Distribution","Telecom","Autre"},0),10,12,13,14,8,12),12)</f>
         <v>0</v>
       </c>
@@ -4165,7 +4219,7 @@
       <c r="A159" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B159" s="37">
+      <c r="B159" s="39">
         <v>5</v>
       </c>
       <c r="C159" s="14" t="s">
@@ -4181,11 +4235,11 @@
       <c r="A161" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="38">
         <f>IFERROR(B30,"")</f>
         <v>0</v>
       </c>
-      <c r="C161" s="22">
+      <c r="C161" s="23">
         <f>B158</f>
         <v>0</v>
       </c>
@@ -4202,11 +4256,11 @@
       <c r="A162" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="38">
         <f>IFERROR(AVERAGE(E39:E43),"")</f>
         <v>0</v>
       </c>
-      <c r="C162" s="22">
+      <c r="C162" s="23">
         <f>B159</f>
         <v>0</v>
       </c>
@@ -4250,7 +4304,7 @@
       <c r="A166" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B166" s="38">
+      <c r="B166" s="40">
         <f>COUNTIF(B39:B43,"&gt;0")</f>
         <v>0</v>
       </c>
@@ -4258,7 +4312,7 @@
         <f>IFERROR(IF(B166=5,"Regulier 5/5 — fiable",IF(B166&gt;=4,"Quasi-regulier 4/5",IF(B166&gt;=3,"Irregulier 3/5","Tres irregulier — risque dividende"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D166" s="38">
+      <c r="D166" s="40">
         <f>IF(B166=5,2,IF(B166&gt;=4,1,0))</f>
         <v>0</v>
       </c>
@@ -4275,16 +4329,16 @@
         <f>IFERROR(IF(NOT(ISNUMBER(B167)),"Dividende absent",IF(B167&gt;0.05,"Forte croissance dividende",IF(B167&gt;0,"Croissance modeste","Dividende en baisse"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D167" s="38">
+      <c r="D167" s="40">
         <f>IFERROR(IF(ISNUMBER(B167),IF(B167&gt;0,1,0),0),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="19" t="s">
+      <c r="A168" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="B168" s="39">
+      <c r="B168" s="41">
         <f>IFERROR(D166+D167,0)</f>
         <v>0</v>
       </c>
@@ -4292,7 +4346,7 @@
         <f>IFERROR(IF(D166+D167&gt;=3,"Dividende tres fiable",IF(D166+D167&gt;=2,"Dividende assez fiable","Dividende peu fiable — risque")),"-")</f>
         <v>0</v>
       </c>
-      <c r="D168" s="21" t="s">
+      <c r="D168" s="22" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4335,7 +4389,7 @@
         <f>IFERROR("PER="&amp;ROUND(B30,1)&amp;" vs sectoriel="&amp;B158,"-")</f>
         <v>0</v>
       </c>
-      <c r="D172" s="38">
+      <c r="D172" s="40">
         <f>IFERROR(IF(B30&lt;B158*0.85,2,IF(B30&lt;B158,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4352,7 +4406,7 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs VMC="&amp;ROUND(B31,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D173" s="38">
+      <c r="D173" s="40">
         <f>IFERROR(IF(B24&lt;B31*0.85,2,IF(B24&lt;B31,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4369,7 +4423,7 @@
         <f>IFERROR("ROE="&amp;ROUND(B33,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D174" s="38">
+      <c r="D174" s="40">
         <f>IFERROR(IF(B33&gt;=15,2,IF(B33&gt;=10,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4386,7 +4440,7 @@
         <f>IFERROR(C168,"-")</f>
         <v>0</v>
       </c>
-      <c r="D175" s="38">
+      <c r="D175" s="40">
         <f>IFERROR(MIN(B168,2),0)</f>
         <v>0</v>
       </c>
@@ -4403,7 +4457,7 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs PM1an="&amp;ROUND(D95,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D176" s="38">
+      <c r="D176" s="40">
         <f>IFERROR(IF(B24&lt;D95,1,0),0)</f>
         <v>0</v>
       </c>
@@ -4420,38 +4474,38 @@
         <f>IFERROR("Marge moy="&amp;ROUND(G16,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D177" s="38">
+      <c r="D177" s="40">
         <f>IFERROR(IF(G16&gt;=10,2,IF(G16&gt;=5,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="19" t="s">
+      <c r="A178" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B178" s="12"/>
-      <c r="C178" s="21" t="s">
+      <c r="C178" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="D178" s="40">
+      <c r="D178" s="42">
         <f>IFERROR(SUM(D172:D177),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="30" customHeight="1">
-      <c r="A179" s="41" t="s">
+      <c r="A179" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="B179" s="41"/>
-      <c r="C179" s="41"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="42">
+      <c r="B179" s="43"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="43"/>
+      <c r="E179" s="44">
         <f>IFERROR(IF(D178&gt;=7,"FORTE OPPORTUNITE CONTRARIAN — fondamentaux sains, titre boude",IF(D178&gt;=5,"A SURVEILLER — signaux contrarians partiels","PAS DE SIGNAL CONTRARIAN — attendre")),"-")</f>
         <v>0</v>
       </c>
-      <c r="F179" s="42"/>
-      <c r="G179" s="42"/>
-      <c r="H179" s="42"/>
+      <c r="F179" s="44"/>
+      <c r="G179" s="44"/>
+      <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="5" customHeight="1"/>
     <row r="181" spans="1:8" ht="5" customHeight="1"/>
@@ -4498,7 +4552,7 @@
       <c r="A186" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="16">
         <f>IFERROR(PROFIL!B16,"")</f>
         <v>0</v>
       </c>
@@ -4513,7 +4567,7 @@
       <c r="A187" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B187" s="9">
+      <c r="B187" s="16">
         <f>IFERROR(PROFIL!B17,"")</f>
         <v>0</v>
       </c>
@@ -4528,7 +4582,7 @@
       <c r="A188" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B188" s="43">
+      <c r="B188" s="45">
         <f>IFERROR(PROFIL!B18,"")</f>
         <v>0</v>
       </c>
@@ -4543,7 +4597,7 @@
       <c r="A189" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B189" s="43">
+      <c r="B189" s="45">
         <f>IFERROR(PROFIL!B19,"")</f>
         <v>0</v>
       </c>
@@ -4585,7 +4639,7 @@
       <c r="A193" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B193" s="16">
         <f>IFERROR(PROFIL!B22,"")</f>
         <v>0</v>
       </c>
@@ -4600,7 +4654,7 @@
       <c r="A194" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="16">
         <f>IFERROR(PROFIL!B23,"")</f>
         <v>0</v>
       </c>
@@ -4615,7 +4669,7 @@
       <c r="A195" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B195" s="43">
+      <c r="B195" s="45">
         <f>IFERROR(PROFIL!B24,"")</f>
         <v>0</v>
       </c>
@@ -4630,7 +4684,7 @@
       <c r="A196" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B196" s="43">
+      <c r="B196" s="45">
         <f>IFERROR(PROFIL!B25,"")</f>
         <v>0</v>
       </c>
@@ -4672,7 +4726,7 @@
       <c r="A200" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B200" s="43">
+      <c r="B200" s="45">
         <f>IFERROR(PROFIL!B28,"")</f>
         <v>0</v>
       </c>
@@ -4687,7 +4741,7 @@
       <c r="A201" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B201" s="43">
+      <c r="B201" s="45">
         <f>IFERROR(PROFIL!B29,"")</f>
         <v>0</v>
       </c>
@@ -4702,7 +4756,7 @@
       <c r="A202" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B202" s="43">
+      <c r="B202" s="45">
         <f>IFERROR(PROFIL!B30,"")</f>
         <v>0</v>
       </c>
@@ -4717,7 +4771,7 @@
       <c r="A203" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B203" s="43">
+      <c r="B203" s="45">
         <f>IFERROR(PROFIL!B31,"")</f>
         <v>0</v>
       </c>
@@ -4730,6 +4784,7 @@
     </row>
     <row r="204" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="44">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -4865,13 +4920,13 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
@@ -4894,159 +4949,159 @@
       <c r="A6" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="47">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="48">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="47"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="47">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="48">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="47"/>
+      <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="47">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="48">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="47"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="47">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="47"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="47">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="47"/>
+      <c r="E10" s="49"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="47">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="48">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="47">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="48">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="47"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="47">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="48">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="47"/>
+      <c r="E13" s="49"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="49">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -5069,108 +5124,108 @@
       <c r="A18" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="52">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="48">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="47"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B19" s="50">
+      <c r="B19" s="52">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="48">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="47"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="52">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="48">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="47"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B21" s="50">
+      <c r="B21" s="52">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="48">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="47"/>
+      <c r="E21" s="49"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="52">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="48">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="47"/>
+      <c r="E22" s="49"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="49">
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="51">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -5193,18 +5248,18 @@
       <c r="A27" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B27" s="52">
+      <c r="B27" s="54">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="55">
         <v>24</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="56">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="57">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
@@ -5213,51 +5268,51 @@
       <c r="A28" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B28" s="52">
+      <c r="B28" s="54">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="55">
         <v>15</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="56">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="57">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="58">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="59">
         <v>39</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="56">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="60">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
@@ -5277,73 +5332,74 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="59">
+      <c r="A33" s="61">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="60">
+      <c r="B33" s="62">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="63">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="63">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="62">
+      <c r="E33" s="64">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="8">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
@@ -5483,42 +5539,42 @@
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="67" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="65" t="s">
         <v>286</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65" t="s">
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="67" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="65" t="s">
         <v>290</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="67" t="s">
         <v>291</v>
       </c>
     </row>
@@ -5535,56 +5591,56 @@
       <c r="A9" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="45">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="66"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="45">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D10" s="66"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="45">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
@@ -5599,33 +5655,33 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
@@ -5643,16 +5699,16 @@
       <c r="B22" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
@@ -5661,8 +5717,8 @@
       <c r="B24" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
@@ -5671,8 +5727,8 @@
       <c r="B25" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
@@ -5687,25 +5743,25 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="67"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="67"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
@@ -5714,8 +5770,8 @@
       <c r="B31" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
@@ -5733,16 +5789,16 @@
       <c r="B34" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
@@ -5751,8 +5807,8 @@
       <c r="B36" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
@@ -5761,11 +5817,12 @@
       <c r="B37" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="11">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -5806,318 +5863,319 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="69" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="70" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="71" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="70" t="s">
         <v>324</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="71" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="70" t="s">
         <v>327</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="70" t="s">
         <v>329</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="71" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="70" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="71" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="70" t="s">
         <v>336</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="71" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="70" t="s">
         <v>339</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="71" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="71" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="70" t="s">
         <v>345</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="71" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="70" t="s">
         <v>348</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>350</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="70" t="s">
         <v>352</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="71" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="70" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="70" t="s">
+      <c r="C16" s="55"/>
+      <c r="D16" s="71" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="70" t="s">
         <v>355</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="70" t="s">
+      <c r="C17" s="55"/>
+      <c r="D17" s="71" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="70" t="s">
         <v>358</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D18" s="70" t="s">
+      <c r="D18" s="71" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="70" t="s">
         <v>361</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="71" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D20" s="71" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="46" t="s">
         <v>366</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="70" t="s">
         <v>368</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D22" s="70" t="s">
+      <c r="D22" s="71" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="70" t="s">
         <v>371</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="55" t="s">
         <v>372</v>
       </c>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="71" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="70" t="s">
         <v>375</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D24" s="70" t="s">
+      <c r="D24" s="71" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="70" t="s">
         <v>378</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="71" t="s">
         <v>379</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1569,22 +1569,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1606,86 +1611,112 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1694,91 +1725,111 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1786,14 +1837,17 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2652,7 +2706,7 @@
       <c r="A28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="16">
         <f>IFERROR(PROFIL!B17,"")</f>
         <v>0</v>
       </c>
@@ -2685,7 +2739,7 @@
       <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="17">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
@@ -2779,21 +2833,21 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="25" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
       <c r="D39" s="7">
         <f>IFERROR((B39/0.85)/C39*100,"")</f>
         <v>0</v>
@@ -2808,8 +2862,8 @@
       <c r="A40" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
       <c r="D40" s="7">
         <f>IFERROR((B40/0.85)/C40*100,"")</f>
         <v>0</v>
@@ -2827,8 +2881,8 @@
       <c r="A41" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="7">
         <f>IFERROR((B41/0.85)/C41*100,"")</f>
         <v>0</v>
@@ -2846,8 +2900,8 @@
       <c r="A42" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="7">
         <f>IFERROR((B42/0.85)/C42*100,"")</f>
         <v>0</v>
@@ -2865,8 +2919,8 @@
       <c r="A43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
       <c r="D43" s="7">
         <f>IFERROR((B43/0.85)/C43*100,"")</f>
         <v>0</v>
@@ -2881,10 +2935,10 @@
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="19" t="s">
+      <c r="A44" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="17">
         <f>SUM(B39:B43)</f>
         <v>0</v>
       </c>
@@ -2981,7 +3035,7 @@
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="19" t="s">
+      <c r="A52" s="20" t="s">
         <v>64</v>
       </c>
       <c r="B52" s="9">
@@ -3028,45 +3082,45 @@
       <c r="A56" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D56" s="21"/>
+      <c r="D56" s="22"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D57" s="21"/>
+      <c r="D57" s="22"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="21" t="s">
+      <c r="B58" s="21"/>
+      <c r="C58" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="21"/>
+      <c r="D58" s="22"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="21" t="s">
+      <c r="B59" s="21"/>
+      <c r="C59" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D59" s="21"/>
+      <c r="D59" s="22"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="20" customHeight="1">
@@ -3098,7 +3152,7 @@
         <v>82</v>
       </c>
       <c r="B63" s="6"/>
-      <c r="C63" s="22"/>
+      <c r="C63" s="23"/>
       <c r="D63" s="12"/>
     </row>
     <row r="64" spans="1:8">
@@ -3106,121 +3160,121 @@
         <v>83</v>
       </c>
       <c r="B64" s="6"/>
-      <c r="C64" s="22"/>
+      <c r="C64" s="23"/>
       <c r="D64" s="12"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B65" s="24">
         <f>IFERROR(B64*1.014,"")</f>
         <v>0</v>
       </c>
-      <c r="C65" s="22"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="12"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B66" s="24">
         <f>IFERROR(B63/B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C66" s="22"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="12"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B67" s="25">
         <f>IFERROR(B24,"")</f>
         <v>0</v>
       </c>
-      <c r="C67" s="22"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="12"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B68" s="24">
         <f>IFERROR(B67-(B67*0.014),"")</f>
         <v>0</v>
       </c>
-      <c r="C68" s="22"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="12"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B69" s="24">
         <f>IFERROR(B68-B65,"")</f>
         <v>0</v>
       </c>
-      <c r="C69" s="22"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="12"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B70" s="25">
         <f>IFERROR(B69*B66,"")</f>
         <v>0</v>
       </c>
-      <c r="C70" s="22"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="12"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B71" s="18"/>
-      <c r="C71" s="22"/>
+      <c r="B71" s="19"/>
+      <c r="C71" s="23"/>
       <c r="D71" s="12"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B72" s="25">
         <f>IFERROR(B71*B66,"")</f>
         <v>0</v>
       </c>
-      <c r="C72" s="22"/>
+      <c r="C72" s="23"/>
       <c r="D72" s="12"/>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="19" t="s">
+      <c r="A73" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B73" s="25">
         <f>IFERROR(B70+B72,"")</f>
         <v>0</v>
       </c>
-      <c r="C73" s="22"/>
+      <c r="C73" s="23"/>
       <c r="D73" s="12"/>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="19" t="s">
+      <c r="A74" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B74" s="25">
+      <c r="B74" s="26">
         <f>IFERROR(B73/B63*100,"")</f>
         <v>0</v>
       </c>
-      <c r="C74" s="22"/>
+      <c r="C74" s="23"/>
       <c r="D74" s="12"/>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="19" t="s">
+      <c r="A75" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B75" s="26">
+      <c r="B75" s="27">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
@@ -3243,34 +3297,34 @@
       <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:8" ht="40" customHeight="1">
-      <c r="A78" s="27"/>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="28"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="28"/>
+      <c r="G78" s="28"/>
+      <c r="H78" s="28"/>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="27"/>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="28"/>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="27"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
+      <c r="A80" s="28"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
+      <c r="D80" s="28"/>
+      <c r="E80" s="28"/>
+      <c r="F80" s="28"/>
+      <c r="G80" s="28"/>
+      <c r="H80" s="28"/>
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="1" t="s">
@@ -3321,12 +3375,12 @@
       <c r="B86" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C86" s="22"/>
-      <c r="D86" s="28">
+      <c r="C86" s="23"/>
+      <c r="D86" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B86)),1,IF(ISNUMBER(SEARCH("surachat",B86)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E86" s="29" t="s">
+      <c r="E86" s="30" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3337,12 +3391,12 @@
       <c r="B87" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C87" s="22"/>
-      <c r="D87" s="28">
+      <c r="C87" s="23"/>
+      <c r="D87" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B87)),1,IF(ISNUMBER(SEARCH("surachat",B87)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E87" s="29" t="s">
+      <c r="E87" s="30" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3353,12 +3407,12 @@
       <c r="B88" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C88" s="22"/>
-      <c r="D88" s="28">
+      <c r="C88" s="23"/>
+      <c r="D88" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B88)),1,IF(ISNUMBER(SEARCH("surachat",B88)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E88" s="29" t="s">
+      <c r="E88" s="30" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3369,12 +3423,12 @@
       <c r="B89" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C89" s="22"/>
-      <c r="D89" s="28">
+      <c r="C89" s="23"/>
+      <c r="D89" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B89)),1,IF(ISNUMBER(SEARCH("surachat",B89)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E89" s="29" t="s">
+      <c r="E89" s="30" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3385,26 +3439,26 @@
       <c r="B90" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C90" s="22"/>
-      <c r="D90" s="28">
+      <c r="C90" s="23"/>
+      <c r="D90" s="29">
         <f>IFERROR(IF(ISNUMBER(SEARCH("survente",B90)),1,IF(ISNUMBER(SEARCH("surachat",B90)),-1,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E90" s="29" t="s">
+      <c r="E90" s="30" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="19" t="s">
+      <c r="A91" s="20" t="s">
         <v>114</v>
       </c>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
-      <c r="D91" s="30">
+      <c r="D91" s="31">
         <f>SUM(D86:D90)</f>
         <v>0</v>
       </c>
-      <c r="E91" s="31">
+      <c r="E91" s="32">
         <f>IFERROR(IF(D91&gt;0,"Zone SURVENTE - Achat possible",IF(D91&lt;0,"Zone SURACHAT - Vente possible","NEUTRE")),"-")</f>
         <v>0</v>
       </c>
@@ -3445,7 +3499,7 @@
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="16">
+      <c r="D95" s="17">
         <f>IFERROR((B95+C95)/2,"")</f>
         <v>0</v>
       </c>
@@ -3460,7 +3514,7 @@
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="16">
+      <c r="D96" s="17">
         <f>IFERROR((B96+C96)/2,"")</f>
         <v>0</v>
       </c>
@@ -3500,11 +3554,11 @@
       <c r="A100" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B100" s="24">
+      <c r="B100" s="25">
         <f>B24</f>
         <v>0</v>
       </c>
-      <c r="C100" s="21" t="s">
+      <c r="C100" s="22" t="s">
         <v>126</v>
       </c>
       <c r="D100" s="12"/>
@@ -3513,11 +3567,11 @@
       <c r="A101" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B101" s="24">
         <f>B25</f>
         <v>0</v>
       </c>
-      <c r="C101" s="21" t="s">
+      <c r="C101" s="22" t="s">
         <v>128</v>
       </c>
       <c r="D101" s="12"/>
@@ -3526,8 +3580,8 @@
       <c r="A102" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B102" s="32"/>
-      <c r="C102" s="21" t="s">
+      <c r="B102" s="33"/>
+      <c r="C102" s="22" t="s">
         <v>130</v>
       </c>
       <c r="D102" s="12"/>
@@ -3536,11 +3590,11 @@
       <c r="A103" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B103" s="24">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
-      <c r="C103" s="21" t="s">
+      <c r="C103" s="22" t="s">
         <v>132</v>
       </c>
       <c r="D103" s="12"/>
@@ -3549,11 +3603,11 @@
       <c r="A104" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B104" s="25">
+      <c r="B104" s="26">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
-      <c r="C104" s="21" t="s">
+      <c r="C104" s="22" t="s">
         <v>134</v>
       </c>
       <c r="D104" s="10">
@@ -3575,16 +3629,16 @@
       <c r="H106" s="3"/>
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
-      <c r="A107" s="33" t="s">
+      <c r="A107" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B107" s="33"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="33"/>
-      <c r="G107" s="33"/>
-      <c r="H107" s="33"/>
+      <c r="B107" s="34"/>
+      <c r="C107" s="34"/>
+      <c r="D107" s="34"/>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+      <c r="G107" s="34"/>
+      <c r="H107" s="34"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
@@ -3604,8 +3658,8 @@
       <c r="A109" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B109" s="32"/>
-      <c r="C109" s="21" t="s">
+      <c r="B109" s="33"/>
+      <c r="C109" s="22" t="s">
         <v>139</v>
       </c>
       <c r="D109" s="12"/>
@@ -3614,8 +3668,8 @@
       <c r="A110" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B110" s="18"/>
-      <c r="C110" s="21" t="s">
+      <c r="B110" s="19"/>
+      <c r="C110" s="22" t="s">
         <v>141</v>
       </c>
       <c r="D110" s="12"/>
@@ -3624,11 +3678,11 @@
       <c r="A111" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B111" s="24">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
-      <c r="C111" s="21" t="s">
+      <c r="C111" s="22" t="s">
         <v>143</v>
       </c>
       <c r="D111" s="12"/>
@@ -3637,10 +3691,10 @@
       <c r="A112" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B112" s="32">
+      <c r="B112" s="33">
         <v>6.5</v>
       </c>
-      <c r="C112" s="21" t="s">
+      <c r="C112" s="22" t="s">
         <v>145</v>
       </c>
       <c r="D112" s="12"/>
@@ -3649,11 +3703,11 @@
       <c r="A113" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B113" s="23">
+      <c r="B113" s="24">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
-      <c r="C113" s="21" t="s">
+      <c r="C113" s="22" t="s">
         <v>147</v>
       </c>
       <c r="D113" s="12"/>
@@ -3662,11 +3716,11 @@
       <c r="A114" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B114" s="23">
+      <c r="B114" s="24">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C114" s="21" t="s">
+      <c r="C114" s="22" t="s">
         <v>149</v>
       </c>
       <c r="D114" s="12"/>
@@ -3675,11 +3729,11 @@
       <c r="A115" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B115" s="23">
+      <c r="B115" s="24">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
-      <c r="C115" s="21" t="s">
+      <c r="C115" s="22" t="s">
         <v>151</v>
       </c>
       <c r="D115" s="12"/>
@@ -3688,11 +3742,11 @@
       <c r="A116" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B116" s="31">
+      <c r="B116" s="32">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C116" s="21" t="s">
+      <c r="C116" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D116" s="12"/>
@@ -3711,16 +3765,16 @@
       <c r="H118" s="3"/>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="34" t="s">
+      <c r="A119" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="B119" s="34"/>
-      <c r="C119" s="34"/>
-      <c r="D119" s="34"/>
-      <c r="E119" s="34"/>
-      <c r="F119" s="34"/>
-      <c r="G119" s="34"/>
-      <c r="H119" s="34"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="35"/>
+      <c r="E119" s="35"/>
+      <c r="F119" s="35"/>
+      <c r="G119" s="35"/>
+      <c r="H119" s="35"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
@@ -3740,8 +3794,8 @@
       <c r="A121" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B121" s="18"/>
-      <c r="C121" s="21" t="s">
+      <c r="B121" s="19"/>
+      <c r="C121" s="22" t="s">
         <v>158</v>
       </c>
       <c r="D121" s="12"/>
@@ -3750,10 +3804,10 @@
       <c r="A122" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B122" s="32">
+      <c r="B122" s="33">
         <v>8</v>
       </c>
-      <c r="C122" s="21" t="s">
+      <c r="C122" s="22" t="s">
         <v>160</v>
       </c>
       <c r="D122" s="12"/>
@@ -3762,10 +3816,10 @@
       <c r="A123" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B123" s="32">
+      <c r="B123" s="33">
         <v>2</v>
       </c>
-      <c r="C123" s="21" t="s">
+      <c r="C123" s="22" t="s">
         <v>162</v>
       </c>
       <c r="D123" s="12"/>
@@ -3774,11 +3828,11 @@
       <c r="A124" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B124" s="35">
+      <c r="B124" s="36">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
-      <c r="C124" s="21" t="s">
+      <c r="C124" s="22" t="s">
         <v>164</v>
       </c>
       <c r="D124" s="12"/>
@@ -3787,11 +3841,11 @@
       <c r="A125" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B125" s="31">
+      <c r="B125" s="32">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
-      <c r="C125" s="21" t="s">
+      <c r="C125" s="22" t="s">
         <v>153</v>
       </c>
       <c r="D125" s="12"/>
@@ -3828,7 +3882,7 @@
         <v>168</v>
       </c>
       <c r="B130" s="6"/>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="22" t="s">
         <v>169</v>
       </c>
       <c r="D130" s="12"/>
@@ -3837,11 +3891,11 @@
       <c r="A131" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B131" s="23">
+      <c r="B131" s="24">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
-      <c r="C131" s="21" t="s">
+      <c r="C131" s="22" t="s">
         <v>171</v>
       </c>
       <c r="D131" s="12"/>
@@ -3851,7 +3905,7 @@
         <v>172</v>
       </c>
       <c r="B132" s="6"/>
-      <c r="C132" s="21" t="s">
+      <c r="C132" s="22" t="s">
         <v>173</v>
       </c>
       <c r="D132" s="12"/>
@@ -3860,11 +3914,11 @@
       <c r="A133" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B133" s="23">
+      <c r="B133" s="24">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
-      <c r="C133" s="21" t="s">
+      <c r="C133" s="22" t="s">
         <v>175</v>
       </c>
       <c r="D133" s="12"/>
@@ -3873,11 +3927,11 @@
       <c r="A134" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B134" s="23">
+      <c r="B134" s="24">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
-      <c r="C134" s="21" t="s">
+      <c r="C134" s="22" t="s">
         <v>177</v>
       </c>
       <c r="D134" s="12"/>
@@ -3886,11 +3940,11 @@
       <c r="A135" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B135" s="25">
+      <c r="B135" s="26">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
-      <c r="C135" s="21" t="s">
+      <c r="C135" s="22" t="s">
         <v>179</v>
       </c>
       <c r="D135" s="10">
@@ -3912,34 +3966,34 @@
       <c r="H137" s="3"/>
     </row>
     <row r="138" spans="1:8" ht="40" customHeight="1">
-      <c r="A138" s="27"/>
-      <c r="B138" s="27"/>
-      <c r="C138" s="27"/>
-      <c r="D138" s="27"/>
-      <c r="E138" s="27"/>
-      <c r="F138" s="27"/>
-      <c r="G138" s="27"/>
-      <c r="H138" s="27"/>
+      <c r="A138" s="28"/>
+      <c r="B138" s="28"/>
+      <c r="C138" s="28"/>
+      <c r="D138" s="28"/>
+      <c r="E138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="28"/>
+      <c r="H138" s="28"/>
     </row>
     <row r="139" spans="1:8">
-      <c r="A139" s="27"/>
-      <c r="B139" s="27"/>
-      <c r="C139" s="27"/>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="27"/>
-      <c r="H139" s="27"/>
+      <c r="A139" s="28"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="28"/>
+      <c r="D139" s="28"/>
+      <c r="E139" s="28"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="28"/>
+      <c r="H139" s="28"/>
     </row>
     <row r="140" spans="1:8">
-      <c r="A140" s="27"/>
-      <c r="B140" s="27"/>
-      <c r="C140" s="27"/>
-      <c r="D140" s="27"/>
-      <c r="E140" s="27"/>
-      <c r="F140" s="27"/>
-      <c r="G140" s="27"/>
-      <c r="H140" s="27"/>
+      <c r="A140" s="28"/>
+      <c r="B140" s="28"/>
+      <c r="C140" s="28"/>
+      <c r="D140" s="28"/>
+      <c r="E140" s="28"/>
+      <c r="F140" s="28"/>
+      <c r="G140" s="28"/>
+      <c r="H140" s="28"/>
     </row>
     <row r="141" spans="1:8" ht="26" customHeight="1">
       <c r="A141" s="1" t="s">
@@ -3967,16 +4021,16 @@
       <c r="H144" s="3"/>
     </row>
     <row r="145" spans="1:8" ht="30" customHeight="1">
-      <c r="A145" s="36" t="s">
+      <c r="A145" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="B145" s="36"/>
-      <c r="C145" s="36"/>
-      <c r="D145" s="36"/>
-      <c r="E145" s="36"/>
-      <c r="F145" s="36"/>
-      <c r="G145" s="36"/>
-      <c r="H145" s="36"/>
+      <c r="B145" s="37"/>
+      <c r="C145" s="37"/>
+      <c r="D145" s="37"/>
+      <c r="E145" s="37"/>
+      <c r="F145" s="37"/>
+      <c r="G145" s="37"/>
+      <c r="H145" s="37"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
@@ -4090,7 +4144,7 @@
       <c r="A153" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="B153" s="16">
+      <c r="B153" s="17">
         <f>IFERROR(D151*1000000/B28,"")</f>
         <v>0</v>
       </c>
@@ -4149,7 +4203,7 @@
       <c r="A158" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="38">
         <f>IFERROR(CHOOSE(MATCH(PROFIL!B5,{"Banque","Assurance","Industrie","Distribution","Telecom","Autre"},0),10,12,13,14,8,12),12)</f>
         <v>0</v>
       </c>
@@ -4165,7 +4219,7 @@
       <c r="A159" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="B159" s="37">
+      <c r="B159" s="39">
         <v>5</v>
       </c>
       <c r="C159" s="14" t="s">
@@ -4181,11 +4235,11 @@
       <c r="A161" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="38">
         <f>IFERROR(B30,"")</f>
         <v>0</v>
       </c>
-      <c r="C161" s="22">
+      <c r="C161" s="23">
         <f>B158</f>
         <v>0</v>
       </c>
@@ -4202,11 +4256,11 @@
       <c r="A162" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="38">
         <f>IFERROR(AVERAGE(E39:E43),"")</f>
         <v>0</v>
       </c>
-      <c r="C162" s="22">
+      <c r="C162" s="23">
         <f>B159</f>
         <v>0</v>
       </c>
@@ -4250,7 +4304,7 @@
       <c r="A166" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="B166" s="38">
+      <c r="B166" s="40">
         <f>COUNTIF(B39:B43,"&gt;0")</f>
         <v>0</v>
       </c>
@@ -4258,7 +4312,7 @@
         <f>IFERROR(IF(B166=5,"Regulier 5/5 — fiable",IF(B166&gt;=4,"Quasi-regulier 4/5",IF(B166&gt;=3,"Irregulier 3/5","Tres irregulier — risque dividende"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D166" s="38">
+      <c r="D166" s="40">
         <f>IF(B166=5,2,IF(B166&gt;=4,1,0))</f>
         <v>0</v>
       </c>
@@ -4275,16 +4329,16 @@
         <f>IFERROR(IF(NOT(ISNUMBER(B167)),"Dividende absent",IF(B167&gt;0.05,"Forte croissance dividende",IF(B167&gt;0,"Croissance modeste","Dividende en baisse"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="D167" s="38">
+      <c r="D167" s="40">
         <f>IFERROR(IF(ISNUMBER(B167),IF(B167&gt;0,1,0),0),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:8">
-      <c r="A168" s="19" t="s">
+      <c r="A168" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="B168" s="39">
+      <c r="B168" s="41">
         <f>IFERROR(D166+D167,0)</f>
         <v>0</v>
       </c>
@@ -4292,7 +4346,7 @@
         <f>IFERROR(IF(D166+D167&gt;=3,"Dividende tres fiable",IF(D166+D167&gt;=2,"Dividende assez fiable","Dividende peu fiable — risque")),"-")</f>
         <v>0</v>
       </c>
-      <c r="D168" s="21" t="s">
+      <c r="D168" s="22" t="s">
         <v>205</v>
       </c>
     </row>
@@ -4335,7 +4389,7 @@
         <f>IFERROR("PER="&amp;ROUND(B30,1)&amp;" vs sectoriel="&amp;B158,"-")</f>
         <v>0</v>
       </c>
-      <c r="D172" s="38">
+      <c r="D172" s="40">
         <f>IFERROR(IF(B30&lt;B158*0.85,2,IF(B30&lt;B158,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4352,7 +4406,7 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs VMC="&amp;ROUND(B31,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D173" s="38">
+      <c r="D173" s="40">
         <f>IFERROR(IF(B24&lt;B31*0.85,2,IF(B24&lt;B31,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4369,7 +4423,7 @@
         <f>IFERROR("ROE="&amp;ROUND(B33,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D174" s="38">
+      <c r="D174" s="40">
         <f>IFERROR(IF(B33&gt;=15,2,IF(B33&gt;=10,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -4386,7 +4440,7 @@
         <f>IFERROR(C168,"-")</f>
         <v>0</v>
       </c>
-      <c r="D175" s="38">
+      <c r="D175" s="40">
         <f>IFERROR(MIN(B168,2),0)</f>
         <v>0</v>
       </c>
@@ -4403,7 +4457,7 @@
         <f>IFERROR("Prix="&amp;B24&amp;" FCFA  vs PM1an="&amp;ROUND(D95,0)&amp;" FCFA","-")</f>
         <v>0</v>
       </c>
-      <c r="D176" s="38">
+      <c r="D176" s="40">
         <f>IFERROR(IF(B24&lt;D95,1,0),0)</f>
         <v>0</v>
       </c>
@@ -4420,38 +4474,38 @@
         <f>IFERROR("Marge moy="&amp;ROUND(G16,1)&amp;"%","-")</f>
         <v>0</v>
       </c>
-      <c r="D177" s="38">
+      <c r="D177" s="40">
         <f>IFERROR(IF(G16&gt;=10,2,IF(G16&gt;=5,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:8">
-      <c r="A178" s="19" t="s">
+      <c r="A178" s="20" t="s">
         <v>216</v>
       </c>
       <c r="B178" s="12"/>
-      <c r="C178" s="21" t="s">
+      <c r="C178" s="22" t="s">
         <v>217</v>
       </c>
-      <c r="D178" s="40">
+      <c r="D178" s="42">
         <f>IFERROR(SUM(D172:D177),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="30" customHeight="1">
-      <c r="A179" s="41" t="s">
+      <c r="A179" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="B179" s="41"/>
-      <c r="C179" s="41"/>
-      <c r="D179" s="41"/>
-      <c r="E179" s="42">
+      <c r="B179" s="43"/>
+      <c r="C179" s="43"/>
+      <c r="D179" s="43"/>
+      <c r="E179" s="44">
         <f>IFERROR(IF(D178&gt;=7,"FORTE OPPORTUNITE CONTRARIAN — fondamentaux sains, titre boude",IF(D178&gt;=5,"A SURVEILLER — signaux contrarians partiels","PAS DE SIGNAL CONTRARIAN — attendre")),"-")</f>
         <v>0</v>
       </c>
-      <c r="F179" s="42"/>
-      <c r="G179" s="42"/>
-      <c r="H179" s="42"/>
+      <c r="F179" s="44"/>
+      <c r="G179" s="44"/>
+      <c r="H179" s="44"/>
     </row>
     <row r="180" spans="1:8" ht="5" customHeight="1"/>
     <row r="181" spans="1:8" ht="5" customHeight="1"/>
@@ -4498,7 +4552,7 @@
       <c r="A186" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="16">
         <f>IFERROR(PROFIL!B16,"")</f>
         <v>0</v>
       </c>
@@ -4513,7 +4567,7 @@
       <c r="A187" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B187" s="9">
+      <c r="B187" s="16">
         <f>IFERROR(PROFIL!B17,"")</f>
         <v>0</v>
       </c>
@@ -4528,7 +4582,7 @@
       <c r="A188" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B188" s="43">
+      <c r="B188" s="45">
         <f>IFERROR(PROFIL!B18,"")</f>
         <v>0</v>
       </c>
@@ -4543,7 +4597,7 @@
       <c r="A189" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B189" s="43">
+      <c r="B189" s="45">
         <f>IFERROR(PROFIL!B19,"")</f>
         <v>0</v>
       </c>
@@ -4585,7 +4639,7 @@
       <c r="A193" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B193" s="16">
         <f>IFERROR(PROFIL!B22,"")</f>
         <v>0</v>
       </c>
@@ -4600,7 +4654,7 @@
       <c r="A194" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="16">
         <f>IFERROR(PROFIL!B23,"")</f>
         <v>0</v>
       </c>
@@ -4615,7 +4669,7 @@
       <c r="A195" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="B195" s="43">
+      <c r="B195" s="45">
         <f>IFERROR(PROFIL!B24,"")</f>
         <v>0</v>
       </c>
@@ -4630,7 +4684,7 @@
       <c r="A196" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B196" s="43">
+      <c r="B196" s="45">
         <f>IFERROR(PROFIL!B25,"")</f>
         <v>0</v>
       </c>
@@ -4672,7 +4726,7 @@
       <c r="A200" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B200" s="43">
+      <c r="B200" s="45">
         <f>IFERROR(PROFIL!B28,"")</f>
         <v>0</v>
       </c>
@@ -4687,7 +4741,7 @@
       <c r="A201" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B201" s="43">
+      <c r="B201" s="45">
         <f>IFERROR(PROFIL!B29,"")</f>
         <v>0</v>
       </c>
@@ -4702,7 +4756,7 @@
       <c r="A202" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B202" s="43">
+      <c r="B202" s="45">
         <f>IFERROR(PROFIL!B30,"")</f>
         <v>0</v>
       </c>
@@ -4717,7 +4771,7 @@
       <c r="A203" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B203" s="43">
+      <c r="B203" s="45">
         <f>IFERROR(PROFIL!B31,"")</f>
         <v>0</v>
       </c>
@@ -4866,13 +4920,13 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
@@ -4895,159 +4949,159 @@
       <c r="A6" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B6" s="45">
+      <c r="B6" s="47">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D6" s="46">
+      <c r="D6" s="48">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="47"/>
+      <c r="E6" s="49"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="47">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="48">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="47"/>
+      <c r="E7" s="49"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="47">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="48">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="47"/>
+      <c r="E8" s="49"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="47">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="48">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="47"/>
+      <c r="E9" s="49"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="47">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="47"/>
+      <c r="E10" s="49"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="47">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="48">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="47"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="47">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="48">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="47"/>
+      <c r="E12" s="49"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="B13" s="45">
+      <c r="B13" s="47">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D13" s="46">
+      <c r="D13" s="48">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="47"/>
+      <c r="E13" s="49"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="49">
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="44" t="s">
+      <c r="A16" s="46" t="s">
         <v>256</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -5070,108 +5124,108 @@
       <c r="A18" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="52">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D18" s="48">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="47"/>
+      <c r="E18" s="49"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B19" s="50">
+      <c r="B19" s="52">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="D19" s="46">
+      <c r="D19" s="48">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="47"/>
+      <c r="E19" s="49"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="52">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D20" s="46">
+      <c r="D20" s="48">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="47"/>
+      <c r="E20" s="49"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B21" s="50">
+      <c r="B21" s="52">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D21" s="46">
+      <c r="D21" s="48">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="47"/>
+      <c r="E21" s="49"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="52">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="48">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="47"/>
+      <c r="E22" s="49"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="49">
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="51">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -5194,18 +5248,18 @@
       <c r="A27" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="B27" s="52">
+      <c r="B27" s="54">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="55">
         <v>24</v>
       </c>
-      <c r="D27" s="54">
+      <c r="D27" s="56">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="55">
+      <c r="E27" s="57">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
@@ -5214,51 +5268,51 @@
       <c r="A28" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="B28" s="52">
+      <c r="B28" s="54">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="53">
+      <c r="C28" s="55">
         <v>15</v>
       </c>
-      <c r="D28" s="54">
+      <c r="D28" s="56">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="55">
+      <c r="E28" s="57">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="B29" s="56">
+      <c r="B29" s="58">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="59">
         <v>39</v>
       </c>
-      <c r="D29" s="54">
+      <c r="D29" s="56">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="60">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="44" t="s">
+      <c r="A31" s="46" t="s">
         <v>276</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
@@ -5278,71 +5332,71 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="59">
+      <c r="A33" s="61">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="60">
+      <c r="B33" s="62">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="61">
+      <c r="C33" s="63">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="63">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="62">
+      <c r="E33" s="64">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="46"/>
+      <c r="D35" s="46"/>
+      <c r="E35" s="46"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -5485,42 +5539,42 @@
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="65" t="s">
         <v>284</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65" t="s">
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="67" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="65" t="s">
         <v>286</v>
       </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="65" t="s">
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="67" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="65" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="65" t="s">
+      <c r="B5" s="66"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="65" t="s">
         <v>290</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="65" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="67" t="s">
         <v>291</v>
       </c>
     </row>
@@ -5537,56 +5591,56 @@
       <c r="A9" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="45">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D9" s="66"/>
+      <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="45">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D10" s="66"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="45">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
+      <c r="B12" s="68"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
@@ -5601,33 +5655,33 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
+      <c r="B17" s="68"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
@@ -5645,16 +5699,16 @@
       <c r="B22" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="67"/>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
+      <c r="B23" s="68"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="5" t="s">
@@ -5663,8 +5717,8 @@
       <c r="B24" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="5" t="s">
@@ -5673,8 +5727,8 @@
       <c r="B25" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
     </row>
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
@@ -5689,25 +5743,25 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="66"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="67"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
+      <c r="B29" s="68"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="67"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="5" t="s">
@@ -5716,8 +5770,8 @@
       <c r="B31" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
     </row>
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
@@ -5735,16 +5789,16 @@
       <c r="B34" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C34" s="66"/>
-      <c r="D34" s="66"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B35" s="67"/>
-      <c r="C35" s="66"/>
-      <c r="D35" s="66"/>
+      <c r="B35" s="68"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
@@ -5753,8 +5807,8 @@
       <c r="B36" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C36" s="66"/>
-      <c r="D36" s="66"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
@@ -5763,8 +5817,8 @@
       <c r="B37" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
@@ -5809,314 +5863,314 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="69" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="68" t="s">
+      <c r="C2" s="69" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="69" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="46" t="s">
         <v>318</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="70" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="71" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="70" t="s">
         <v>324</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="71" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="70" t="s">
         <v>327</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="71" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="70" t="s">
         <v>329</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D7" s="70" t="s">
+      <c r="D7" s="71" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="70" t="s">
         <v>333</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="70" t="s">
+      <c r="D8" s="71" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="70" t="s">
         <v>336</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="71" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="70" t="s">
         <v>339</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="71" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="70" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="53"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="71" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="70" t="s">
         <v>345</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="71" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="70" t="s">
         <v>348</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="46" t="s">
         <v>350</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="70" t="s">
         <v>352</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="71" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="70" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="70" t="s">
+      <c r="C16" s="55"/>
+      <c r="D16" s="71" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="70" t="s">
         <v>355</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="70" t="s">
+      <c r="C17" s="55"/>
+      <c r="D17" s="71" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="70" t="s">
         <v>358</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D18" s="70" t="s">
+      <c r="D18" s="71" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="70" t="s">
         <v>361</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D19" s="70" t="s">
+      <c r="D19" s="71" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D20" s="71" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="46" t="s">
         <v>366</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="70" t="s">
         <v>368</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D22" s="70" t="s">
+      <c r="D22" s="71" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="70" t="s">
         <v>371</v>
       </c>
-      <c r="C23" s="53" t="s">
+      <c r="C23" s="55" t="s">
         <v>372</v>
       </c>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="71" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="70" t="s">
         <v>375</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D24" s="70" t="s">
+      <c r="D24" s="71" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="70" t="s">
         <v>378</v>
       </c>
-      <c r="C25" s="53" t="s">
+      <c r="C25" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D25" s="70" t="s">
+      <c r="D25" s="71" t="s">
         <v>379</v>
       </c>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -2316,7 +2316,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1">
       <c r="A1" s="1">
-        <f>IFERROR("FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"   ("&amp;PROFIL!B4&amp;")   |   "&amp;PROFIL!B5&amp;"   |   "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]")</f>
+        <f>IF(PROFIL!B3="","FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]","FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  "&amp;PROFIL!B6)</f>
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2">
-        <f>IFERROR("Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date analyse : "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"Completer le PROFIL : nom, ticker, secteur, date")</f>
+        <f>IF(PROFIL!B3="","Completer le PROFIL : nom, ticker, secteur, date","Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date : "&amp;PROFIL!B6)</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="2">
-        <f>IFERROR(PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;TEXT(ETUDE!B24,"#,##0")&amp;" FCFA  |  Date : "&amp;TEXT(PROFIL!B6,"dd/mm/yyyy"),"Completer le PROFIL")</f>
+        <f>IF(PROFIL!B3="","Completer le PROFIL",PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;ETUDE!B24&amp;" FCFA  |  Date : "&amp;PROFIL!B6)</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1163,12 +1163,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="#,##0.00"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1569,7 +1570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1830,6 +1831,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="169" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -5572,8 +5577,8 @@
       <c r="A6" s="65" t="s">
         <v>290</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
       <c r="D6" s="67" t="s">
         <v>291</v>
       </c>
@@ -5630,7 +5635,7 @@
       <c r="A12" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B12" s="68"/>
+      <c r="B12" s="69"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
@@ -5638,7 +5643,7 @@
       <c r="A13" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B13" s="68"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
@@ -5655,7 +5660,7 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="68"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
@@ -5663,7 +5668,7 @@
       <c r="A17" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="B17" s="68"/>
+      <c r="B17" s="69"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
@@ -5671,7 +5676,7 @@
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="68"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
@@ -5679,7 +5684,7 @@
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="68"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
@@ -5706,7 +5711,7 @@
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="68"/>
+      <c r="B23" s="69"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
@@ -5743,7 +5748,7 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="68"/>
+      <c r="B28" s="69"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
@@ -5751,7 +5756,7 @@
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="68"/>
+      <c r="B29" s="69"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
@@ -5759,7 +5764,7 @@
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="68"/>
+      <c r="B30" s="69"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
@@ -5796,7 +5801,7 @@
       <c r="A35" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="B35" s="68"/>
+      <c r="B35" s="69"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
@@ -5863,16 +5868,16 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="70" t="s">
         <v>315</v>
       </c>
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="70" t="s">
         <v>316</v>
       </c>
-      <c r="D2" s="69" t="s">
+      <c r="D2" s="70" t="s">
         <v>317</v>
       </c>
     </row>
@@ -5888,13 +5893,13 @@
       <c r="A4" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="71" t="s">
         <v>320</v>
       </c>
       <c r="C4" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D4" s="71" t="s">
+      <c r="D4" s="72" t="s">
         <v>322</v>
       </c>
     </row>
@@ -5902,13 +5907,13 @@
       <c r="A5" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="71" t="s">
         <v>324</v>
       </c>
       <c r="C5" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="72" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5916,13 +5921,13 @@
       <c r="A6" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="71" t="s">
         <v>327</v>
       </c>
       <c r="C6" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="72" t="s">
         <v>328</v>
       </c>
     </row>
@@ -5930,13 +5935,13 @@
       <c r="A7" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="71" t="s">
         <v>329</v>
       </c>
       <c r="C7" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="72" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5944,13 +5949,13 @@
       <c r="A8" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="71" t="s">
         <v>333</v>
       </c>
       <c r="C8" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="72" t="s">
         <v>335</v>
       </c>
     </row>
@@ -5958,13 +5963,13 @@
       <c r="A9" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="71" t="s">
         <v>336</v>
       </c>
       <c r="C9" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="72" t="s">
         <v>337</v>
       </c>
     </row>
@@ -5972,13 +5977,13 @@
       <c r="A10" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="71" t="s">
         <v>339</v>
       </c>
       <c r="C10" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="72" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5986,11 +5991,11 @@
       <c r="A11" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="71" t="s">
         <v>342</v>
       </c>
       <c r="C11" s="55"/>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="72" t="s">
         <v>343</v>
       </c>
     </row>
@@ -5998,13 +6003,13 @@
       <c r="A12" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="71" t="s">
         <v>345</v>
       </c>
       <c r="C12" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="72" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6012,13 +6017,13 @@
       <c r="A13" s="20" t="s">
         <v>347</v>
       </c>
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="71" t="s">
         <v>348</v>
       </c>
       <c r="C13" s="55" t="s">
         <v>321</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="72" t="s">
         <v>349</v>
       </c>
     </row>
@@ -6034,13 +6039,13 @@
       <c r="A15" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="71" t="s">
         <v>352</v>
       </c>
       <c r="C15" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D15" s="71" t="s">
+      <c r="D15" s="72" t="s">
         <v>353</v>
       </c>
     </row>
@@ -6048,11 +6053,11 @@
       <c r="A16" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="B16" s="70" t="s">
+      <c r="B16" s="71" t="s">
         <v>355</v>
       </c>
       <c r="C16" s="55"/>
-      <c r="D16" s="71" t="s">
+      <c r="D16" s="72" t="s">
         <v>356</v>
       </c>
     </row>
@@ -6060,11 +6065,11 @@
       <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="71" t="s">
         <v>355</v>
       </c>
       <c r="C17" s="55"/>
-      <c r="D17" s="71" t="s">
+      <c r="D17" s="72" t="s">
         <v>357</v>
       </c>
     </row>
@@ -6072,13 +6077,13 @@
       <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="71" t="s">
         <v>358</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>330</v>
       </c>
-      <c r="D18" s="71" t="s">
+      <c r="D18" s="72" t="s">
         <v>359</v>
       </c>
     </row>
@@ -6086,13 +6091,13 @@
       <c r="A19" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="71" t="s">
         <v>361</v>
       </c>
       <c r="C19" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D19" s="71" t="s">
+      <c r="D19" s="72" t="s">
         <v>362</v>
       </c>
     </row>
@@ -6100,13 +6105,13 @@
       <c r="A20" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="71" t="s">
         <v>364</v>
       </c>
       <c r="C20" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D20" s="71" t="s">
+      <c r="D20" s="72" t="s">
         <v>365</v>
       </c>
     </row>
@@ -6122,13 +6127,13 @@
       <c r="A22" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="B22" s="70" t="s">
+      <c r="B22" s="71" t="s">
         <v>368</v>
       </c>
       <c r="C22" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D22" s="71" t="s">
+      <c r="D22" s="72" t="s">
         <v>369</v>
       </c>
     </row>
@@ -6136,13 +6141,13 @@
       <c r="A23" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="70" t="s">
+      <c r="B23" s="71" t="s">
         <v>371</v>
       </c>
       <c r="C23" s="55" t="s">
         <v>372</v>
       </c>
-      <c r="D23" s="71" t="s">
+      <c r="D23" s="72" t="s">
         <v>373</v>
       </c>
     </row>
@@ -6150,13 +6155,13 @@
       <c r="A24" s="20" t="s">
         <v>374</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="71" t="s">
         <v>375</v>
       </c>
       <c r="C24" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D24" s="71" t="s">
+      <c r="D24" s="72" t="s">
         <v>376</v>
       </c>
     </row>
@@ -6164,13 +6169,13 @@
       <c r="A25" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="71" t="s">
         <v>378</v>
       </c>
       <c r="C25" s="55" t="s">
         <v>334</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="D25" s="72" t="s">
         <v>379</v>
       </c>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -2321,7 +2321,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26" customHeight="1">
       <c r="A1" s="1">
-        <f>IF(PROFIL!B3="","FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]","FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  "&amp;PROFIL!B6)</f>
+        <f>IF(PROFIL!B3="","FICHE D'ANALYSE BRVM — [Completer onglet PROFIL]","FICHE D'ANALYSE BRVM — "&amp;PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  "&amp;IF(ISNUMBER(PROFIL!B6),TEXT(PROFIL!B6,"dd/mm/yyyy"),PROFIL!B6))</f>
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2">
-        <f>IF(PROFIL!B3="","Completer le PROFIL : nom, ticker, secteur, date","Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date : "&amp;PROFIL!B6)</f>
+        <f>IF(PROFIL!B3="","Completer le PROFIL : nom, ticker, secteur, date","Nom : "&amp;PROFIL!B3&amp;"  |  Ticker : "&amp;PROFIL!B4&amp;"  |  Secteur : "&amp;PROFIL!B5&amp;"  |  Date : "&amp;IF(ISNUMBER(PROFIL!B6),TEXT(PROFIL!B6,"dd/mm/yyyy"),PROFIL!B6))</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1">
       <c r="A2" s="2">
-        <f>IF(PROFIL!B3="","Completer le PROFIL",PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;ETUDE!B24&amp;" FCFA  |  Date : "&amp;PROFIL!B6)</f>
+        <f>IF(PROFIL!B3="","Completer le PROFIL",PROFIL!B3&amp;"  ("&amp;PROFIL!B4&amp;")  |  "&amp;PROFIL!B5&amp;"  |  Prix : "&amp;ETUDE!B24&amp;" FCFA  |  Date : "&amp;IF(ISNUMBER(PROFIL!B6),TEXT(PROFIL!B6,"dd/mm/yyyy"),PROFIL!B6))</f>
         <v>0</v>
       </c>
       <c r="B2" s="2"/>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -1423,7 +1423,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1504,12 +1504,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1758,11 +1752,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1774,7 +1767,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1782,7 +1775,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1798,7 +1791,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -4965,7 +4958,10 @@
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="49">
+        <f>IFERROR(IF(ETUDE!G8&gt;=15,3,IF(ETUDE!G8&gt;=5,2,IF(ETUDE!G8&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
@@ -4982,7 +4978,10 @@
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="49">
+        <f>IFERROR(IF(ETUDE!G12&gt;=15,3,IF(ETUDE!G12&gt;=5,2,IF(ETUDE!G12&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
@@ -4999,7 +4998,10 @@
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="49"/>
+      <c r="E8" s="49">
+        <f>IFERROR(IF(ETUDE!G16&gt;=10,3,IF(ETUDE!G16&gt;=5,2,IF(ETUDE!G16&gt;=2,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
@@ -5016,7 +5018,10 @@
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="49"/>
+      <c r="E9" s="49">
+        <f>IFERROR(IF(ETUDE!B30&lt;9,3,IF(ETUDE!B30&lt;=15,2,IF(ETUDE!B30&lt;=20,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
@@ -5033,7 +5038,10 @@
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="49">
+        <f>IFERROR(IF(ETUDE!B32&lt;1,3,IF(ETUDE!B32&lt;2,1,0)),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
@@ -5050,7 +5058,10 @@
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="49"/>
+      <c r="E11" s="49">
+        <f>IFERROR(IF(ETUDE!B33&gt;=15,3,IF(ETUDE!B33&gt;=10,2,IF(ETUDE!B33&gt;=5,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
@@ -5067,7 +5078,10 @@
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="49">
+        <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=6,3,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,2,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=1,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
@@ -5084,7 +5098,10 @@
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="49"/>
+      <c r="E13" s="49">
+        <f>IFERROR(IF(ETUDE!B34&lt;10,3,IF(ETUDE!B34&lt;22,2,IF(ETUDE!B34&lt;30,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
@@ -5140,7 +5157,10 @@
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="49"/>
+      <c r="E18" s="49">
+        <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
@@ -5157,7 +5177,10 @@
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="49"/>
+      <c r="E19" s="49">
+        <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
@@ -5174,7 +5197,10 @@
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49"/>
+      <c r="E20" s="49">
+        <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
@@ -5191,7 +5217,10 @@
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="49"/>
+      <c r="E21" s="49">
+        <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
@@ -5208,7 +5237,10 @@
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="49"/>
+      <c r="E22" s="49">
+        <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="20" t="s">

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -10,14 +10,15 @@
     <sheet name="ETUDE" sheetId="1" r:id="rId1"/>
     <sheet name="SYNTHESE" sheetId="2" r:id="rId2"/>
     <sheet name="PROFIL" sheetId="3" r:id="rId3"/>
-    <sheet name="FORMULE" sheetId="4" r:id="rId4"/>
+    <sheet name="PORTEFEUILLE" sheetId="4" r:id="rId4"/>
+    <sheet name="FORMULE" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="465">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -724,6 +725,174 @@
     <t>Dividende verse regulierement ?</t>
   </si>
   <si>
+    <t>E — ANALYSE DU BILAN  (saisir dans PROFIL — section BILAN)</t>
+  </si>
+  <si>
+    <t>E1 — STRUCTURE DE LA DETTE</t>
+  </si>
+  <si>
+    <t>Reference / Seuils</t>
+  </si>
+  <si>
+    <t>Dette long terme (FCFA)</t>
+  </si>
+  <si>
+    <t>Bilan passif non courant</t>
+  </si>
+  <si>
+    <t>Dette court terme (FCFA)</t>
+  </si>
+  <si>
+    <t>Bilan passif courant</t>
+  </si>
+  <si>
+    <t>Dette totale (FCFA)</t>
+  </si>
+  <si>
+    <t>= LT + CT</t>
+  </si>
+  <si>
+    <t>Gearing (Dette totale / Fonds propres %)</t>
+  </si>
+  <si>
+    <t>&lt; 50% sain | 50-100% eleve | &gt; 100% risque</t>
+  </si>
+  <si>
+    <t>Dette nette / RN annuel (nb annees)</t>
+  </si>
+  <si>
+    <t>&lt; 3 ans sain | 3-5 ans acceptable | &gt; 5 ans excessif</t>
+  </si>
+  <si>
+    <t>E2 — SOLVABILITE &amp; COUVERTURE DES INTERETS</t>
+  </si>
+  <si>
+    <t>EBIT (M FCFA) — depuis PROFIL</t>
+  </si>
+  <si>
+    <t>Resultat avant interets et impots</t>
+  </si>
+  <si>
+    <t>Charges financieres nettes (FCFA)</t>
+  </si>
+  <si>
+    <t>Interets nets payes sur la dette</t>
+  </si>
+  <si>
+    <t>Couverture des interets (x)</t>
+  </si>
+  <si>
+    <t>&gt; 3x sain | 1.5-3x vigilance | &lt; 1.5x risque</t>
+  </si>
+  <si>
+    <t>Ratio Fonds propres / Dette totale (%)</t>
+  </si>
+  <si>
+    <t>&gt; 100% solide | 50-100% moyen | &lt; 50% fragile</t>
+  </si>
+  <si>
+    <t>E3 — LIQUIDITE DU BILAN</t>
+  </si>
+  <si>
+    <t>Actifs courants (FCFA)</t>
+  </si>
+  <si>
+    <t>Tresorerie + creances + stocks</t>
+  </si>
+  <si>
+    <t>Passifs courants (FCFA)</t>
+  </si>
+  <si>
+    <t>Dettes court terme &lt; 1 an</t>
+  </si>
+  <si>
+    <t>Ratio de liquidite courant (x)</t>
+  </si>
+  <si>
+    <t>&gt; 2 = tres liquide | 1-2 = OK | &lt; 1 = tension tresorerie</t>
+  </si>
+  <si>
+    <t>Fonds de roulement net (FCFA)</t>
+  </si>
+  <si>
+    <t>&gt; 0 = excedent | &lt; 0 = deficit de liquidite</t>
+  </si>
+  <si>
+    <t>F — ALERTES DE PRIX &amp; VALEUR INTRINSEQUE</t>
+  </si>
+  <si>
+    <t>F1 — VALEUR INTRINSEQUE COMPOSITE  (VMC x2  +  PCD  +  Gordon  quand disponibles)</t>
+  </si>
+  <si>
+    <t>Modele</t>
+  </si>
+  <si>
+    <t>VI estimee (FCFA)</t>
+  </si>
+  <si>
+    <t>Poids</t>
+  </si>
+  <si>
+    <t>Signal vs prix actuel</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>VALEUR INTRINSEQUE COMPOSITE (VI)</t>
+  </si>
+  <si>
+    <t>composite</t>
+  </si>
+  <si>
+    <t>F2 — ZONES D ALERTE PRIX  (depuis VI composite B238)</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Prix seuil (FCFA)</t>
+  </si>
+  <si>
+    <t>Ecart vs prix actuel (%)</t>
+  </si>
+  <si>
+    <t>Action recommandee</t>
+  </si>
+  <si>
+    <t>FORTE OPPORTUNITE  (VI x 0.75)</t>
+  </si>
+  <si>
+    <t>Achat agressif — decote &gt; 25% sur VI</t>
+  </si>
+  <si>
+    <t>ACHAT IDEAL  (VI x 0.85)</t>
+  </si>
+  <si>
+    <t>Achat — marge de securite confortable (15-25%)</t>
+  </si>
+  <si>
+    <t>JUSTE VALEUR  (VI x 1.00)</t>
+  </si>
+  <si>
+    <t>Achat si fondamentaux solides — prime nulle</t>
+  </si>
+  <si>
+    <t>ZONE NEUTRE  (VI x 1.10)</t>
+  </si>
+  <si>
+    <t>Surveiller — prime moderee</t>
+  </si>
+  <si>
+    <t>SURACHAT  (VI x 1.20)</t>
+  </si>
+  <si>
+    <t>Allegement conseille — prime &gt; 20% sur VI</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -790,9 +959,6 @@
     <t>SCORECARD TECHNIQUE</t>
   </si>
   <si>
-    <t>Zone</t>
-  </si>
-  <si>
     <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
   </si>
   <si>
@@ -959,6 +1125,105 @@
   </si>
   <si>
     <t>&lt;-- brvm.org</t>
+  </si>
+  <si>
+    <t>BILAN (depuis rapport annuel)</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan passif non courant</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan passif courant</t>
+  </si>
+  <si>
+    <t>EBIT - Res. avant interets et impots (M FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Compte de resultat</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan actif courant</t>
+  </si>
+  <si>
+    <t>PORTEFEUILLE BRVM — SUIVI DES POSITIONS &amp; RECOMMANDATIONS</t>
+  </si>
+  <si>
+    <t>Saisir Ticker, Secteur, Nb titres, Prix achat, Prix actuel, Dividendes recus/titre, Note ETUDE /39  —  Reste calculé automatiquement</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Secteur</t>
+  </si>
+  <si>
+    <t>Nb titres</t>
+  </si>
+  <si>
+    <t>Prix achat moy.
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Prix actuel
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Div. recus/titre
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Note
+/39</t>
+  </si>
+  <si>
+    <t>Cout total achat
+(auto)</t>
+  </si>
+  <si>
+    <t>Val. actuelle
+(auto)</t>
+  </si>
+  <si>
+    <t>PV/MV+Div
+(auto)</t>
+  </si>
+  <si>
+    <t>Rend. total %
+(auto)</t>
+  </si>
+  <si>
+    <t>Recommandation
+(auto)</t>
+  </si>
+  <si>
+    <t>TOTAL PORTEFEUILLE</t>
+  </si>
+  <si>
+    <t>LEGENDE RECOMMANDATIONS</t>
+  </si>
+  <si>
+    <t>RENFORCER</t>
+  </si>
+  <si>
+    <t>Note &gt;= 24/39 ET rendement total &gt;= 0%   — Fondamentaux solides, titre en gain</t>
+  </si>
+  <si>
+    <t>CONSERVER</t>
+  </si>
+  <si>
+    <t>Note &gt;= 15/39 ET rendement &gt; -5%   — Garder la position, surveiller</t>
+  </si>
+  <si>
+    <t>SURVEILLER</t>
+  </si>
+  <si>
+    <t>Situation ambiguë   — Attendre confirmation avant d'agir</t>
+  </si>
+  <si>
+    <t>VENDRE — Stop</t>
+  </si>
+  <si>
+    <t>Rendement total &lt; -10%   — Stop-loss déclenché, limiter la perte</t>
   </si>
   <si>
     <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
@@ -1171,7 +1436,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1330,6 +1595,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
@@ -1377,14 +1675,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
@@ -1422,8 +1712,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFCBD5E1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92400E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF064E3B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1E40AF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF374151"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E40AF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF374151"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1514,6 +1857,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1564,7 +1919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1740,15 +2095,36 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="24" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1763,7 +2139,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1771,7 +2147,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="27" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1787,27 +2163,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="28" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="30" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="32" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1819,15 +2195,15 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="33" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1835,11 +2211,54 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2301,7 +2720,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -4781,9 +5200,590 @@
       <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8" ht="5" customHeight="1"/>
+    <row r="205" spans="1:8" ht="5" customHeight="1"/>
+    <row r="206" spans="1:8" ht="22" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="1:8" ht="5" customHeight="1"/>
+    <row r="208" spans="1:8" ht="20" customHeight="1">
+      <c r="A208" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4"/>
+      <c r="G209" s="4"/>
+      <c r="H209" s="4"/>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B210" s="9">
+        <f>IFERROR(PROFIL!B40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C210" s="12"/>
+      <c r="D210" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E210" s="12"/>
+      <c r="F210" s="12"/>
+      <c r="G210" s="12"/>
+      <c r="H210" s="12"/>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B211" s="9">
+        <f>IFERROR(PROFIL!B41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C211" s="12"/>
+      <c r="D211" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
+      <c r="G211" s="12"/>
+      <c r="H211" s="12"/>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B212" s="9">
+        <f>IFERROR(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C212" s="12"/>
+      <c r="D212" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12"/>
+      <c r="G212" s="12"/>
+      <c r="H212" s="12"/>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B213" s="7">
+        <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/B26*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C213" s="12"/>
+      <c r="D213" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
+      <c r="G213" s="12"/>
+      <c r="H213" s="12"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B214" s="7">
+        <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/(F12*1000000),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C214" s="12"/>
+      <c r="D214" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
+      <c r="G214" s="12"/>
+      <c r="H214" s="12"/>
+    </row>
+    <row r="215" spans="1:8" ht="5" customHeight="1"/>
+    <row r="216" spans="1:8" ht="20" customHeight="1">
+      <c r="A216" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="3"/>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B218" s="9">
+        <f>IFERROR(PROFIL!B42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C218" s="12"/>
+      <c r="D218" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E218" s="12"/>
+      <c r="F218" s="12"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="12"/>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B219" s="9">
+        <f>IFERROR(PROFIL!B43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C219" s="12"/>
+      <c r="D219" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
+      <c r="G219" s="12"/>
+      <c r="H219" s="12"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B220" s="7">
+        <f>IFERROR(PROFIL!B42*1000000/PROFIL!B43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C220" s="12"/>
+      <c r="D220" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="E220" s="12"/>
+      <c r="F220" s="12"/>
+      <c r="G220" s="12"/>
+      <c r="H220" s="12"/>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B221" s="7">
+        <f>IFERROR(B26/(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C221" s="12"/>
+      <c r="D221" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
+      <c r="G221" s="12"/>
+      <c r="H221" s="12"/>
+    </row>
+    <row r="222" spans="1:8" ht="5" customHeight="1"/>
+    <row r="223" spans="1:8" ht="20" customHeight="1">
+      <c r="A223" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="3"/>
+      <c r="G223" s="3"/>
+      <c r="H223" s="3"/>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4"/>
+      <c r="H224" s="4"/>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B225" s="9">
+        <f>IFERROR(PROFIL!B44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C225" s="12"/>
+      <c r="D225" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
+      <c r="G225" s="12"/>
+      <c r="H225" s="12"/>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B226" s="9">
+        <f>IFERROR(PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C226" s="12"/>
+      <c r="D226" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E226" s="12"/>
+      <c r="F226" s="12"/>
+      <c r="G226" s="12"/>
+      <c r="H226" s="12"/>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B227" s="7">
+        <f>IFERROR(PROFIL!B44/PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C227" s="12"/>
+      <c r="D227" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
+      <c r="G227" s="12"/>
+      <c r="H227" s="12"/>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B228" s="9">
+        <f>IFERROR(PROFIL!B44-PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C228" s="12"/>
+      <c r="D228" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="E228" s="12"/>
+      <c r="F228" s="12"/>
+      <c r="G228" s="12"/>
+      <c r="H228" s="12"/>
+    </row>
+    <row r="229" spans="1:8" ht="5" customHeight="1"/>
+    <row r="230" spans="1:8" ht="5" customHeight="1"/>
+    <row r="231" spans="1:8" ht="22" customHeight="1">
+      <c r="A231" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+    </row>
+    <row r="232" spans="1:8" ht="5" customHeight="1"/>
+    <row r="233" spans="1:8" ht="20" customHeight="1">
+      <c r="A233" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
+      <c r="E233" s="3"/>
+      <c r="F233" s="3"/>
+      <c r="G233" s="3"/>
+      <c r="H233" s="3"/>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4"/>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="5">
+        <f>IF(ISNUMBER(B31),"VMC  =  "&amp;TEXT(ROUND(B31,0),"#,##0")&amp;" FCFA","VMC — N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="B235" s="9">
+        <f>IFERROR(B31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C235" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="D235" s="47">
+        <f>IFERROR(IF(B24&lt;B31,"Prix SOUS VMC — decote comptable","Prix AU-DESSUS VMC"),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="5">
+        <f>IF(ISNUMBER(B113),"PCD  =  "&amp;TEXT(ROUND(B113,0),"#,##0")&amp;" FCFA","PCD — N/A (pas de dividende)")</f>
+        <v>0</v>
+      </c>
+      <c r="B236" s="9">
+        <f>IFERROR(IF(ISNUMBER(B113),B113,""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C236" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D236" s="47">
+        <f>IFERROR(IF(NOT(ISNUMBER(B113)),"Non disponible — dividend = 0",IF(B24&lt;B113,"Prix SOUS PCD — survente","Prix AU-DESSUS PCD — surachat")),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+      <c r="G236" s="12"/>
+      <c r="H236" s="12"/>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="5">
+        <f>IF(ISNUMBER(B124),"Gordon P0  =  "&amp;TEXT(ROUND(B124,0),"#,##0")&amp;" FCFA","Gordon P0 — N/A (saisir D1)")</f>
+        <v>0</v>
+      </c>
+      <c r="B237" s="9">
+        <f>IFERROR(IF(ISNUMBER(B124),B124,""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C237" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D237" s="47">
+        <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Non disponible — saisir D1",IF(B24&lt;B124,"Prix SOUS P0 — opportunite","Prix AU-DESSUS P0 — surevalue")),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
+      <c r="G237" s="12"/>
+      <c r="H237" s="12"/>
+    </row>
+    <row r="238" spans="1:8" ht="30" customHeight="1">
+      <c r="A238" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B238" s="48">
+        <f>IFERROR((B31*2+IF(ISNUMBER(B113),B113,0)+IF(ISNUMBER(B124),B124,0))/(2+IF(ISNUMBER(B113),1,0)+IF(ISNUMBER(B124),1,0)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C238" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="D238" s="49">
+        <f>IFERROR(IF(B24&lt;B238*0.75,"FORTE OPPORTUNITE — decote &gt; 25%",IF(B24&lt;B238*0.85,"Achat ideal — decote 15-25%",IF(B24&lt;B238,"Legerement sous-evalue",IF(B24&lt;B238*1.20,"Zone normale / prime moderee","ATTENTION — surevaluation &gt; 20%")))),"Saisir prix actuel (B24)")</f>
+        <v>0</v>
+      </c>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12"/>
+    </row>
+    <row r="239" spans="1:8" ht="5" customHeight="1"/>
+    <row r="240" spans="1:8" ht="20" customHeight="1">
+      <c r="A240" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="3"/>
+      <c r="G240" s="3"/>
+      <c r="H240" s="3"/>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="4"/>
+      <c r="H241" s="4"/>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B242" s="9">
+        <f>IFERROR(B238*0.75,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C242" s="50">
+        <f>IFERROR((B24/(B238*0.75)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D242" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
+      <c r="G242" s="12"/>
+      <c r="H242" s="12"/>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B243" s="9">
+        <f>IFERROR(B238*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C243" s="50">
+        <f>IFERROR((B24/(B238*0.85)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D243" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
+      <c r="G243" s="12"/>
+      <c r="H243" s="12"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B244" s="9">
+        <f>IFERROR(B238,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C244" s="50">
+        <f>IFERROR((B24/B238-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D244" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="12"/>
+      <c r="H244" s="12"/>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B245" s="9">
+        <f>IFERROR(B238*1.10,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C245" s="50">
+        <f>IFERROR((B24/(B238*1.10)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D245" s="51" t="s">
+        <v>288</v>
+      </c>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
+      <c r="G245" s="12"/>
+      <c r="H245" s="12"/>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B246" s="9">
+        <f>IFERROR(B238*1.20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C246" s="50">
+        <f>IFERROR((B24/(B238*1.20)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D246" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
+      <c r="G246" s="12"/>
+      <c r="H246" s="12"/>
+    </row>
+    <row r="247" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="44">
+  <mergeCells count="51">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -4828,6 +5828,13 @@
     <mergeCell ref="A184:H184"/>
     <mergeCell ref="A191:H191"/>
     <mergeCell ref="A198:H198"/>
+    <mergeCell ref="A206:H206"/>
+    <mergeCell ref="A208:H208"/>
+    <mergeCell ref="A216:H216"/>
+    <mergeCell ref="A223:H223"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A233:H233"/>
+    <mergeCell ref="A240:H240"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -4899,7 +5906,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4918,212 +5925,212 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
+      <c r="A4" s="52" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
         <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>237</v>
+        <v>293</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>238</v>
+        <v>294</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>239</v>
+        <v>295</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="47">
+        <v>297</v>
+      </c>
+      <c r="B6" s="53">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6" s="48">
+        <v>298</v>
+      </c>
+      <c r="D6" s="54">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="55">
         <f>IFERROR(IF(ETUDE!G8&gt;=15,3,IF(ETUDE!G8&gt;=5,2,IF(ETUDE!G8&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="47">
+        <v>299</v>
+      </c>
+      <c r="B7" s="53">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="48">
+        <v>298</v>
+      </c>
+      <c r="D7" s="54">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="55">
         <f>IFERROR(IF(ETUDE!G12&gt;=15,3,IF(ETUDE!G12&gt;=5,2,IF(ETUDE!G12&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="47">
+        <v>300</v>
+      </c>
+      <c r="B8" s="53">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="48">
+        <v>301</v>
+      </c>
+      <c r="D8" s="54">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="49">
+      <c r="E8" s="55">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,3,IF(ETUDE!G16&gt;=5,2,IF(ETUDE!G16&gt;=2,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="47">
+        <v>302</v>
+      </c>
+      <c r="B9" s="53">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="48">
+        <v>303</v>
+      </c>
+      <c r="D9" s="54">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="49">
+      <c r="E9" s="55">
         <f>IFERROR(IF(ETUDE!B30&lt;9,3,IF(ETUDE!B30&lt;=15,2,IF(ETUDE!B30&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B10" s="47">
+        <v>304</v>
+      </c>
+      <c r="B10" s="53">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="48">
+        <v>305</v>
+      </c>
+      <c r="D10" s="54">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="49">
+      <c r="E10" s="55">
         <f>IFERROR(IF(ETUDE!B32&lt;1,3,IF(ETUDE!B32&lt;2,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="47">
+        <v>306</v>
+      </c>
+      <c r="B11" s="53">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="48">
+        <v>298</v>
+      </c>
+      <c r="D11" s="54">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="49">
+      <c r="E11" s="55">
         <f>IFERROR(IF(ETUDE!B33&gt;=15,3,IF(ETUDE!B33&gt;=10,2,IF(ETUDE!B33&gt;=5,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12" s="47">
+        <v>307</v>
+      </c>
+      <c r="B12" s="53">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="48">
+        <v>308</v>
+      </c>
+      <c r="D12" s="54">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="55">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=6,3,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,2,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B13" s="47">
+        <v>309</v>
+      </c>
+      <c r="B13" s="53">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="48">
+        <v>310</v>
+      </c>
+      <c r="D13" s="54">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="55">
         <f>IFERROR(IF(ETUDE!B34&lt;10,3,IF(ETUDE!B34&lt;22,2,IF(ETUDE!B34&lt;30,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+        <v>311</v>
+      </c>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="57">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="A16" s="52" t="s">
+        <v>312</v>
+      </c>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -5133,7 +6140,7 @@
         <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>17</v>
@@ -5144,125 +6151,125 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B18" s="52">
+        <v>313</v>
+      </c>
+      <c r="B18" s="58">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="48">
+        <v>314</v>
+      </c>
+      <c r="D18" s="54">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="55">
         <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B19" s="52">
+        <v>315</v>
+      </c>
+      <c r="B19" s="58">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="48">
+        <v>316</v>
+      </c>
+      <c r="D19" s="54">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="55">
         <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B20" s="52">
+        <v>317</v>
+      </c>
+      <c r="B20" s="58">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="48">
+        <v>318</v>
+      </c>
+      <c r="D20" s="54">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49">
+      <c r="E20" s="55">
         <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B21" s="52">
+        <v>319</v>
+      </c>
+      <c r="B21" s="58">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="48">
+        <v>320</v>
+      </c>
+      <c r="D21" s="54">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="49">
+      <c r="E21" s="55">
         <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="52">
+        <v>321</v>
+      </c>
+      <c r="B22" s="58">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D22" s="48">
+        <v>322</v>
+      </c>
+      <c r="D22" s="54">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="55">
         <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="51">
+        <v>323</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="57">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="53" t="s">
-        <v>269</v>
-      </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
+      <c r="A25" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -5272,133 +6279,133 @@
         <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="54">
+        <v>328</v>
+      </c>
+      <c r="B27" s="60">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="61">
         <v>24</v>
       </c>
-      <c r="D27" s="56">
+      <c r="D27" s="62">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="63">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B28" s="54">
+        <v>329</v>
+      </c>
+      <c r="B28" s="60">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="61">
         <v>15</v>
       </c>
-      <c r="D28" s="56">
+      <c r="D28" s="62">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="63">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="58">
+        <v>330</v>
+      </c>
+      <c r="B29" s="64">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="65">
         <v>39</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="62">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="66">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
+      <c r="A31" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>280</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="61">
+      <c r="A33" s="67">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="62">
+      <c r="B33" s="68">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="63">
+      <c r="C33" s="69">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="69">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="64">
+      <c r="E33" s="70">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
+      <c r="A35" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
       <c r="A36" s="28"/>
@@ -5550,7 +6557,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -5561,7 +6568,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>282</v>
+        <v>337</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5569,56 +6576,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>338</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="67" t="s">
-        <v>285</v>
+      <c r="A3" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="73" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="65" t="s">
-        <v>286</v>
-      </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="67" t="s">
-        <v>287</v>
+      <c r="A4" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="72"/>
+      <c r="D4" s="73" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="67" t="s">
-        <v>289</v>
+      <c r="A5" s="71" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="73" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="65" t="s">
-        <v>290</v>
-      </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="67" t="s">
-        <v>291</v>
+      <c r="A6" s="71" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="73" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>292</v>
+        <v>347</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5626,63 +6633,63 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>293</v>
+        <v>348</v>
       </c>
       <c r="B9" s="45">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>286</v>
+        <v>341</v>
       </c>
       <c r="B10" s="45">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="B11" s="45">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>294</v>
+        <v>349</v>
       </c>
       <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B12" s="69"/>
+        <v>351</v>
+      </c>
+      <c r="B12" s="75"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B13" s="69"/>
+        <v>352</v>
+      </c>
+      <c r="B13" s="75"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>353</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5692,15 +6699,15 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="75"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B17" s="69"/>
+        <v>354</v>
+      </c>
+      <c r="B17" s="75"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
@@ -5708,7 +6715,7 @@
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="69"/>
+      <c r="B18" s="75"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
@@ -5716,14 +6723,14 @@
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="69"/>
+      <c r="B19" s="75"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5734,7 +6741,7 @@
         <v>227</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -5743,7 +6750,7 @@
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="69"/>
+      <c r="B23" s="75"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
@@ -5752,7 +6759,7 @@
         <v>229</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -5762,7 +6769,7 @@
         <v>230</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>303</v>
+        <v>358</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -5770,7 +6777,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -5780,7 +6787,7 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="69"/>
+      <c r="B28" s="75"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
@@ -5788,7 +6795,7 @@
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="69"/>
+      <c r="B29" s="75"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
@@ -5796,7 +6803,7 @@
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="69"/>
+      <c r="B30" s="75"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
@@ -5805,7 +6812,7 @@
         <v>234</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>305</v>
+        <v>360</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -5813,7 +6820,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>306</v>
+        <v>361</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5821,46 +6828,115 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>307</v>
+        <v>362</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>308</v>
+        <v>363</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B35" s="69"/>
+        <v>364</v>
+      </c>
+      <c r="B35" s="75"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>310</v>
+        <v>365</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>311</v>
+        <v>366</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>312</v>
+        <v>367</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
+    <row r="39" spans="1:4" ht="20" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>373</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>374</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:C3"/>
@@ -5872,12 +6948,675 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF059669"/>
+  </sheetPr>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="26" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" ht="16" customHeight="1">
+      <c r="A2" s="76" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+    </row>
+    <row r="3" spans="1:12" ht="5" customHeight="1"/>
+    <row r="4" spans="1:12" ht="32" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20" customHeight="1">
+      <c r="A5" s="77"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="79">
+        <f>IFERROR(IF(A5="","",C5*D5*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="79">
+        <f>IFERROR(IF(A5="","",C5*E5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="79">
+        <f>IFERROR(IF(A5="","",(C5*E5)-(C5*D5*1.014)+(C5*F5)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="80">
+        <f>IFERROR(IF(A5="","",J5/H5*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="81">
+        <f>IFERROR(IF(A5="","—",IF(K5&lt;-10,"VENDRE — Stop-loss",IF(AND(G5&gt;=24,K5&gt;=0),"RENFORCER",IF(AND(G5&gt;=15,K5&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="20" customHeight="1">
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="79">
+        <f>IFERROR(IF(A6="","",C6*D6*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="79">
+        <f>IFERROR(IF(A6="","",C6*E6),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="79">
+        <f>IFERROR(IF(A6="","",(C6*E6)-(C6*D6*1.014)+(C6*F6)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="80">
+        <f>IFERROR(IF(A6="","",J6/H6*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="81">
+        <f>IFERROR(IF(A6="","—",IF(K6&lt;-10,"VENDRE — Stop-loss",IF(AND(G6&gt;=24,K6&gt;=0),"RENFORCER",IF(AND(G6&gt;=15,K6&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="20" customHeight="1">
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="78"/>
+      <c r="E7" s="78"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="79">
+        <f>IFERROR(IF(A7="","",C7*D7*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="79">
+        <f>IFERROR(IF(A7="","",C7*E7),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="79">
+        <f>IFERROR(IF(A7="","",(C7*E7)-(C7*D7*1.014)+(C7*F7)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="80">
+        <f>IFERROR(IF(A7="","",J7/H7*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="81">
+        <f>IFERROR(IF(A7="","—",IF(K7&lt;-10,"VENDRE — Stop-loss",IF(AND(G7&gt;=24,K7&gt;=0),"RENFORCER",IF(AND(G7&gt;=15,K7&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20" customHeight="1">
+      <c r="A8" s="77"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
+      <c r="D8" s="78"/>
+      <c r="E8" s="78"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79">
+        <f>IFERROR(IF(A8="","",C8*D8*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="79">
+        <f>IFERROR(IF(A8="","",C8*E8),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="79">
+        <f>IFERROR(IF(A8="","",(C8*E8)-(C8*D8*1.014)+(C8*F8)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="80">
+        <f>IFERROR(IF(A8="","",J8/H8*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="81">
+        <f>IFERROR(IF(A8="","—",IF(K8&lt;-10,"VENDRE — Stop-loss",IF(AND(G8&gt;=24,K8&gt;=0),"RENFORCER",IF(AND(G8&gt;=15,K8&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="20" customHeight="1">
+      <c r="A9" s="77"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79">
+        <f>IFERROR(IF(A9="","",C9*D9*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="79">
+        <f>IFERROR(IF(A9="","",C9*E9),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="79">
+        <f>IFERROR(IF(A9="","",(C9*E9)-(C9*D9*1.014)+(C9*F9)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="80">
+        <f>IFERROR(IF(A9="","",J9/H9*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="81">
+        <f>IFERROR(IF(A9="","—",IF(K9&lt;-10,"VENDRE — Stop-loss",IF(AND(G9&gt;=24,K9&gt;=0),"RENFORCER",IF(AND(G9&gt;=15,K9&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="20" customHeight="1">
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="78"/>
+      <c r="G10" s="78"/>
+      <c r="H10" s="79">
+        <f>IFERROR(IF(A10="","",C10*D10*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="79">
+        <f>IFERROR(IF(A10="","",C10*E10),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="79">
+        <f>IFERROR(IF(A10="","",(C10*E10)-(C10*D10*1.014)+(C10*F10)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="80">
+        <f>IFERROR(IF(A10="","",J10/H10*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="81">
+        <f>IFERROR(IF(A10="","—",IF(K10&lt;-10,"VENDRE — Stop-loss",IF(AND(G10&gt;=24,K10&gt;=0),"RENFORCER",IF(AND(G10&gt;=15,K10&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="20" customHeight="1">
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79">
+        <f>IFERROR(IF(A11="","",C11*D11*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="79">
+        <f>IFERROR(IF(A11="","",C11*E11),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="79">
+        <f>IFERROR(IF(A11="","",(C11*E11)-(C11*D11*1.014)+(C11*F11)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="80">
+        <f>IFERROR(IF(A11="","",J11/H11*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="81">
+        <f>IFERROR(IF(A11="","—",IF(K11&lt;-10,"VENDRE — Stop-loss",IF(AND(G11&gt;=24,K11&gt;=0),"RENFORCER",IF(AND(G11&gt;=15,K11&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="20" customHeight="1">
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="79">
+        <f>IFERROR(IF(A12="","",C12*D12*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="79">
+        <f>IFERROR(IF(A12="","",C12*E12),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="79">
+        <f>IFERROR(IF(A12="","",(C12*E12)-(C12*D12*1.014)+(C12*F12)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="80">
+        <f>IFERROR(IF(A12="","",J12/H12*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="81">
+        <f>IFERROR(IF(A12="","—",IF(K12&lt;-10,"VENDRE — Stop-loss",IF(AND(G12&gt;=24,K12&gt;=0),"RENFORCER",IF(AND(G12&gt;=15,K12&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="20" customHeight="1">
+      <c r="A13" s="77"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="78"/>
+      <c r="F13" s="78"/>
+      <c r="G13" s="78"/>
+      <c r="H13" s="79">
+        <f>IFERROR(IF(A13="","",C13*D13*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="79">
+        <f>IFERROR(IF(A13="","",C13*E13),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="79">
+        <f>IFERROR(IF(A13="","",(C13*E13)-(C13*D13*1.014)+(C13*F13)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="80">
+        <f>IFERROR(IF(A13="","",J13/H13*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="81">
+        <f>IFERROR(IF(A13="","—",IF(K13&lt;-10,"VENDRE — Stop-loss",IF(AND(G13&gt;=24,K13&gt;=0),"RENFORCER",IF(AND(G13&gt;=15,K13&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="20" customHeight="1">
+      <c r="A14" s="77"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="79">
+        <f>IFERROR(IF(A14="","",C14*D14*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="79">
+        <f>IFERROR(IF(A14="","",C14*E14),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="79">
+        <f>IFERROR(IF(A14="","",(C14*E14)-(C14*D14*1.014)+(C14*F14)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="80">
+        <f>IFERROR(IF(A14="","",J14/H14*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="81">
+        <f>IFERROR(IF(A14="","—",IF(K14&lt;-10,"VENDRE — Stop-loss",IF(AND(G14&gt;=24,K14&gt;=0),"RENFORCER",IF(AND(G14&gt;=15,K14&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="20" customHeight="1">
+      <c r="A15" s="77"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="79">
+        <f>IFERROR(IF(A15="","",C15*D15*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="79">
+        <f>IFERROR(IF(A15="","",C15*E15),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="79">
+        <f>IFERROR(IF(A15="","",(C15*E15)-(C15*D15*1.014)+(C15*F15)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="80">
+        <f>IFERROR(IF(A15="","",J15/H15*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="81">
+        <f>IFERROR(IF(A15="","—",IF(K15&lt;-10,"VENDRE — Stop-loss",IF(AND(G15&gt;=24,K15&gt;=0),"RENFORCER",IF(AND(G15&gt;=15,K15&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="20" customHeight="1">
+      <c r="A16" s="77"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="78"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="79">
+        <f>IFERROR(IF(A16="","",C16*D16*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="79">
+        <f>IFERROR(IF(A16="","",C16*E16),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="79">
+        <f>IFERROR(IF(A16="","",(C16*E16)-(C16*D16*1.014)+(C16*F16)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="80">
+        <f>IFERROR(IF(A16="","",J16/H16*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="81">
+        <f>IFERROR(IF(A16="","—",IF(K16&lt;-10,"VENDRE — Stop-loss",IF(AND(G16&gt;=24,K16&gt;=0),"RENFORCER",IF(AND(G16&gt;=15,K16&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20" customHeight="1">
+      <c r="A17" s="77"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="79">
+        <f>IFERROR(IF(A17="","",C17*D17*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="79">
+        <f>IFERROR(IF(A17="","",C17*E17),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="79">
+        <f>IFERROR(IF(A17="","",(C17*E17)-(C17*D17*1.014)+(C17*F17)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="80">
+        <f>IFERROR(IF(A17="","",J17/H17*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="81">
+        <f>IFERROR(IF(A17="","—",IF(K17&lt;-10,"VENDRE — Stop-loss",IF(AND(G17&gt;=24,K17&gt;=0),"RENFORCER",IF(AND(G17&gt;=15,K17&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="20" customHeight="1">
+      <c r="A18" s="77"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="79">
+        <f>IFERROR(IF(A18="","",C18*D18*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="79">
+        <f>IFERROR(IF(A18="","",C18*E18),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="79">
+        <f>IFERROR(IF(A18="","",(C18*E18)-(C18*D18*1.014)+(C18*F18)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="80">
+        <f>IFERROR(IF(A18="","",J18/H18*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="81">
+        <f>IFERROR(IF(A18="","—",IF(K18&lt;-10,"VENDRE — Stop-loss",IF(AND(G18&gt;=24,K18&gt;=0),"RENFORCER",IF(AND(G18&gt;=15,K18&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="20" customHeight="1">
+      <c r="A19" s="77"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="79">
+        <f>IFERROR(IF(A19="","",C19*D19*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="79">
+        <f>IFERROR(IF(A19="","",C19*E19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="79">
+        <f>IFERROR(IF(A19="","",(C19*E19)-(C19*D19*1.014)+(C19*F19)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="80">
+        <f>IFERROR(IF(A19="","",J19/H19*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="81">
+        <f>IFERROR(IF(A19="","—",IF(K19&lt;-10,"VENDRE — Stop-loss",IF(AND(G19&gt;=24,K19&gt;=0),"RENFORCER",IF(AND(G19&gt;=15,K19&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="5" customHeight="1"/>
+    <row r="21" spans="1:12" ht="22" customHeight="1">
+      <c r="A21" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="82"/>
+      <c r="G21" s="82"/>
+      <c r="H21" s="83">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="83">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="83">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="84">
+        <f>IFERROR(J21/H21*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="81">
+        <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="8" customHeight="1"/>
+    <row r="23" spans="1:12" ht="18" customHeight="1">
+      <c r="A23" s="85" t="s">
+        <v>390</v>
+      </c>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="85"/>
+      <c r="I23" s="85"/>
+      <c r="J23" s="85"/>
+      <c r="K23" s="85"/>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" spans="1:12" ht="16" customHeight="1">
+      <c r="A24" s="86" t="s">
+        <v>391</v>
+      </c>
+      <c r="B24" s="87" t="s">
+        <v>392</v>
+      </c>
+      <c r="C24" s="87"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+      <c r="I24" s="87"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="87"/>
+      <c r="L24" s="87"/>
+    </row>
+    <row r="25" spans="1:12" ht="16" customHeight="1">
+      <c r="A25" s="86" t="s">
+        <v>393</v>
+      </c>
+      <c r="B25" s="87" t="s">
+        <v>394</v>
+      </c>
+      <c r="C25" s="87"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
+      <c r="L25" s="87"/>
+    </row>
+    <row r="26" spans="1:12" ht="16" customHeight="1">
+      <c r="A26" s="86" t="s">
+        <v>395</v>
+      </c>
+      <c r="B26" s="87" t="s">
+        <v>396</v>
+      </c>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
+      <c r="L26" s="87"/>
+    </row>
+    <row r="27" spans="1:12" ht="16" customHeight="1">
+      <c r="A27" s="86" t="s">
+        <v>397</v>
+      </c>
+      <c r="B27" s="87" t="s">
+        <v>398</v>
+      </c>
+      <c r="C27" s="87"/>
+      <c r="D27" s="87"/>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+      <c r="I27" s="87"/>
+      <c r="J27" s="87"/>
+      <c r="K27" s="87"/>
+      <c r="L27" s="87"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="B25:L25"/>
+    <mergeCell ref="B26:L26"/>
+    <mergeCell ref="B27:L27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF374151"/>
@@ -5893,322 +7632,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="88" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="70" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>316</v>
-      </c>
-      <c r="D2" s="70" t="s">
-        <v>317</v>
+      <c r="B2" s="88" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="88" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="88" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="A3" s="52" t="s">
+        <v>403</v>
+      </c>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>320</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>322</v>
+        <v>404</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D4" s="90" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>324</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>325</v>
+        <v>408</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>409</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>328</v>
+        <v>411</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>412</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" s="90" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="71" t="s">
-        <v>329</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>331</v>
+        <v>302</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>414</v>
+      </c>
+      <c r="C7" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="D7" s="90" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B8" s="71" t="s">
-        <v>333</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>335</v>
+        <v>417</v>
+      </c>
+      <c r="B8" s="89" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>336</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>337</v>
+        <v>304</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>421</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="D9" s="90" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>340</v>
+        <v>423</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>424</v>
+      </c>
+      <c r="C10" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="72" t="s">
-        <v>343</v>
+        <v>426</v>
+      </c>
+      <c r="B11" s="89" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="90" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" s="71" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>346</v>
+        <v>429</v>
+      </c>
+      <c r="B12" s="89" t="s">
+        <v>430</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>348</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>349</v>
+        <v>432</v>
+      </c>
+      <c r="B13" s="89" t="s">
+        <v>433</v>
+      </c>
+      <c r="C13" s="61" t="s">
+        <v>406</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="46" t="s">
-        <v>350</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
+      <c r="A14" s="52" t="s">
+        <v>435</v>
+      </c>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>352</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D15" s="72" t="s">
-        <v>353</v>
+        <v>436</v>
+      </c>
+      <c r="B15" s="89" t="s">
+        <v>437</v>
+      </c>
+      <c r="C15" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D15" s="90" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="B16" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="72" t="s">
-        <v>356</v>
+        <v>439</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>440</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="90" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="72" t="s">
-        <v>357</v>
+      <c r="B17" s="89" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="90" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="71" t="s">
-        <v>358</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="72" t="s">
-        <v>359</v>
+      <c r="B18" s="89" t="s">
+        <v>443</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>415</v>
+      </c>
+      <c r="D18" s="90" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B19" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="72" t="s">
-        <v>362</v>
+        <v>445</v>
+      </c>
+      <c r="B19" s="89" t="s">
+        <v>446</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D19" s="90" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>364</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>365</v>
+        <v>448</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D20" s="90" t="s">
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="46" t="s">
-        <v>366</v>
-      </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
+      <c r="A21" s="52" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>369</v>
+        <v>452</v>
+      </c>
+      <c r="B22" s="89" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D22" s="90" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="B23" s="71" t="s">
-        <v>371</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>372</v>
-      </c>
-      <c r="D23" s="72" t="s">
-        <v>373</v>
+        <v>455</v>
+      </c>
+      <c r="B23" s="89" t="s">
+        <v>456</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>457</v>
+      </c>
+      <c r="D23" s="90" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="B24" s="71" t="s">
-        <v>375</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>376</v>
+        <v>459</v>
+      </c>
+      <c r="B24" s="89" t="s">
+        <v>460</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="B25" s="71" t="s">
-        <v>378</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>379</v>
+        <v>462</v>
+      </c>
+      <c r="B25" s="89" t="s">
+        <v>463</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="D25" s="90" t="s">
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="486">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -891,6 +891,69 @@
   </si>
   <si>
     <t>Allegement conseille — prime &gt; 20% sur VI</t>
+  </si>
+  <si>
+    <t>G — ANALYSE CYCLIQUE  (agro-industrie BRVM : caoutchouc, huile de palme, cacao...)</t>
+  </si>
+  <si>
+    <t>G1 — EXPOSITION AUX MATIERES PREMIERES  (jusqu'a 3 matieres par societe)</t>
+  </si>
+  <si>
+    <t>Liste : choisir la matiere | saisir % CA et prix actuel | moy. LT 10 ans auto-remplie | Pour 'Autre' : laisser D vide et saisir la moy. LT en colonne E</t>
+  </si>
+  <si>
+    <t>Matiere premiere</t>
+  </si>
+  <si>
+    <t>% CA</t>
+  </si>
+  <si>
+    <t>Prix actuel</t>
+  </si>
+  <si>
+    <t>Moy. LT auto</t>
+  </si>
+  <si>
+    <t>Moy. LT (Autre)</t>
+  </si>
+  <si>
+    <t>Ratio cycle</t>
+  </si>
+  <si>
+    <t>Total % CA renseigne</t>
+  </si>
+  <si>
+    <t>G2 — INDICE DE CYCLE COMPOSITE  (pondere par le % du CA de chaque matiere)</t>
+  </si>
+  <si>
+    <t>Interpretation &amp; Conduite a tenir</t>
+  </si>
+  <si>
+    <t>Indice cycle composite (pondere % CA)</t>
+  </si>
+  <si>
+    <t>Phase du cycle detectee</t>
+  </si>
+  <si>
+    <t>Nb matieres renseignees</t>
+  </si>
+  <si>
+    <t>G3 — VALORISATION ADAPTEE AUX CYCLIQUES  (PER normalise sur cycle 5 ans)</t>
+  </si>
+  <si>
+    <t>Signal / Interpretation</t>
+  </si>
+  <si>
+    <t>BPA normalise 5 ans (FCFA)</t>
+  </si>
+  <si>
+    <t>= RN moyen 5 ans / Nb titres. Lisse les pics et creux de cycle.</t>
+  </si>
+  <si>
+    <t>PER normalise cycle (Prix / BPA moyen 5 ans)</t>
+  </si>
+  <si>
+    <t>VERDICT CYCLIQUE FINAL</t>
   </si>
   <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
@@ -1436,7 +1499,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1628,6 +1691,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
@@ -1700,14 +1779,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF1E293B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF6B7280"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1919,7 +1990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2116,15 +2187,41 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="26" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2139,7 +2236,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2147,7 +2244,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="29" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2163,11 +2260,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="30" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2175,15 +2272,15 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="30" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="32" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="34" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2195,44 +2292,36 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="35" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="33" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="37" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="38" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2246,11 +2335,11 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2258,7 +2347,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2720,7 +2809,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -5781,9 +5870,309 @@
       <c r="H246" s="12"/>
     </row>
     <row r="247" spans="1:8" ht="5" customHeight="1"/>
+    <row r="248" spans="1:8" ht="5" customHeight="1"/>
+    <row r="249" spans="1:8" ht="22" customHeight="1">
+      <c r="A249" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+    </row>
+    <row r="250" spans="1:8" ht="5" customHeight="1"/>
+    <row r="251" spans="1:8" ht="20" customHeight="1">
+      <c r="A251" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
+      <c r="E251" s="3"/>
+      <c r="F251" s="3"/>
+      <c r="G251" s="3"/>
+      <c r="H251" s="3"/>
+    </row>
+    <row r="252" spans="1:8" ht="14" customHeight="1">
+      <c r="A252" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="B252" s="34"/>
+      <c r="C252" s="34"/>
+      <c r="D252" s="34"/>
+      <c r="E252" s="34"/>
+      <c r="F252" s="34"/>
+      <c r="G252" s="34"/>
+      <c r="H252" s="34"/>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H253" s="4"/>
+    </row>
+    <row r="254" spans="1:8" ht="18" customHeight="1">
+      <c r="A254" s="52"/>
+      <c r="B254" s="33"/>
+      <c r="C254" s="33"/>
+      <c r="D254" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A254,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E254" s="33"/>
+      <c r="F254" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C254),OR(D254&lt;&gt;"",ISNUMBER(E254))),C254/IF(D254&lt;&gt;"",D254,E254),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G254" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F254)),"—",IF(F254&lt;0.85,"BAS — opportunite acheteur",IF(F254&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H254" s="12"/>
+    </row>
+    <row r="255" spans="1:8" ht="18" customHeight="1">
+      <c r="A255" s="52"/>
+      <c r="B255" s="33"/>
+      <c r="C255" s="33"/>
+      <c r="D255" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A255,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E255" s="33"/>
+      <c r="F255" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C255),OR(D255&lt;&gt;"",ISNUMBER(E255))),C255/IF(D255&lt;&gt;"",D255,E255),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G255" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F255)),"—",IF(F255&lt;0.85,"BAS — opportunite acheteur",IF(F255&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H255" s="12"/>
+    </row>
+    <row r="256" spans="1:8" ht="18" customHeight="1">
+      <c r="A256" s="52"/>
+      <c r="B256" s="33"/>
+      <c r="C256" s="33"/>
+      <c r="D256" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A256,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E256" s="33"/>
+      <c r="F256" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C256),OR(D256&lt;&gt;"",ISNUMBER(E256))),C256/IF(D256&lt;&gt;"",D256,E256),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G256" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F256)),"—",IF(F256&lt;0.85,"BAS — opportunite acheteur",IF(F256&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H256" s="12"/>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B257" s="50">
+        <f>IFERROR(SUM(B254:B256),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C257" s="53">
+        <f>IFERROR(IF(ABS(SUM(B254:B256)-100)&lt;0.1,"Total = 100% OK","ATTENTION : total "&amp;TEXT(SUM(B254:B256),"0.0")&amp;"% — verifier les %"),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="D257" s="12"/>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
+      <c r="G257" s="12"/>
+      <c r="H257" s="12"/>
+    </row>
+    <row r="258" spans="1:8" ht="5" customHeight="1"/>
+    <row r="259" spans="1:8" ht="20" customHeight="1">
+      <c r="A259" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B259" s="3"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3"/>
+      <c r="E259" s="3"/>
+      <c r="F259" s="3"/>
+      <c r="G259" s="3"/>
+      <c r="H259" s="3"/>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="4"/>
+      <c r="H260" s="4"/>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B261" s="54">
+        <f>IFERROR((IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254*F254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255*F255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256*F256,0))/(IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256,0)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C261" s="12"/>
+      <c r="D261" s="53">
+        <f>IFERROR("Indice "&amp;TEXT(B261,"0.00")&amp;" — "&amp; IF(B261&lt;0.85,"en dessous moy LT : bas de cycle",IF(B261&lt;1.15,"proche moy LT : milieu de cycle","au-dessus moy LT : haut de cycle")),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
+      <c r="G261" s="12"/>
+      <c r="H261" s="12"/>
+    </row>
+    <row r="262" spans="1:8" ht="40" customHeight="1">
+      <c r="A262" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B262" s="55">
+        <f>IFERROR(IF(B261&lt;0.85,"BAS DE CYCLE",IF(B261&lt;1.15,"MILIEU DE CYCLE","HAUT DE CYCLE")),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="C262" s="12"/>
+      <c r="D262" s="56">
+        <f>IFERROR(IF(B261&lt;0.85,"ACHETER : RN comprime par bas cycle, actifs (plantations) solides. PER eleve = normal, ne pas vendre sur cette base.",IF(B261&lt;1.15,"ANALYSE STANDARD applicable. PER historique fiable.","PRUDENCE : RN gonfle par haut cycle. PER bas = TROMPEUR. Preferer PER normalise cycle (G3) avant toute decision.")),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E262" s="12"/>
+      <c r="F262" s="12"/>
+      <c r="G262" s="12"/>
+      <c r="H262" s="12"/>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B263" s="10">
+        <f>IFERROR(COUNTA(A254:A256),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C263" s="12"/>
+      <c r="D263" s="53">
+        <f>IFERROR(IF(COUNTA(A254:A256)&gt;=2,"Multi-matieres : diversification naturelle — cycles partiellement decoreles (ex: SOGB)","Mono-matiere : exposition totale au cycle unique (ex: SAPH, PALMCI)"),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E263" s="12"/>
+      <c r="F263" s="12"/>
+      <c r="G263" s="12"/>
+      <c r="H263" s="12"/>
+    </row>
+    <row r="264" spans="1:8" ht="5" customHeight="1"/>
+    <row r="265" spans="1:8" ht="20" customHeight="1">
+      <c r="A265" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="3"/>
+      <c r="F265" s="3"/>
+      <c r="G265" s="3"/>
+      <c r="H265" s="3"/>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="4"/>
+      <c r="H266" s="4"/>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B267" s="9">
+        <f>IFERROR(AVERAGE(B12:F12)*1000000/B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C267" s="12"/>
+      <c r="D267" s="57" t="s">
+        <v>309</v>
+      </c>
+      <c r="E267" s="12"/>
+      <c r="F267" s="12"/>
+      <c r="G267" s="12"/>
+      <c r="H267" s="12"/>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B268" s="54">
+        <f>IFERROR(B24/B267,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C268" s="12"/>
+      <c r="D268" s="58">
+        <f>IFERROR(IF(B268&lt;9,"Sous-evalue sur cycle complet — forte opportunite",IF(B268&lt;15,"Zone normale sur cycle — achat raisonnable",IF(B268&lt;22,"Prime moderee sur cycle — attendre correction","Fortement surevalue sur cycle — eviter"))),"Saisir donnees A1 et A2")</f>
+        <v>0</v>
+      </c>
+      <c r="E268" s="12"/>
+      <c r="F268" s="12"/>
+      <c r="G268" s="12"/>
+      <c r="H268" s="12"/>
+    </row>
+    <row r="269" spans="1:8" ht="28" customHeight="1">
+      <c r="A269" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B269" s="59">
+        <f>IFERROR(IF(AND(B261&lt;0.85,B268&lt;15),"ACHAT FORT — bas cycle + sous-evalue sur cycle",IF(AND(B261&lt;1.15,B268&lt;15),"ACHAT — milieu cycle + juste valorisation cycle",IF(AND(B261&gt;1.15,B268&lt;9),"SURVEILLER — haut cycle mais tres sous-evalue cycle",IF(AND(B261&gt;1.15,B268&gt;=15),"EVITER — haut cycle ET surevalue sur cycle","NEUTRE — analyser fondamentaux en detail")))),"Saisir matieres en G1")</f>
+        <v>0</v>
+      </c>
+      <c r="C269" s="59"/>
+      <c r="D269" s="59"/>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
+      <c r="G269" s="12"/>
+      <c r="H269" s="12"/>
+    </row>
+    <row r="270" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="51">
+  <mergeCells count="57">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -5835,6 +6224,12 @@
     <mergeCell ref="A231:H231"/>
     <mergeCell ref="A233:H233"/>
     <mergeCell ref="A240:H240"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A251:H251"/>
+    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A259:H259"/>
+    <mergeCell ref="A265:H265"/>
+    <mergeCell ref="B269:D269"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -5885,6 +6280,11 @@
       <formula>NOT(ISERROR(SEARCH("Moyen",D30)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Matiere premiere" prompt="Choisir dans la liste. Pour 'Autre' : saisir moy. LT en col. E" sqref="A254:A256">
+      <formula1>"Caoutchouc RSS3 (USD/kg),Huile de palme CPO (USD/t),Cacao (USD/t),Coton (USD/lb),Cafe Robusta (USD/t),Autre"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5906,7 +6306,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5925,212 +6325,212 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="52" t="s">
-        <v>292</v>
-      </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
+      <c r="A4" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
         <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B6" s="53">
+        <v>318</v>
+      </c>
+      <c r="B6" s="61">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="54">
+        <v>319</v>
+      </c>
+      <c r="D6" s="62">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="63">
         <f>IFERROR(IF(ETUDE!G8&gt;=15,3,IF(ETUDE!G8&gt;=5,2,IF(ETUDE!G8&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" s="53">
+        <v>320</v>
+      </c>
+      <c r="B7" s="61">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="54">
+        <v>319</v>
+      </c>
+      <c r="D7" s="62">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="63">
         <f>IFERROR(IF(ETUDE!G12&gt;=15,3,IF(ETUDE!G12&gt;=5,2,IF(ETUDE!G12&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B8" s="53">
+        <v>321</v>
+      </c>
+      <c r="B8" s="61">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D8" s="54">
+        <v>322</v>
+      </c>
+      <c r="D8" s="62">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="63">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,3,IF(ETUDE!G16&gt;=5,2,IF(ETUDE!G16&gt;=2,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="53">
+        <v>323</v>
+      </c>
+      <c r="B9" s="61">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="D9" s="54">
+        <v>324</v>
+      </c>
+      <c r="D9" s="62">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="63">
         <f>IFERROR(IF(ETUDE!B30&lt;9,3,IF(ETUDE!B30&lt;=15,2,IF(ETUDE!B30&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B10" s="53">
+        <v>325</v>
+      </c>
+      <c r="B10" s="61">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" s="54">
+        <v>326</v>
+      </c>
+      <c r="D10" s="62">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="63">
         <f>IFERROR(IF(ETUDE!B32&lt;1,3,IF(ETUDE!B32&lt;2,1,0)),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="53">
+        <v>327</v>
+      </c>
+      <c r="B11" s="61">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D11" s="54">
+        <v>319</v>
+      </c>
+      <c r="D11" s="62">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="63">
         <f>IFERROR(IF(ETUDE!B33&gt;=15,3,IF(ETUDE!B33&gt;=10,2,IF(ETUDE!B33&gt;=5,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B12" s="53">
+        <v>328</v>
+      </c>
+      <c r="B12" s="61">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="D12" s="54">
+        <v>329</v>
+      </c>
+      <c r="D12" s="62">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="55">
+      <c r="E12" s="63">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=6,3,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,2,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B13" s="53">
+        <v>330</v>
+      </c>
+      <c r="B13" s="61">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" s="54">
+        <v>331</v>
+      </c>
+      <c r="D13" s="62">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="55">
+      <c r="E13" s="63">
         <f>IFERROR(IF(ETUDE!B34&lt;10,3,IF(ETUDE!B34&lt;22,2,IF(ETUDE!B34&lt;30,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57">
+        <v>332</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="65">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="52" t="s">
-        <v>312</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="A16" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -6151,125 +6551,125 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B18" s="58">
+        <v>334</v>
+      </c>
+      <c r="B18" s="66">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="D18" s="54">
+        <v>335</v>
+      </c>
+      <c r="D18" s="62">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="55">
+      <c r="E18" s="63">
         <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="B19" s="58">
+        <v>336</v>
+      </c>
+      <c r="B19" s="66">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="D19" s="54">
+        <v>337</v>
+      </c>
+      <c r="D19" s="62">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="63">
         <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="B20" s="58">
+        <v>338</v>
+      </c>
+      <c r="B20" s="66">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D20" s="54">
+        <v>339</v>
+      </c>
+      <c r="D20" s="62">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="55">
+      <c r="E20" s="63">
         <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="B21" s="58">
+        <v>340</v>
+      </c>
+      <c r="B21" s="66">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D21" s="54">
+        <v>341</v>
+      </c>
+      <c r="D21" s="62">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="55">
+      <c r="E21" s="63">
         <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="B22" s="58">
+        <v>342</v>
+      </c>
+      <c r="B22" s="66">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D22" s="54">
+        <v>343</v>
+      </c>
+      <c r="D22" s="62">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="55">
+      <c r="E22" s="63">
         <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="57">
+        <v>344</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
+      <c r="A25" s="67" t="s">
+        <v>345</v>
+      </c>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -6279,133 +6679,133 @@
         <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B27" s="60">
+        <v>349</v>
+      </c>
+      <c r="B27" s="68">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="61">
+      <c r="C27" s="69">
         <v>24</v>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="70">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="63">
+      <c r="E27" s="71">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B28" s="60">
+        <v>350</v>
+      </c>
+      <c r="B28" s="68">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="69">
         <v>15</v>
       </c>
-      <c r="D28" s="62">
+      <c r="D28" s="70">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="63">
+      <c r="E28" s="71">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="B29" s="64">
+        <v>351</v>
+      </c>
+      <c r="B29" s="72">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="65">
+      <c r="C29" s="73">
         <v>39</v>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="70">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="66">
+      <c r="E29" s="74">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
+      <c r="A31" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="67">
+      <c r="A33" s="75">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="68">
+      <c r="B33" s="76">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="69">
+      <c r="C33" s="77">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="69">
+      <c r="D33" s="77">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="70">
+      <c r="E33" s="78">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="52" t="s">
-        <v>336</v>
-      </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
+      <c r="A35" s="60" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
       <c r="A36" s="28"/>
@@ -6568,7 +6968,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6576,56 +6976,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73" t="s">
-        <v>340</v>
+      <c r="A3" s="79" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="57" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="71" t="s">
-        <v>341</v>
-      </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="73" t="s">
-        <v>342</v>
+      <c r="A4" s="79" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="57" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="71" t="s">
-        <v>343</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="73" t="s">
-        <v>344</v>
+      <c r="A5" s="79" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="57" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="71" t="s">
-        <v>345</v>
-      </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="73" t="s">
-        <v>346</v>
+      <c r="A6" s="79" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="57" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -6633,63 +7033,63 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B9" s="45">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B10" s="45">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="B11" s="45">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B12" s="75"/>
+        <v>372</v>
+      </c>
+      <c r="B12" s="52"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="B13" s="75"/>
+        <v>373</v>
+      </c>
+      <c r="B13" s="52"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -6699,15 +7099,15 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="75"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="B17" s="75"/>
+        <v>375</v>
+      </c>
+      <c r="B17" s="52"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
@@ -6715,7 +7115,7 @@
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="75"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
@@ -6723,14 +7123,14 @@
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="75"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -6741,7 +7141,7 @@
         <v>227</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -6750,7 +7150,7 @@
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="75"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
@@ -6759,7 +7159,7 @@
         <v>229</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -6769,7 +7169,7 @@
         <v>230</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -6777,7 +7177,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -6787,7 +7187,7 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="75"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
@@ -6795,7 +7195,7 @@
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="75"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
@@ -6803,7 +7203,7 @@
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="75"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
@@ -6812,7 +7212,7 @@
         <v>234</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -6820,7 +7220,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -6828,38 +7228,38 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="B35" s="75"/>
+        <v>385</v>
+      </c>
+      <c r="B35" s="52"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -6867,7 +7267,7 @@
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
     <row r="39" spans="1:4" ht="20" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -6878,7 +7278,7 @@
         <v>238</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
@@ -6888,17 +7288,17 @@
         <v>240</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="5" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
@@ -6908,7 +7308,7 @@
         <v>251</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C43" s="12"/>
       <c r="D43" s="12"/>
@@ -6918,7 +7318,7 @@
         <v>258</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
@@ -6928,7 +7328,7 @@
         <v>260</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C45" s="12"/>
       <c r="D45" s="12"/>
@@ -6976,7 +7376,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6991,491 +7391,491 @@
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" ht="16" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>376</v>
-      </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
+      <c r="A2" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
     </row>
     <row r="3" spans="1:12" ht="5" customHeight="1"/>
     <row r="4" spans="1:12" ht="32" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1">
-      <c r="A5" s="77"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="79">
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="85">
         <f>IFERROR(IF(A5="","",C5*D5*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="79">
+      <c r="I5" s="85">
         <f>IFERROR(IF(A5="","",C5*E5),"")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="79">
+      <c r="J5" s="85">
         <f>IFERROR(IF(A5="","",(C5*E5)-(C5*D5*1.014)+(C5*F5)),"")</f>
         <v>0</v>
       </c>
-      <c r="K5" s="80">
+      <c r="K5" s="86">
         <f>IFERROR(IF(A5="","",J5/H5*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L5" s="81">
+      <c r="L5" s="87">
         <f>IFERROR(IF(A5="","—",IF(K5&lt;-10,"VENDRE — Stop-loss",IF(AND(G5&gt;=24,K5&gt;=0),"RENFORCER",IF(AND(G5&gt;=15,K5&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="78"/>
-      <c r="D6" s="78"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="79">
+      <c r="A6" s="83"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="85">
         <f>IFERROR(IF(A6="","",C6*D6*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I6" s="79">
+      <c r="I6" s="85">
         <f>IFERROR(IF(A6="","",C6*E6),"")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="79">
+      <c r="J6" s="85">
         <f>IFERROR(IF(A6="","",(C6*E6)-(C6*D6*1.014)+(C6*F6)),"")</f>
         <v>0</v>
       </c>
-      <c r="K6" s="80">
+      <c r="K6" s="86">
         <f>IFERROR(IF(A6="","",J6/H6*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="81">
+      <c r="L6" s="87">
         <f>IFERROR(IF(A6="","—",IF(K6&lt;-10,"VENDRE — Stop-loss",IF(AND(G6&gt;=24,K6&gt;=0),"RENFORCER",IF(AND(G6&gt;=15,K6&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1">
-      <c r="A7" s="77"/>
-      <c r="B7" s="77"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="79">
+      <c r="A7" s="83"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="85">
         <f>IFERROR(IF(A7="","",C7*D7*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="85">
         <f>IFERROR(IF(A7="","",C7*E7),"")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="79">
+      <c r="J7" s="85">
         <f>IFERROR(IF(A7="","",(C7*E7)-(C7*D7*1.014)+(C7*F7)),"")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="80">
+      <c r="K7" s="86">
         <f>IFERROR(IF(A7="","",J7/H7*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="81">
+      <c r="L7" s="87">
         <f>IFERROR(IF(A7="","—",IF(K7&lt;-10,"VENDRE — Stop-loss",IF(AND(G7&gt;=24,K7&gt;=0),"RENFORCER",IF(AND(G7&gt;=15,K7&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="77"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="78"/>
-      <c r="E8" s="78"/>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79">
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="85">
         <f>IFERROR(IF(A8="","",C8*D8*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="85">
         <f>IFERROR(IF(A8="","",C8*E8),"")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="85">
         <f>IFERROR(IF(A8="","",(C8*E8)-(C8*D8*1.014)+(C8*F8)),"")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="86">
         <f>IFERROR(IF(A8="","",J8/H8*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="87">
         <f>IFERROR(IF(A8="","—",IF(K8&lt;-10,"VENDRE — Stop-loss",IF(AND(G8&gt;=24,K8&gt;=0),"RENFORCER",IF(AND(G8&gt;=15,K8&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1">
-      <c r="A9" s="77"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="78"/>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79">
+      <c r="A9" s="83"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="85">
         <f>IFERROR(IF(A9="","",C9*D9*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I9" s="79">
+      <c r="I9" s="85">
         <f>IFERROR(IF(A9="","",C9*E9),"")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="85">
         <f>IFERROR(IF(A9="","",(C9*E9)-(C9*D9*1.014)+(C9*F9)),"")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="86">
         <f>IFERROR(IF(A9="","",J9/H9*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="81">
+      <c r="L9" s="87">
         <f>IFERROR(IF(A9="","—",IF(K9&lt;-10,"VENDRE — Stop-loss",IF(AND(G9&gt;=24,K9&gt;=0),"RENFORCER",IF(AND(G9&gt;=15,K9&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1">
-      <c r="A10" s="77"/>
-      <c r="B10" s="77"/>
-      <c r="C10" s="78"/>
-      <c r="D10" s="78"/>
-      <c r="E10" s="78"/>
-      <c r="F10" s="78"/>
-      <c r="G10" s="78"/>
-      <c r="H10" s="79">
+      <c r="A10" s="83"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="85">
         <f>IFERROR(IF(A10="","",C10*D10*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="79">
+      <c r="I10" s="85">
         <f>IFERROR(IF(A10="","",C10*E10),"")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="79">
+      <c r="J10" s="85">
         <f>IFERROR(IF(A10="","",(C10*E10)-(C10*D10*1.014)+(C10*F10)),"")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="80">
+      <c r="K10" s="86">
         <f>IFERROR(IF(A10="","",J10/H10*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="81">
+      <c r="L10" s="87">
         <f>IFERROR(IF(A10="","—",IF(K10&lt;-10,"VENDRE — Stop-loss",IF(AND(G10&gt;=24,K10&gt;=0),"RENFORCER",IF(AND(G10&gt;=15,K10&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1">
-      <c r="A11" s="77"/>
-      <c r="B11" s="77"/>
-      <c r="C11" s="78"/>
-      <c r="D11" s="78"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79">
+      <c r="A11" s="83"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="85">
         <f>IFERROR(IF(A11="","",C11*D11*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="79">
+      <c r="I11" s="85">
         <f>IFERROR(IF(A11="","",C11*E11),"")</f>
         <v>0</v>
       </c>
-      <c r="J11" s="79">
+      <c r="J11" s="85">
         <f>IFERROR(IF(A11="","",(C11*E11)-(C11*D11*1.014)+(C11*F11)),"")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="80">
+      <c r="K11" s="86">
         <f>IFERROR(IF(A11="","",J11/H11*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="81">
+      <c r="L11" s="87">
         <f>IFERROR(IF(A11="","—",IF(K11&lt;-10,"VENDRE — Stop-loss",IF(AND(G11&gt;=24,K11&gt;=0),"RENFORCER",IF(AND(G11&gt;=15,K11&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1">
-      <c r="A12" s="77"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="H12" s="79">
+      <c r="A12" s="83"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="85">
         <f>IFERROR(IF(A12="","",C12*D12*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="79">
+      <c r="I12" s="85">
         <f>IFERROR(IF(A12="","",C12*E12),"")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="79">
+      <c r="J12" s="85">
         <f>IFERROR(IF(A12="","",(C12*E12)-(C12*D12*1.014)+(C12*F12)),"")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="80">
+      <c r="K12" s="86">
         <f>IFERROR(IF(A12="","",J12/H12*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="81">
+      <c r="L12" s="87">
         <f>IFERROR(IF(A12="","—",IF(K12&lt;-10,"VENDRE — Stop-loss",IF(AND(G12&gt;=24,K12&gt;=0),"RENFORCER",IF(AND(G12&gt;=15,K12&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="77"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="78"/>
-      <c r="D13" s="78"/>
-      <c r="E13" s="78"/>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="79">
+      <c r="A13" s="83"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="85">
         <f>IFERROR(IF(A13="","",C13*D13*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="79">
+      <c r="I13" s="85">
         <f>IFERROR(IF(A13="","",C13*E13),"")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="79">
+      <c r="J13" s="85">
         <f>IFERROR(IF(A13="","",(C13*E13)-(C13*D13*1.014)+(C13*F13)),"")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="80">
+      <c r="K13" s="86">
         <f>IFERROR(IF(A13="","",J13/H13*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="81">
+      <c r="L13" s="87">
         <f>IFERROR(IF(A13="","—",IF(K13&lt;-10,"VENDRE — Stop-loss",IF(AND(G13&gt;=24,K13&gt;=0),"RENFORCER",IF(AND(G13&gt;=15,K13&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1">
-      <c r="A14" s="77"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="79">
+      <c r="A14" s="83"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="85">
         <f>IFERROR(IF(A14="","",C14*D14*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="79">
+      <c r="I14" s="85">
         <f>IFERROR(IF(A14="","",C14*E14),"")</f>
         <v>0</v>
       </c>
-      <c r="J14" s="79">
+      <c r="J14" s="85">
         <f>IFERROR(IF(A14="","",(C14*E14)-(C14*D14*1.014)+(C14*F14)),"")</f>
         <v>0</v>
       </c>
-      <c r="K14" s="80">
+      <c r="K14" s="86">
         <f>IFERROR(IF(A14="","",J14/H14*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L14" s="81">
+      <c r="L14" s="87">
         <f>IFERROR(IF(A14="","—",IF(K14&lt;-10,"VENDRE — Stop-loss",IF(AND(G14&gt;=24,K14&gt;=0),"RENFORCER",IF(AND(G14&gt;=15,K14&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1">
-      <c r="A15" s="77"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="79">
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="85">
         <f>IFERROR(IF(A15="","",C15*D15*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="79">
+      <c r="I15" s="85">
         <f>IFERROR(IF(A15="","",C15*E15),"")</f>
         <v>0</v>
       </c>
-      <c r="J15" s="79">
+      <c r="J15" s="85">
         <f>IFERROR(IF(A15="","",(C15*E15)-(C15*D15*1.014)+(C15*F15)),"")</f>
         <v>0</v>
       </c>
-      <c r="K15" s="80">
+      <c r="K15" s="86">
         <f>IFERROR(IF(A15="","",J15/H15*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L15" s="81">
+      <c r="L15" s="87">
         <f>IFERROR(IF(A15="","—",IF(K15&lt;-10,"VENDRE — Stop-loss",IF(AND(G15&gt;=24,K15&gt;=0),"RENFORCER",IF(AND(G15&gt;=15,K15&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1">
-      <c r="A16" s="77"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="79">
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="85">
         <f>IFERROR(IF(A16="","",C16*D16*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="79">
+      <c r="I16" s="85">
         <f>IFERROR(IF(A16="","",C16*E16),"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="79">
+      <c r="J16" s="85">
         <f>IFERROR(IF(A16="","",(C16*E16)-(C16*D16*1.014)+(C16*F16)),"")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="80">
+      <c r="K16" s="86">
         <f>IFERROR(IF(A16="","",J16/H16*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L16" s="81">
+      <c r="L16" s="87">
         <f>IFERROR(IF(A16="","—",IF(K16&lt;-10,"VENDRE — Stop-loss",IF(AND(G16&gt;=24,K16&gt;=0),"RENFORCER",IF(AND(G16&gt;=15,K16&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1">
-      <c r="A17" s="77"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="79">
+      <c r="A17" s="83"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="85">
         <f>IFERROR(IF(A17="","",C17*D17*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="79">
+      <c r="I17" s="85">
         <f>IFERROR(IF(A17="","",C17*E17),"")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="79">
+      <c r="J17" s="85">
         <f>IFERROR(IF(A17="","",(C17*E17)-(C17*D17*1.014)+(C17*F17)),"")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="80">
+      <c r="K17" s="86">
         <f>IFERROR(IF(A17="","",J17/H17*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L17" s="81">
+      <c r="L17" s="87">
         <f>IFERROR(IF(A17="","—",IF(K17&lt;-10,"VENDRE — Stop-loss",IF(AND(G17&gt;=24,K17&gt;=0),"RENFORCER",IF(AND(G17&gt;=15,K17&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1">
-      <c r="A18" s="77"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="79">
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="85">
         <f>IFERROR(IF(A18="","",C18*D18*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="79">
+      <c r="I18" s="85">
         <f>IFERROR(IF(A18="","",C18*E18),"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="79">
+      <c r="J18" s="85">
         <f>IFERROR(IF(A18="","",(C18*E18)-(C18*D18*1.014)+(C18*F18)),"")</f>
         <v>0</v>
       </c>
-      <c r="K18" s="80">
+      <c r="K18" s="86">
         <f>IFERROR(IF(A18="","",J18/H18*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L18" s="81">
+      <c r="L18" s="87">
         <f>IFERROR(IF(A18="","—",IF(K18&lt;-10,"VENDRE — Stop-loss",IF(AND(G18&gt;=24,K18&gt;=0),"RENFORCER",IF(AND(G18&gt;=15,K18&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1">
-      <c r="A19" s="77"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="79">
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="85">
         <f>IFERROR(IF(A19="","",C19*D19*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="79">
+      <c r="I19" s="85">
         <f>IFERROR(IF(A19="","",C19*E19),"")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="79">
+      <c r="J19" s="85">
         <f>IFERROR(IF(A19="","",(C19*E19)-(C19*D19*1.014)+(C19*F19)),"")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="80">
+      <c r="K19" s="86">
         <f>IFERROR(IF(A19="","",J19/H19*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L19" s="81">
+      <c r="L19" s="87">
         <f>IFERROR(IF(A19="","—",IF(K19&lt;-10,"VENDRE — Stop-loss",IF(AND(G19&gt;=24,K19&gt;=0),"RENFORCER",IF(AND(G19&gt;=15,K19&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
@@ -7483,123 +7883,123 @@
     <row r="20" spans="1:12" ht="5" customHeight="1"/>
     <row r="21" spans="1:12" ht="22" customHeight="1">
       <c r="A21" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="82"/>
-      <c r="G21" s="82"/>
-      <c r="H21" s="83">
+        <v>410</v>
+      </c>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="83">
+      <c r="I21" s="89">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="83">
+      <c r="J21" s="89">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
         <v>0</v>
       </c>
-      <c r="K21" s="84">
+      <c r="K21" s="90">
         <f>IFERROR(J21/H21*100,"")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="81">
+      <c r="L21" s="87">
         <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="8" customHeight="1"/>
     <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="85" t="s">
-        <v>390</v>
-      </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
+      <c r="A23" s="91" t="s">
+        <v>411</v>
+      </c>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
     </row>
     <row r="24" spans="1:12" ht="16" customHeight="1">
-      <c r="A24" s="86" t="s">
-        <v>391</v>
-      </c>
-      <c r="B24" s="87" t="s">
-        <v>392</v>
-      </c>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="87"/>
-      <c r="G24" s="87"/>
-      <c r="H24" s="87"/>
-      <c r="I24" s="87"/>
-      <c r="J24" s="87"/>
-      <c r="K24" s="87"/>
-      <c r="L24" s="87"/>
+      <c r="A24" s="92" t="s">
+        <v>412</v>
+      </c>
+      <c r="B24" s="93" t="s">
+        <v>413</v>
+      </c>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
     </row>
     <row r="25" spans="1:12" ht="16" customHeight="1">
-      <c r="A25" s="86" t="s">
-        <v>393</v>
-      </c>
-      <c r="B25" s="87" t="s">
-        <v>394</v>
-      </c>
-      <c r="C25" s="87"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="87"/>
-      <c r="I25" s="87"/>
-      <c r="J25" s="87"/>
-      <c r="K25" s="87"/>
-      <c r="L25" s="87"/>
+      <c r="A25" s="92" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" s="93" t="s">
+        <v>415</v>
+      </c>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1">
-      <c r="A26" s="86" t="s">
-        <v>395</v>
-      </c>
-      <c r="B26" s="87" t="s">
-        <v>396</v>
-      </c>
-      <c r="C26" s="87"/>
-      <c r="D26" s="87"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="87"/>
-      <c r="G26" s="87"/>
-      <c r="H26" s="87"/>
-      <c r="I26" s="87"/>
-      <c r="J26" s="87"/>
-      <c r="K26" s="87"/>
-      <c r="L26" s="87"/>
+      <c r="A26" s="92" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" s="93" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1">
-      <c r="A27" s="86" t="s">
-        <v>397</v>
-      </c>
-      <c r="B27" s="87" t="s">
-        <v>398</v>
-      </c>
-      <c r="C27" s="87"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="87"/>
-      <c r="I27" s="87"/>
-      <c r="J27" s="87"/>
-      <c r="K27" s="87"/>
-      <c r="L27" s="87"/>
+      <c r="A27" s="92" t="s">
+        <v>418</v>
+      </c>
+      <c r="B27" s="93" t="s">
+        <v>419</v>
+      </c>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -7632,322 +8032,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="88" t="s">
-        <v>400</v>
-      </c>
-      <c r="C2" s="88" t="s">
-        <v>401</v>
-      </c>
-      <c r="D2" s="88" t="s">
-        <v>402</v>
+      <c r="B2" s="94" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="94" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
+      <c r="A3" s="60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>404</v>
-      </c>
-      <c r="B4" s="89" t="s">
-        <v>405</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D4" s="90" t="s">
-        <v>407</v>
+        <v>425</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="B5" s="89" t="s">
-        <v>409</v>
-      </c>
-      <c r="C5" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D5" s="90" t="s">
-        <v>410</v>
+        <v>429</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B6" s="89" t="s">
-        <v>412</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D6" s="90" t="s">
-        <v>413</v>
+        <v>432</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>302</v>
-      </c>
-      <c r="B7" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="C7" s="61" t="s">
-        <v>415</v>
-      </c>
-      <c r="D7" s="90" t="s">
-        <v>416</v>
+        <v>323</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>417</v>
-      </c>
-      <c r="B8" s="89" t="s">
-        <v>418</v>
-      </c>
-      <c r="C8" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>420</v>
+        <v>438</v>
+      </c>
+      <c r="B8" s="95" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>421</v>
-      </c>
-      <c r="C9" s="61" t="s">
-        <v>415</v>
-      </c>
-      <c r="D9" s="90" t="s">
-        <v>422</v>
+        <v>325</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D9" s="96" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="B10" s="89" t="s">
-        <v>424</v>
-      </c>
-      <c r="C10" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D10" s="90" t="s">
-        <v>425</v>
+        <v>444</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>445</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="B11" s="89" t="s">
-        <v>427</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="90" t="s">
-        <v>428</v>
+        <v>447</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>448</v>
+      </c>
+      <c r="C11" s="69"/>
+      <c r="D11" s="96" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="B12" s="89" t="s">
-        <v>430</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D12" s="90" t="s">
-        <v>431</v>
+        <v>450</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>451</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>432</v>
-      </c>
-      <c r="B13" s="89" t="s">
-        <v>433</v>
-      </c>
-      <c r="C13" s="61" t="s">
-        <v>406</v>
-      </c>
-      <c r="D13" s="90" t="s">
-        <v>434</v>
+        <v>453</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="52" t="s">
-        <v>435</v>
-      </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
+      <c r="A14" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>436</v>
-      </c>
-      <c r="B15" s="89" t="s">
-        <v>437</v>
-      </c>
-      <c r="C15" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D15" s="90" t="s">
-        <v>438</v>
+        <v>457</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>458</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="96" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="B16" s="89" t="s">
-        <v>440</v>
-      </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="90" t="s">
-        <v>441</v>
+        <v>460</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="C16" s="69"/>
+      <c r="D16" s="96" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="89" t="s">
-        <v>440</v>
-      </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="90" t="s">
-        <v>442</v>
+      <c r="B17" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="C17" s="69"/>
+      <c r="D17" s="96" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="89" t="s">
-        <v>443</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>415</v>
-      </c>
-      <c r="D18" s="90" t="s">
-        <v>444</v>
+      <c r="B18" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="B19" s="89" t="s">
-        <v>446</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D19" s="90" t="s">
-        <v>447</v>
+        <v>466</v>
+      </c>
+      <c r="B19" s="95" t="s">
+        <v>467</v>
+      </c>
+      <c r="C19" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="96" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="B20" s="89" t="s">
-        <v>449</v>
-      </c>
-      <c r="C20" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D20" s="90" t="s">
-        <v>450</v>
+        <v>469</v>
+      </c>
+      <c r="B20" s="95" t="s">
+        <v>470</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D20" s="96" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>451</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
+      <c r="A21" s="60" t="s">
+        <v>472</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>452</v>
-      </c>
-      <c r="B22" s="89" t="s">
-        <v>453</v>
-      </c>
-      <c r="C22" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="90" t="s">
-        <v>454</v>
+        <v>473</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D22" s="96" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>455</v>
-      </c>
-      <c r="B23" s="89" t="s">
-        <v>456</v>
-      </c>
-      <c r="C23" s="61" t="s">
-        <v>457</v>
-      </c>
-      <c r="D23" s="90" t="s">
-        <v>458</v>
+        <v>476</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>477</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>478</v>
+      </c>
+      <c r="D23" s="96" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>459</v>
-      </c>
-      <c r="B24" s="89" t="s">
-        <v>460</v>
-      </c>
-      <c r="C24" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D24" s="90" t="s">
-        <v>461</v>
+        <v>480</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D24" s="96" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>462</v>
-      </c>
-      <c r="B25" s="89" t="s">
-        <v>463</v>
-      </c>
-      <c r="C25" s="61" t="s">
-        <v>419</v>
-      </c>
-      <c r="D25" s="90" t="s">
-        <v>464</v>
+        <v>483</v>
+      </c>
+      <c r="B25" s="95" t="s">
+        <v>484</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -10,14 +10,15 @@
     <sheet name="ETUDE" sheetId="1" r:id="rId1"/>
     <sheet name="SYNTHESE" sheetId="2" r:id="rId2"/>
     <sheet name="PROFIL" sheetId="3" r:id="rId3"/>
-    <sheet name="FORMULE" sheetId="4" r:id="rId4"/>
+    <sheet name="PORTEFEUILLE" sheetId="4" r:id="rId4"/>
+    <sheet name="FORMULE" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="486">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -724,6 +725,237 @@
     <t>Dividende verse regulierement ?</t>
   </si>
   <si>
+    <t>E — ANALYSE DU BILAN  (saisir dans PROFIL — section BILAN)</t>
+  </si>
+  <si>
+    <t>E1 — STRUCTURE DE LA DETTE</t>
+  </si>
+  <si>
+    <t>Reference / Seuils</t>
+  </si>
+  <si>
+    <t>Dette long terme (FCFA)</t>
+  </si>
+  <si>
+    <t>Bilan passif non courant</t>
+  </si>
+  <si>
+    <t>Dette court terme (FCFA)</t>
+  </si>
+  <si>
+    <t>Bilan passif courant</t>
+  </si>
+  <si>
+    <t>Dette totale (FCFA)</t>
+  </si>
+  <si>
+    <t>= LT + CT</t>
+  </si>
+  <si>
+    <t>Gearing (Dette totale / Fonds propres %)</t>
+  </si>
+  <si>
+    <t>&lt; 50% sain | 50-100% eleve | &gt; 100% risque</t>
+  </si>
+  <si>
+    <t>Dette nette / RN annuel (nb annees)</t>
+  </si>
+  <si>
+    <t>&lt; 3 ans sain | 3-5 ans acceptable | &gt; 5 ans excessif</t>
+  </si>
+  <si>
+    <t>E2 — SOLVABILITE &amp; COUVERTURE DES INTERETS</t>
+  </si>
+  <si>
+    <t>EBIT (M FCFA) — depuis PROFIL</t>
+  </si>
+  <si>
+    <t>Resultat avant interets et impots</t>
+  </si>
+  <si>
+    <t>Charges financieres nettes (FCFA)</t>
+  </si>
+  <si>
+    <t>Interets nets payes sur la dette</t>
+  </si>
+  <si>
+    <t>Couverture des interets (x)</t>
+  </si>
+  <si>
+    <t>&gt; 3x sain | 1.5-3x vigilance | &lt; 1.5x risque</t>
+  </si>
+  <si>
+    <t>Ratio Fonds propres / Dette totale (%)</t>
+  </si>
+  <si>
+    <t>&gt; 100% solide | 50-100% moyen | &lt; 50% fragile</t>
+  </si>
+  <si>
+    <t>E3 — LIQUIDITE DU BILAN</t>
+  </si>
+  <si>
+    <t>Actifs courants (FCFA)</t>
+  </si>
+  <si>
+    <t>Tresorerie + creances + stocks</t>
+  </si>
+  <si>
+    <t>Passifs courants (FCFA)</t>
+  </si>
+  <si>
+    <t>Dettes court terme &lt; 1 an</t>
+  </si>
+  <si>
+    <t>Ratio de liquidite courant (x)</t>
+  </si>
+  <si>
+    <t>&gt; 2 = tres liquide | 1-2 = OK | &lt; 1 = tension tresorerie</t>
+  </si>
+  <si>
+    <t>Fonds de roulement net (FCFA)</t>
+  </si>
+  <si>
+    <t>&gt; 0 = excedent | &lt; 0 = deficit de liquidite</t>
+  </si>
+  <si>
+    <t>F — ALERTES DE PRIX &amp; VALEUR INTRINSEQUE</t>
+  </si>
+  <si>
+    <t>F1 — VALEUR INTRINSEQUE COMPOSITE  (VMC x2  +  PCD  +  Gordon  quand disponibles)</t>
+  </si>
+  <si>
+    <t>Modele</t>
+  </si>
+  <si>
+    <t>VI estimee (FCFA)</t>
+  </si>
+  <si>
+    <t>Poids</t>
+  </si>
+  <si>
+    <t>Signal vs prix actuel</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>VALEUR INTRINSEQUE COMPOSITE (VI)</t>
+  </si>
+  <si>
+    <t>composite</t>
+  </si>
+  <si>
+    <t>F2 — ZONES D ALERTE PRIX  (depuis VI composite B238)</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Prix seuil (FCFA)</t>
+  </si>
+  <si>
+    <t>Ecart vs prix actuel (%)</t>
+  </si>
+  <si>
+    <t>Action recommandee</t>
+  </si>
+  <si>
+    <t>FORTE OPPORTUNITE  (VI x 0.75)</t>
+  </si>
+  <si>
+    <t>Achat agressif — decote &gt; 25% sur VI</t>
+  </si>
+  <si>
+    <t>ACHAT IDEAL  (VI x 0.85)</t>
+  </si>
+  <si>
+    <t>Achat — marge de securite confortable (15-25%)</t>
+  </si>
+  <si>
+    <t>JUSTE VALEUR  (VI x 1.00)</t>
+  </si>
+  <si>
+    <t>Achat si fondamentaux solides — prime nulle</t>
+  </si>
+  <si>
+    <t>ZONE NEUTRE  (VI x 1.10)</t>
+  </si>
+  <si>
+    <t>Surveiller — prime moderee</t>
+  </si>
+  <si>
+    <t>SURACHAT  (VI x 1.20)</t>
+  </si>
+  <si>
+    <t>Allegement conseille — prime &gt; 20% sur VI</t>
+  </si>
+  <si>
+    <t>G — ANALYSE CYCLIQUE  (agro-industrie BRVM : caoutchouc, huile de palme, cacao...)</t>
+  </si>
+  <si>
+    <t>G1 — EXPOSITION AUX MATIERES PREMIERES  (jusqu'a 3 matieres par societe)</t>
+  </si>
+  <si>
+    <t>Liste : choisir la matiere | saisir % CA et prix actuel | moy. LT 10 ans auto-remplie | Pour 'Autre' : laisser D vide et saisir la moy. LT en colonne E</t>
+  </si>
+  <si>
+    <t>Matiere premiere</t>
+  </si>
+  <si>
+    <t>% CA</t>
+  </si>
+  <si>
+    <t>Prix actuel</t>
+  </si>
+  <si>
+    <t>Moy. LT auto</t>
+  </si>
+  <si>
+    <t>Moy. LT (Autre)</t>
+  </si>
+  <si>
+    <t>Ratio cycle</t>
+  </si>
+  <si>
+    <t>Total % CA renseigne</t>
+  </si>
+  <si>
+    <t>G2 — INDICE DE CYCLE COMPOSITE  (pondere par le % du CA de chaque matiere)</t>
+  </si>
+  <si>
+    <t>Interpretation &amp; Conduite a tenir</t>
+  </si>
+  <si>
+    <t>Indice cycle composite (pondere % CA)</t>
+  </si>
+  <si>
+    <t>Phase du cycle detectee</t>
+  </si>
+  <si>
+    <t>Nb matieres renseignees</t>
+  </si>
+  <si>
+    <t>G3 — VALORISATION ADAPTEE AUX CYCLIQUES  (PER normalise sur cycle 5 ans)</t>
+  </si>
+  <si>
+    <t>Signal / Interpretation</t>
+  </si>
+  <si>
+    <t>BPA normalise 5 ans (FCFA)</t>
+  </si>
+  <si>
+    <t>= RN moyen 5 ans / Nb titres. Lisse les pics et creux de cycle.</t>
+  </si>
+  <si>
+    <t>PER normalise cycle (Prix / BPA moyen 5 ans)</t>
+  </si>
+  <si>
+    <t>VERDICT CYCLIQUE FINAL</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -790,9 +1022,6 @@
     <t>SCORECARD TECHNIQUE</t>
   </si>
   <si>
-    <t>Zone</t>
-  </si>
-  <si>
     <t>MM20+Bollinger+MACD+RSI+Volume (score B1)</t>
   </si>
   <si>
@@ -959,6 +1188,105 @@
   </si>
   <si>
     <t>&lt;-- brvm.org</t>
+  </si>
+  <si>
+    <t>BILAN (depuis rapport annuel)</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan passif non courant</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan passif courant</t>
+  </si>
+  <si>
+    <t>EBIT - Res. avant interets et impots (M FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Compte de resultat</t>
+  </si>
+  <si>
+    <t>&lt;-- Bilan actif courant</t>
+  </si>
+  <si>
+    <t>PORTEFEUILLE BRVM — SUIVI DES POSITIONS &amp; RECOMMANDATIONS</t>
+  </si>
+  <si>
+    <t>Saisir Ticker, Secteur, Nb titres, Prix achat, Prix actuel, Dividendes recus/titre, Note ETUDE /39  —  Reste calculé automatiquement</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Secteur</t>
+  </si>
+  <si>
+    <t>Nb titres</t>
+  </si>
+  <si>
+    <t>Prix achat moy.
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Prix actuel
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Div. recus/titre
+(FCFA)</t>
+  </si>
+  <si>
+    <t>Note
+/39</t>
+  </si>
+  <si>
+    <t>Cout total achat
+(auto)</t>
+  </si>
+  <si>
+    <t>Val. actuelle
+(auto)</t>
+  </si>
+  <si>
+    <t>PV/MV+Div
+(auto)</t>
+  </si>
+  <si>
+    <t>Rend. total %
+(auto)</t>
+  </si>
+  <si>
+    <t>Recommandation
+(auto)</t>
+  </si>
+  <si>
+    <t>TOTAL PORTEFEUILLE</t>
+  </si>
+  <si>
+    <t>LEGENDE RECOMMANDATIONS</t>
+  </si>
+  <si>
+    <t>RENFORCER</t>
+  </si>
+  <si>
+    <t>Note &gt;= 24/39 ET rendement total &gt;= 0%   — Fondamentaux solides, titre en gain</t>
+  </si>
+  <si>
+    <t>CONSERVER</t>
+  </si>
+  <si>
+    <t>Note &gt;= 15/39 ET rendement &gt; -5%   — Garder la position, surveiller</t>
+  </si>
+  <si>
+    <t>SURVEILLER</t>
+  </si>
+  <si>
+    <t>Situation ambiguë   — Attendre confirmation avant d'agir</t>
+  </si>
+  <si>
+    <t>VENDRE — Stop</t>
+  </si>
+  <si>
+    <t>Rendement total &lt; -10%   — Stop-loss déclenché, limiter la perte</t>
   </si>
   <si>
     <t>REFERENTIEL DES FORMULES &amp; INDICATEURS BRVM</t>
@@ -1171,7 +1499,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1330,6 +1658,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
@@ -1377,14 +1754,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF1F3864"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
@@ -1416,14 +1785,59 @@
     </font>
     <font>
       <i/>
+      <sz val="9"/>
+      <color rgb="FFCBD5E1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF92400E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF064E3B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1E40AF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF374151"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FF6B7280"/>
+      <color rgb="FF1E40AF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF374151"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1504,12 +1918,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1517,6 +1925,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF6FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1570,7 +1990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1746,23 +2166,69 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="26" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1770,19 +2236,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="23" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="29" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1794,27 +2260,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="30" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="27" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="32" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="34" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1826,19 +2292,54 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="35" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="30" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="38" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1846,7 +2347,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2308,7 +2809,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H270"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -4788,9 +5289,890 @@
       <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8" ht="5" customHeight="1"/>
+    <row r="205" spans="1:8" ht="5" customHeight="1"/>
+    <row r="206" spans="1:8" ht="22" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+      <c r="E206" s="1"/>
+      <c r="F206" s="1"/>
+      <c r="G206" s="1"/>
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="1:8" ht="5" customHeight="1"/>
+    <row r="208" spans="1:8" ht="20" customHeight="1">
+      <c r="A208" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+      <c r="E208" s="3"/>
+      <c r="F208" s="3"/>
+      <c r="G208" s="3"/>
+      <c r="H208" s="3"/>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C209" s="4"/>
+      <c r="D209" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4"/>
+      <c r="G209" s="4"/>
+      <c r="H209" s="4"/>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B210" s="9">
+        <f>IFERROR(PROFIL!B40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C210" s="12"/>
+      <c r="D210" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="E210" s="12"/>
+      <c r="F210" s="12"/>
+      <c r="G210" s="12"/>
+      <c r="H210" s="12"/>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B211" s="9">
+        <f>IFERROR(PROFIL!B41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C211" s="12"/>
+      <c r="D211" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
+      <c r="G211" s="12"/>
+      <c r="H211" s="12"/>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B212" s="9">
+        <f>IFERROR(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C212" s="12"/>
+      <c r="D212" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12"/>
+      <c r="G212" s="12"/>
+      <c r="H212" s="12"/>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B213" s="7">
+        <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/B26*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C213" s="12"/>
+      <c r="D213" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
+      <c r="G213" s="12"/>
+      <c r="H213" s="12"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B214" s="7">
+        <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/(F12*1000000),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C214" s="12"/>
+      <c r="D214" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
+      <c r="G214" s="12"/>
+      <c r="H214" s="12"/>
+    </row>
+    <row r="215" spans="1:8" ht="5" customHeight="1"/>
+    <row r="216" spans="1:8" ht="20" customHeight="1">
+      <c r="A216" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="3"/>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3"/>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C217" s="4"/>
+      <c r="D217" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+      <c r="G217" s="4"/>
+      <c r="H217" s="4"/>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B218" s="9">
+        <f>IFERROR(PROFIL!B42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C218" s="12"/>
+      <c r="D218" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="E218" s="12"/>
+      <c r="F218" s="12"/>
+      <c r="G218" s="12"/>
+      <c r="H218" s="12"/>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B219" s="9">
+        <f>IFERROR(PROFIL!B43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C219" s="12"/>
+      <c r="D219" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
+      <c r="G219" s="12"/>
+      <c r="H219" s="12"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B220" s="7">
+        <f>IFERROR(PROFIL!B42*1000000/PROFIL!B43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C220" s="12"/>
+      <c r="D220" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="E220" s="12"/>
+      <c r="F220" s="12"/>
+      <c r="G220" s="12"/>
+      <c r="H220" s="12"/>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B221" s="7">
+        <f>IFERROR(B26/(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C221" s="12"/>
+      <c r="D221" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
+      <c r="G221" s="12"/>
+      <c r="H221" s="12"/>
+    </row>
+    <row r="222" spans="1:8" ht="5" customHeight="1"/>
+    <row r="223" spans="1:8" ht="20" customHeight="1">
+      <c r="A223" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="3"/>
+      <c r="G223" s="3"/>
+      <c r="H223" s="3"/>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C224" s="4"/>
+      <c r="D224" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4"/>
+      <c r="H224" s="4"/>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B225" s="9">
+        <f>IFERROR(PROFIL!B44,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C225" s="12"/>
+      <c r="D225" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
+      <c r="G225" s="12"/>
+      <c r="H225" s="12"/>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B226" s="9">
+        <f>IFERROR(PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C226" s="12"/>
+      <c r="D226" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="E226" s="12"/>
+      <c r="F226" s="12"/>
+      <c r="G226" s="12"/>
+      <c r="H226" s="12"/>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B227" s="7">
+        <f>IFERROR(PROFIL!B44/PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C227" s="12"/>
+      <c r="D227" s="30" t="s">
+        <v>263</v>
+      </c>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
+      <c r="G227" s="12"/>
+      <c r="H227" s="12"/>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B228" s="9">
+        <f>IFERROR(PROFIL!B44-PROFIL!B45,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C228" s="12"/>
+      <c r="D228" s="30" t="s">
+        <v>265</v>
+      </c>
+      <c r="E228" s="12"/>
+      <c r="F228" s="12"/>
+      <c r="G228" s="12"/>
+      <c r="H228" s="12"/>
+    </row>
+    <row r="229" spans="1:8" ht="5" customHeight="1"/>
+    <row r="230" spans="1:8" ht="5" customHeight="1"/>
+    <row r="231" spans="1:8" ht="22" customHeight="1">
+      <c r="A231" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+      <c r="F231" s="1"/>
+      <c r="G231" s="1"/>
+      <c r="H231" s="1"/>
+    </row>
+    <row r="232" spans="1:8" ht="5" customHeight="1"/>
+    <row r="233" spans="1:8" ht="20" customHeight="1">
+      <c r="A233" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
+      <c r="E233" s="3"/>
+      <c r="F233" s="3"/>
+      <c r="G233" s="3"/>
+      <c r="H233" s="3"/>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E234" s="4"/>
+      <c r="F234" s="4"/>
+      <c r="G234" s="4"/>
+      <c r="H234" s="4"/>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="5">
+        <f>IF(ISNUMBER(B31),"VMC  =  "&amp;TEXT(ROUND(B31,0),"#,##0")&amp;" FCFA","VMC — N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="B235" s="9">
+        <f>IFERROR(B31,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C235" s="46" t="s">
+        <v>272</v>
+      </c>
+      <c r="D235" s="47">
+        <f>IFERROR(IF(B24&lt;B31,"Prix SOUS VMC — decote comptable","Prix AU-DESSUS VMC"),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
+      <c r="G235" s="12"/>
+      <c r="H235" s="12"/>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="5">
+        <f>IF(ISNUMBER(B113),"PCD  =  "&amp;TEXT(ROUND(B113,0),"#,##0")&amp;" FCFA","PCD — N/A (pas de dividende)")</f>
+        <v>0</v>
+      </c>
+      <c r="B236" s="9">
+        <f>IFERROR(IF(ISNUMBER(B113),B113,""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C236" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D236" s="47">
+        <f>IFERROR(IF(NOT(ISNUMBER(B113)),"Non disponible — dividend = 0",IF(B24&lt;B113,"Prix SOUS PCD — survente","Prix AU-DESSUS PCD — surachat")),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
+      <c r="G236" s="12"/>
+      <c r="H236" s="12"/>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="5">
+        <f>IF(ISNUMBER(B124),"Gordon P0  =  "&amp;TEXT(ROUND(B124,0),"#,##0")&amp;" FCFA","Gordon P0 — N/A (saisir D1)")</f>
+        <v>0</v>
+      </c>
+      <c r="B237" s="9">
+        <f>IFERROR(IF(ISNUMBER(B124),B124,""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C237" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="D237" s="47">
+        <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Non disponible — saisir D1",IF(B24&lt;B124,"Prix SOUS P0 — opportunite","Prix AU-DESSUS P0 — surevalue")),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
+      <c r="G237" s="12"/>
+      <c r="H237" s="12"/>
+    </row>
+    <row r="238" spans="1:8" ht="30" customHeight="1">
+      <c r="A238" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B238" s="48">
+        <f>IFERROR((B31*2+IF(ISNUMBER(B113),B113,0)+IF(ISNUMBER(B124),B124,0))/(2+IF(ISNUMBER(B113),1,0)+IF(ISNUMBER(B124),1,0)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C238" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="D238" s="49">
+        <f>IFERROR(IF(B24&lt;B238*0.75,"FORTE OPPORTUNITE — decote &gt; 25%",IF(B24&lt;B238*0.85,"Achat ideal — decote 15-25%",IF(B24&lt;B238,"Legerement sous-evalue",IF(B24&lt;B238*1.20,"Zone normale / prime moderee","ATTENTION — surevaluation &gt; 20%")))),"Saisir prix actuel (B24)")</f>
+        <v>0</v>
+      </c>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
+      <c r="G238" s="12"/>
+      <c r="H238" s="12"/>
+    </row>
+    <row r="239" spans="1:8" ht="5" customHeight="1"/>
+    <row r="240" spans="1:8" ht="20" customHeight="1">
+      <c r="A240" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="3"/>
+      <c r="G240" s="3"/>
+      <c r="H240" s="3"/>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E241" s="4"/>
+      <c r="F241" s="4"/>
+      <c r="G241" s="4"/>
+      <c r="H241" s="4"/>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B242" s="9">
+        <f>IFERROR(B238*0.75,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C242" s="50">
+        <f>IFERROR((B24/(B238*0.75)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D242" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
+      <c r="G242" s="12"/>
+      <c r="H242" s="12"/>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B243" s="9">
+        <f>IFERROR(B238*0.85,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C243" s="50">
+        <f>IFERROR((B24/(B238*0.85)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D243" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
+      <c r="G243" s="12"/>
+      <c r="H243" s="12"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="B244" s="9">
+        <f>IFERROR(B238,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C244" s="50">
+        <f>IFERROR((B24/B238-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D244" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
+      <c r="G244" s="12"/>
+      <c r="H244" s="12"/>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B245" s="9">
+        <f>IFERROR(B238*1.10,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C245" s="50">
+        <f>IFERROR((B24/(B238*1.10)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D245" s="51" t="s">
+        <v>288</v>
+      </c>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
+      <c r="G245" s="12"/>
+      <c r="H245" s="12"/>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B246" s="9">
+        <f>IFERROR(B238*1.20,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C246" s="50">
+        <f>IFERROR((B24/(B238*1.20)-1)*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D246" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
+      <c r="G246" s="12"/>
+      <c r="H246" s="12"/>
+    </row>
+    <row r="247" spans="1:8" ht="5" customHeight="1"/>
+    <row r="248" spans="1:8" ht="5" customHeight="1"/>
+    <row r="249" spans="1:8" ht="22" customHeight="1">
+      <c r="A249" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+      <c r="E249" s="1"/>
+      <c r="F249" s="1"/>
+      <c r="G249" s="1"/>
+      <c r="H249" s="1"/>
+    </row>
+    <row r="250" spans="1:8" ht="5" customHeight="1"/>
+    <row r="251" spans="1:8" ht="20" customHeight="1">
+      <c r="A251" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
+      <c r="E251" s="3"/>
+      <c r="F251" s="3"/>
+      <c r="G251" s="3"/>
+      <c r="H251" s="3"/>
+    </row>
+    <row r="252" spans="1:8" ht="14" customHeight="1">
+      <c r="A252" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="B252" s="34"/>
+      <c r="C252" s="34"/>
+      <c r="D252" s="34"/>
+      <c r="E252" s="34"/>
+      <c r="F252" s="34"/>
+      <c r="G252" s="34"/>
+      <c r="H252" s="34"/>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F253" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H253" s="4"/>
+    </row>
+    <row r="254" spans="1:8" ht="18" customHeight="1">
+      <c r="A254" s="52"/>
+      <c r="B254" s="33"/>
+      <c r="C254" s="33"/>
+      <c r="D254" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A254,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E254" s="33"/>
+      <c r="F254" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C254),OR(D254&lt;&gt;"",ISNUMBER(E254))),C254/IF(D254&lt;&gt;"",D254,E254),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G254" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F254)),"—",IF(F254&lt;0.85,"BAS — opportunite acheteur",IF(F254&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H254" s="12"/>
+    </row>
+    <row r="255" spans="1:8" ht="18" customHeight="1">
+      <c r="A255" s="52"/>
+      <c r="B255" s="33"/>
+      <c r="C255" s="33"/>
+      <c r="D255" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A255,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E255" s="33"/>
+      <c r="F255" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C255),OR(D255&lt;&gt;"",ISNUMBER(E255))),C255/IF(D255&lt;&gt;"",D255,E255),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G255" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F255)),"—",IF(F255&lt;0.85,"BAS — opportunite acheteur",IF(F255&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H255" s="12"/>
+    </row>
+    <row r="256" spans="1:8" ht="18" customHeight="1">
+      <c r="A256" s="52"/>
+      <c r="B256" s="33"/>
+      <c r="C256" s="33"/>
+      <c r="D256" s="7">
+        <f>IFERROR(CHOOSE(MATCH(A256,{"Caoutchouc RSS3 (USD/kg)","Huile de palme CPO (USD/t)","Cacao (USD/t)","Coton (USD/lb)","Cafe Robusta (USD/t)"},0),1.65,820,2500,0.85,1800),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E256" s="33"/>
+      <c r="F256" s="7">
+        <f>IFERROR(IF(AND(ISNUMBER(C256),OR(D256&lt;&gt;"",ISNUMBER(E256))),C256/IF(D256&lt;&gt;"",D256,E256),""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="G256" s="53">
+        <f>IFERROR(IF(NOT(ISNUMBER(F256)),"—",IF(F256&lt;0.85,"BAS — opportunite acheteur",IF(F256&lt;1.15,"MILIEU — cycle normal","HAUT — PER annuel trompeur"))),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="H256" s="12"/>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B257" s="50">
+        <f>IFERROR(SUM(B254:B256),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C257" s="53">
+        <f>IFERROR(IF(ABS(SUM(B254:B256)-100)&lt;0.1,"Total = 100% OK","ATTENTION : total "&amp;TEXT(SUM(B254:B256),"0.0")&amp;"% — verifier les %"),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="D257" s="12"/>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
+      <c r="G257" s="12"/>
+      <c r="H257" s="12"/>
+    </row>
+    <row r="258" spans="1:8" ht="5" customHeight="1"/>
+    <row r="259" spans="1:8" ht="20" customHeight="1">
+      <c r="A259" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B259" s="3"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3"/>
+      <c r="E259" s="3"/>
+      <c r="F259" s="3"/>
+      <c r="G259" s="3"/>
+      <c r="H259" s="3"/>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="4"/>
+      <c r="H260" s="4"/>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B261" s="54">
+        <f>IFERROR((IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254*F254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255*F255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256*F256,0))/(IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256,0)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C261" s="12"/>
+      <c r="D261" s="53">
+        <f>IFERROR("Indice "&amp;TEXT(B261,"0.00")&amp;" — "&amp; IF(B261&lt;0.85,"en dessous moy LT : bas de cycle",IF(B261&lt;1.15,"proche moy LT : milieu de cycle","au-dessus moy LT : haut de cycle")),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
+      <c r="G261" s="12"/>
+      <c r="H261" s="12"/>
+    </row>
+    <row r="262" spans="1:8" ht="40" customHeight="1">
+      <c r="A262" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B262" s="55">
+        <f>IFERROR(IF(B261&lt;0.85,"BAS DE CYCLE",IF(B261&lt;1.15,"MILIEU DE CYCLE","HAUT DE CYCLE")),"—")</f>
+        <v>0</v>
+      </c>
+      <c r="C262" s="12"/>
+      <c r="D262" s="56">
+        <f>IFERROR(IF(B261&lt;0.85,"ACHETER : RN comprime par bas cycle, actifs (plantations) solides. PER eleve = normal, ne pas vendre sur cette base.",IF(B261&lt;1.15,"ANALYSE STANDARD applicable. PER historique fiable.","PRUDENCE : RN gonfle par haut cycle. PER bas = TROMPEUR. Preferer PER normalise cycle (G3) avant toute decision.")),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E262" s="12"/>
+      <c r="F262" s="12"/>
+      <c r="G262" s="12"/>
+      <c r="H262" s="12"/>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B263" s="10">
+        <f>IFERROR(COUNTA(A254:A256),0)</f>
+        <v>0</v>
+      </c>
+      <c r="C263" s="12"/>
+      <c r="D263" s="53">
+        <f>IFERROR(IF(COUNTA(A254:A256)&gt;=2,"Multi-matieres : diversification naturelle — cycles partiellement decoreles (ex: SOGB)","Mono-matiere : exposition totale au cycle unique (ex: SAPH, PALMCI)"),"")</f>
+        <v>0</v>
+      </c>
+      <c r="E263" s="12"/>
+      <c r="F263" s="12"/>
+      <c r="G263" s="12"/>
+      <c r="H263" s="12"/>
+    </row>
+    <row r="264" spans="1:8" ht="5" customHeight="1"/>
+    <row r="265" spans="1:8" ht="20" customHeight="1">
+      <c r="A265" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B265" s="3"/>
+      <c r="C265" s="3"/>
+      <c r="D265" s="3"/>
+      <c r="E265" s="3"/>
+      <c r="F265" s="3"/>
+      <c r="G265" s="3"/>
+      <c r="H265" s="3"/>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B266" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4"/>
+      <c r="G266" s="4"/>
+      <c r="H266" s="4"/>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B267" s="9">
+        <f>IFERROR(AVERAGE(B12:F12)*1000000/B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C267" s="12"/>
+      <c r="D267" s="57" t="s">
+        <v>309</v>
+      </c>
+      <c r="E267" s="12"/>
+      <c r="F267" s="12"/>
+      <c r="G267" s="12"/>
+      <c r="H267" s="12"/>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="B268" s="54">
+        <f>IFERROR(B24/B267,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C268" s="12"/>
+      <c r="D268" s="58">
+        <f>IFERROR(IF(B268&lt;9,"Sous-evalue sur cycle complet — forte opportunite",IF(B268&lt;15,"Zone normale sur cycle — achat raisonnable",IF(B268&lt;22,"Prime moderee sur cycle — attendre correction","Fortement surevalue sur cycle — eviter"))),"Saisir donnees A1 et A2")</f>
+        <v>0</v>
+      </c>
+      <c r="E268" s="12"/>
+      <c r="F268" s="12"/>
+      <c r="G268" s="12"/>
+      <c r="H268" s="12"/>
+    </row>
+    <row r="269" spans="1:8" ht="28" customHeight="1">
+      <c r="A269" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B269" s="59">
+        <f>IFERROR(IF(AND(B261&lt;0.85,B268&lt;15),"ACHAT FORT — bas cycle + sous-evalue sur cycle",IF(AND(B261&lt;1.15,B268&lt;15),"ACHAT — milieu cycle + juste valorisation cycle",IF(AND(B261&gt;1.15,B268&lt;9),"SURVEILLER — haut cycle mais tres sous-evalue cycle",IF(AND(B261&gt;1.15,B268&gt;=15),"EVITER — haut cycle ET surevalue sur cycle","NEUTRE — analyser fondamentaux en detail")))),"Saisir matieres en G1")</f>
+        <v>0</v>
+      </c>
+      <c r="C269" s="59"/>
+      <c r="D269" s="59"/>
+      <c r="E269" s="12"/>
+      <c r="F269" s="12"/>
+      <c r="G269" s="12"/>
+      <c r="H269" s="12"/>
+    </row>
+    <row r="270" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="44">
+  <mergeCells count="57">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -4835,6 +6217,19 @@
     <mergeCell ref="A184:H184"/>
     <mergeCell ref="A191:H191"/>
     <mergeCell ref="A198:H198"/>
+    <mergeCell ref="A206:H206"/>
+    <mergeCell ref="A208:H208"/>
+    <mergeCell ref="A216:H216"/>
+    <mergeCell ref="A223:H223"/>
+    <mergeCell ref="A231:H231"/>
+    <mergeCell ref="A233:H233"/>
+    <mergeCell ref="A240:H240"/>
+    <mergeCell ref="A249:H249"/>
+    <mergeCell ref="A251:H251"/>
+    <mergeCell ref="A252:H252"/>
+    <mergeCell ref="A259:H259"/>
+    <mergeCell ref="A265:H265"/>
+    <mergeCell ref="B269:D269"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -4885,6 +6280,11 @@
       <formula>NOT(ISERROR(SEARCH("Moyen",D30)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Matiere premiere" prompt="Choisir dans la liste. Pour 'Autre' : saisir moy. LT en col. E" sqref="A254:A256">
+      <formula1>"Caoutchouc RSS3 (USD/kg),Huile de palme CPO (USD/t),Cacao (USD/t),Coton (USD/lb),Cafe Robusta (USD/t),Autre"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4906,7 +6306,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4925,188 +6325,212 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
+      <c r="A4" s="60" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" s="60"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
         <v>207</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>237</v>
+        <v>314</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>238</v>
+        <v>315</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>239</v>
+        <v>316</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>240</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="47">
+        <v>318</v>
+      </c>
+      <c r="B6" s="61">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D6" s="48">
+        <v>319</v>
+      </c>
+      <c r="D6" s="62">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="49"/>
+      <c r="E6" s="63">
+        <f>IFERROR(IF(ETUDE!G8&gt;=15,3,IF(ETUDE!G8&gt;=5,2,IF(ETUDE!G8&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="47">
+        <v>320</v>
+      </c>
+      <c r="B7" s="61">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D7" s="48">
+        <v>319</v>
+      </c>
+      <c r="D7" s="62">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="49"/>
+      <c r="E7" s="63">
+        <f>IFERROR(IF(ETUDE!G12&gt;=15,3,IF(ETUDE!G12&gt;=5,2,IF(ETUDE!G12&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="47">
+        <v>321</v>
+      </c>
+      <c r="B8" s="61">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="48">
+        <v>322</v>
+      </c>
+      <c r="D8" s="62">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="49"/>
+      <c r="E8" s="63">
+        <f>IFERROR(IF(ETUDE!G16&gt;=10,3,IF(ETUDE!G16&gt;=5,2,IF(ETUDE!G16&gt;=2,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B9" s="47">
+        <v>323</v>
+      </c>
+      <c r="B9" s="61">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="D9" s="48">
+        <v>324</v>
+      </c>
+      <c r="D9" s="62">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="49"/>
+      <c r="E9" s="63">
+        <f>IFERROR(IF(ETUDE!B30&lt;9,3,IF(ETUDE!B30&lt;=15,2,IF(ETUDE!B30&lt;=20,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B10" s="47">
+        <v>325</v>
+      </c>
+      <c r="B10" s="61">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="48">
+        <v>326</v>
+      </c>
+      <c r="D10" s="62">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="49"/>
+      <c r="E10" s="63">
+        <f>IFERROR(IF(ETUDE!B32&lt;1,3,IF(ETUDE!B32&lt;2,1,0)),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B11" s="47">
+        <v>327</v>
+      </c>
+      <c r="B11" s="61">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="48">
+        <v>319</v>
+      </c>
+      <c r="D11" s="62">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="49"/>
+      <c r="E11" s="63">
+        <f>IFERROR(IF(ETUDE!B33&gt;=15,3,IF(ETUDE!B33&gt;=10,2,IF(ETUDE!B33&gt;=5,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B12" s="47">
+        <v>328</v>
+      </c>
+      <c r="B12" s="61">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12" s="48">
+        <v>329</v>
+      </c>
+      <c r="D12" s="62">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="49"/>
+      <c r="E12" s="63">
+        <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=6,3,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,2,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=1,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B13" s="47">
+        <v>330</v>
+      </c>
+      <c r="B13" s="61">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="D13" s="48">
+        <v>331</v>
+      </c>
+      <c r="D13" s="62">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="49"/>
+      <c r="E13" s="63">
+        <f>IFERROR(IF(ETUDE!B34&lt;10,3,IF(ETUDE!B34&lt;22,2,IF(ETUDE!B34&lt;30,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="51">
+        <v>332</v>
+      </c>
+      <c r="B14" s="64"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="65">
         <f>SUM(E6:E13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="5" customHeight="1"/>
     <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
+      <c r="A16" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
@@ -5116,7 +6540,7 @@
         <v>99</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>17</v>
@@ -5127,110 +6551,125 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B18" s="52">
+        <v>334</v>
+      </c>
+      <c r="B18" s="66">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18" s="48">
+        <v>335</v>
+      </c>
+      <c r="D18" s="62">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="49"/>
+      <c r="E18" s="63">
+        <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B19" s="52">
+        <v>336</v>
+      </c>
+      <c r="B19" s="66">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="D19" s="48">
+        <v>337</v>
+      </c>
+      <c r="D19" s="62">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="49"/>
+      <c r="E19" s="63">
+        <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B20" s="52">
+        <v>338</v>
+      </c>
+      <c r="B20" s="66">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="48">
+        <v>339</v>
+      </c>
+      <c r="D20" s="62">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="49"/>
+      <c r="E20" s="63">
+        <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B21" s="52">
+        <v>340</v>
+      </c>
+      <c r="B21" s="66">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="48">
+        <v>341</v>
+      </c>
+      <c r="D21" s="62">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="49"/>
+      <c r="E21" s="63">
+        <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="52">
+        <v>342</v>
+      </c>
+      <c r="B22" s="66">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D22" s="48">
+        <v>343</v>
+      </c>
+      <c r="D22" s="62">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="49"/>
+      <c r="E22" s="63">
+        <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="51">
+        <v>344</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
+      <c r="E23" s="65">
         <f>SUM(E18:E22)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="53" t="s">
-        <v>269</v>
-      </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
+      <c r="A25" s="67" t="s">
+        <v>345</v>
+      </c>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
@@ -5240,133 +6679,133 @@
         <v>209</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>270</v>
+        <v>346</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="54">
+        <v>349</v>
+      </c>
+      <c r="B27" s="68">
         <f>E14</f>
         <v>0</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="69">
         <v>24</v>
       </c>
-      <c r="D27" s="56">
+      <c r="D27" s="70">
         <f>IFERROR(E14/24*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="71">
         <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B28" s="54">
+        <v>350</v>
+      </c>
+      <c r="B28" s="68">
         <f>E23</f>
         <v>0</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="69">
         <v>15</v>
       </c>
-      <c r="D28" s="56">
+      <c r="D28" s="70">
         <f>IFERROR(E23/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="57">
+      <c r="E28" s="71">
         <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B29" s="58">
+        <v>351</v>
+      </c>
+      <c r="B29" s="72">
         <f>IFERROR(E14+E23,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="59">
+      <c r="C29" s="73">
         <v>39</v>
       </c>
-      <c r="D29" s="56">
+      <c r="D29" s="70">
         <f>IFERROR(B29/39*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="74">
         <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="46" t="s">
-        <v>276</v>
-      </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="46"/>
+      <c r="A31" s="60" t="s">
+        <v>352</v>
+      </c>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="4" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="61">
+      <c r="A33" s="75">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="62">
+      <c r="B33" s="76">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="63">
+      <c r="C33" s="77">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="63">
+      <c r="D33" s="77">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="64">
+      <c r="E33" s="78">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="B35" s="46"/>
-      <c r="C35" s="46"/>
-      <c r="D35" s="46"/>
-      <c r="E35" s="46"/>
+      <c r="A35" s="60" t="s">
+        <v>357</v>
+      </c>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
     </row>
     <row r="36" spans="1:5" ht="50" customHeight="1">
       <c r="A36" s="28"/>
@@ -5518,7 +6957,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -5529,7 +6968,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5537,56 +6976,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="67" t="s">
-        <v>285</v>
+      <c r="A3" s="79" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="57" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="65" t="s">
-        <v>286</v>
-      </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="67" t="s">
-        <v>287</v>
+      <c r="A4" s="79" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="57" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" s="66"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="67" t="s">
-        <v>289</v>
+      <c r="A5" s="79" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="57" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="65" t="s">
-        <v>290</v>
-      </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="67" t="s">
-        <v>291</v>
+      <c r="A6" s="79" t="s">
+        <v>366</v>
+      </c>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="57" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -5594,63 +7033,63 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="B9" s="45">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="D9" s="12"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="B10" s="45">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="D10" s="12"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="B11" s="45">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="D11" s="12"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B12" s="69"/>
+        <v>372</v>
+      </c>
+      <c r="B12" s="52"/>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B13" s="69"/>
+        <v>373</v>
+      </c>
+      <c r="B13" s="52"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
     </row>
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>374</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -5660,15 +7099,15 @@
       <c r="A16" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="69"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B17" s="69"/>
+        <v>375</v>
+      </c>
+      <c r="B17" s="52"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
@@ -5676,7 +7115,7 @@
       <c r="A18" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B18" s="69"/>
+      <c r="B18" s="52"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
@@ -5684,14 +7123,14 @@
       <c r="A19" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B19" s="69"/>
+      <c r="B19" s="52"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>300</v>
+        <v>376</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -5702,7 +7141,7 @@
         <v>227</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>301</v>
+        <v>377</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -5711,7 +7150,7 @@
       <c r="A23" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B23" s="69"/>
+      <c r="B23" s="52"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
@@ -5720,7 +7159,7 @@
         <v>229</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>302</v>
+        <v>378</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -5730,7 +7169,7 @@
         <v>230</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>303</v>
+        <v>379</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
@@ -5738,7 +7177,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -5748,7 +7187,7 @@
       <c r="A28" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="69"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
@@ -5756,7 +7195,7 @@
       <c r="A29" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="69"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
@@ -5764,7 +7203,7 @@
       <c r="A30" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B30" s="69"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
@@ -5773,7 +7212,7 @@
         <v>234</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>305</v>
+        <v>381</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -5781,7 +7220,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>306</v>
+        <v>382</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -5789,46 +7228,115 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>307</v>
+        <v>383</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>308</v>
+        <v>384</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B35" s="69"/>
+        <v>385</v>
+      </c>
+      <c r="B35" s="52"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="5" t="s">
-        <v>310</v>
+        <v>386</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>311</v>
+        <v>387</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="5" t="s">
-        <v>312</v>
+        <v>388</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
+    <row r="39" spans="1:4" ht="20" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:C3"/>
@@ -5840,12 +7348,675 @@
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FF059669"/>
+  </sheetPr>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="12" max="12" width="22.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="26" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:12" ht="16" customHeight="1">
+      <c r="A2" s="82" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+    </row>
+    <row r="3" spans="1:12" ht="5" customHeight="1"/>
+    <row r="4" spans="1:12" ht="32" customHeight="1">
+      <c r="A4" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="20" customHeight="1">
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="85">
+        <f>IFERROR(IF(A5="","",C5*D5*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="85">
+        <f>IFERROR(IF(A5="","",C5*E5),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="85">
+        <f>IFERROR(IF(A5="","",(C5*E5)-(C5*D5*1.014)+(C5*F5)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="86">
+        <f>IFERROR(IF(A5="","",J5/H5*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="87">
+        <f>IFERROR(IF(A5="","—",IF(K5&lt;-10,"VENDRE — Stop-loss",IF(AND(G5&gt;=24,K5&gt;=0),"RENFORCER",IF(AND(G5&gt;=15,K5&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="20" customHeight="1">
+      <c r="A6" s="83"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="85">
+        <f>IFERROR(IF(A6="","",C6*D6*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="85">
+        <f>IFERROR(IF(A6="","",C6*E6),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="85">
+        <f>IFERROR(IF(A6="","",(C6*E6)-(C6*D6*1.014)+(C6*F6)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="86">
+        <f>IFERROR(IF(A6="","",J6/H6*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="87">
+        <f>IFERROR(IF(A6="","—",IF(K6&lt;-10,"VENDRE — Stop-loss",IF(AND(G6&gt;=24,K6&gt;=0),"RENFORCER",IF(AND(G6&gt;=15,K6&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="20" customHeight="1">
+      <c r="A7" s="83"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="85">
+        <f>IFERROR(IF(A7="","",C7*D7*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="85">
+        <f>IFERROR(IF(A7="","",C7*E7),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="85">
+        <f>IFERROR(IF(A7="","",(C7*E7)-(C7*D7*1.014)+(C7*F7)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="86">
+        <f>IFERROR(IF(A7="","",J7/H7*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="87">
+        <f>IFERROR(IF(A7="","—",IF(K7&lt;-10,"VENDRE — Stop-loss",IF(AND(G7&gt;=24,K7&gt;=0),"RENFORCER",IF(AND(G7&gt;=15,K7&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="20" customHeight="1">
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="85">
+        <f>IFERROR(IF(A8="","",C8*D8*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="85">
+        <f>IFERROR(IF(A8="","",C8*E8),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="85">
+        <f>IFERROR(IF(A8="","",(C8*E8)-(C8*D8*1.014)+(C8*F8)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="86">
+        <f>IFERROR(IF(A8="","",J8/H8*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="87">
+        <f>IFERROR(IF(A8="","—",IF(K8&lt;-10,"VENDRE — Stop-loss",IF(AND(G8&gt;=24,K8&gt;=0),"RENFORCER",IF(AND(G8&gt;=15,K8&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="20" customHeight="1">
+      <c r="A9" s="83"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="85">
+        <f>IFERROR(IF(A9="","",C9*D9*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="85">
+        <f>IFERROR(IF(A9="","",C9*E9),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="85">
+        <f>IFERROR(IF(A9="","",(C9*E9)-(C9*D9*1.014)+(C9*F9)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="86">
+        <f>IFERROR(IF(A9="","",J9/H9*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="87">
+        <f>IFERROR(IF(A9="","—",IF(K9&lt;-10,"VENDRE — Stop-loss",IF(AND(G9&gt;=24,K9&gt;=0),"RENFORCER",IF(AND(G9&gt;=15,K9&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="20" customHeight="1">
+      <c r="A10" s="83"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="85">
+        <f>IFERROR(IF(A10="","",C10*D10*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="85">
+        <f>IFERROR(IF(A10="","",C10*E10),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="85">
+        <f>IFERROR(IF(A10="","",(C10*E10)-(C10*D10*1.014)+(C10*F10)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="86">
+        <f>IFERROR(IF(A10="","",J10/H10*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="87">
+        <f>IFERROR(IF(A10="","—",IF(K10&lt;-10,"VENDRE — Stop-loss",IF(AND(G10&gt;=24,K10&gt;=0),"RENFORCER",IF(AND(G10&gt;=15,K10&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="20" customHeight="1">
+      <c r="A11" s="83"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="84"/>
+      <c r="F11" s="84"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="85">
+        <f>IFERROR(IF(A11="","",C11*D11*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="85">
+        <f>IFERROR(IF(A11="","",C11*E11),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="85">
+        <f>IFERROR(IF(A11="","",(C11*E11)-(C11*D11*1.014)+(C11*F11)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="86">
+        <f>IFERROR(IF(A11="","",J11/H11*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="87">
+        <f>IFERROR(IF(A11="","—",IF(K11&lt;-10,"VENDRE — Stop-loss",IF(AND(G11&gt;=24,K11&gt;=0),"RENFORCER",IF(AND(G11&gt;=15,K11&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="20" customHeight="1">
+      <c r="A12" s="83"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="85">
+        <f>IFERROR(IF(A12="","",C12*D12*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="85">
+        <f>IFERROR(IF(A12="","",C12*E12),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="85">
+        <f>IFERROR(IF(A12="","",(C12*E12)-(C12*D12*1.014)+(C12*F12)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="86">
+        <f>IFERROR(IF(A12="","",J12/H12*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="87">
+        <f>IFERROR(IF(A12="","—",IF(K12&lt;-10,"VENDRE — Stop-loss",IF(AND(G12&gt;=24,K12&gt;=0),"RENFORCER",IF(AND(G12&gt;=15,K12&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="20" customHeight="1">
+      <c r="A13" s="83"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="85">
+        <f>IFERROR(IF(A13="","",C13*D13*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="85">
+        <f>IFERROR(IF(A13="","",C13*E13),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="85">
+        <f>IFERROR(IF(A13="","",(C13*E13)-(C13*D13*1.014)+(C13*F13)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="86">
+        <f>IFERROR(IF(A13="","",J13/H13*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="87">
+        <f>IFERROR(IF(A13="","—",IF(K13&lt;-10,"VENDRE — Stop-loss",IF(AND(G13&gt;=24,K13&gt;=0),"RENFORCER",IF(AND(G13&gt;=15,K13&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="20" customHeight="1">
+      <c r="A14" s="83"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="85">
+        <f>IFERROR(IF(A14="","",C14*D14*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="85">
+        <f>IFERROR(IF(A14="","",C14*E14),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="85">
+        <f>IFERROR(IF(A14="","",(C14*E14)-(C14*D14*1.014)+(C14*F14)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="86">
+        <f>IFERROR(IF(A14="","",J14/H14*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="87">
+        <f>IFERROR(IF(A14="","—",IF(K14&lt;-10,"VENDRE — Stop-loss",IF(AND(G14&gt;=24,K14&gt;=0),"RENFORCER",IF(AND(G14&gt;=15,K14&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="20" customHeight="1">
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="85">
+        <f>IFERROR(IF(A15="","",C15*D15*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="85">
+        <f>IFERROR(IF(A15="","",C15*E15),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="85">
+        <f>IFERROR(IF(A15="","",(C15*E15)-(C15*D15*1.014)+(C15*F15)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="86">
+        <f>IFERROR(IF(A15="","",J15/H15*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="87">
+        <f>IFERROR(IF(A15="","—",IF(K15&lt;-10,"VENDRE — Stop-loss",IF(AND(G15&gt;=24,K15&gt;=0),"RENFORCER",IF(AND(G15&gt;=15,K15&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="20" customHeight="1">
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="85">
+        <f>IFERROR(IF(A16="","",C16*D16*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="85">
+        <f>IFERROR(IF(A16="","",C16*E16),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="85">
+        <f>IFERROR(IF(A16="","",(C16*E16)-(C16*D16*1.014)+(C16*F16)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="86">
+        <f>IFERROR(IF(A16="","",J16/H16*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="87">
+        <f>IFERROR(IF(A16="","—",IF(K16&lt;-10,"VENDRE — Stop-loss",IF(AND(G16&gt;=24,K16&gt;=0),"RENFORCER",IF(AND(G16&gt;=15,K16&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20" customHeight="1">
+      <c r="A17" s="83"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="85">
+        <f>IFERROR(IF(A17="","",C17*D17*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="85">
+        <f>IFERROR(IF(A17="","",C17*E17),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="85">
+        <f>IFERROR(IF(A17="","",(C17*E17)-(C17*D17*1.014)+(C17*F17)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="86">
+        <f>IFERROR(IF(A17="","",J17/H17*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="87">
+        <f>IFERROR(IF(A17="","—",IF(K17&lt;-10,"VENDRE — Stop-loss",IF(AND(G17&gt;=24,K17&gt;=0),"RENFORCER",IF(AND(G17&gt;=15,K17&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="20" customHeight="1">
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="85">
+        <f>IFERROR(IF(A18="","",C18*D18*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="85">
+        <f>IFERROR(IF(A18="","",C18*E18),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="85">
+        <f>IFERROR(IF(A18="","",(C18*E18)-(C18*D18*1.014)+(C18*F18)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="86">
+        <f>IFERROR(IF(A18="","",J18/H18*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="87">
+        <f>IFERROR(IF(A18="","—",IF(K18&lt;-10,"VENDRE — Stop-loss",IF(AND(G18&gt;=24,K18&gt;=0),"RENFORCER",IF(AND(G18&gt;=15,K18&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="20" customHeight="1">
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="85">
+        <f>IFERROR(IF(A19="","",C19*D19*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="85">
+        <f>IFERROR(IF(A19="","",C19*E19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="85">
+        <f>IFERROR(IF(A19="","",(C19*E19)-(C19*D19*1.014)+(C19*F19)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="86">
+        <f>IFERROR(IF(A19="","",J19/H19*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="87">
+        <f>IFERROR(IF(A19="","—",IF(K19&lt;-10,"VENDRE — Stop-loss",IF(AND(G19&gt;=24,K19&gt;=0),"RENFORCER",IF(AND(G19&gt;=15,K19&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="5" customHeight="1"/>
+    <row r="21" spans="1:12" ht="22" customHeight="1">
+      <c r="A21" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="B21" s="88"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="88"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="89">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="89">
+        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="90">
+        <f>IFERROR(J21/H21*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="87">
+        <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="8" customHeight="1"/>
+    <row r="23" spans="1:12" ht="18" customHeight="1">
+      <c r="A23" s="91" t="s">
+        <v>411</v>
+      </c>
+      <c r="B23" s="91"/>
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="91"/>
+      <c r="I23" s="91"/>
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="91"/>
+    </row>
+    <row r="24" spans="1:12" ht="16" customHeight="1">
+      <c r="A24" s="92" t="s">
+        <v>412</v>
+      </c>
+      <c r="B24" s="93" t="s">
+        <v>413</v>
+      </c>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
+      <c r="F24" s="93"/>
+      <c r="G24" s="93"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93"/>
+      <c r="J24" s="93"/>
+      <c r="K24" s="93"/>
+      <c r="L24" s="93"/>
+    </row>
+    <row r="25" spans="1:12" ht="16" customHeight="1">
+      <c r="A25" s="92" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" s="93" t="s">
+        <v>415</v>
+      </c>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="93"/>
+      <c r="G25" s="93"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93"/>
+      <c r="J25" s="93"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+    </row>
+    <row r="26" spans="1:12" ht="16" customHeight="1">
+      <c r="A26" s="92" t="s">
+        <v>416</v>
+      </c>
+      <c r="B26" s="93" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" s="93"/>
+      <c r="D26" s="93"/>
+      <c r="E26" s="93"/>
+      <c r="F26" s="93"/>
+      <c r="G26" s="93"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93"/>
+      <c r="J26" s="93"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+    </row>
+    <row r="27" spans="1:12" ht="16" customHeight="1">
+      <c r="A27" s="92" t="s">
+        <v>418</v>
+      </c>
+      <c r="B27" s="93" t="s">
+        <v>419</v>
+      </c>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="B24:L24"/>
+    <mergeCell ref="B25:L25"/>
+    <mergeCell ref="B26:L26"/>
+    <mergeCell ref="B27:L27"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF374151"/>
@@ -5861,322 +8032,322 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>420</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="70" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>316</v>
-      </c>
-      <c r="D2" s="70" t="s">
-        <v>317</v>
+      <c r="B2" s="94" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2" s="94" t="s">
+        <v>422</v>
+      </c>
+      <c r="D2" s="94" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
+      <c r="A3" s="60" t="s">
+        <v>424</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="B4" s="71" t="s">
-        <v>320</v>
-      </c>
-      <c r="C4" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D4" s="72" t="s">
-        <v>322</v>
+        <v>425</v>
+      </c>
+      <c r="B4" s="95" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D4" s="96" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>324</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>325</v>
+        <v>429</v>
+      </c>
+      <c r="B5" s="95" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D5" s="96" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>328</v>
+        <v>432</v>
+      </c>
+      <c r="B6" s="95" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="71" t="s">
-        <v>329</v>
-      </c>
-      <c r="C7" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>331</v>
+        <v>323</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" s="96" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B8" s="71" t="s">
-        <v>333</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>335</v>
+        <v>438</v>
+      </c>
+      <c r="B8" s="95" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="96" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="71" t="s">
-        <v>336</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>337</v>
+        <v>325</v>
+      </c>
+      <c r="B9" s="95" t="s">
+        <v>442</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D9" s="96" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="C10" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D10" s="72" t="s">
-        <v>340</v>
+        <v>444</v>
+      </c>
+      <c r="B10" s="95" t="s">
+        <v>445</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B11" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="72" t="s">
-        <v>343</v>
+        <v>447</v>
+      </c>
+      <c r="B11" s="95" t="s">
+        <v>448</v>
+      </c>
+      <c r="C11" s="69"/>
+      <c r="D11" s="96" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" s="71" t="s">
-        <v>345</v>
-      </c>
-      <c r="C12" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="72" t="s">
-        <v>346</v>
+        <v>450</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>451</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D12" s="96" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B13" s="71" t="s">
-        <v>348</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>349</v>
+        <v>453</v>
+      </c>
+      <c r="B13" s="95" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" s="96" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="46" t="s">
-        <v>350</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
+      <c r="A14" s="60" t="s">
+        <v>456</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>352</v>
-      </c>
-      <c r="C15" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D15" s="72" t="s">
-        <v>353</v>
+        <v>457</v>
+      </c>
+      <c r="B15" s="95" t="s">
+        <v>458</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="96" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="B16" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="72" t="s">
-        <v>356</v>
+        <v>460</v>
+      </c>
+      <c r="B16" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="C16" s="69"/>
+      <c r="D16" s="96" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B17" s="71" t="s">
-        <v>355</v>
-      </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="72" t="s">
-        <v>357</v>
+      <c r="B17" s="95" t="s">
+        <v>461</v>
+      </c>
+      <c r="C17" s="69"/>
+      <c r="D17" s="96" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="B18" s="71" t="s">
-        <v>358</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="72" t="s">
-        <v>359</v>
+      <c r="B18" s="95" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" s="96" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B19" s="71" t="s">
-        <v>361</v>
-      </c>
-      <c r="C19" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="72" t="s">
-        <v>362</v>
+        <v>466</v>
+      </c>
+      <c r="B19" s="95" t="s">
+        <v>467</v>
+      </c>
+      <c r="C19" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="96" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>364</v>
-      </c>
-      <c r="C20" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>365</v>
+        <v>469</v>
+      </c>
+      <c r="B20" s="95" t="s">
+        <v>470</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D20" s="96" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="46" t="s">
-        <v>366</v>
-      </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46"/>
+      <c r="A21" s="60" t="s">
+        <v>472</v>
+      </c>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B22" s="71" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>369</v>
+        <v>473</v>
+      </c>
+      <c r="B22" s="95" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D22" s="96" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="B23" s="71" t="s">
-        <v>371</v>
-      </c>
-      <c r="C23" s="55" t="s">
-        <v>372</v>
-      </c>
-      <c r="D23" s="72" t="s">
-        <v>373</v>
+        <v>476</v>
+      </c>
+      <c r="B23" s="95" t="s">
+        <v>477</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>478</v>
+      </c>
+      <c r="D23" s="96" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="B24" s="71" t="s">
-        <v>375</v>
-      </c>
-      <c r="C24" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D24" s="72" t="s">
-        <v>376</v>
+        <v>480</v>
+      </c>
+      <c r="B24" s="95" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D24" s="96" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="B25" s="71" t="s">
-        <v>378</v>
-      </c>
-      <c r="C25" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>379</v>
+        <v>483</v>
+      </c>
+      <c r="B25" s="95" t="s">
+        <v>484</v>
+      </c>
+      <c r="C25" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="D25" s="96" t="s">
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="533">
   <si>
     <t>A — ANALYSE FONDAMENTALE</t>
   </si>
@@ -1485,6 +1485,147 @@
   </si>
   <si>
     <t>Taxe applicable a la vente sur BRVM</t>
+  </si>
+  <si>
+    <t>SOURCES DE DONNEES RECOMMANDEES</t>
+  </si>
+  <si>
+    <t>MARCHE BRVM</t>
+  </si>
+  <si>
+    <t>Cours &amp; volumes BRVM</t>
+  </si>
+  <si>
+    <t>https://www.brvm.org</t>
+  </si>
+  <si>
+    <t>Cours officiels, volumes, capitalisation, indices</t>
+  </si>
+  <si>
+    <t>Profils societes BRVM</t>
+  </si>
+  <si>
+    <t>https://www.richbourse.com</t>
+  </si>
+  <si>
+    <t>Rapports, bilans, ratios, actualites par societe</t>
+  </si>
+  <si>
+    <t>Actualites &amp; analyses</t>
+  </si>
+  <si>
+    <t>https://www.sika-finance.com</t>
+  </si>
+  <si>
+    <t>News, dividendes, resultats semestriels</t>
+  </si>
+  <si>
+    <t>MATIERES PREMIERES</t>
+  </si>
+  <si>
+    <t>Caoutchouc RSS3/TSR20</t>
+  </si>
+  <si>
+    <t>https://www.indexmundi.com/commodities/?commodity=rubber</t>
+  </si>
+  <si>
+    <t>Prix journalier + historique + graphique</t>
+  </si>
+  <si>
+    <t>Huile de palme CPO</t>
+  </si>
+  <si>
+    <t>https://www.indexmundi.com/commodities/?commodity=palm-oil</t>
+  </si>
+  <si>
+    <t>Cacao</t>
+  </si>
+  <si>
+    <t>https://www.indexmundi.com/commodities/?commodity=cocoa</t>
+  </si>
+  <si>
+    <t>Coton</t>
+  </si>
+  <si>
+    <t>https://www.indexmundi.com/commodities/?commodity=cotton</t>
+  </si>
+  <si>
+    <t>Cafe Robusta</t>
+  </si>
+  <si>
+    <t>https://www.indexmundi.com/commodities/?commodity=coffee-robusta</t>
+  </si>
+  <si>
+    <t>Toutes matieres (synthese)</t>
+  </si>
+  <si>
+    <t>https://www.worldbank.org/en/research/commodity-markets</t>
+  </si>
+  <si>
+    <t>Pink Sheet mensuel — moyennes LT officielles Banque Mondiale</t>
+  </si>
+  <si>
+    <t>TAUX &amp; MACROECONOMIE</t>
+  </si>
+  <si>
+    <t>Taux UEMOA / BCEAO</t>
+  </si>
+  <si>
+    <t>https://www.bceao.int</t>
+  </si>
+  <si>
+    <t>Taux directeur, inflation, statistiques zone UEMOA</t>
+  </si>
+  <si>
+    <t>Taux sans risque UEMOA</t>
+  </si>
+  <si>
+    <t>https://www.boad.org</t>
+  </si>
+  <si>
+    <t>Obligations BOAD — reference taux sans risque</t>
+  </si>
+  <si>
+    <t>Indicateurs macro Afrique</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org</t>
+  </si>
+  <si>
+    <t>PIB, inflation, taux de change par pays</t>
+  </si>
+  <si>
+    <t>RAPPORTS ANNUELS</t>
+  </si>
+  <si>
+    <t>SOGB</t>
+  </si>
+  <si>
+    <t>https://www.sogb.ci</t>
+  </si>
+  <si>
+    <t>Rapports annuels, chiffres cles, dividendes</t>
+  </si>
+  <si>
+    <t>SAPH</t>
+  </si>
+  <si>
+    <t>https://www.saph.ci</t>
+  </si>
+  <si>
+    <t>PALMCI</t>
+  </si>
+  <si>
+    <t>https://www.palmci.ci</t>
+  </si>
+  <si>
+    <t>Toutes societes BRVM</t>
+  </si>
+  <si>
+    <t>https://www.brvm.org/fr/societes-cotees</t>
+  </si>
+  <si>
+    <t>Acces aux profils et publications officielles</t>
   </si>
 </sst>
 </file>
@@ -1499,7 +1640,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="@"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1836,6 +1977,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1E3A5F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1D4ED8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -1990,7 +2146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2353,6 +2509,14 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -8021,13 +8185,12 @@
   <sheetPr>
     <tabColor rgb="FF374151"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" customWidth="1"/>
+    <col min="3" max="4" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
@@ -8350,14 +8513,270 @@
         <v>485</v>
       </c>
     </row>
+    <row r="26" spans="1:4" ht="8" customHeight="1"/>
+    <row r="27" spans="1:4" ht="20" customHeight="1">
+      <c r="A27" s="60" t="s">
+        <v>486</v>
+      </c>
+      <c r="B27" s="60"/>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+    </row>
+    <row r="28" spans="1:4" ht="16" customHeight="1">
+      <c r="A28" s="91" t="s">
+        <v>487</v>
+      </c>
+      <c r="B28" s="91"/>
+      <c r="C28" s="91"/>
+      <c r="D28" s="91"/>
+    </row>
+    <row r="29" spans="1:4" ht="18" customHeight="1">
+      <c r="A29" s="97" t="s">
+        <v>488</v>
+      </c>
+      <c r="B29" s="98" t="s">
+        <v>489</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>490</v>
+      </c>
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="1:4" ht="18" customHeight="1">
+      <c r="A30" s="97" t="s">
+        <v>491</v>
+      </c>
+      <c r="B30" s="98" t="s">
+        <v>492</v>
+      </c>
+      <c r="C30" s="57" t="s">
+        <v>493</v>
+      </c>
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="1:4" ht="18" customHeight="1">
+      <c r="A31" s="97" t="s">
+        <v>494</v>
+      </c>
+      <c r="B31" s="98" t="s">
+        <v>495</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>496</v>
+      </c>
+      <c r="D31" s="12"/>
+    </row>
+    <row r="32" spans="1:4" ht="16" customHeight="1">
+      <c r="A32" s="91" t="s">
+        <v>497</v>
+      </c>
+      <c r="B32" s="91"/>
+      <c r="C32" s="91"/>
+      <c r="D32" s="91"/>
+    </row>
+    <row r="33" spans="1:4" ht="18" customHeight="1">
+      <c r="A33" s="97" t="s">
+        <v>498</v>
+      </c>
+      <c r="B33" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="C33" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D33" s="12"/>
+    </row>
+    <row r="34" spans="1:4" ht="18" customHeight="1">
+      <c r="A34" s="97" t="s">
+        <v>501</v>
+      </c>
+      <c r="B34" s="98" t="s">
+        <v>502</v>
+      </c>
+      <c r="C34" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D34" s="12"/>
+    </row>
+    <row r="35" spans="1:4" ht="18" customHeight="1">
+      <c r="A35" s="97" t="s">
+        <v>503</v>
+      </c>
+      <c r="B35" s="98" t="s">
+        <v>504</v>
+      </c>
+      <c r="C35" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D35" s="12"/>
+    </row>
+    <row r="36" spans="1:4" ht="18" customHeight="1">
+      <c r="A36" s="97" t="s">
+        <v>505</v>
+      </c>
+      <c r="B36" s="98" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D36" s="12"/>
+    </row>
+    <row r="37" spans="1:4" ht="18" customHeight="1">
+      <c r="A37" s="97" t="s">
+        <v>507</v>
+      </c>
+      <c r="B37" s="98" t="s">
+        <v>508</v>
+      </c>
+      <c r="C37" s="57" t="s">
+        <v>500</v>
+      </c>
+      <c r="D37" s="12"/>
+    </row>
+    <row r="38" spans="1:4" ht="18" customHeight="1">
+      <c r="A38" s="97" t="s">
+        <v>509</v>
+      </c>
+      <c r="B38" s="98" t="s">
+        <v>510</v>
+      </c>
+      <c r="C38" s="57" t="s">
+        <v>511</v>
+      </c>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:4" ht="16" customHeight="1">
+      <c r="A39" s="91" t="s">
+        <v>512</v>
+      </c>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+    </row>
+    <row r="40" spans="1:4" ht="18" customHeight="1">
+      <c r="A40" s="97" t="s">
+        <v>513</v>
+      </c>
+      <c r="B40" s="98" t="s">
+        <v>514</v>
+      </c>
+      <c r="C40" s="57" t="s">
+        <v>515</v>
+      </c>
+      <c r="D40" s="12"/>
+    </row>
+    <row r="41" spans="1:4" ht="18" customHeight="1">
+      <c r="A41" s="97" t="s">
+        <v>516</v>
+      </c>
+      <c r="B41" s="98" t="s">
+        <v>517</v>
+      </c>
+      <c r="C41" s="57" t="s">
+        <v>518</v>
+      </c>
+      <c r="D41" s="12"/>
+    </row>
+    <row r="42" spans="1:4" ht="18" customHeight="1">
+      <c r="A42" s="97" t="s">
+        <v>519</v>
+      </c>
+      <c r="B42" s="98" t="s">
+        <v>520</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>521</v>
+      </c>
+      <c r="D42" s="12"/>
+    </row>
+    <row r="43" spans="1:4" ht="16" customHeight="1">
+      <c r="A43" s="91" t="s">
+        <v>522</v>
+      </c>
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+    </row>
+    <row r="44" spans="1:4" ht="18" customHeight="1">
+      <c r="A44" s="97" t="s">
+        <v>523</v>
+      </c>
+      <c r="B44" s="98" t="s">
+        <v>524</v>
+      </c>
+      <c r="C44" s="57" t="s">
+        <v>525</v>
+      </c>
+      <c r="D44" s="12"/>
+    </row>
+    <row r="45" spans="1:4" ht="18" customHeight="1">
+      <c r="A45" s="97" t="s">
+        <v>526</v>
+      </c>
+      <c r="B45" s="98" t="s">
+        <v>527</v>
+      </c>
+      <c r="C45" s="57" t="s">
+        <v>525</v>
+      </c>
+      <c r="D45" s="12"/>
+    </row>
+    <row r="46" spans="1:4" ht="18" customHeight="1">
+      <c r="A46" s="97" t="s">
+        <v>528</v>
+      </c>
+      <c r="B46" s="98" t="s">
+        <v>529</v>
+      </c>
+      <c r="C46" s="57" t="s">
+        <v>525</v>
+      </c>
+      <c r="D46" s="12"/>
+    </row>
+    <row r="47" spans="1:4" ht="18" customHeight="1">
+      <c r="A47" s="97" t="s">
+        <v>530</v>
+      </c>
+      <c r="B47" s="98" t="s">
+        <v>531</v>
+      </c>
+      <c r="C47" s="57" t="s">
+        <v>532</v>
+      </c>
+      <c r="D47" s="12"/>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="4">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A43:D43"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B29" r:id="rId1"/>
+    <hyperlink ref="B30" r:id="rId2"/>
+    <hyperlink ref="B31" r:id="rId3"/>
+    <hyperlink ref="B33" r:id="rId4"/>
+    <hyperlink ref="B34" r:id="rId5"/>
+    <hyperlink ref="B35" r:id="rId6"/>
+    <hyperlink ref="B36" r:id="rId7"/>
+    <hyperlink ref="B37" r:id="rId8"/>
+    <hyperlink ref="B38" r:id="rId9"/>
+    <hyperlink ref="B40" r:id="rId10"/>
+    <hyperlink ref="B41" r:id="rId11"/>
+    <hyperlink ref="B42" r:id="rId12"/>
+    <hyperlink ref="B44" r:id="rId13"/>
+    <hyperlink ref="B45" r:id="rId14"/>
+    <hyperlink ref="B46" r:id="rId15"/>
+    <hyperlink ref="B47" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="562">
   <si>
     <t>FICHE D'ANALYSE BOURSIERE BRVM</t>
   </si>
@@ -1092,7 +1092,16 @@
     <t>&lt; 22</t>
   </si>
   <si>
-    <t>SCORE FONDAMENTAL TOTAL (/24)</t>
+    <t>Tendance dividende (CAGR 4 ans %)</t>
+  </si>
+  <si>
+    <t>&gt; 0%</t>
+  </si>
+  <si>
+    <t>Reaction marche post-resultats (%)</t>
+  </si>
+  <si>
+    <t>SCORE FONDAMENTAL TOTAL (/30)</t>
   </si>
   <si>
     <t>SCORECARD TECHNIQUE</t>
@@ -1273,6 +1282,21 @@
   </si>
   <si>
     <t>&lt;-- Bilan actif courant</t>
+  </si>
+  <si>
+    <t>PSYCHOLOGIE DU MARCHE</t>
+  </si>
+  <si>
+    <t>Prix avant publication resultats (J-1, FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Cours de cloture J-1 avant annonce</t>
+  </si>
+  <si>
+    <t>Prix apres resultats J+5 (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Cours 5 jours apres publication</t>
   </si>
   <si>
     <t>PORTEFEUILLE BRVM — SUIVI DES POSITIONS &amp; RECOMMANDATIONS</t>
@@ -7299,167 +7323,194 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="23" t="s">
         <v>356</v>
       </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="83">
-        <f>SUM(E6:E13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="5" customHeight="1"/>
-    <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="A16" s="78" t="s">
+      <c r="B14" s="79">
+        <f>IFERROR(IF(ISNUMBER(ETUDE!B167),ETUDE!B167*100,"N/A"),"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="B16" s="78"/>
-      <c r="C16" s="78"/>
-      <c r="D16" s="78"/>
-      <c r="E16" s="78"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="22" t="s">
+      <c r="D14" s="80">
+        <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),"Pas de dividende",IF(ETUDE!B167&gt;=0.10,"Croissant fort (&gt;10%/an)",IF(ETUDE!B167&gt;=0.02,"Croissant (2-10%/an)",IF(ETUDE!B167&gt;=0,"Stable","Dividende en BAISSE")))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="81">
+        <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),0,IF(ETUDE!B167&gt;=0.10,3,IF(ETUDE!B167&gt;=0.02,2,IF(ETUDE!B167&gt;=0,1,0)))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="B15" s="79">
+        <f>IFERROR(IF(AND(ISNUMBER(PROFIL!B48),ISNUMBER(PROFIL!B49),PROFIL!B48&gt;0),(PROFIL!B49-PROFIL!B48)/PROFIL!B48*100,"Non renseigne"),"Non renseigne")</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>357</v>
+      </c>
+      <c r="D15" s="80">
+        <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),"Non renseigne — saisir dans PROFIL",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,"Accueil tres favorable — marche recompense",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,"Accueil positif",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,"Reaction mitigee","Punition marche — forte baisse")))),"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="81">
+        <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),0,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,3,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,2,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,1,0)))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="83">
+        <f>SUM(E6:E15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="5" customHeight="1"/>
+    <row r="18" spans="1:5" ht="18" customHeight="1">
+      <c r="A18" s="78" t="s">
+        <v>360</v>
+      </c>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B19" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C19" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D19" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="B18" s="84">
-        <f>IFERROR(ETUDE!D91,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="D18" s="80">
-        <f>IFERROR(ETUDE!E91,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="81">
-        <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="B19" s="84">
-        <f>IFERROR(ETUDE!E95,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="D19" s="80">
-        <f>IFERROR(ETUDE!E96,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="81">
-        <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="B20" s="84">
+        <f>IFERROR(ETUDE!D91,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="29" t="s">
         <v>362</v>
       </c>
-      <c r="B20" s="84">
-        <f>IFERROR(ETUDE!B104,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>363</v>
-      </c>
       <c r="D20" s="80">
-        <f>IFERROR(ETUDE!D104,"-")</f>
+        <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
       <c r="E20" s="81">
-        <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
+        <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="B21" s="84">
+        <f>IFERROR(ETUDE!E95,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C21" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="B21" s="84">
-        <f>IFERROR(ETUDE!B116,"")</f>
-        <v>0</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>365</v>
-      </c>
       <c r="D21" s="80">
-        <f>IFERROR(ETUDE!B125,"-")</f>
+        <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
       <c r="E21" s="81">
-        <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
+        <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="84">
+        <f>IFERROR(ETUDE!B104,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="B22" s="84">
+      <c r="D22" s="80">
+        <f>IFERROR(ETUDE!D104,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="81">
+        <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="84">
+        <f>IFERROR(ETUDE!B116,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="D23" s="80">
+        <f>IFERROR(ETUDE!B125,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="81">
+        <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="B24" s="84">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
-      <c r="C22" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="D22" s="80">
+      <c r="C24" s="29" t="s">
+        <v>370</v>
+      </c>
+      <c r="D24" s="80">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E24" s="81">
         <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="B23" s="82"/>
-      <c r="C23" s="82"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="83">
-        <f>SUM(E18:E22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="5" customHeight="1"/>
     <row r="25" spans="1:5" ht="18" customHeight="1">
       <c r="A25" s="85" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B25" s="85"/>
       <c r="C25" s="85"/>
       <c r="D25" s="85"/>
       <c r="E25" s="85"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="5" customHeight="1">
       <c r="A26" s="22" t="s">
         <v>84</v>
       </c>
@@ -7467,13 +7518,13 @@
         <v>236</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -7481,18 +7532,18 @@
         <v>9</v>
       </c>
       <c r="B27" s="86">
-        <f>E14</f>
+        <f>E16</f>
         <v>0</v>
       </c>
       <c r="C27" s="87">
         <v>24</v>
       </c>
       <c r="D27" s="88">
-        <f>IFERROR(E14/24*100,"")</f>
+        <f>IFERROR(E16/24*100,"")</f>
         <v>0</v>
       </c>
       <c r="E27" s="89">
-        <f>IFERROR(IF(E14/24&gt;=0.7,"Solide",IF(E14/24&gt;=0.5,"Moyen","Faible")),"-")</f>
+        <f>IFERROR(IF(E16/24&gt;=0.7,"Solide",IF(E16/24&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
@@ -7501,27 +7552,27 @@
         <v>10</v>
       </c>
       <c r="B28" s="86">
-        <f>E23</f>
+        <f>E25</f>
         <v>0</v>
       </c>
       <c r="C28" s="87">
         <v>15</v>
       </c>
       <c r="D28" s="88">
-        <f>IFERROR(E23/15*100,"")</f>
+        <f>IFERROR(E25/15*100,"")</f>
         <v>0</v>
       </c>
       <c r="E28" s="89">
-        <f>IFERROR(IF(E23/15&gt;=0.7,"Solide",IF(E23/15&gt;=0.5,"Moyen","Faible")),"-")</f>
+        <f>IFERROR(IF(E25/15&gt;=0.7,"Solide",IF(E25/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="38" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B29" s="90">
-        <f>IFERROR(E14+E23,"")</f>
+        <f>IFERROR(E16+E25,"")</f>
         <v>0</v>
       </c>
       <c r="C29" s="91">
@@ -7539,7 +7590,7 @@
     <row r="30" spans="1:5" ht="5" customHeight="1"/>
     <row r="31" spans="1:5" ht="18" customHeight="1">
       <c r="A31" s="78" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B31" s="78"/>
       <c r="C31" s="78"/>
@@ -7548,7 +7599,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="22" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>15</v>
@@ -7557,10 +7608,10 @@
         <v>216</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" customHeight="1">
@@ -7588,7 +7639,7 @@
     <row r="34" spans="1:5" ht="5" customHeight="1"/>
     <row r="35" spans="1:5" ht="18" customHeight="1">
       <c r="A35" s="78" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B35" s="78"/>
       <c r="C35" s="78"/>
@@ -7636,60 +7687,60 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="A36:E40"/>
   </mergeCells>
-  <conditionalFormatting sqref="D18:D22">
+  <conditionalFormatting sqref="D20:D24">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
-      <formula>NOT(ISERROR(SEARCH("Bon",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Bon",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="rentable">
-      <formula>NOT(ISERROR(SEARCH("rentable",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("rentable",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Sous-evalue">
-      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Sous-evalue",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="Decote">
-      <formula>NOT(ISERROR(SEARCH("Decote",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Decote",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="Opportunite">
-      <formula>NOT(ISERROR(SEARCH("Opportunite",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Opportunite",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="12" operator="containsText" text="SURVENTE">
-      <formula>NOT(ISERROR(SEARCH("SURVENTE",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SURVENTE",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="14" operator="containsText" text="ACHETER">
-      <formula>NOT(ISERROR(SEARCH("ACHETER",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("ACHETER",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Surevalue">
-      <formula>NOT(ISERROR(SEARCH("Surevalue",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Surevalue",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="SURACHAT">
-      <formula>NOT(ISERROR(SEARCH("SURACHAT",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SURACHAT",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="20" operator="containsText" text="Prime">
-      <formula>NOT(ISERROR(SEARCH("Prime",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Prime",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="22" operator="containsText" text="Negatif">
-      <formula>NOT(ISERROR(SEARCH("Negatif",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Negatif",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="24" operator="containsText" text="Normal">
-      <formula>NOT(ISERROR(SEARCH("Normal",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Normal",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="26" operator="containsText" text="Faible">
-      <formula>NOT(ISERROR(SEARCH("Faible",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Faible",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="28" operator="containsText" text="Moyen">
-      <formula>NOT(ISERROR(SEARCH("Moyen",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Moyen",D20)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="30" operator="containsText" text="NEUTRE">
-      <formula>NOT(ISERROR(SEARCH("NEUTRE",D18)))</formula>
+      <formula>NOT(ISERROR(SEARCH("NEUTRE",D20)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:D13">
+  <conditionalFormatting sqref="D6:D15">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Bon">
       <formula>NOT(ISERROR(SEARCH("Bon",D6)))</formula>
     </cfRule>
@@ -7745,7 +7796,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -7756,7 +7807,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7764,7 +7815,7 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -7772,48 +7823,48 @@
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
       <c r="A3" s="97" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B3" s="98"/>
       <c r="C3" s="98"/>
       <c r="D3" s="75" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
       <c r="A4" s="97" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B4" s="98"/>
       <c r="C4" s="98"/>
       <c r="D4" s="75" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
       <c r="A5" s="97" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B5" s="98"/>
       <c r="C5" s="98"/>
       <c r="D5" s="75" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
       <c r="A6" s="97" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B6" s="99"/>
       <c r="C6" s="99"/>
       <c r="D6" s="75" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -7821,46 +7872,46 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="23" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B9" s="63">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="23" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B10" s="63">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="23" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B11" s="63">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="23" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B12" s="70"/>
       <c r="C12" s="30"/>
@@ -7868,7 +7919,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="23" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B13" s="70"/>
       <c r="C13" s="30"/>
@@ -7877,7 +7928,7 @@
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -7893,7 +7944,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B17" s="70"/>
       <c r="C17" s="30"/>
@@ -7918,7 +7969,7 @@
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -7929,7 +7980,7 @@
         <v>254</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
@@ -7947,7 +7998,7 @@
         <v>256</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -7957,7 +8008,7 @@
         <v>257</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
@@ -7965,7 +8016,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -8000,7 +8051,7 @@
         <v>261</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="30"/>
@@ -8008,7 +8059,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="21" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -8016,17 +8067,17 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="23" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="30"/>
@@ -8034,20 +8085,20 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="23" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="23" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
@@ -8055,7 +8106,7 @@
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
     <row r="39" spans="1:4" ht="20" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -8066,7 +8117,7 @@
         <v>265</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
@@ -8076,17 +8127,17 @@
         <v>267</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="23" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
@@ -8096,7 +8147,7 @@
         <v>278</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
@@ -8106,7 +8157,7 @@
         <v>285</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
@@ -8116,15 +8167,44 @@
         <v>287</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="5" customHeight="1"/>
+    <row r="47" spans="1:4" ht="20" customHeight="1">
+      <c r="A47" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>422</v>
+      </c>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+    </row>
+    <row r="50" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:C3"/>
@@ -8137,6 +8217,7 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8164,7 +8245,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8180,7 +8261,7 @@
     </row>
     <row r="2" spans="1:12" ht="16" customHeight="1">
       <c r="A2" s="100" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -8197,40 +8278,40 @@
     <row r="3" spans="1:12" ht="5" customHeight="1"/>
     <row r="4" spans="1:12" ht="32" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1">
@@ -8671,7 +8752,7 @@
     <row r="20" spans="1:12" ht="5" customHeight="1"/>
     <row r="21" spans="1:12" ht="22" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B21" s="106"/>
       <c r="C21" s="106"/>
@@ -8703,7 +8784,7 @@
     <row r="22" spans="1:12" ht="8" customHeight="1"/>
     <row r="23" spans="1:12" ht="18" customHeight="1">
       <c r="A23" s="109" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B23" s="109"/>
       <c r="C23" s="109"/>
@@ -8719,10 +8800,10 @@
     </row>
     <row r="24" spans="1:12" ht="16" customHeight="1">
       <c r="A24" s="110" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B24" s="111" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="C24" s="111"/>
       <c r="D24" s="111"/>
@@ -8737,10 +8818,10 @@
     </row>
     <row r="25" spans="1:12" ht="16" customHeight="1">
       <c r="A25" s="110" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B25" s="111" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C25" s="111"/>
       <c r="D25" s="111"/>
@@ -8755,10 +8836,10 @@
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1">
       <c r="A26" s="110" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B26" s="111" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C26" s="111"/>
       <c r="D26" s="111"/>
@@ -8773,10 +8854,10 @@
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1">
       <c r="A27" s="110" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B27" s="111" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C27" s="111"/>
       <c r="D27" s="111"/>
@@ -8819,7 +8900,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8830,18 +8911,18 @@
         <v>94</v>
       </c>
       <c r="B2" s="112" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="C2" s="112" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="D2" s="112" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
       <c r="A3" s="78" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78"/>
@@ -8849,44 +8930,44 @@
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B4" s="113" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D4" s="114" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B5" s="113" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B6" s="113" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
@@ -8894,27 +8975,27 @@
         <v>4</v>
       </c>
       <c r="B7" s="113" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B8" s="113" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D8" s="114" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
@@ -8922,72 +9003,72 @@
         <v>5</v>
       </c>
       <c r="B9" s="113" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="C9" s="87" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D9" s="114" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B10" s="113" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C10" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B11" s="113" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="C11" s="87"/>
       <c r="D11" s="114" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B12" s="113" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D12" s="114" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="38" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B13" s="113" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D13" s="114" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
       <c r="A14" s="78" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B14" s="78"/>
       <c r="C14" s="78"/>
@@ -8995,28 +9076,28 @@
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="B15" s="113" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D15" s="114" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B16" s="113" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C16" s="87"/>
       <c r="D16" s="114" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
@@ -9024,11 +9105,11 @@
         <v>136</v>
       </c>
       <c r="B17" s="113" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C17" s="87"/>
       <c r="D17" s="114" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
@@ -9036,46 +9117,46 @@
         <v>160</v>
       </c>
       <c r="B18" s="113" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="C18" s="87" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D18" s="114" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="38" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B19" s="113" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D19" s="114" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="38" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="B20" s="113" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D20" s="114" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
       <c r="A21" s="78" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B21" s="78"/>
       <c r="C21" s="78"/>
@@ -9083,64 +9164,64 @@
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B22" s="113" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D22" s="114" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B23" s="113" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B24" s="113" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="38" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B25" s="113" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C25" s="87" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="D25" s="114" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="8" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="78" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B27" s="78"/>
       <c r="C27" s="78"/>
@@ -9148,7 +9229,7 @@
     </row>
     <row r="28" spans="1:4" ht="16" customHeight="1">
       <c r="A28" s="109" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B28" s="109"/>
       <c r="C28" s="109"/>
@@ -9156,43 +9237,43 @@
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1">
       <c r="A29" s="115" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B29" s="116" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C29" s="75" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D29" s="30"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1">
       <c r="A30" s="115" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B30" s="116" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D30" s="30"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1">
       <c r="A31" s="115" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B31" s="116" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C31" s="75" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D31" s="30"/>
     </row>
     <row r="32" spans="1:4" ht="16" customHeight="1">
       <c r="A32" s="109" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B32" s="109"/>
       <c r="C32" s="109"/>
@@ -9200,79 +9281,79 @@
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1">
       <c r="A33" s="115" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B33" s="116" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D33" s="30"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1">
       <c r="A34" s="115" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B34" s="116" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C34" s="75" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1">
       <c r="A35" s="115" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B35" s="116" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C35" s="75" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D35" s="30"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1">
       <c r="A36" s="115" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B36" s="116" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="C36" s="75" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1">
       <c r="A37" s="115" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="B37" s="116" t="s">
+        <v>537</v>
+      </c>
+      <c r="C37" s="75" t="s">
         <v>529</v>
-      </c>
-      <c r="C37" s="75" t="s">
-        <v>521</v>
       </c>
       <c r="D37" s="30"/>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1">
       <c r="A38" s="115" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="B38" s="116" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C38" s="75" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="16" customHeight="1">
       <c r="A39" s="109" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="B39" s="109"/>
       <c r="C39" s="109"/>
@@ -9280,43 +9361,43 @@
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1">
       <c r="A40" s="115" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="B40" s="116" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C40" s="75" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D40" s="30"/>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1">
       <c r="A41" s="115" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B41" s="116" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C41" s="75" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1">
       <c r="A42" s="115" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B42" s="116" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C42" s="75" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D42" s="30"/>
     </row>
     <row r="43" spans="1:4" ht="16" customHeight="1">
       <c r="A43" s="109" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="B43" s="109"/>
       <c r="C43" s="109"/>
@@ -9324,49 +9405,49 @@
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
       <c r="A44" s="115" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="B44" s="116" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="C44" s="75" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1">
       <c r="A45" s="115" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="B45" s="116" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="C45" s="75" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1">
       <c r="A46" s="115" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="B46" s="116" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="C46" s="75" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="D46" s="30"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1">
       <c r="A47" s="115" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="B47" s="116" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C47" s="75" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D47" s="30"/>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="577">
   <si>
     <t>FICHE D'ANALYSE BOURSIERE BRVM</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Score Technique</t>
   </si>
   <si>
-    <t>SCORE TOTAL /39</t>
+    <t>SCORE TOTAL /45</t>
   </si>
   <si>
     <t>Signal VI</t>
@@ -1039,6 +1039,60 @@
   </si>
   <si>
     <t>VERDICT CYCLIQUE FINAL</t>
+  </si>
+  <si>
+    <t>H — PSYCHOLOGIE DU MARCHE &amp; REACTION AUX RESULTATS</t>
+  </si>
+  <si>
+    <t>H1 — REACTION COURS POST-RESULTATS  (saisir dans PROFIL — section Psychologie)</t>
+  </si>
+  <si>
+    <t>Unite</t>
+  </si>
+  <si>
+    <t>Prix avant publication resultats (J-1)</t>
+  </si>
+  <si>
+    <t>FCFA</t>
+  </si>
+  <si>
+    <t>Saisir dans PROFIL &gt; Psychologie</t>
+  </si>
+  <si>
+    <t>Prix apres publication resultats (J+5)</t>
+  </si>
+  <si>
+    <t>Reaction marche (%)</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>H2 — TENDANCE DIVIDENDES  (auto depuis A5)</t>
+  </si>
+  <si>
+    <t>CAGR 4 ans</t>
+  </si>
+  <si>
+    <t>Dividende NET verse (FCFA)</t>
+  </si>
+  <si>
+    <t>H3 — IMPACT PSYCHOLOGIQUE SUR LE COURS  (rappel des scores)</t>
+  </si>
+  <si>
+    <t>Critere psychologique</t>
+  </si>
+  <si>
+    <t>Tendance dividendes (score auto dans SYNTHESE)</t>
+  </si>
+  <si>
+    <t>Un dividende croissant attire les investisseurs et soutient le cours. Une coupe de dividende provoque souvent une chute brutale (-10% a -30%).</t>
+  </si>
+  <si>
+    <t>Reaction marche post-resultats (score auto dans SYNTHESE)</t>
+  </si>
+  <si>
+    <t>Le marche BRVM punit fortement les mauvaises surprises (illiquidite amplifie les mouvements). Une forte reaction positive est un signal de confiance durable des investisseurs.</t>
   </si>
   <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
@@ -1386,9 +1440,6 @@
     <t>Expression mathematique</t>
   </si>
   <si>
-    <t>Unite</t>
-  </si>
-  <si>
     <t>Interpretation / Seuils BRVM</t>
   </si>
   <si>
@@ -1401,9 +1452,6 @@
     <t>(N - N-4) / |N-4| x 100</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>Positif = croissance. Negatif = contraction. Seuil : &gt; 10%/an = excellent</t>
   </si>
   <si>
@@ -1438,9 +1486,6 @@
   </si>
   <si>
     <t>Capitaux Propres / Nb titres</t>
-  </si>
-  <si>
-    <t>FCFA</t>
   </si>
   <si>
     <t>Prix &lt; VMC = action decotee (achat potentiellement interessant)</t>
@@ -1725,7 +1770,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0"/>
-    <numFmt numFmtId="165" formatCode="0&quot;/24&quot;"/>
+    <numFmt numFmtId="165" formatCode="0&quot;/30&quot;"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="0&quot;/15&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
@@ -2297,7 +2342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2582,6 +2627,13 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="21" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -2593,9 +2645,6 @@
     <xf numFmtId="0" fontId="35" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="21" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3290,7 +3339,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="7">
-        <f>IFERROR(SYNTHESE!E14,"")</f>
+        <f>IFERROR(SYNTHESE!E16,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3307,7 +3356,7 @@
         <v>10</v>
       </c>
       <c r="E6" s="9">
-        <f>IFERROR(SYNTHESE!E23,"")</f>
+        <f>IFERROR(SYNTHESE!E25,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3324,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(SYNTHESE!B29,"")</f>
+        <f>IFERROR(SYNTHESE!B31,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3338,7 +3387,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="11">
-        <f>IFERROR(SYNTHESE!E29,"—")</f>
+        <f>IFERROR(SYNTHESE!E31,"—")</f>
         <v>0</v>
       </c>
       <c r="E8" s="11"/>
@@ -3397,7 +3446,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="13">
-        <f>IFERROR(SYNTHESE!A33,"")</f>
+        <f>IFERROR(SYNTHESE!A35,"")</f>
         <v>0</v>
       </c>
       <c r="C14" s="1"/>
@@ -3405,7 +3454,7 @@
         <v>15</v>
       </c>
       <c r="E14" s="12">
-        <f>IFERROR(SYNTHESE!B33,"")</f>
+        <f>IFERROR(SYNTHESE!B35,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3471,7 +3520,7 @@
     </row>
     <row r="21" spans="1:5" ht="22" customHeight="1">
       <c r="A21" s="14">
-        <f>IFERROR(IF(SYNTHESE!A36="","[Completer la recommandation dans SYNTHESE &gt; ligne 36]",SYNTHESE!A36),"[—]")</f>
+        <f>IFERROR(IF(SYNTHESE!A38="","[Completer la recommandation dans SYNTHESE &gt; ligne 38]",SYNTHESE!A38),"[—]")</f>
         <v>0</v>
       </c>
       <c r="B21" s="14"/>
@@ -3621,7 +3670,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H270"/>
+  <dimension ref="A1:H287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -6982,9 +7031,232 @@
       <c r="H269" s="30"/>
     </row>
     <row r="270" spans="1:8" ht="5" customHeight="1"/>
+    <row r="271" spans="1:8" ht="5" customHeight="1"/>
+    <row r="272" spans="1:8" ht="22" customHeight="1">
+      <c r="A272" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B272" s="19"/>
+      <c r="C272" s="19"/>
+      <c r="D272" s="19"/>
+      <c r="E272" s="19"/>
+      <c r="F272" s="19"/>
+      <c r="G272" s="19"/>
+      <c r="H272" s="19"/>
+    </row>
+    <row r="273" spans="1:8" ht="20" customHeight="1">
+      <c r="A273" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B273" s="21"/>
+      <c r="C273" s="21"/>
+      <c r="D273" s="21"/>
+      <c r="E273" s="21"/>
+      <c r="F273" s="21"/>
+      <c r="G273" s="21"/>
+      <c r="H273" s="21"/>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B274" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="C274" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="D274" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E274" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="F274" s="22"/>
+      <c r="G274" s="22"/>
+      <c r="H274" s="22"/>
+    </row>
+    <row r="275" spans="1:8">
+      <c r="A275" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B275" s="27">
+        <f>IFERROR(PROFIL!B48,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C275" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="D275" s="32" t="s">
+        <v>344</v>
+      </c>
+      <c r="E275" s="32"/>
+    </row>
+    <row r="276" spans="1:8">
+      <c r="A276" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="B276" s="27">
+        <f>IFERROR(PROFIL!B49,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C276" s="40" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8">
+      <c r="A277" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="B277" s="25">
+        <f>IFERROR(IF(AND(ISNUMBER(PROFIL!B48),ISNUMBER(PROFIL!B49),PROFIL!B48&gt;0),(PROFIL!B49-PROFIL!B48)/PROFIL!B48*100,""),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C277" s="40" t="s">
+        <v>347</v>
+      </c>
+      <c r="D277" s="28">
+        <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),"Saisir J-1 et J+5 dans PROFIL",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,"Accueil tres favorable — marche recompense les resultats",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,"Accueil positif — marche satisfait",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,"Reaction mitigee — marche decu","PUNITION MARCHE — resultats fortement sanctionnes")))),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="5" customHeight="1"/>
+    <row r="279" spans="1:8" ht="20" customHeight="1">
+      <c r="A279" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="B279" s="21"/>
+      <c r="C279" s="21"/>
+      <c r="D279" s="21"/>
+      <c r="E279" s="21"/>
+      <c r="F279" s="21"/>
+      <c r="G279" s="21"/>
+      <c r="H279" s="21"/>
+    </row>
+    <row r="280" spans="1:8">
+      <c r="A280" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B280" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C280" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D280" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E280" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F280" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="G280" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="H280" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8">
+      <c r="A281" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="B281" s="35">
+        <f>IFERROR(ETUDE!B39,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C281" s="35">
+        <f>IFERROR(ETUDE!B40,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D281" s="35">
+        <f>IFERROR(ETUDE!B41,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E281" s="35">
+        <f>IFERROR(ETUDE!B42,"")</f>
+        <v>0</v>
+      </c>
+      <c r="F281" s="35">
+        <f>IFERROR(ETUDE!B43,"")</f>
+        <v>0</v>
+      </c>
+      <c r="G281" s="25">
+        <f>IFERROR(ETUDE!B167*100,"N/A")</f>
+        <v>0</v>
+      </c>
+      <c r="H281" s="28">
+        <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),"Pas de dividende",IF(ETUDE!B167&gt;=0.10,"Dividende CROISSANT fort (&gt;10%/an)",IF(ETUDE!B167&gt;=0.02,"Dividende croissant (2-10%/an)",IF(ETUDE!B167&gt;=0,"Dividende stable / faible croissance","DIVIDENDE EN BAISSE — signal negatif pour le marche")))),"N/A")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="5" customHeight="1"/>
+    <row r="283" spans="1:8" ht="20" customHeight="1">
+      <c r="A283" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="B283" s="21"/>
+      <c r="C283" s="21"/>
+      <c r="D283" s="21"/>
+      <c r="E283" s="21"/>
+      <c r="F283" s="21"/>
+      <c r="G283" s="21"/>
+      <c r="H283" s="21"/>
+    </row>
+    <row r="284" spans="1:8">
+      <c r="A284" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="B284" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C284" s="22"/>
+      <c r="D284" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E284" s="22"/>
+      <c r="F284" s="22"/>
+      <c r="G284" s="22"/>
+      <c r="H284" s="22"/>
+    </row>
+    <row r="285" spans="1:8">
+      <c r="A285" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="B285" s="78">
+        <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),0,IF(ETUDE!B167&gt;=0.10,3,IF(ETUDE!B167&gt;=0.02,2,IF(ETUDE!B167&gt;=0,1,0)))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D285" s="79" t="s">
+        <v>354</v>
+      </c>
+      <c r="E285" s="79"/>
+      <c r="F285" s="79"/>
+      <c r="G285" s="79"/>
+      <c r="H285" s="79"/>
+    </row>
+    <row r="286" spans="1:8" ht="28" customHeight="1">
+      <c r="A286" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="B286" s="78">
+        <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),0,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,3,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,2,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,1,0)))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D286" s="79" t="s">
+        <v>356</v>
+      </c>
+      <c r="E286" s="79"/>
+      <c r="F286" s="79"/>
+      <c r="G286" s="79"/>
+      <c r="H286" s="79"/>
+    </row>
+    <row r="287" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="57">
+  <mergeCells count="64">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -7042,6 +7314,13 @@
     <mergeCell ref="A259:H259"/>
     <mergeCell ref="A265:H265"/>
     <mergeCell ref="B269:D269"/>
+    <mergeCell ref="A272:H272"/>
+    <mergeCell ref="A273:H273"/>
+    <mergeCell ref="D275:E275"/>
+    <mergeCell ref="A279:H279"/>
+    <mergeCell ref="A283:H283"/>
+    <mergeCell ref="D285:H285"/>
+    <mergeCell ref="D286:H286"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -7106,7 +7385,7 @@
   <sheetPr>
     <tabColor rgb="FF1E3A5F"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7118,7 +7397,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7137,87 +7416,87 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="78" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
+      <c r="A4" s="80" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="22" t="s">
         <v>234</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="B6" s="79">
+        <v>363</v>
+      </c>
+      <c r="B6" s="81">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="D6" s="80">
+        <v>364</v>
+      </c>
+      <c r="D6" s="82">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="78">
         <f>IFERROR(IF(ETUDE!G8&gt;=15,3,IF(ETUDE!G8&gt;=5,2,IF(ETUDE!G8&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="B7" s="79">
+        <v>365</v>
+      </c>
+      <c r="B7" s="81">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="D7" s="80">
+        <v>364</v>
+      </c>
+      <c r="D7" s="82">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="78">
         <f>IFERROR(IF(ETUDE!G12&gt;=15,3,IF(ETUDE!G12&gt;=5,2,IF(ETUDE!G12&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="B8" s="79">
+        <v>366</v>
+      </c>
+      <c r="B8" s="81">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="D8" s="80">
+        <v>367</v>
+      </c>
+      <c r="D8" s="82">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="78">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,3,IF(ETUDE!G16&gt;=5,2,IF(ETUDE!G16&gt;=2,1,0))),0)</f>
         <v>0</v>
       </c>
@@ -7226,18 +7505,18 @@
       <c r="A9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="81">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>350</v>
-      </c>
-      <c r="D9" s="80">
+        <v>368</v>
+      </c>
+      <c r="D9" s="82">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="78">
         <f>IFERROR(IF(ETUDE!B30&lt;9,3,IF(ETUDE!B30&lt;=15,2,IF(ETUDE!B30&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
@@ -7246,18 +7525,18 @@
       <c r="A10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="79">
+      <c r="B10" s="81">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="D10" s="80">
+        <v>369</v>
+      </c>
+      <c r="D10" s="82">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="78">
         <f>IFERROR(IF(ETUDE!B32&lt;1,3,IF(ETUDE!B32&lt;2,1,0)),0)</f>
         <v>0</v>
       </c>
@@ -7266,123 +7545,123 @@
       <c r="A11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="79">
+      <c r="B11" s="81">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="D11" s="80">
+        <v>364</v>
+      </c>
+      <c r="D11" s="82">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="78">
         <f>IFERROR(IF(ETUDE!B33&gt;=15,3,IF(ETUDE!B33&gt;=10,2,IF(ETUDE!B33&gt;=5,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23" t="s">
-        <v>352</v>
-      </c>
-      <c r="B12" s="79">
+        <v>370</v>
+      </c>
+      <c r="B12" s="81">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>353</v>
-      </c>
-      <c r="D12" s="80">
+        <v>371</v>
+      </c>
+      <c r="D12" s="82">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="78">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=6,3,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,2,IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="B13" s="79">
+        <v>372</v>
+      </c>
+      <c r="B13" s="81">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="D13" s="80">
+        <v>373</v>
+      </c>
+      <c r="D13" s="82">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="78">
         <f>IFERROR(IF(ETUDE!B34&lt;10,3,IF(ETUDE!B34&lt;22,2,IF(ETUDE!B34&lt;30,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>356</v>
-      </c>
-      <c r="B14" s="79">
+        <v>374</v>
+      </c>
+      <c r="B14" s="81">
         <f>IFERROR(IF(ISNUMBER(ETUDE!B167),ETUDE!B167*100,"N/A"),"N/A")</f>
         <v>0</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="D14" s="80">
+        <v>375</v>
+      </c>
+      <c r="D14" s="82">
         <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),"Pas de dividende",IF(ETUDE!B167&gt;=0.10,"Croissant fort (&gt;10%/an)",IF(ETUDE!B167&gt;=0.02,"Croissant (2-10%/an)",IF(ETUDE!B167&gt;=0,"Stable","Dividende en BAISSE")))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="78">
         <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),0,IF(ETUDE!B167&gt;=0.10,3,IF(ETUDE!B167&gt;=0.02,2,IF(ETUDE!B167&gt;=0,1,0)))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="B15" s="79">
+        <v>376</v>
+      </c>
+      <c r="B15" s="81">
         <f>IFERROR(IF(AND(ISNUMBER(PROFIL!B48),ISNUMBER(PROFIL!B49),PROFIL!B48&gt;0),(PROFIL!B49-PROFIL!B48)/PROFIL!B48*100,"Non renseigne"),"Non renseigne")</f>
         <v>0</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="D15" s="80">
+        <v>375</v>
+      </c>
+      <c r="D15" s="82">
         <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),"Non renseigne — saisir dans PROFIL",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,"Accueil tres favorable — marche recompense",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,"Accueil positif",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,"Reaction mitigee","Punition marche — forte baisse")))),"-")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="78">
         <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),0,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,3,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,2,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,1,0)))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="83">
+        <v>377</v>
+      </c>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="84">
         <f>SUM(E6:E15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="5" customHeight="1"/>
     <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="A18" s="78" t="s">
-        <v>360</v>
-      </c>
-      <c r="B18" s="78"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
+      <c r="A18" s="80" t="s">
+        <v>378</v>
+      </c>
+      <c r="B18" s="80"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="22" t="s">
@@ -7403,264 +7682,263 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="B20" s="84">
+        <v>379</v>
+      </c>
+      <c r="B20" s="85">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="D20" s="80">
+        <v>380</v>
+      </c>
+      <c r="D20" s="82">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="78">
         <f>IFERROR(IF(ETUDE!D91&gt;=4,3,IF(ETUDE!D91&gt;=2,2,IF(ETUDE!D91&gt;=0,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="B21" s="84">
+        <v>381</v>
+      </c>
+      <c r="B21" s="85">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D21" s="80">
+        <v>382</v>
+      </c>
+      <c r="D21" s="82">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="78">
         <f>IFERROR(IF(AND(ETUDE!B24&lt;ETUDE!D95,ETUDE!B24&lt;ETUDE!D96),3,IF(ETUDE!B24&lt;ETUDE!D95,2,IF(ETUDE!B24&lt;ETUDE!D96,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="B22" s="84">
+        <v>383</v>
+      </c>
+      <c r="B22" s="85">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="D22" s="80">
+        <v>384</v>
+      </c>
+      <c r="D22" s="82">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="78">
         <f>IFERROR(IF(ETUDE!B104&lt;9,3,IF(ETUDE!B104&lt;=15,2,IF(ETUDE!B104&lt;=20,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="B23" s="84">
+        <v>385</v>
+      </c>
+      <c r="B23" s="85">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="D23" s="80">
+        <v>386</v>
+      </c>
+      <c r="D23" s="82">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="78">
         <f>IFERROR(IF(AND(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),3,IF(OR(ISNUMBER(SEARCH("DESSOUS",ETUDE!B116)),ISNUMBER(SEARCH("SOUS P0",ETUDE!B125))),2,IF(OR(ISNUMBER(SEARCH("ZONE CIBLE",ETUDE!B116)),ISNUMBER(SEARCH("zone P0",ETUDE!B125))),1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="23" t="s">
-        <v>369</v>
-      </c>
-      <c r="B24" s="84">
+        <v>387</v>
+      </c>
+      <c r="B24" s="85">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="D24" s="80">
+        <v>388</v>
+      </c>
+      <c r="D24" s="82">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
-      <c r="E24" s="81">
+      <c r="E24" s="78">
         <f>IFERROR(IF(ETUDE!B135&gt;=3,3,IF(ETUDE!B135&gt;=2,2,IF(ETUDE!B135&gt;=1,1,0))),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18" customHeight="1">
-      <c r="A25" s="85" t="s">
-        <v>372</v>
-      </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-    </row>
-    <row r="26" spans="1:5" ht="5" customHeight="1">
-      <c r="A26" s="22" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="84">
+        <f>SUM(E20:E24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="5" customHeight="1"/>
+    <row r="27" spans="1:5" ht="18" customHeight="1">
+      <c r="A27" s="86" t="s">
+        <v>390</v>
+      </c>
+      <c r="B27" s="86"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
+      <c r="E27" s="86"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B28" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="C26" s="22" t="s">
-        <v>373</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="23" t="s">
+      <c r="C28" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="86">
+      <c r="B29" s="87">
         <f>E16</f>
         <v>0</v>
       </c>
-      <c r="C27" s="87">
-        <v>24</v>
-      </c>
-      <c r="D27" s="88">
-        <f>IFERROR(E16/24*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="89">
-        <f>IFERROR(IF(E16/24&gt;=0.7,"Solide",IF(E16/24&gt;=0.5,"Moyen","Faible")),"-")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="23" t="s">
+      <c r="C29" s="88">
+        <v>30</v>
+      </c>
+      <c r="D29" s="89">
+        <f>IFERROR(E16/30*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="90">
+        <f>IFERROR(IF(E16/30&gt;=0.7,"Solide",IF(E16/30&gt;=0.5,"Moyen","Faible")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="86">
+      <c r="B30" s="87">
         <f>E25</f>
         <v>0</v>
       </c>
-      <c r="C28" s="87">
+      <c r="C30" s="88">
         <v>15</v>
       </c>
-      <c r="D28" s="88">
+      <c r="D30" s="89">
         <f>IFERROR(E25/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="89">
+      <c r="E30" s="90">
         <f>IFERROR(IF(E25/15&gt;=0.7,"Solide",IF(E25/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="B29" s="90">
+    <row r="31" spans="1:5">
+      <c r="A31" s="38" t="s">
+        <v>394</v>
+      </c>
+      <c r="B31" s="91">
         <f>IFERROR(E16+E25,"")</f>
         <v>0</v>
       </c>
-      <c r="C29" s="91">
-        <v>39</v>
-      </c>
-      <c r="D29" s="88">
-        <f>IFERROR(B29/39*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="92">
-        <f>IFERROR(IF(B29/39&gt;=0.7,"ACHETER",IF(B29/39&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="5" customHeight="1"/>
-    <row r="31" spans="1:5" ht="18" customHeight="1">
-      <c r="A31" s="78" t="s">
-        <v>377</v>
-      </c>
-      <c r="B31" s="78"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="22" t="s">
-        <v>378</v>
-      </c>
-      <c r="B32" s="22" t="s">
+      <c r="C31" s="92">
+        <v>45</v>
+      </c>
+      <c r="D31" s="89">
+        <f>IFERROR(B31/45*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="93">
+        <f>IFERROR(IF(B31/45&gt;=0.7,"ACHETER",IF(B31/45&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="5" customHeight="1"/>
+    <row r="33" spans="1:5" ht="18" customHeight="1">
+      <c r="A33" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="B33" s="80"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="B34" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C34" s="22" t="s">
         <v>216</v>
       </c>
-      <c r="D32" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="30" customHeight="1">
-      <c r="A33" s="93">
+      <c r="D34" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="30" customHeight="1">
+      <c r="A35" s="94">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B33" s="94">
+      <c r="B35" s="95">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C33" s="95">
+      <c r="C35" s="96">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D33" s="95">
+      <c r="D35" s="96">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="96">
+      <c r="E35" s="97">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="5" customHeight="1"/>
-    <row r="35" spans="1:5" ht="18" customHeight="1">
-      <c r="A35" s="78" t="s">
-        <v>381</v>
-      </c>
-      <c r="B35" s="78"/>
-      <c r="C35" s="78"/>
-      <c r="D35" s="78"/>
-      <c r="E35" s="78"/>
-    </row>
-    <row r="36" spans="1:5" ht="50" customHeight="1">
-      <c r="A36" s="46"/>
-      <c r="B36" s="46"/>
-      <c r="C36" s="46"/>
-      <c r="D36" s="46"/>
-      <c r="E36" s="46"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="46"/>
-      <c r="B37" s="46"/>
-      <c r="C37" s="46"/>
-      <c r="D37" s="46"/>
-      <c r="E37" s="46"/>
-    </row>
-    <row r="38" spans="1:5">
+    <row r="36" spans="1:5" ht="5" customHeight="1"/>
+    <row r="37" spans="1:5" ht="18" customHeight="1">
+      <c r="A37" s="80" t="s">
+        <v>399</v>
+      </c>
+      <c r="B37" s="80"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+    </row>
+    <row r="38" spans="1:5" ht="50" customHeight="1">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
       <c r="C38" s="46"/>
@@ -7680,6 +7958,20 @@
       <c r="C40" s="46"/>
       <c r="D40" s="46"/>
       <c r="E40" s="46"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="46"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="46"/>
+      <c r="D41" s="46"/>
+      <c r="E41" s="46"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="46"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -7688,10 +7980,10 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A36:E40"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E42"/>
   </mergeCells>
   <conditionalFormatting sqref="D20:D24">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
@@ -7807,7 +8099,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7815,56 +8107,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="97" t="s">
-        <v>384</v>
-      </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
+      <c r="A3" s="98" t="s">
+        <v>402</v>
+      </c>
+      <c r="B3" s="99"/>
+      <c r="C3" s="99"/>
       <c r="D3" s="75" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="97" t="s">
-        <v>386</v>
-      </c>
-      <c r="B4" s="98"/>
-      <c r="C4" s="98"/>
+      <c r="A4" s="98" t="s">
+        <v>404</v>
+      </c>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="75" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="97" t="s">
-        <v>388</v>
-      </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
+      <c r="A5" s="98" t="s">
+        <v>406</v>
+      </c>
+      <c r="B5" s="99"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="75" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="97" t="s">
-        <v>390</v>
-      </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="99"/>
+      <c r="A6" s="98" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
       <c r="D6" s="75" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -7872,46 +8164,46 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="23" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B9" s="63">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="23" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="B10" s="63">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="23" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B11" s="63">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="23" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="B12" s="70"/>
       <c r="C12" s="30"/>
@@ -7919,7 +8211,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="23" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B13" s="70"/>
       <c r="C13" s="30"/>
@@ -7928,7 +8220,7 @@
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -7944,7 +8236,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="B17" s="70"/>
       <c r="C17" s="30"/>
@@ -7969,7 +8261,7 @@
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -7980,7 +8272,7 @@
         <v>254</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
@@ -7998,7 +8290,7 @@
         <v>256</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -8008,7 +8300,7 @@
         <v>257</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
@@ -8016,7 +8308,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -8051,7 +8343,7 @@
         <v>261</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="30"/>
@@ -8059,7 +8351,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="21" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -8067,17 +8359,17 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="23" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="30"/>
@@ -8085,20 +8377,20 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="23" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="23" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
@@ -8106,7 +8398,7 @@
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
     <row r="39" spans="1:4" ht="20" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -8117,7 +8409,7 @@
         <v>265</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
@@ -8127,17 +8419,17 @@
         <v>267</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="23" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
@@ -8147,7 +8439,7 @@
         <v>278</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
@@ -8157,7 +8449,7 @@
         <v>285</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
@@ -8167,7 +8459,7 @@
         <v>287</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -8175,7 +8467,7 @@
     <row r="46" spans="1:4" ht="5" customHeight="1"/>
     <row r="47" spans="1:4" ht="20" customHeight="1">
       <c r="A47" s="21" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -8183,20 +8475,20 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="23" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="C48" s="30"/>
       <c r="D48" s="30"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="23" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="30"/>
@@ -8245,7 +8537,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8260,491 +8552,491 @@
       <c r="L1" s="19"/>
     </row>
     <row r="2" spans="1:12" ht="16" customHeight="1">
-      <c r="A2" s="100" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
+      <c r="A2" s="101" t="s">
+        <v>444</v>
+      </c>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
     </row>
     <row r="3" spans="1:12" ht="5" customHeight="1"/>
     <row r="4" spans="1:12" ht="32" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1">
-      <c r="A5" s="101"/>
-      <c r="B5" s="101"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="103">
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="104">
         <f>IFERROR(IF(A5="","",C5*D5*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="103">
+      <c r="I5" s="104">
         <f>IFERROR(IF(A5="","",C5*E5),"")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="103">
+      <c r="J5" s="104">
         <f>IFERROR(IF(A5="","",(C5*E5)-(C5*D5*1.014)+(C5*F5)),"")</f>
         <v>0</v>
       </c>
-      <c r="K5" s="104">
+      <c r="K5" s="105">
         <f>IFERROR(IF(A5="","",J5/H5*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L5" s="105">
+      <c r="L5" s="106">
         <f>IFERROR(IF(A5="","—",IF(K5&lt;-10,"VENDRE — Stop-loss",IF(AND(G5&gt;=24,K5&gt;=0),"RENFORCER",IF(AND(G5&gt;=15,K5&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1">
-      <c r="A6" s="101"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103">
+      <c r="A6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="104">
         <f>IFERROR(IF(A6="","",C6*D6*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I6" s="103">
+      <c r="I6" s="104">
         <f>IFERROR(IF(A6="","",C6*E6),"")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="103">
+      <c r="J6" s="104">
         <f>IFERROR(IF(A6="","",(C6*E6)-(C6*D6*1.014)+(C6*F6)),"")</f>
         <v>0</v>
       </c>
-      <c r="K6" s="104">
+      <c r="K6" s="105">
         <f>IFERROR(IF(A6="","",J6/H6*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="105">
+      <c r="L6" s="106">
         <f>IFERROR(IF(A6="","—",IF(K6&lt;-10,"VENDRE — Stop-loss",IF(AND(G6&gt;=24,K6&gt;=0),"RENFORCER",IF(AND(G6&gt;=15,K6&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="101"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="103">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="104">
         <f>IFERROR(IF(A7="","",C7*D7*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I7" s="103">
+      <c r="I7" s="104">
         <f>IFERROR(IF(A7="","",C7*E7),"")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="103">
+      <c r="J7" s="104">
         <f>IFERROR(IF(A7="","",(C7*E7)-(C7*D7*1.014)+(C7*F7)),"")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="104">
+      <c r="K7" s="105">
         <f>IFERROR(IF(A7="","",J7/H7*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="105">
+      <c r="L7" s="106">
         <f>IFERROR(IF(A7="","—",IF(K7&lt;-10,"VENDRE — Stop-loss",IF(AND(G7&gt;=24,K7&gt;=0),"RENFORCER",IF(AND(G7&gt;=15,K7&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="101"/>
-      <c r="B8" s="101"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="103">
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103"/>
+      <c r="G8" s="103"/>
+      <c r="H8" s="104">
         <f>IFERROR(IF(A8="","",C8*D8*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="103">
+      <c r="I8" s="104">
         <f>IFERROR(IF(A8="","",C8*E8),"")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="103">
+      <c r="J8" s="104">
         <f>IFERROR(IF(A8="","",(C8*E8)-(C8*D8*1.014)+(C8*F8)),"")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="104">
+      <c r="K8" s="105">
         <f>IFERROR(IF(A8="","",J8/H8*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="105">
+      <c r="L8" s="106">
         <f>IFERROR(IF(A8="","—",IF(K8&lt;-10,"VENDRE — Stop-loss",IF(AND(G8&gt;=24,K8&gt;=0),"RENFORCER",IF(AND(G8&gt;=15,K8&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1">
-      <c r="A9" s="101"/>
-      <c r="B9" s="101"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="102"/>
-      <c r="H9" s="103">
+      <c r="A9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="104">
         <f>IFERROR(IF(A9="","",C9*D9*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="104">
         <f>IFERROR(IF(A9="","",C9*E9),"")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="104">
         <f>IFERROR(IF(A9="","",(C9*E9)-(C9*D9*1.014)+(C9*F9)),"")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="105">
         <f>IFERROR(IF(A9="","",J9/H9*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="105">
+      <c r="L9" s="106">
         <f>IFERROR(IF(A9="","—",IF(K9&lt;-10,"VENDRE — Stop-loss",IF(AND(G9&gt;=24,K9&gt;=0),"RENFORCER",IF(AND(G9&gt;=15,K9&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1">
-      <c r="A10" s="101"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="102"/>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="103">
+      <c r="A10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103"/>
+      <c r="G10" s="103"/>
+      <c r="H10" s="104">
         <f>IFERROR(IF(A10="","",C10*D10*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="104">
         <f>IFERROR(IF(A10="","",C10*E10),"")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="103">
+      <c r="J10" s="104">
         <f>IFERROR(IF(A10="","",(C10*E10)-(C10*D10*1.014)+(C10*F10)),"")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="104">
+      <c r="K10" s="105">
         <f>IFERROR(IF(A10="","",J10/H10*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="106">
         <f>IFERROR(IF(A10="","—",IF(K10&lt;-10,"VENDRE — Stop-loss",IF(AND(G10&gt;=24,K10&gt;=0),"RENFORCER",IF(AND(G10&gt;=15,K10&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1">
-      <c r="A11" s="101"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="103">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="104">
         <f>IFERROR(IF(A11="","",C11*D11*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="103">
+      <c r="I11" s="104">
         <f>IFERROR(IF(A11="","",C11*E11),"")</f>
         <v>0</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="104">
         <f>IFERROR(IF(A11="","",(C11*E11)-(C11*D11*1.014)+(C11*F11)),"")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="104">
+      <c r="K11" s="105">
         <f>IFERROR(IF(A11="","",J11/H11*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="105">
+      <c r="L11" s="106">
         <f>IFERROR(IF(A11="","—",IF(K11&lt;-10,"VENDRE — Stop-loss",IF(AND(G11&gt;=24,K11&gt;=0),"RENFORCER",IF(AND(G11&gt;=15,K11&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1">
-      <c r="A12" s="101"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="103">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
+      <c r="G12" s="103"/>
+      <c r="H12" s="104">
         <f>IFERROR(IF(A12="","",C12*D12*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="103">
+      <c r="I12" s="104">
         <f>IFERROR(IF(A12="","",C12*E12),"")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="103">
+      <c r="J12" s="104">
         <f>IFERROR(IF(A12="","",(C12*E12)-(C12*D12*1.014)+(C12*F12)),"")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="104">
+      <c r="K12" s="105">
         <f>IFERROR(IF(A12="","",J12/H12*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="105">
+      <c r="L12" s="106">
         <f>IFERROR(IF(A12="","—",IF(K12&lt;-10,"VENDRE — Stop-loss",IF(AND(G12&gt;=24,K12&gt;=0),"RENFORCER",IF(AND(G12&gt;=15,K12&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="101"/>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="103">
+      <c r="A13" s="102"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
+      <c r="G13" s="103"/>
+      <c r="H13" s="104">
         <f>IFERROR(IF(A13="","",C13*D13*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="103">
+      <c r="I13" s="104">
         <f>IFERROR(IF(A13="","",C13*E13),"")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="103">
+      <c r="J13" s="104">
         <f>IFERROR(IF(A13="","",(C13*E13)-(C13*D13*1.014)+(C13*F13)),"")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="104">
+      <c r="K13" s="105">
         <f>IFERROR(IF(A13="","",J13/H13*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="105">
+      <c r="L13" s="106">
         <f>IFERROR(IF(A13="","—",IF(K13&lt;-10,"VENDRE — Stop-loss",IF(AND(G13&gt;=24,K13&gt;=0),"RENFORCER",IF(AND(G13&gt;=15,K13&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1">
-      <c r="A14" s="101"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="102"/>
-      <c r="F14" s="102"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="103">
+      <c r="A14" s="102"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103"/>
+      <c r="G14" s="103"/>
+      <c r="H14" s="104">
         <f>IFERROR(IF(A14="","",C14*D14*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="103">
+      <c r="I14" s="104">
         <f>IFERROR(IF(A14="","",C14*E14),"")</f>
         <v>0</v>
       </c>
-      <c r="J14" s="103">
+      <c r="J14" s="104">
         <f>IFERROR(IF(A14="","",(C14*E14)-(C14*D14*1.014)+(C14*F14)),"")</f>
         <v>0</v>
       </c>
-      <c r="K14" s="104">
+      <c r="K14" s="105">
         <f>IFERROR(IF(A14="","",J14/H14*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L14" s="105">
+      <c r="L14" s="106">
         <f>IFERROR(IF(A14="","—",IF(K14&lt;-10,"VENDRE — Stop-loss",IF(AND(G14&gt;=24,K14&gt;=0),"RENFORCER",IF(AND(G14&gt;=15,K14&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1">
-      <c r="A15" s="101"/>
-      <c r="B15" s="101"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="103">
+      <c r="A15" s="102"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="104">
         <f>IFERROR(IF(A15="","",C15*D15*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="103">
+      <c r="I15" s="104">
         <f>IFERROR(IF(A15="","",C15*E15),"")</f>
         <v>0</v>
       </c>
-      <c r="J15" s="103">
+      <c r="J15" s="104">
         <f>IFERROR(IF(A15="","",(C15*E15)-(C15*D15*1.014)+(C15*F15)),"")</f>
         <v>0</v>
       </c>
-      <c r="K15" s="104">
+      <c r="K15" s="105">
         <f>IFERROR(IF(A15="","",J15/H15*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L15" s="105">
+      <c r="L15" s="106">
         <f>IFERROR(IF(A15="","—",IF(K15&lt;-10,"VENDRE — Stop-loss",IF(AND(G15&gt;=24,K15&gt;=0),"RENFORCER",IF(AND(G15&gt;=15,K15&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1">
-      <c r="A16" s="101"/>
-      <c r="B16" s="101"/>
-      <c r="C16" s="102"/>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
-      <c r="H16" s="103">
+      <c r="A16" s="102"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="104">
         <f>IFERROR(IF(A16="","",C16*D16*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="103">
+      <c r="I16" s="104">
         <f>IFERROR(IF(A16="","",C16*E16),"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="103">
+      <c r="J16" s="104">
         <f>IFERROR(IF(A16="","",(C16*E16)-(C16*D16*1.014)+(C16*F16)),"")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="104">
+      <c r="K16" s="105">
         <f>IFERROR(IF(A16="","",J16/H16*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L16" s="105">
+      <c r="L16" s="106">
         <f>IFERROR(IF(A16="","—",IF(K16&lt;-10,"VENDRE — Stop-loss",IF(AND(G16&gt;=24,K16&gt;=0),"RENFORCER",IF(AND(G16&gt;=15,K16&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1">
-      <c r="A17" s="101"/>
-      <c r="B17" s="101"/>
-      <c r="C17" s="102"/>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102"/>
-      <c r="F17" s="102"/>
-      <c r="G17" s="102"/>
-      <c r="H17" s="103">
+      <c r="A17" s="102"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="104">
         <f>IFERROR(IF(A17="","",C17*D17*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="103">
+      <c r="I17" s="104">
         <f>IFERROR(IF(A17="","",C17*E17),"")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="103">
+      <c r="J17" s="104">
         <f>IFERROR(IF(A17="","",(C17*E17)-(C17*D17*1.014)+(C17*F17)),"")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="104">
+      <c r="K17" s="105">
         <f>IFERROR(IF(A17="","",J17/H17*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L17" s="105">
+      <c r="L17" s="106">
         <f>IFERROR(IF(A17="","—",IF(K17&lt;-10,"VENDRE — Stop-loss",IF(AND(G17&gt;=24,K17&gt;=0),"RENFORCER",IF(AND(G17&gt;=15,K17&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="101"/>
-      <c r="C18" s="102"/>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
-      <c r="F18" s="102"/>
-      <c r="G18" s="102"/>
-      <c r="H18" s="103">
+      <c r="A18" s="102"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="104">
         <f>IFERROR(IF(A18="","",C18*D18*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="103">
+      <c r="I18" s="104">
         <f>IFERROR(IF(A18="","",C18*E18),"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="103">
+      <c r="J18" s="104">
         <f>IFERROR(IF(A18="","",(C18*E18)-(C18*D18*1.014)+(C18*F18)),"")</f>
         <v>0</v>
       </c>
-      <c r="K18" s="104">
+      <c r="K18" s="105">
         <f>IFERROR(IF(A18="","",J18/H18*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L18" s="105">
+      <c r="L18" s="106">
         <f>IFERROR(IF(A18="","—",IF(K18&lt;-10,"VENDRE — Stop-loss",IF(AND(G18&gt;=24,K18&gt;=0),"RENFORCER",IF(AND(G18&gt;=15,K18&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="101"/>
-      <c r="C19" s="102"/>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102"/>
-      <c r="H19" s="103">
+      <c r="A19" s="102"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="104">
         <f>IFERROR(IF(A19="","",C19*D19*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="103">
+      <c r="I19" s="104">
         <f>IFERROR(IF(A19="","",C19*E19),"")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="103">
+      <c r="J19" s="104">
         <f>IFERROR(IF(A19="","",(C19*E19)-(C19*D19*1.014)+(C19*F19)),"")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="104">
+      <c r="K19" s="105">
         <f>IFERROR(IF(A19="","",J19/H19*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L19" s="105">
+      <c r="L19" s="106">
         <f>IFERROR(IF(A19="","—",IF(K19&lt;-10,"VENDRE — Stop-loss",IF(AND(G19&gt;=24,K19&gt;=0),"RENFORCER",IF(AND(G19&gt;=15,K19&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
@@ -8752,123 +9044,123 @@
     <row r="20" spans="1:12" ht="5" customHeight="1"/>
     <row r="21" spans="1:12" ht="22" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>439</v>
-      </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="106"/>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="107">
+        <v>457</v>
+      </c>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="108">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="107">
+      <c r="I21" s="108">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="107">
+      <c r="J21" s="108">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
         <v>0</v>
       </c>
-      <c r="K21" s="108">
+      <c r="K21" s="109">
         <f>IFERROR(J21/H21*100,"")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="105">
+      <c r="L21" s="106">
         <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="8" customHeight="1"/>
     <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="109" t="s">
-        <v>440</v>
-      </c>
-      <c r="B23" s="109"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="109"/>
-      <c r="H23" s="109"/>
-      <c r="I23" s="109"/>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="109"/>
+      <c r="A23" s="110" t="s">
+        <v>458</v>
+      </c>
+      <c r="B23" s="110"/>
+      <c r="C23" s="110"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
+      <c r="G23" s="110"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="110"/>
     </row>
     <row r="24" spans="1:12" ht="16" customHeight="1">
-      <c r="A24" s="110" t="s">
-        <v>441</v>
-      </c>
-      <c r="B24" s="111" t="s">
-        <v>442</v>
-      </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="111"/>
-      <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="111"/>
-      <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
-      <c r="L24" s="111"/>
+      <c r="A24" s="111" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" s="112" t="s">
+        <v>460</v>
+      </c>
+      <c r="C24" s="112"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="112"/>
+      <c r="F24" s="112"/>
+      <c r="G24" s="112"/>
+      <c r="H24" s="112"/>
+      <c r="I24" s="112"/>
+      <c r="J24" s="112"/>
+      <c r="K24" s="112"/>
+      <c r="L24" s="112"/>
     </row>
     <row r="25" spans="1:12" ht="16" customHeight="1">
-      <c r="A25" s="110" t="s">
-        <v>443</v>
-      </c>
-      <c r="B25" s="111" t="s">
-        <v>444</v>
-      </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="111"/>
-      <c r="L25" s="111"/>
+      <c r="A25" s="111" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" s="112" t="s">
+        <v>462</v>
+      </c>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
+      <c r="E25" s="112"/>
+      <c r="F25" s="112"/>
+      <c r="G25" s="112"/>
+      <c r="H25" s="112"/>
+      <c r="I25" s="112"/>
+      <c r="J25" s="112"/>
+      <c r="K25" s="112"/>
+      <c r="L25" s="112"/>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1">
-      <c r="A26" s="110" t="s">
-        <v>445</v>
-      </c>
-      <c r="B26" s="111" t="s">
-        <v>446</v>
-      </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="111"/>
-      <c r="L26" s="111"/>
+      <c r="A26" s="111" t="s">
+        <v>463</v>
+      </c>
+      <c r="B26" s="112" t="s">
+        <v>464</v>
+      </c>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
+      <c r="E26" s="112"/>
+      <c r="F26" s="112"/>
+      <c r="G26" s="112"/>
+      <c r="H26" s="112"/>
+      <c r="I26" s="112"/>
+      <c r="J26" s="112"/>
+      <c r="K26" s="112"/>
+      <c r="L26" s="112"/>
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1">
-      <c r="A27" s="110" t="s">
-        <v>447</v>
-      </c>
-      <c r="B27" s="111" t="s">
-        <v>448</v>
-      </c>
-      <c r="C27" s="111"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="111"/>
-      <c r="L27" s="111"/>
+      <c r="A27" s="111" t="s">
+        <v>465</v>
+      </c>
+      <c r="B27" s="112" t="s">
+        <v>466</v>
+      </c>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="112"/>
+      <c r="I27" s="112"/>
+      <c r="J27" s="112"/>
+      <c r="K27" s="112"/>
+      <c r="L27" s="112"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -8900,554 +9192,554 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="B2" s="112" t="s">
-        <v>450</v>
-      </c>
-      <c r="C2" s="112" t="s">
-        <v>451</v>
-      </c>
-      <c r="D2" s="112" t="s">
-        <v>452</v>
+      <c r="B2" s="113" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2" s="113" t="s">
+        <v>341</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="78" t="s">
-        <v>453</v>
-      </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
+      <c r="A3" s="80" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" s="80"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>454</v>
-      </c>
-      <c r="B4" s="113" t="s">
-        <v>455</v>
-      </c>
-      <c r="C4" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D4" s="114" t="s">
-        <v>457</v>
+        <v>471</v>
+      </c>
+      <c r="B4" s="114" t="s">
+        <v>472</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" s="115" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>458</v>
-      </c>
-      <c r="B5" s="113" t="s">
-        <v>459</v>
-      </c>
-      <c r="C5" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D5" s="114" t="s">
-        <v>460</v>
+        <v>474</v>
+      </c>
+      <c r="B5" s="114" t="s">
+        <v>475</v>
+      </c>
+      <c r="C5" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" s="115" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="B6" s="113" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D6" s="114" t="s">
-        <v>463</v>
+        <v>477</v>
+      </c>
+      <c r="B6" s="114" t="s">
+        <v>478</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="115" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="113" t="s">
-        <v>464</v>
-      </c>
-      <c r="C7" s="87" t="s">
-        <v>465</v>
-      </c>
-      <c r="D7" s="114" t="s">
-        <v>466</v>
+      <c r="B7" s="114" t="s">
+        <v>480</v>
+      </c>
+      <c r="C7" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="D7" s="115" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>467</v>
-      </c>
-      <c r="B8" s="113" t="s">
-        <v>468</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D8" s="114" t="s">
-        <v>470</v>
+        <v>483</v>
+      </c>
+      <c r="B8" s="114" t="s">
+        <v>484</v>
+      </c>
+      <c r="C8" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="115" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="113" t="s">
-        <v>471</v>
-      </c>
-      <c r="C9" s="87" t="s">
-        <v>465</v>
-      </c>
-      <c r="D9" s="114" t="s">
-        <v>472</v>
+      <c r="B9" s="114" t="s">
+        <v>486</v>
+      </c>
+      <c r="C9" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="D9" s="115" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>473</v>
-      </c>
-      <c r="B10" s="113" t="s">
-        <v>474</v>
-      </c>
-      <c r="C10" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D10" s="114" t="s">
-        <v>475</v>
+        <v>488</v>
+      </c>
+      <c r="B10" s="114" t="s">
+        <v>489</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" s="115" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>476</v>
-      </c>
-      <c r="B11" s="113" t="s">
-        <v>477</v>
-      </c>
-      <c r="C11" s="87"/>
-      <c r="D11" s="114" t="s">
-        <v>478</v>
+        <v>491</v>
+      </c>
+      <c r="B11" s="114" t="s">
+        <v>492</v>
+      </c>
+      <c r="C11" s="88"/>
+      <c r="D11" s="115" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>479</v>
-      </c>
-      <c r="B12" s="113" t="s">
-        <v>480</v>
-      </c>
-      <c r="C12" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D12" s="114" t="s">
-        <v>481</v>
+        <v>494</v>
+      </c>
+      <c r="B12" s="114" t="s">
+        <v>495</v>
+      </c>
+      <c r="C12" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D12" s="115" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="38" t="s">
-        <v>482</v>
-      </c>
-      <c r="B13" s="113" t="s">
-        <v>483</v>
-      </c>
-      <c r="C13" s="87" t="s">
-        <v>456</v>
-      </c>
-      <c r="D13" s="114" t="s">
-        <v>484</v>
+        <v>497</v>
+      </c>
+      <c r="B13" s="114" t="s">
+        <v>498</v>
+      </c>
+      <c r="C13" s="88" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="115" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="78" t="s">
-        <v>485</v>
-      </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
+      <c r="A14" s="80" t="s">
+        <v>500</v>
+      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="80"/>
+      <c r="D14" s="80"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>486</v>
-      </c>
-      <c r="B15" s="113" t="s">
-        <v>487</v>
-      </c>
-      <c r="C15" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D15" s="114" t="s">
-        <v>488</v>
+        <v>501</v>
+      </c>
+      <c r="B15" s="114" t="s">
+        <v>502</v>
+      </c>
+      <c r="C15" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D15" s="115" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>489</v>
-      </c>
-      <c r="B16" s="113" t="s">
-        <v>490</v>
-      </c>
-      <c r="C16" s="87"/>
-      <c r="D16" s="114" t="s">
-        <v>491</v>
+        <v>504</v>
+      </c>
+      <c r="B16" s="114" t="s">
+        <v>505</v>
+      </c>
+      <c r="C16" s="88"/>
+      <c r="D16" s="115" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="B17" s="113" t="s">
-        <v>490</v>
-      </c>
-      <c r="C17" s="87"/>
-      <c r="D17" s="114" t="s">
-        <v>492</v>
+      <c r="B17" s="114" t="s">
+        <v>505</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="115" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="113" t="s">
-        <v>493</v>
-      </c>
-      <c r="C18" s="87" t="s">
-        <v>465</v>
-      </c>
-      <c r="D18" s="114" t="s">
-        <v>494</v>
+      <c r="B18" s="114" t="s">
+        <v>508</v>
+      </c>
+      <c r="C18" s="88" t="s">
+        <v>481</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="38" t="s">
-        <v>495</v>
-      </c>
-      <c r="B19" s="113" t="s">
-        <v>496</v>
-      </c>
-      <c r="C19" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D19" s="114" t="s">
-        <v>497</v>
+        <v>510</v>
+      </c>
+      <c r="B19" s="114" t="s">
+        <v>511</v>
+      </c>
+      <c r="C19" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" s="115" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="38" t="s">
-        <v>498</v>
-      </c>
-      <c r="B20" s="113" t="s">
-        <v>499</v>
-      </c>
-      <c r="C20" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D20" s="114" t="s">
-        <v>500</v>
+        <v>513</v>
+      </c>
+      <c r="B20" s="114" t="s">
+        <v>514</v>
+      </c>
+      <c r="C20" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D20" s="115" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="78" t="s">
-        <v>501</v>
-      </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
+      <c r="A21" s="80" t="s">
+        <v>516</v>
+      </c>
+      <c r="B21" s="80"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="80"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>502</v>
-      </c>
-      <c r="B22" s="113" t="s">
-        <v>503</v>
-      </c>
-      <c r="C22" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D22" s="114" t="s">
-        <v>504</v>
+        <v>517</v>
+      </c>
+      <c r="B22" s="114" t="s">
+        <v>518</v>
+      </c>
+      <c r="C22" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D22" s="115" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>505</v>
-      </c>
-      <c r="B23" s="113" t="s">
-        <v>506</v>
-      </c>
-      <c r="C23" s="87" t="s">
-        <v>507</v>
-      </c>
-      <c r="D23" s="114" t="s">
-        <v>508</v>
+        <v>520</v>
+      </c>
+      <c r="B23" s="114" t="s">
+        <v>521</v>
+      </c>
+      <c r="C23" s="88" t="s">
+        <v>522</v>
+      </c>
+      <c r="D23" s="115" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>509</v>
-      </c>
-      <c r="B24" s="113" t="s">
-        <v>510</v>
-      </c>
-      <c r="C24" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D24" s="114" t="s">
-        <v>511</v>
+        <v>524</v>
+      </c>
+      <c r="B24" s="114" t="s">
+        <v>525</v>
+      </c>
+      <c r="C24" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="115" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="38" t="s">
-        <v>512</v>
-      </c>
-      <c r="B25" s="113" t="s">
-        <v>513</v>
-      </c>
-      <c r="C25" s="87" t="s">
-        <v>469</v>
-      </c>
-      <c r="D25" s="114" t="s">
-        <v>514</v>
+        <v>527</v>
+      </c>
+      <c r="B25" s="114" t="s">
+        <v>528</v>
+      </c>
+      <c r="C25" s="88" t="s">
+        <v>343</v>
+      </c>
+      <c r="D25" s="115" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="8" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
-      <c r="A27" s="78" t="s">
-        <v>515</v>
-      </c>
-      <c r="B27" s="78"/>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
+      <c r="A27" s="80" t="s">
+        <v>530</v>
+      </c>
+      <c r="B27" s="80"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="80"/>
     </row>
     <row r="28" spans="1:4" ht="16" customHeight="1">
-      <c r="A28" s="109" t="s">
-        <v>516</v>
-      </c>
-      <c r="B28" s="109"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="109"/>
+      <c r="A28" s="110" t="s">
+        <v>531</v>
+      </c>
+      <c r="B28" s="110"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1">
-      <c r="A29" s="115" t="s">
-        <v>517</v>
-      </c>
-      <c r="B29" s="116" t="s">
-        <v>518</v>
+      <c r="A29" s="116" t="s">
+        <v>532</v>
+      </c>
+      <c r="B29" s="117" t="s">
+        <v>533</v>
       </c>
       <c r="C29" s="75" t="s">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="D29" s="30"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1">
-      <c r="A30" s="115" t="s">
-        <v>520</v>
-      </c>
-      <c r="B30" s="116" t="s">
-        <v>521</v>
+      <c r="A30" s="116" t="s">
+        <v>535</v>
+      </c>
+      <c r="B30" s="117" t="s">
+        <v>536</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="D30" s="30"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1">
-      <c r="A31" s="115" t="s">
-        <v>523</v>
-      </c>
-      <c r="B31" s="116" t="s">
-        <v>524</v>
+      <c r="A31" s="116" t="s">
+        <v>538</v>
+      </c>
+      <c r="B31" s="117" t="s">
+        <v>539</v>
       </c>
       <c r="C31" s="75" t="s">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="D31" s="30"/>
     </row>
     <row r="32" spans="1:4" ht="16" customHeight="1">
-      <c r="A32" s="109" t="s">
-        <v>526</v>
-      </c>
-      <c r="B32" s="109"/>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
+      <c r="A32" s="110" t="s">
+        <v>541</v>
+      </c>
+      <c r="B32" s="110"/>
+      <c r="C32" s="110"/>
+      <c r="D32" s="110"/>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1">
-      <c r="A33" s="115" t="s">
-        <v>527</v>
-      </c>
-      <c r="B33" s="116" t="s">
-        <v>528</v>
+      <c r="A33" s="116" t="s">
+        <v>542</v>
+      </c>
+      <c r="B33" s="117" t="s">
+        <v>543</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D33" s="30"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1">
-      <c r="A34" s="115" t="s">
-        <v>530</v>
-      </c>
-      <c r="B34" s="116" t="s">
-        <v>531</v>
+      <c r="A34" s="116" t="s">
+        <v>545</v>
+      </c>
+      <c r="B34" s="117" t="s">
+        <v>546</v>
       </c>
       <c r="C34" s="75" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1">
-      <c r="A35" s="115" t="s">
-        <v>532</v>
-      </c>
-      <c r="B35" s="116" t="s">
-        <v>533</v>
+      <c r="A35" s="116" t="s">
+        <v>547</v>
+      </c>
+      <c r="B35" s="117" t="s">
+        <v>548</v>
       </c>
       <c r="C35" s="75" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D35" s="30"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1">
-      <c r="A36" s="115" t="s">
-        <v>534</v>
-      </c>
-      <c r="B36" s="116" t="s">
-        <v>535</v>
+      <c r="A36" s="116" t="s">
+        <v>549</v>
+      </c>
+      <c r="B36" s="117" t="s">
+        <v>550</v>
       </c>
       <c r="C36" s="75" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1">
-      <c r="A37" s="115" t="s">
-        <v>536</v>
-      </c>
-      <c r="B37" s="116" t="s">
-        <v>537</v>
+      <c r="A37" s="116" t="s">
+        <v>551</v>
+      </c>
+      <c r="B37" s="117" t="s">
+        <v>552</v>
       </c>
       <c r="C37" s="75" t="s">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="D37" s="30"/>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1">
-      <c r="A38" s="115" t="s">
-        <v>538</v>
-      </c>
-      <c r="B38" s="116" t="s">
-        <v>539</v>
+      <c r="A38" s="116" t="s">
+        <v>553</v>
+      </c>
+      <c r="B38" s="117" t="s">
+        <v>554</v>
       </c>
       <c r="C38" s="75" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="D38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="16" customHeight="1">
-      <c r="A39" s="109" t="s">
-        <v>541</v>
-      </c>
-      <c r="B39" s="109"/>
-      <c r="C39" s="109"/>
-      <c r="D39" s="109"/>
+      <c r="A39" s="110" t="s">
+        <v>556</v>
+      </c>
+      <c r="B39" s="110"/>
+      <c r="C39" s="110"/>
+      <c r="D39" s="110"/>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1">
-      <c r="A40" s="115" t="s">
-        <v>542</v>
-      </c>
-      <c r="B40" s="116" t="s">
-        <v>543</v>
+      <c r="A40" s="116" t="s">
+        <v>557</v>
+      </c>
+      <c r="B40" s="117" t="s">
+        <v>558</v>
       </c>
       <c r="C40" s="75" t="s">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="D40" s="30"/>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1">
-      <c r="A41" s="115" t="s">
-        <v>545</v>
-      </c>
-      <c r="B41" s="116" t="s">
-        <v>546</v>
+      <c r="A41" s="116" t="s">
+        <v>560</v>
+      </c>
+      <c r="B41" s="117" t="s">
+        <v>561</v>
       </c>
       <c r="C41" s="75" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1">
-      <c r="A42" s="115" t="s">
-        <v>548</v>
-      </c>
-      <c r="B42" s="116" t="s">
-        <v>549</v>
+      <c r="A42" s="116" t="s">
+        <v>563</v>
+      </c>
+      <c r="B42" s="117" t="s">
+        <v>564</v>
       </c>
       <c r="C42" s="75" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="D42" s="30"/>
     </row>
     <row r="43" spans="1:4" ht="16" customHeight="1">
-      <c r="A43" s="109" t="s">
-        <v>551</v>
-      </c>
-      <c r="B43" s="109"/>
-      <c r="C43" s="109"/>
-      <c r="D43" s="109"/>
+      <c r="A43" s="110" t="s">
+        <v>566</v>
+      </c>
+      <c r="B43" s="110"/>
+      <c r="C43" s="110"/>
+      <c r="D43" s="110"/>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
-      <c r="A44" s="115" t="s">
-        <v>552</v>
-      </c>
-      <c r="B44" s="116" t="s">
-        <v>553</v>
+      <c r="A44" s="116" t="s">
+        <v>567</v>
+      </c>
+      <c r="B44" s="117" t="s">
+        <v>568</v>
       </c>
       <c r="C44" s="75" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1">
-      <c r="A45" s="115" t="s">
-        <v>555</v>
-      </c>
-      <c r="B45" s="116" t="s">
-        <v>556</v>
+      <c r="A45" s="116" t="s">
+        <v>570</v>
+      </c>
+      <c r="B45" s="117" t="s">
+        <v>571</v>
       </c>
       <c r="C45" s="75" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1">
-      <c r="A46" s="115" t="s">
-        <v>557</v>
-      </c>
-      <c r="B46" s="116" t="s">
-        <v>558</v>
+      <c r="A46" s="116" t="s">
+        <v>572</v>
+      </c>
+      <c r="B46" s="117" t="s">
+        <v>573</v>
       </c>
       <c r="C46" s="75" t="s">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="D46" s="30"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1">
-      <c r="A47" s="115" t="s">
-        <v>559</v>
-      </c>
-      <c r="B47" s="116" t="s">
-        <v>560</v>
+      <c r="A47" s="116" t="s">
+        <v>574</v>
+      </c>
+      <c r="B47" s="117" t="s">
+        <v>575</v>
       </c>
       <c r="C47" s="75" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="D47" s="30"/>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -15,14 +15,14 @@
     <sheet name="FORMULE" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RAPPORT!$A$1:$E$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RAPPORT!$A$1:$E$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="623">
   <si>
     <t>FICHE D'ANALYSE BOURSIERE BRVM</t>
   </si>
@@ -51,6 +51,12 @@
     <t>Valeur Intrinseque VI</t>
   </si>
   <si>
+    <t>FCF Yield (%)</t>
+  </si>
+  <si>
+    <t>Prime de risque (pts%)</t>
+  </si>
+  <si>
     <t>Score Fondamental</t>
   </si>
   <si>
@@ -1095,6 +1101,105 @@
     <t>Le marche BRVM punit fortement les mauvaises surprises (illiquidite amplifie les mouvements). Une forte reaction positive est un signal de confiance durable des investisseurs.</t>
   </si>
   <si>
+    <t>I — FREE CASH FLOW &amp; PRIME DE RISQUE  (depuis rapport annuel + marche UEMOA)</t>
+  </si>
+  <si>
+    <t>I1 — FREE CASH FLOW  (saisir Amort / CAPEX / ΔBFR dans PROFIL — section Flux de Tresorerie)</t>
+  </si>
+  <si>
+    <t>Composante FCF</t>
+  </si>
+  <si>
+    <t>Valeur (FCFA)</t>
+  </si>
+  <si>
+    <t>Resultat Net N  (reference A2)</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>= RN annee N depuis A2 x 1 000 000</t>
+  </si>
+  <si>
+    <t>(+) Amortissements &amp; depreciations</t>
+  </si>
+  <si>
+    <t>PROFIL!B52</t>
+  </si>
+  <si>
+    <t>Tableau des flux — charges non decaissees</t>
+  </si>
+  <si>
+    <t>(-) CAPEX — Investissements nets</t>
+  </si>
+  <si>
+    <t>PROFIL!B53</t>
+  </si>
+  <si>
+    <t>Acquisitions d'immobilisations nettes de cessions</t>
+  </si>
+  <si>
+    <t>(-) Variation du BFR</t>
+  </si>
+  <si>
+    <t>PROFIL!B54</t>
+  </si>
+  <si>
+    <t>Positif = BFR en hausse = consommation de cash</t>
+  </si>
+  <si>
+    <t>FREE CASH FLOW (FCF)</t>
+  </si>
+  <si>
+    <t>FCF par titre (FCFA)</t>
+  </si>
+  <si>
+    <t>FCFA/titre</t>
+  </si>
+  <si>
+    <t>FCF Yield (FCF / Capitalisation boursiere)</t>
+  </si>
+  <si>
+    <t>I2 — SOUTENABILITE DU DIVIDENDE  (FCF coverage ratio)</t>
+  </si>
+  <si>
+    <t>Dividendes totaux verses N  (Div NET / 0.85 x Nb titres)</t>
+  </si>
+  <si>
+    <t>= dividende brut reconstitue x nombre de titres</t>
+  </si>
+  <si>
+    <t>FCF Coverage Ratio  (FCF / Dividendes verses)</t>
+  </si>
+  <si>
+    <t>ratio</t>
+  </si>
+  <si>
+    <t>I3 — PRIME DE RISQUE  vs  TAUX SANS RISQUE UEMOA  (OAT 5 ans BCEAO / BOAD)</t>
+  </si>
+  <si>
+    <t>Taux sans risque UEMOA (OAT 5 ans)</t>
+  </si>
+  <si>
+    <t>Modifier si necessaire — source : boad.org / bceao.int</t>
+  </si>
+  <si>
+    <t>Rendement dividende actuel (Div N / Prix)</t>
+  </si>
+  <si>
+    <t>FCF Yield (reference complementaire)</t>
+  </si>
+  <si>
+    <t>Prime de risque  (Rendement Div - Taux sans risque)</t>
+  </si>
+  <si>
+    <t>pts %</t>
+  </si>
+  <si>
+    <t>Prime FCF Yield - Taux sans risque</t>
+  </si>
+  <si>
     <t>TABLEAU DE BORD — SYNTHESE DE L'ANALYSE</t>
   </si>
   <si>
@@ -1224,6 +1329,21 @@
     <t>RECOMMANDATION FINALE (texte libre)</t>
   </si>
   <si>
+    <t>D — FREE CASH FLOW &amp; PRIME DE RISQUE  (depuis ETUDE Section I)</t>
+  </si>
+  <si>
+    <t>Valeur (auto)</t>
+  </si>
+  <si>
+    <t>FCF Coverage Ratio (FCF / Dividendes)</t>
+  </si>
+  <si>
+    <t>Prime de risque vs OAT UEMOA (pts %)</t>
+  </si>
+  <si>
+    <t>Prime FCF Yield vs taux sans risque (pts %)</t>
+  </si>
+  <si>
     <t>PROFIL DE LA SOCIETE</t>
   </si>
   <si>
@@ -1351,6 +1471,27 @@
   </si>
   <si>
     <t>&lt;-- Cours 5 jours apres publication</t>
+  </si>
+  <si>
+    <t>FLUX DE TRESORERIE (tableau des flux du rapport annuel)</t>
+  </si>
+  <si>
+    <t>Amortissements &amp; depreciations (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Tableau des flux — produits non decaissés</t>
+  </si>
+  <si>
+    <t>CAPEX — Investissements nets (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Tableau des flux — acquisitions immobilisations</t>
+  </si>
+  <si>
+    <t>Variation du BFR (FCFA)</t>
+  </si>
+  <si>
+    <t>&lt;-- Positif = besoin en hausse (consomme du cash)</t>
   </si>
   <si>
     <t>PORTEFEUILLE BRVM — SUIVI DES POSITIONS &amp; RECOMMANDATIONS</t>
@@ -1597,9 +1738,6 @@
   </si>
   <si>
     <t>Gain potentiel / Perte potentielle</t>
-  </si>
-  <si>
-    <t>ratio</t>
   </si>
   <si>
     <t>&lt; 1 = mauvais | 1-2 = acceptable | &gt;= 2 = bon</t>
@@ -1778,7 +1916,7 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="@"/>
   </numFmts>
-  <fonts count="51">
+  <fonts count="52">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2048,6 +2186,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFD97706"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1E293B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
@@ -2096,14 +2250,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF0D1B2A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1E293B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2342,7 +2488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2634,15 +2780,31 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="35" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="34" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="36" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2654,7 +2816,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2662,7 +2824,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="37" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="39" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2678,11 +2840,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="38" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="40" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2698,7 +2860,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="42" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2706,40 +2868,48 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="21" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="171" fontId="41" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="35" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="43" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="45" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="44" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="45" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="46" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2753,11 +2923,11 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="49" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2765,7 +2935,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2773,11 +2943,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3336,7 +3506,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="7">
         <f>IFERROR(SYNTHESE!E16,"")</f>
@@ -3353,7 +3523,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(SYNTHESE!E25,"")</f>
@@ -3370,7 +3540,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" s="10">
         <f>IFERROR(SYNTHESE!B31,"")</f>
@@ -3417,8 +3587,16 @@
       <c r="E10" s="11"/>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1">
+      <c r="A11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8">
+        <f>IFERROR(ETUDE!B298,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" s="12">
         <f>IFERROR(ETUDE!D238,"")</f>
@@ -3434,7 +3612,7 @@
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3443,7 +3621,7 @@
     </row>
     <row r="14" spans="1:5" ht="22" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B14" s="13">
         <f>IFERROR(SYNTHESE!A35,"")</f>
@@ -3451,7 +3629,7 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E14" s="12">
         <f>IFERROR(SYNTHESE!B35,"")</f>
@@ -3467,7 +3645,7 @@
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -3476,7 +3654,7 @@
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B17" s="12">
         <f>IFERROR(IF(ETUDE!B261="","N/A",ETUDE!B261),"N/A")</f>
@@ -3484,7 +3662,7 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E17" s="12">
         <f>IFERROR(IF(ETUDE!B268="","N/A",ETUDE!B268),"N/A")</f>
@@ -3493,7 +3671,7 @@
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" s="5"/>
       <c r="D18" s="12">
@@ -3511,7 +3689,7 @@
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -3558,7 +3736,7 @@
     </row>
     <row r="26" spans="1:5" ht="18" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -3567,18 +3745,18 @@
     </row>
     <row r="27" spans="1:5" ht="22" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="1"/>
       <c r="D27" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5" ht="22" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -3594,7 +3772,7 @@
     </row>
     <row r="30" spans="1:5" ht="14" customHeight="1">
       <c r="A30" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -3603,7 +3781,7 @@
     </row>
     <row r="31" spans="1:5" ht="14" customHeight="1">
       <c r="A31" s="17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
@@ -3626,7 +3804,7 @@
     </row>
     <row r="34" spans="1:5" ht="12" customHeight="1">
       <c r="A34" s="18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -3670,7 +3848,7 @@
   <sheetPr>
     <tabColor rgb="FF0EA5E9"/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.7109375" customWidth="1"/>
@@ -3710,7 +3888,7 @@
     <row r="3" spans="1:8" ht="5" customHeight="1"/>
     <row r="4" spans="1:8" ht="22" customHeight="1">
       <c r="A4" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3723,7 +3901,7 @@
     <row r="5" spans="1:8" ht="5" customHeight="1"/>
     <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="21"/>
@@ -3736,30 +3914,30 @@
     <row r="7" spans="1:8">
       <c r="A7" s="22"/>
       <c r="B7" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -3778,7 +3956,7 @@
     <row r="9" spans="1:8" ht="5" customHeight="1"/>
     <row r="10" spans="1:8" ht="20" customHeight="1">
       <c r="A10" s="21" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
@@ -3791,30 +3969,30 @@
     <row r="11" spans="1:8">
       <c r="A11" s="22"/>
       <c r="B11" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B12" s="24"/>
       <c r="C12" s="24"/>
@@ -3833,7 +4011,7 @@
     <row r="13" spans="1:8" ht="5" customHeight="1"/>
     <row r="14" spans="1:8" ht="20" customHeight="1">
       <c r="A14" s="21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="21"/>
       <c r="C14" s="21"/>
@@ -3845,30 +4023,30 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" s="27">
         <f>B12</f>
@@ -3887,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G16" s="25">
         <f>IFERROR(AVERAGE(D16:D20),"")</f>
@@ -3896,7 +4074,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B17" s="27">
         <f>C12</f>
@@ -3919,7 +4097,7 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B18" s="27">
         <f>D12</f>
@@ -3942,7 +4120,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" s="27">
         <f>E12</f>
@@ -3965,7 +4143,7 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="27">
         <f>F12</f>
@@ -3989,7 +4167,7 @@
     <row r="21" spans="1:8" ht="5" customHeight="1"/>
     <row r="22" spans="1:8" ht="20" customHeight="1">
       <c r="A22" s="21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
@@ -4001,16 +4179,16 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
@@ -4019,11 +4197,11 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" s="32"/>
       <c r="E24" s="32"/>
@@ -4032,11 +4210,11 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="23" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="32"/>
@@ -4045,11 +4223,11 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D26" s="32"/>
       <c r="E26" s="32"/>
@@ -4058,11 +4236,11 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="32"/>
@@ -4071,14 +4249,14 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B28" s="34">
         <f>IFERROR(PROFIL!B17,"")</f>
         <v>0</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="32"/>
       <c r="E28" s="32"/>
@@ -4088,14 +4266,14 @@
     <row r="29" spans="1:8" ht="5" customHeight="1"/>
     <row r="30" spans="1:8">
       <c r="A30" s="23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="25">
         <f>IFERROR(B24/B25,"")</f>
         <v>0</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D30" s="28">
         <f>IFERROR(IF(B30&gt;15,"Surevalue",IF(B30&lt;9,"Sous-evalue","Zone normale (9-15)")),"-")</f>
@@ -4104,14 +4282,14 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B31" s="35">
         <f>IFERROR(B26/B28,"")</f>
         <v>0</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D31" s="28">
         <f>IFERROR(IF(B24&gt;B31,"Action surevaluee vs VMC","Action sous-evaluee vs VMC"),"-")</f>
@@ -4120,14 +4298,14 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B32" s="25">
         <f>IFERROR(B27/B26,"")</f>
         <v>0</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D32" s="28">
         <f>IFERROR(IF(B32&lt;1,"Decote comptable",IF(B32&lt;2,"Normal","Prime elevee")),"-")</f>
@@ -4136,14 +4314,14 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B33" s="25">
         <f>IFERROR(F12*1000000/B26*100,"")</f>
         <v>0</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D33" s="28">
         <f>IFERROR(IF(B33&gt;=15,"Excellent",IF(B33&gt;=10,"Bon",IF(B33&gt;=5,"Moyen","Faible"))),"-")</f>
@@ -4152,14 +4330,14 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B34" s="25">
         <f>IFERROR(B30*B32,"")</f>
         <v>0</v>
       </c>
       <c r="C34" s="29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D34" s="28">
         <f>IFERROR(IF(B34&lt;22,"Decote globale (achat possible)","Surevaluation"),"-")</f>
@@ -4169,7 +4347,7 @@
     <row r="35" spans="1:8" ht="5" customHeight="1"/>
     <row r="36" spans="1:8" ht="20" customHeight="1">
       <c r="A36" s="21" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B36" s="21"/>
       <c r="C36" s="21"/>
@@ -4181,27 +4359,27 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="25" customHeight="1">
       <c r="A38" s="36" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
@@ -4211,7 +4389,7 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B39" s="37"/>
       <c r="C39" s="37"/>
@@ -4227,7 +4405,7 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B40" s="37"/>
       <c r="C40" s="37"/>
@@ -4246,7 +4424,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B41" s="37"/>
       <c r="C41" s="37"/>
@@ -4265,7 +4443,7 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B42" s="37"/>
       <c r="C42" s="37"/>
@@ -4284,7 +4462,7 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="37"/>
       <c r="C43" s="37"/>
@@ -4303,7 +4481,7 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B44" s="35">
         <f>SUM(B39:B43)</f>
@@ -4322,7 +4500,7 @@
     </row>
     <row r="45" spans="1:8" ht="20" customHeight="1">
       <c r="A45" s="21" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B45" s="21"/>
       <c r="C45" s="21"/>
@@ -4334,21 +4512,21 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="24"/>
@@ -4359,7 +4537,7 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="24"/>
@@ -4370,7 +4548,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="24"/>
@@ -4381,7 +4559,7 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="24"/>
@@ -4392,7 +4570,7 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="23" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="24"/>
@@ -4403,7 +4581,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="38" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B52" s="27">
         <f>SUM(B47:B51)</f>
@@ -4421,7 +4599,7 @@
     <row r="53" spans="1:8" ht="5" customHeight="1"/>
     <row r="54" spans="1:8" ht="20" customHeight="1">
       <c r="A54" s="21" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B54" s="21"/>
       <c r="C54" s="21"/>
@@ -4433,66 +4611,66 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B56" s="39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D56" s="40"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="23" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B57" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="40" t="s">
         <v>102</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="D57" s="40"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="23" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B58" s="39"/>
       <c r="C58" s="40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D58" s="40"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B59" s="39"/>
       <c r="C59" s="40" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D59" s="40"/>
     </row>
     <row r="60" spans="1:8" ht="5" customHeight="1"/>
     <row r="61" spans="1:8" ht="20" customHeight="1">
       <c r="A61" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B61" s="21"/>
       <c r="C61" s="21"/>
@@ -4504,19 +4682,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D62" s="22"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B63" s="24"/>
       <c r="C63" s="41"/>
@@ -4524,7 +4702,7 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="23" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B64" s="24"/>
       <c r="C64" s="41"/>
@@ -4532,7 +4710,7 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B65" s="42">
         <f>IFERROR(B64*1.014,"")</f>
@@ -4543,7 +4721,7 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="23" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B66" s="42">
         <f>IFERROR(B63/B65,"")</f>
@@ -4554,7 +4732,7 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B67" s="43">
         <f>IFERROR(B24,"")</f>
@@ -4565,7 +4743,7 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B68" s="42">
         <f>IFERROR(B67-(B67*0.014),"")</f>
@@ -4576,7 +4754,7 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B69" s="42">
         <f>IFERROR(B68-B65,"")</f>
@@ -4587,7 +4765,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B70" s="43">
         <f>IFERROR(B69*B66,"")</f>
@@ -4598,7 +4776,7 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B71" s="37"/>
       <c r="C71" s="41"/>
@@ -4606,7 +4784,7 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B72" s="43">
         <f>IFERROR(B71*B66,"")</f>
@@ -4617,7 +4795,7 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="38" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B73" s="43">
         <f>IFERROR(B70+B72,"")</f>
@@ -4628,7 +4806,7 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B74" s="44">
         <f>IFERROR(B73/B63*100,"")</f>
@@ -4639,21 +4817,21 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B75" s="45">
         <f>IFERROR(IF(B74&gt;C74,"MARCHE BOURSIER","EPARGNE"),"Saisir les donnees")</f>
         <v>0</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D75" s="30"/>
     </row>
     <row r="76" spans="1:8" ht="5" customHeight="1"/>
     <row r="77" spans="1:8" ht="20" customHeight="1">
       <c r="A77" s="21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B77" s="21"/>
       <c r="C77" s="21"/>
@@ -4695,7 +4873,7 @@
     </row>
     <row r="81" spans="1:8" ht="22" customHeight="1">
       <c r="A81" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -4708,7 +4886,7 @@
     <row r="83" spans="1:8" ht="5" customHeight="1"/>
     <row r="84" spans="1:8" ht="20" customHeight="1">
       <c r="A84" s="21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B84" s="21"/>
       <c r="C84" s="21"/>
@@ -4720,27 +4898,27 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E85" s="22" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B86" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C86" s="41"/>
       <c r="D86" s="47">
@@ -4748,15 +4926,15 @@
         <v>0</v>
       </c>
       <c r="E86" s="48" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B87" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="B87" s="32" t="s">
-        <v>132</v>
       </c>
       <c r="C87" s="41"/>
       <c r="D87" s="47">
@@ -4764,15 +4942,15 @@
         <v>0</v>
       </c>
       <c r="E87" s="48" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B88" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C88" s="41"/>
       <c r="D88" s="47">
@@ -4780,15 +4958,15 @@
         <v>0</v>
       </c>
       <c r="E88" s="48" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C89" s="41"/>
       <c r="D89" s="47">
@@ -4796,15 +4974,15 @@
         <v>0</v>
       </c>
       <c r="E89" s="48" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="23" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="32" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C90" s="41"/>
       <c r="D90" s="47">
@@ -4812,12 +4990,12 @@
         <v>0</v>
       </c>
       <c r="E90" s="48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="38" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B91" s="30"/>
       <c r="C91" s="30"/>
@@ -4833,7 +5011,7 @@
     <row r="92" spans="1:8" ht="5" customHeight="1"/>
     <row r="93" spans="1:8" ht="20" customHeight="1">
       <c r="A93" s="21" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="21"/>
       <c r="C93" s="21"/>
@@ -4845,24 +5023,24 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="22" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="22" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E94" s="22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="23" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B95" s="24"/>
       <c r="C95" s="24"/>
@@ -4877,7 +5055,7 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="23" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B96" s="24"/>
       <c r="C96" s="24"/>
@@ -4893,7 +5071,7 @@
     <row r="97" spans="1:8" ht="5" customHeight="1"/>
     <row r="98" spans="1:8" ht="20" customHeight="1">
       <c r="A98" s="21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B98" s="21"/>
       <c r="C98" s="21"/>
@@ -4905,16 +5083,16 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C99" s="22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -4926,56 +5104,56 @@
         <v>0</v>
       </c>
       <c r="C100" s="40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D100" s="30"/>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B101" s="42">
         <f>B25</f>
         <v>0</v>
       </c>
       <c r="C101" s="40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D101" s="30"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B102" s="51"/>
       <c r="C102" s="40" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D102" s="30"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B103" s="42">
         <f>IFERROR(B25*(1+B102/100),"")</f>
         <v>0</v>
       </c>
       <c r="C103" s="40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D103" s="30"/>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B104" s="44">
         <f>IFERROR(B24/B103,"")</f>
         <v>0</v>
       </c>
       <c r="C104" s="40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D104" s="28">
         <f>IFERROR(IF(B104&gt;15,"Surevalue - Surachat",IF(B104&lt;9,"Sous-evalue - Survente","Normal (9-15)")),"-")</f>
@@ -4985,7 +5163,7 @@
     <row r="105" spans="1:8" ht="5" customHeight="1"/>
     <row r="106" spans="1:8" ht="20" customHeight="1">
       <c r="A106" s="21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B106" s="21"/>
       <c r="C106" s="21"/>
@@ -4997,7 +5175,7 @@
     </row>
     <row r="107" spans="1:8" ht="25" customHeight="1">
       <c r="A107" s="52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B107" s="52"/>
       <c r="C107" s="52"/>
@@ -5009,119 +5187,119 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C108" s="22" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D108" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B109" s="51"/>
       <c r="C109" s="40" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D109" s="30"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B110" s="37"/>
       <c r="C110" s="40" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D110" s="30"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="23" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B111" s="42">
         <f>IFERROR(IF(B110=0,"Aucun dividende",B110*(1+B109/100)),"")</f>
         <v>0</v>
       </c>
       <c r="C111" s="40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D111" s="30"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="23" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B112" s="51">
         <v>6.5</v>
       </c>
       <c r="C112" s="40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D112" s="30"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="23" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B113" s="42">
         <f>IFERROR(IF(B110=0,"N/A",100*B111/B112),"")</f>
         <v>0</v>
       </c>
       <c r="C113" s="40" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D113" s="30"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B114" s="42">
         <f>IFERROR(IF(ISNUMBER(B113),B113*0.95,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C114" s="40" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D114" s="30"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B115" s="42">
         <f>IFERROR(IF(ISNUMBER(B113),B113*1.05,"N/A"),"")</f>
         <v>0</v>
       </c>
       <c r="C115" s="40" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D115" s="30"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B116" s="50">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"PCD N/A - pas de dividende",IF(B24&lt;B114,"EN DESSOUS zone cible - Survente",IF(B24&gt;B115,"AU-DESSUS zone cible - Surachat","DANS LA ZONE CIBLE"))),"")</f>
         <v>0</v>
       </c>
       <c r="C116" s="40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D116" s="30"/>
     </row>
     <row r="117" spans="1:8" ht="5" customHeight="1"/>
     <row r="118" spans="1:8" ht="20" customHeight="1">
       <c r="A118" s="21" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B118" s="21"/>
       <c r="C118" s="21"/>
@@ -5133,7 +5311,7 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="53" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B119" s="53"/>
       <c r="C119" s="53"/>
@@ -5145,82 +5323,82 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C120" s="22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D120" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B121" s="37"/>
       <c r="C121" s="40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D121" s="30"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="23" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B122" s="51">
         <v>8</v>
       </c>
       <c r="C122" s="40" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D122" s="30"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="23" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B123" s="51">
         <v>2</v>
       </c>
       <c r="C123" s="40" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D123" s="30"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="23" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B124" s="54">
         <f>IFERROR(IF(B121=0,"Saisir D1",B121/((B122/100)-(B123/100))),"")</f>
         <v>0</v>
       </c>
       <c r="C124" s="40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D124" s="30"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="23" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B125" s="50">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Saisir D1",IF(B24&lt;B124*0.95,"Prix SOUS P0 - Opportunite achat",IF(B24&gt;B124*1.05,"Prix SUR P0 - Surevalue","Dans la zone P0"))),"")</f>
         <v>0</v>
       </c>
       <c r="C125" s="40" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D125" s="30"/>
     </row>
     <row r="127" spans="1:8" ht="5" customHeight="1"/>
     <row r="128" spans="1:8" ht="20" customHeight="1">
       <c r="A128" s="21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B128" s="21"/>
       <c r="C128" s="21"/>
@@ -5232,87 +5410,87 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C129" s="22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D129" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="23" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B130" s="24"/>
       <c r="C130" s="40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D130" s="30"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="23" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B131" s="42">
         <f>IFERROR(B130*0.90,"")</f>
         <v>0</v>
       </c>
       <c r="C131" s="40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D131" s="30"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="23" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B132" s="24"/>
       <c r="C132" s="40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D132" s="30"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="23" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B133" s="42">
         <f>IFERROR(B130-B131,"")</f>
         <v>0</v>
       </c>
       <c r="C133" s="40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D133" s="30"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="23" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B134" s="42">
         <f>IFERROR(B132-B130,"")</f>
         <v>0</v>
       </c>
       <c r="C134" s="40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D134" s="30"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="23" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B135" s="44">
         <f>IFERROR(B134/B133,"")</f>
         <v>0</v>
       </c>
       <c r="C135" s="40" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D135" s="28">
         <f>IFERROR(IF(B135&gt;=2,"Bon (&gt;= 2:1)",IF(B135&gt;=1,"Acceptable (1:1)","Mauvais")),"")</f>
@@ -5322,7 +5500,7 @@
     <row r="136" spans="1:8" ht="5" customHeight="1"/>
     <row r="137" spans="1:8" ht="20" customHeight="1">
       <c r="A137" s="21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B137" s="21"/>
       <c r="C137" s="21"/>
@@ -5364,7 +5542,7 @@
     </row>
     <row r="141" spans="1:8" ht="26" customHeight="1">
       <c r="A141" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B141" s="19"/>
       <c r="C141" s="19"/>
@@ -5377,7 +5555,7 @@
     <row r="143" spans="1:8" ht="5" customHeight="1"/>
     <row r="144" spans="1:8" ht="20" customHeight="1">
       <c r="A144" s="21" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B144" s="21"/>
       <c r="C144" s="21"/>
@@ -5389,7 +5567,7 @@
     </row>
     <row r="145" spans="1:8" ht="30" customHeight="1">
       <c r="A145" s="55" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B145" s="55"/>
       <c r="C145" s="55"/>
@@ -5401,24 +5579,24 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D146" s="22" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E146" s="22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B147" s="27">
         <f>B12</f>
@@ -5436,7 +5614,7 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="23" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B148" s="27">
         <f>C12</f>
@@ -5454,7 +5632,7 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B149" s="27">
         <f>D12</f>
@@ -5472,7 +5650,7 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B150" s="27">
         <f>E12</f>
@@ -5490,7 +5668,7 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B151" s="27">
         <f>F12</f>
@@ -5509,14 +5687,14 @@
     <row r="152" spans="1:8" ht="5" customHeight="1"/>
     <row r="153" spans="1:8">
       <c r="A153" s="23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B153" s="35">
         <f>IFERROR(D151*1000000/B28,"")</f>
         <v>0</v>
       </c>
       <c r="C153" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D153" s="25">
         <f>IFERROR(B24/B153,"")</f>
@@ -5529,7 +5707,7 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B154" s="28">
         <f>IFERROR(IF(C151&lt;0,"Mauvais resultat PONCTUEL — RN recurrent &gt; RN publie — opportunite contrarian potentielle",IF(C151&gt;0,"Resultat FLATTE par elements exceptionnels — prudence sur la valorisation","Pas d'element exceptionnel detecte — RN publie = RN recurrent")),"-")</f>
@@ -5539,7 +5717,7 @@
     <row r="155" spans="1:8" ht="5" customHeight="1"/>
     <row r="156" spans="1:8" ht="20" customHeight="1">
       <c r="A156" s="21" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B156" s="21"/>
       <c r="C156" s="21"/>
@@ -5551,31 +5729,31 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E157" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B158" s="56">
         <f>IFERROR(CHOOSE(MATCH(PROFIL!B5,{"Banque","Assurance","Industrie","Distribution","Telecom","Autre"},0),10,12,13,14,8,12),12)</f>
         <v>0</v>
       </c>
       <c r="C158" s="32" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D158" s="32"/>
       <c r="E158" s="32"/>
@@ -5584,13 +5762,13 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="23" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B159" s="57">
         <v>5</v>
       </c>
       <c r="C159" s="32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D159" s="32"/>
       <c r="E159" s="32"/>
@@ -5600,7 +5778,7 @@
     <row r="160" spans="1:8" ht="5" customHeight="1"/>
     <row r="161" spans="1:8">
       <c r="A161" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B161" s="56">
         <f>IFERROR(B30,"")</f>
@@ -5621,7 +5799,7 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B162" s="56">
         <f>IFERROR(AVERAGE(E39:E43),"")</f>
@@ -5643,7 +5821,7 @@
     <row r="163" spans="1:8" ht="5" customHeight="1"/>
     <row r="164" spans="1:8" ht="20" customHeight="1">
       <c r="A164" s="21" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B164" s="21"/>
       <c r="C164" s="21"/>
@@ -5655,21 +5833,21 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C165" s="22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B166" s="58">
         <f>COUNTIF(B39:B43,"&gt;0")</f>
@@ -5686,7 +5864,7 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B167" s="26">
         <f>IFERROR(IF(OR(B39&lt;=0,B43&lt;=0),"N/A",(B43/B39)^(1/4)-1),"N/A")</f>
@@ -5703,7 +5881,7 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="38" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B168" s="59">
         <f>IFERROR(D166+D167,0)</f>
@@ -5714,13 +5892,13 @@
         <v>0</v>
       </c>
       <c r="D168" s="40" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="5" customHeight="1"/>
     <row r="170" spans="1:8" ht="20" customHeight="1">
       <c r="A170" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B170" s="21"/>
       <c r="C170" s="21"/>
@@ -5732,21 +5910,21 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C171" s="22" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D171" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="23" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B172" s="28">
         <f>IFERROR(IF(B30&lt;B158,"OUI","NON"),"-")</f>
@@ -5763,7 +5941,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="23" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B173" s="28">
         <f>IFERROR(IF(B24&lt;B31,"OUI — decote comptable","NON"),"-")</f>
@@ -5780,7 +5958,7 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B174" s="28">
         <f>IFERROR(IF(B33&gt;=10,"OUI","NON"),"-")</f>
@@ -5797,7 +5975,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B175" s="28">
         <f>IFERROR(IF(B168&gt;=2,"OUI","NON"),"-")</f>
@@ -5814,7 +5992,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B176" s="28">
         <f>IFERROR(IF(B24&lt;D95,"OUI — survente","NON"),"-")</f>
@@ -5831,7 +6009,7 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B177" s="28">
         <f>IFERROR(IF(G16&gt;=5,"OUI","NON"),"-")</f>
@@ -5848,11 +6026,11 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="38" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B178" s="30"/>
       <c r="C178" s="40" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D178" s="60">
         <f>IFERROR(SUM(D172:D177),0)</f>
@@ -5861,7 +6039,7 @@
     </row>
     <row r="179" spans="1:8" ht="30" customHeight="1">
       <c r="A179" s="61" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B179" s="61"/>
       <c r="C179" s="61"/>
@@ -5878,7 +6056,7 @@
     <row r="181" spans="1:8" ht="5" customHeight="1"/>
     <row r="182" spans="1:8" ht="22" customHeight="1">
       <c r="A182" s="19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B182" s="19"/>
       <c r="C182" s="19"/>
@@ -5891,7 +6069,7 @@
     <row r="183" spans="1:8" ht="5" customHeight="1"/>
     <row r="184" spans="1:8" ht="20" customHeight="1">
       <c r="A184" s="21" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B184" s="21"/>
       <c r="C184" s="21"/>
@@ -5903,10 +6081,10 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C185" s="22"/>
       <c r="D185" s="22"/>
@@ -5917,7 +6095,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B186" s="34">
         <f>IFERROR(PROFIL!B16,"")</f>
@@ -5932,7 +6110,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B187" s="34">
         <f>IFERROR(PROFIL!B17,"")</f>
@@ -5947,7 +6125,7 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B188" s="63">
         <f>IFERROR(PROFIL!B18,"")</f>
@@ -5962,7 +6140,7 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B189" s="63">
         <f>IFERROR(PROFIL!B19,"")</f>
@@ -5978,7 +6156,7 @@
     <row r="190" spans="1:8" ht="5" customHeight="1"/>
     <row r="191" spans="1:8" ht="20" customHeight="1">
       <c r="A191" s="21" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B191" s="21"/>
       <c r="C191" s="21"/>
@@ -5990,10 +6168,10 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B192" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C192" s="22"/>
       <c r="D192" s="22"/>
@@ -6004,7 +6182,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B193" s="34">
         <f>IFERROR(PROFIL!B22,"")</f>
@@ -6019,7 +6197,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B194" s="34">
         <f>IFERROR(PROFIL!B23,"")</f>
@@ -6034,7 +6212,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B195" s="63">
         <f>IFERROR(PROFIL!B24,"")</f>
@@ -6049,7 +6227,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B196" s="63">
         <f>IFERROR(PROFIL!B25,"")</f>
@@ -6065,7 +6243,7 @@
     <row r="197" spans="1:8" ht="5" customHeight="1"/>
     <row r="198" spans="1:8" ht="20" customHeight="1">
       <c r="A198" s="21" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B198" s="21"/>
       <c r="C198" s="21"/>
@@ -6077,10 +6255,10 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="22" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C199" s="22"/>
       <c r="D199" s="22"/>
@@ -6091,7 +6269,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B200" s="63">
         <f>IFERROR(PROFIL!B28,"")</f>
@@ -6106,7 +6284,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B201" s="63">
         <f>IFERROR(PROFIL!B29,"")</f>
@@ -6121,7 +6299,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B202" s="63">
         <f>IFERROR(PROFIL!B30,"")</f>
@@ -6136,7 +6314,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B203" s="63">
         <f>IFERROR(PROFIL!B31,"")</f>
@@ -6153,7 +6331,7 @@
     <row r="205" spans="1:8" ht="5" customHeight="1"/>
     <row r="206" spans="1:8" ht="22" customHeight="1">
       <c r="A206" s="19" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B206" s="19"/>
       <c r="C206" s="19"/>
@@ -6166,7 +6344,7 @@
     <row r="207" spans="1:8" ht="5" customHeight="1"/>
     <row r="208" spans="1:8" ht="20" customHeight="1">
       <c r="A208" s="21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B208" s="21"/>
       <c r="C208" s="21"/>
@@ -6178,14 +6356,14 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B209" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C209" s="22"/>
       <c r="D209" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E209" s="22"/>
       <c r="F209" s="22"/>
@@ -6194,7 +6372,7 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210" s="23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B210" s="27">
         <f>IFERROR(PROFIL!B40,"")</f>
@@ -6202,7 +6380,7 @@
       </c>
       <c r="C210" s="30"/>
       <c r="D210" s="48" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E210" s="30"/>
       <c r="F210" s="30"/>
@@ -6211,7 +6389,7 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211" s="23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B211" s="27">
         <f>IFERROR(PROFIL!B41,"")</f>
@@ -6219,7 +6397,7 @@
       </c>
       <c r="C211" s="30"/>
       <c r="D211" s="48" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E211" s="30"/>
       <c r="F211" s="30"/>
@@ -6228,7 +6406,7 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212" s="23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B212" s="27">
         <f>IFERROR(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0),"")</f>
@@ -6236,7 +6414,7 @@
       </c>
       <c r="C212" s="30"/>
       <c r="D212" s="48" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E212" s="30"/>
       <c r="F212" s="30"/>
@@ -6245,7 +6423,7 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213" s="23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B213" s="25">
         <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/B26*100,"")</f>
@@ -6253,7 +6431,7 @@
       </c>
       <c r="C213" s="30"/>
       <c r="D213" s="48" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E213" s="30"/>
       <c r="F213" s="30"/>
@@ -6262,7 +6440,7 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214" s="23" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B214" s="25">
         <f>IFERROR((IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))/(F12*1000000),"")</f>
@@ -6270,7 +6448,7 @@
       </c>
       <c r="C214" s="30"/>
       <c r="D214" s="48" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E214" s="30"/>
       <c r="F214" s="30"/>
@@ -6280,7 +6458,7 @@
     <row r="215" spans="1:8" ht="5" customHeight="1"/>
     <row r="216" spans="1:8" ht="20" customHeight="1">
       <c r="A216" s="21" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B216" s="21"/>
       <c r="C216" s="21"/>
@@ -6292,14 +6470,14 @@
     </row>
     <row r="217" spans="1:8">
       <c r="A217" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B217" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C217" s="22"/>
       <c r="D217" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E217" s="22"/>
       <c r="F217" s="22"/>
@@ -6308,7 +6486,7 @@
     </row>
     <row r="218" spans="1:8">
       <c r="A218" s="23" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B218" s="27">
         <f>IFERROR(PROFIL!B42,"")</f>
@@ -6316,7 +6494,7 @@
       </c>
       <c r="C218" s="30"/>
       <c r="D218" s="48" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E218" s="30"/>
       <c r="F218" s="30"/>
@@ -6325,7 +6503,7 @@
     </row>
     <row r="219" spans="1:8">
       <c r="A219" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B219" s="27">
         <f>IFERROR(PROFIL!B43,"")</f>
@@ -6333,7 +6511,7 @@
       </c>
       <c r="C219" s="30"/>
       <c r="D219" s="48" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E219" s="30"/>
       <c r="F219" s="30"/>
@@ -6342,7 +6520,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220" s="23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B220" s="25">
         <f>IFERROR(PROFIL!B42*1000000/PROFIL!B43,"")</f>
@@ -6350,7 +6528,7 @@
       </c>
       <c r="C220" s="30"/>
       <c r="D220" s="48" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E220" s="30"/>
       <c r="F220" s="30"/>
@@ -6359,7 +6537,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221" s="23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B221" s="25">
         <f>IFERROR(B26/(IFERROR(PROFIL!B40,0)+IFERROR(PROFIL!B41,0))*100,"")</f>
@@ -6367,7 +6545,7 @@
       </c>
       <c r="C221" s="30"/>
       <c r="D221" s="48" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E221" s="30"/>
       <c r="F221" s="30"/>
@@ -6377,7 +6555,7 @@
     <row r="222" spans="1:8" ht="5" customHeight="1"/>
     <row r="223" spans="1:8" ht="20" customHeight="1">
       <c r="A223" s="21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B223" s="21"/>
       <c r="C223" s="21"/>
@@ -6389,14 +6567,14 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B224" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C224" s="22"/>
       <c r="D224" s="22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E224" s="22"/>
       <c r="F224" s="22"/>
@@ -6405,7 +6583,7 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B225" s="27">
         <f>IFERROR(PROFIL!B44,"")</f>
@@ -6413,7 +6591,7 @@
       </c>
       <c r="C225" s="30"/>
       <c r="D225" s="48" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E225" s="30"/>
       <c r="F225" s="30"/>
@@ -6422,7 +6600,7 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B226" s="27">
         <f>IFERROR(PROFIL!B45,"")</f>
@@ -6430,7 +6608,7 @@
       </c>
       <c r="C226" s="30"/>
       <c r="D226" s="48" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E226" s="30"/>
       <c r="F226" s="30"/>
@@ -6439,7 +6617,7 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227" s="23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B227" s="25">
         <f>IFERROR(PROFIL!B44/PROFIL!B45,"")</f>
@@ -6447,7 +6625,7 @@
       </c>
       <c r="C227" s="30"/>
       <c r="D227" s="48" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E227" s="30"/>
       <c r="F227" s="30"/>
@@ -6456,7 +6634,7 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228" s="23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B228" s="27">
         <f>IFERROR(PROFIL!B44-PROFIL!B45,"")</f>
@@ -6464,7 +6642,7 @@
       </c>
       <c r="C228" s="30"/>
       <c r="D228" s="48" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E228" s="30"/>
       <c r="F228" s="30"/>
@@ -6475,7 +6653,7 @@
     <row r="230" spans="1:8" ht="5" customHeight="1"/>
     <row r="231" spans="1:8" ht="22" customHeight="1">
       <c r="A231" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B231" s="19"/>
       <c r="C231" s="19"/>
@@ -6488,7 +6666,7 @@
     <row r="232" spans="1:8" ht="5" customHeight="1"/>
     <row r="233" spans="1:8" ht="20" customHeight="1">
       <c r="A233" s="21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B233" s="21"/>
       <c r="C233" s="21"/>
@@ -6500,16 +6678,16 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234" s="22" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B234" s="22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C234" s="22" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E234" s="22"/>
       <c r="F234" s="22"/>
@@ -6526,7 +6704,7 @@
         <v>0</v>
       </c>
       <c r="C235" s="64" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D235" s="65">
         <f>IFERROR(IF(B24&lt;B31,"Prix SOUS VMC — decote comptable","Prix AU-DESSUS VMC"),"")</f>
@@ -6547,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="C236" s="64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D236" s="65">
         <f>IFERROR(IF(NOT(ISNUMBER(B113)),"Non disponible — dividend = 0",IF(B24&lt;B113,"Prix SOUS PCD — survente","Prix AU-DESSUS PCD — surachat")),"N/A")</f>
@@ -6568,7 +6746,7 @@
         <v>0</v>
       </c>
       <c r="C237" s="64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D237" s="65">
         <f>IFERROR(IF(NOT(ISNUMBER(B124)),"Non disponible — saisir D1",IF(B24&lt;B124,"Prix SOUS P0 — opportunite","Prix AU-DESSUS P0 — surevalue")),"N/A")</f>
@@ -6581,14 +6759,14 @@
     </row>
     <row r="238" spans="1:8" ht="30" customHeight="1">
       <c r="A238" s="38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B238" s="66">
         <f>IFERROR((B31*2+IF(ISNUMBER(B113),B113,0)+IF(ISNUMBER(B124),B124,0))/(2+IF(ISNUMBER(B113),1,0)+IF(ISNUMBER(B124),1,0)),"")</f>
         <v>0</v>
       </c>
       <c r="C238" s="64" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D238" s="67">
         <f>IFERROR(IF(B24&lt;B238*0.75,"FORTE OPPORTUNITE — decote &gt; 25%",IF(B24&lt;B238*0.85,"Achat ideal — decote 15-25%",IF(B24&lt;B238,"Legerement sous-evalue",IF(B24&lt;B238*1.20,"Zone normale / prime moderee","ATTENTION — surevaluation &gt; 20%")))),"Saisir prix actuel (B24)")</f>
@@ -6602,7 +6780,7 @@
     <row r="239" spans="1:8" ht="5" customHeight="1"/>
     <row r="240" spans="1:8" ht="20" customHeight="1">
       <c r="A240" s="21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B240" s="21"/>
       <c r="C240" s="21"/>
@@ -6614,16 +6792,16 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241" s="22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B241" s="22" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C241" s="22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E241" s="22"/>
       <c r="F241" s="22"/>
@@ -6632,7 +6810,7 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B242" s="27">
         <f>IFERROR(B238*0.75,"")</f>
@@ -6643,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="D242" s="69" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E242" s="30"/>
       <c r="F242" s="30"/>
@@ -6652,7 +6830,7 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B243" s="27">
         <f>IFERROR(B238*0.85,"")</f>
@@ -6663,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="D243" s="69" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E243" s="30"/>
       <c r="F243" s="30"/>
@@ -6672,7 +6850,7 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244" s="23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B244" s="27">
         <f>IFERROR(B238,"")</f>
@@ -6683,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="D244" s="69" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E244" s="30"/>
       <c r="F244" s="30"/>
@@ -6692,7 +6870,7 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B245" s="27">
         <f>IFERROR(B238*1.10,"")</f>
@@ -6703,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="D245" s="69" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E245" s="30"/>
       <c r="F245" s="30"/>
@@ -6712,7 +6890,7 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B246" s="27">
         <f>IFERROR(B238*1.20,"")</f>
@@ -6723,7 +6901,7 @@
         <v>0</v>
       </c>
       <c r="D246" s="69" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E246" s="30"/>
       <c r="F246" s="30"/>
@@ -6734,7 +6912,7 @@
     <row r="248" spans="1:8" ht="5" customHeight="1"/>
     <row r="249" spans="1:8" ht="22" customHeight="1">
       <c r="A249" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B249" s="19"/>
       <c r="C249" s="19"/>
@@ -6747,7 +6925,7 @@
     <row r="250" spans="1:8" ht="5" customHeight="1"/>
     <row r="251" spans="1:8" ht="20" customHeight="1">
       <c r="A251" s="21" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B251" s="21"/>
       <c r="C251" s="21"/>
@@ -6759,7 +6937,7 @@
     </row>
     <row r="252" spans="1:8" ht="14" customHeight="1">
       <c r="A252" s="52" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B252" s="52"/>
       <c r="C252" s="52"/>
@@ -6771,25 +6949,25 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253" s="22" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B253" s="22" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C253" s="22" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E253" s="22" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F253" s="22" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G253" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H253" s="22"/>
     </row>
@@ -6852,7 +7030,7 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257" s="23" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B257" s="68">
         <f>IFERROR(SUM(B254:B256),"")</f>
@@ -6871,7 +7049,7 @@
     <row r="258" spans="1:8" ht="5" customHeight="1"/>
     <row r="259" spans="1:8" ht="20" customHeight="1">
       <c r="A259" s="21" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B259" s="21"/>
       <c r="C259" s="21"/>
@@ -6883,14 +7061,14 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B260" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C260" s="22"/>
       <c r="D260" s="22" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E260" s="22"/>
       <c r="F260" s="22"/>
@@ -6899,7 +7077,7 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B261" s="72">
         <f>IFERROR((IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254*F254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255*F255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256*F256,0))/(IF(AND(A254&lt;&gt;"",ISNUMBER(F254)),B254,0)+IF(AND(A255&lt;&gt;"",ISNUMBER(F255)),B255,0)+IF(AND(A256&lt;&gt;"",ISNUMBER(F256)),B256,0)),"")</f>
@@ -6917,7 +7095,7 @@
     </row>
     <row r="262" spans="1:8" ht="40" customHeight="1">
       <c r="A262" s="38" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B262" s="73">
         <f>IFERROR(IF(B261&lt;0.85,"BAS DE CYCLE",IF(B261&lt;1.15,"MILIEU DE CYCLE","HAUT DE CYCLE")),"—")</f>
@@ -6935,7 +7113,7 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B263" s="28">
         <f>IFERROR(COUNTA(A254:A256),0)</f>
@@ -6954,7 +7132,7 @@
     <row r="264" spans="1:8" ht="5" customHeight="1"/>
     <row r="265" spans="1:8" ht="20" customHeight="1">
       <c r="A265" s="21" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B265" s="21"/>
       <c r="C265" s="21"/>
@@ -6966,14 +7144,14 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B266" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C266" s="22"/>
       <c r="D266" s="22" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E266" s="22"/>
       <c r="F266" s="22"/>
@@ -6982,7 +7160,7 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B267" s="27">
         <f>IFERROR(AVERAGE(B12:F12)*1000000/B28,"")</f>
@@ -6990,7 +7168,7 @@
       </c>
       <c r="C267" s="30"/>
       <c r="D267" s="75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E267" s="30"/>
       <c r="F267" s="30"/>
@@ -6999,7 +7177,7 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268" s="38" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B268" s="72">
         <f>IFERROR(B24/B267,"")</f>
@@ -7017,7 +7195,7 @@
     </row>
     <row r="269" spans="1:8" ht="28" customHeight="1">
       <c r="A269" s="38" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B269" s="77">
         <f>IFERROR(IF(AND(B261&lt;0.85,B268&lt;15),"ACHAT FORT — bas cycle + sous-evalue sur cycle",IF(AND(B261&lt;1.15,B268&lt;15),"ACHAT — milieu cycle + juste valorisation cycle",IF(AND(B261&gt;1.15,B268&lt;9),"SURVEILLER — haut cycle mais tres sous-evalue cycle",IF(AND(B261&gt;1.15,B268&gt;=15),"EVITER — haut cycle ET surevalue sur cycle","NEUTRE — analyser fondamentaux en detail")))),"Saisir matieres en G1")</f>
@@ -7034,7 +7212,7 @@
     <row r="271" spans="1:8" ht="5" customHeight="1"/>
     <row r="272" spans="1:8" ht="22" customHeight="1">
       <c r="A272" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B272" s="19"/>
       <c r="C272" s="19"/>
@@ -7046,7 +7224,7 @@
     </row>
     <row r="273" spans="1:8" ht="20" customHeight="1">
       <c r="A273" s="21" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B273" s="21"/>
       <c r="C273" s="21"/>
@@ -7058,19 +7236,19 @@
     </row>
     <row r="274" spans="1:8">
       <c r="A274" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B274" s="22" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C274" s="22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E274" s="22" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F274" s="22"/>
       <c r="G274" s="22"/>
@@ -7078,42 +7256,42 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275" s="23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B275" s="27">
         <f>IFERROR(PROFIL!B48,"")</f>
         <v>0</v>
       </c>
       <c r="C275" s="40" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D275" s="32" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E275" s="32"/>
     </row>
     <row r="276" spans="1:8">
       <c r="A276" s="23" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B276" s="27">
         <f>IFERROR(PROFIL!B49,"")</f>
         <v>0</v>
       </c>
       <c r="C276" s="40" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="277" spans="1:8">
       <c r="A277" s="38" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B277" s="25">
         <f>IFERROR(IF(AND(ISNUMBER(PROFIL!B48),ISNUMBER(PROFIL!B49),PROFIL!B48&gt;0),(PROFIL!B49-PROFIL!B48)/PROFIL!B48*100,""),"")</f>
         <v>0</v>
       </c>
       <c r="C277" s="40" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D277" s="28">
         <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),"Saisir J-1 et J+5 dans PROFIL",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,"Accueil tres favorable — marche recompense les resultats",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,"Accueil positif — marche satisfait",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,"Reaction mitigee — marche decu","PUNITION MARCHE — resultats fortement sanctionnes")))),"")</f>
@@ -7123,7 +7301,7 @@
     <row r="278" spans="1:8" ht="5" customHeight="1"/>
     <row r="279" spans="1:8" ht="20" customHeight="1">
       <c r="A279" s="21" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B279" s="21"/>
       <c r="C279" s="21"/>
@@ -7135,33 +7313,33 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280" s="22" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B280" s="22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C280" s="22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E280" s="22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G280" s="22" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H280" s="22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="281" spans="1:8">
       <c r="A281" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B281" s="35">
         <f>IFERROR(ETUDE!B39,"")</f>
@@ -7195,7 +7373,7 @@
     <row r="282" spans="1:8" ht="5" customHeight="1"/>
     <row r="283" spans="1:8" ht="20" customHeight="1">
       <c r="A283" s="21" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B283" s="21"/>
       <c r="C283" s="21"/>
@@ -7207,14 +7385,14 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284" s="22" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B284" s="22" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C284" s="22"/>
       <c r="D284" s="22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E284" s="22"/>
       <c r="F284" s="22"/>
@@ -7223,14 +7401,14 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285" s="23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B285" s="78">
         <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),0,IF(ETUDE!B167&gt;=0.10,3,IF(ETUDE!B167&gt;=0.02,2,IF(ETUDE!B167&gt;=0,1,0)))),0)</f>
         <v>0</v>
       </c>
       <c r="D285" s="79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E285" s="79"/>
       <c r="F285" s="79"/>
@@ -7239,14 +7417,14 @@
     </row>
     <row r="286" spans="1:8" ht="28" customHeight="1">
       <c r="A286" s="23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B286" s="78">
         <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),0,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,3,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,2,IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,1,0)))),0)</f>
         <v>0</v>
       </c>
       <c r="D286" s="79" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E286" s="79"/>
       <c r="F286" s="79"/>
@@ -7254,9 +7432,320 @@
       <c r="H286" s="79"/>
     </row>
     <row r="287" spans="1:8" ht="5" customHeight="1"/>
+    <row r="288" spans="1:8" ht="5" customHeight="1"/>
+    <row r="289" spans="1:8" ht="22" customHeight="1">
+      <c r="A289" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B289" s="19"/>
+      <c r="C289" s="19"/>
+      <c r="D289" s="19"/>
+      <c r="E289" s="19"/>
+      <c r="F289" s="19"/>
+      <c r="G289" s="19"/>
+      <c r="H289" s="19"/>
+    </row>
+    <row r="290" spans="1:8" ht="20" customHeight="1">
+      <c r="A290" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="B290" s="21"/>
+      <c r="C290" s="21"/>
+      <c r="D290" s="21"/>
+      <c r="E290" s="21"/>
+      <c r="F290" s="21"/>
+      <c r="G290" s="21"/>
+      <c r="H290" s="21"/>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="B291" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="C291" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D291" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E291" s="22"/>
+      <c r="F291" s="22"/>
+      <c r="G291" s="22"/>
+      <c r="H291" s="22"/>
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="B292" s="27">
+        <f>IFERROR(F12*1000000,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C292" s="40" t="s">
+        <v>364</v>
+      </c>
+      <c r="D292" s="32" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8">
+      <c r="A293" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B293" s="27">
+        <f>IFERROR(PROFIL!B52,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C293" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="D293" s="32" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8">
+      <c r="A294" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="B294" s="27">
+        <f>IFERROR(PROFIL!B53,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C294" s="40" t="s">
+        <v>370</v>
+      </c>
+      <c r="D294" s="32" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8">
+      <c r="A295" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="B295" s="27">
+        <f>IFERROR(PROFIL!B54,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C295" s="40" t="s">
+        <v>373</v>
+      </c>
+      <c r="D295" s="32" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" ht="20" customHeight="1">
+      <c r="A296" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="B296" s="80">
+        <f>IFERROR(F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C296" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="D296" s="76">
+        <f>IFERROR(IF(F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0)&gt;0,"FCF POSITIF — societe genere du cash","ALERTE — FCF negatif (consomme plus qu'elle ne genere)"),"Saisir Amort/CAPEX dans PROFIL")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8">
+      <c r="A297" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="B297" s="35">
+        <f>IFERROR((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B28,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C297" s="40" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="B298" s="25">
+        <f>IFERROR((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C298" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="D298" s="76">
+        <f>IFERROR(IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100&gt;=8,"Excellent FCF yield (&gt;= 8%)",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100&gt;=5,"Bon FCF yield (5-8%)",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100&gt;=0,"FCF yield faible (&lt; 5%)","FCF negatif — risque de dilution ou dette"))),"Completer PROFIL")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" ht="5" customHeight="1"/>
+    <row r="300" spans="1:8" ht="20" customHeight="1">
+      <c r="A300" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="B300" s="21"/>
+      <c r="C300" s="21"/>
+      <c r="D300" s="21"/>
+      <c r="E300" s="21"/>
+      <c r="F300" s="21"/>
+      <c r="G300" s="21"/>
+      <c r="H300" s="21"/>
+    </row>
+    <row r="301" spans="1:8">
+      <c r="A301" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B301" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C301" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="D301" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E301" s="22"/>
+      <c r="F301" s="22"/>
+      <c r="G301" s="22"/>
+      <c r="H301" s="22"/>
+    </row>
+    <row r="302" spans="1:8">
+      <c r="A302" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="B302" s="27">
+        <f>IFERROR(IF(B43=0,"Aucun dividende",B43/0.85*B28),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C302" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="D302" s="32" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" ht="22" customHeight="1">
+      <c r="A303" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="B303" s="35">
+        <f>IFERROR(IF(B43=0,"N/A - pas de dividende",(F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/(B43/0.85*B28)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C303" s="40" t="s">
+        <v>383</v>
+      </c>
+      <c r="D303" s="81">
+        <f>IFERROR(IF(B43=0,"Pas de dividende verse",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/(B43/0.85*B28)&gt;=2,"Dividende tres soutenable (FCF &gt; 2x dividendes)",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/(B43/0.85*B28)&gt;=1,"Dividende soutenable (FCF couvre les dividendes)",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/(B43/0.85*B28)&gt;=0,"ALERTE — FCF couvre partiellement les dividendes","DANGER — dividende non couvert par le FCF (ponction sur reserves)")))),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="5" customHeight="1"/>
+    <row r="305" spans="1:8" ht="20" customHeight="1">
+      <c r="A305" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B305" s="21"/>
+      <c r="C305" s="21"/>
+      <c r="D305" s="21"/>
+      <c r="E305" s="21"/>
+      <c r="F305" s="21"/>
+      <c r="G305" s="21"/>
+      <c r="H305" s="21"/>
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B306" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C306" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="D306" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E306" s="22"/>
+      <c r="F306" s="22"/>
+      <c r="G306" s="22"/>
+      <c r="H306" s="22"/>
+    </row>
+    <row r="307" spans="1:8">
+      <c r="A307" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="B307" s="82">
+        <v>6.5</v>
+      </c>
+      <c r="C307" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="D307" s="32" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308" s="23" t="s">
+        <v>387</v>
+      </c>
+      <c r="B308" s="25">
+        <f>IFERROR(IF(B43=0,"N/A",B43/B24*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C308" s="40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="B309" s="25">
+        <f>IFERROR((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C309" s="40" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="22" customHeight="1">
+      <c r="A310" s="38" t="s">
+        <v>389</v>
+      </c>
+      <c r="B310" s="83">
+        <f>IFERROR(IF(B43=0,"N/A",B43/B24*100-B307),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C310" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="D310" s="81">
+        <f>IFERROR(IF(B43=0,"N/A - pas de dividende",IF(B43/B24*100-B307&gt;=4,"ACTION TRES REMUNERATRICE vs obligations UEMOA (prime &gt; 4%)",IF(B43/B24*100-B307&gt;=2,"Action remuneratrice vs obligations (prime 2-4%)",IF(B43/B24*100-B307&gt;=0,"Prime de risque faible — obligations presque equivalentes","SOUS-REMUNEREE — les obligations UEMOA rapportent plus que cette action")))),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="B311" s="84">
+        <f>IFERROR((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100-B307,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C311" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="D311" s="76">
+        <f>IFERROR(IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100-B307&gt;=4,"FCF yield tres attractif vs obligations",IF((F12*1000000+IFERROR(PROFIL!B52,0)-IFERROR(PROFIL!B53,0)-IFERROR(PROFIL!B54,0))/B31*100-B307&gt;=0,"FCF yield acceptable","FCF yield inferieur au taux sans risque — risque non remunere")),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="64">
+  <mergeCells count="68">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
@@ -7321,6 +7810,10 @@
     <mergeCell ref="A283:H283"/>
     <mergeCell ref="D285:H285"/>
     <mergeCell ref="D286:H286"/>
+    <mergeCell ref="A289:H289"/>
+    <mergeCell ref="A290:H290"/>
+    <mergeCell ref="A300:H300"/>
+    <mergeCell ref="A305:H305"/>
   </mergeCells>
   <conditionalFormatting sqref="B172:B177">
     <cfRule type="containsText" dxfId="0" priority="14" operator="containsText" text="OUI">
@@ -7385,7 +7878,7 @@
   <sheetPr>
     <tabColor rgb="FF1E3A5F"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7397,7 +7890,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>357</v>
+        <v>392</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -7416,43 +7909,43 @@
     </row>
     <row r="3" spans="1:5" ht="5" customHeight="1"/>
     <row r="4" spans="1:5" ht="18" customHeight="1">
-      <c r="A4" s="80" t="s">
-        <v>358</v>
-      </c>
-      <c r="B4" s="80"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="80"/>
+      <c r="A4" s="85" t="s">
+        <v>393</v>
+      </c>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="85"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>361</v>
+        <v>396</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>362</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" s="81">
+        <v>398</v>
+      </c>
+      <c r="B6" s="86">
         <f>IFERROR(ETUDE!G8,"")</f>
         <v>0</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D6" s="82">
+        <v>399</v>
+      </c>
+      <c r="D6" s="87">
         <f>IFERROR(IF(ETUDE!G8&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G8&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
@@ -7463,16 +7956,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="B7" s="81">
+        <v>400</v>
+      </c>
+      <c r="B7" s="86">
         <f>IFERROR(ETUDE!G12,"")</f>
         <v>0</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D7" s="82">
+        <v>399</v>
+      </c>
+      <c r="D7" s="87">
         <f>IFERROR(IF(ETUDE!G12&gt;=10,"Bon (&gt;=10%)",IF(ETUDE!G12&gt;=0,"Faible (&lt;10%)","Negatif")),"-")</f>
         <v>0</v>
       </c>
@@ -7483,16 +7976,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="B8" s="81">
+        <v>401</v>
+      </c>
+      <c r="B8" s="86">
         <f>IFERROR(ETUDE!G16,"")</f>
         <v>0</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>367</v>
-      </c>
-      <c r="D8" s="82">
+        <v>402</v>
+      </c>
+      <c r="D8" s="87">
         <f>IFERROR(IF(ETUDE!G16&gt;=10,"Tres rentable",IF(ETUDE!G16&gt;=5,"Rentable",IF(ETUDE!G16&gt;=2,"Faiblement rentable","Faible"))),"-")</f>
         <v>0</v>
       </c>
@@ -7505,14 +7998,14 @@
       <c r="A9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="81">
+      <c r="B9" s="86">
         <f>IFERROR(ETUDE!B30,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="D9" s="82">
+        <v>403</v>
+      </c>
+      <c r="D9" s="87">
         <f>IFERROR(ETUDE!D30,"-")</f>
         <v>0</v>
       </c>
@@ -7525,14 +8018,14 @@
       <c r="A10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="81">
+      <c r="B10" s="86">
         <f>IFERROR(ETUDE!B32,"")</f>
         <v>0</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="D10" s="82">
+        <v>404</v>
+      </c>
+      <c r="D10" s="87">
         <f>IFERROR(ETUDE!D32,"-")</f>
         <v>0</v>
       </c>
@@ -7545,14 +8038,14 @@
       <c r="A11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="81">
+      <c r="B11" s="86">
         <f>IFERROR(ETUDE!B33,"")</f>
         <v>0</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="D11" s="82">
+        <v>399</v>
+      </c>
+      <c r="D11" s="87">
         <f>IFERROR(ETUDE!D33,"-")</f>
         <v>0</v>
       </c>
@@ -7563,16 +8056,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="B12" s="81">
+        <v>405</v>
+      </c>
+      <c r="B12" s="86">
         <f>IFERROR(AVERAGE(ETUDE!E39:ETUDE!E43),"")</f>
         <v>0</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="D12" s="82">
+        <v>406</v>
+      </c>
+      <c r="D12" s="87">
         <f>IFERROR(IF(AVERAGE(ETUDE!E39:ETUDE!E43)&gt;=3,"Bon (&gt;=3%)","Faible (&lt;3%)"),"-")</f>
         <v>0</v>
       </c>
@@ -7583,16 +8076,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="81">
+        <v>407</v>
+      </c>
+      <c r="B13" s="86">
         <f>IFERROR(ETUDE!B34,"")</f>
         <v>0</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>373</v>
-      </c>
-      <c r="D13" s="82">
+        <v>408</v>
+      </c>
+      <c r="D13" s="87">
         <f>IFERROR(ETUDE!D34,"-")</f>
         <v>0</v>
       </c>
@@ -7603,16 +8096,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="23" t="s">
-        <v>374</v>
-      </c>
-      <c r="B14" s="81">
+        <v>409</v>
+      </c>
+      <c r="B14" s="86">
         <f>IFERROR(IF(ISNUMBER(ETUDE!B167),ETUDE!B167*100,"N/A"),"N/A")</f>
         <v>0</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="D14" s="82">
+        <v>410</v>
+      </c>
+      <c r="D14" s="87">
         <f>IFERROR(IF(NOT(ISNUMBER(ETUDE!B167)),"Pas de dividende",IF(ETUDE!B167&gt;=0.10,"Croissant fort (&gt;10%/an)",IF(ETUDE!B167&gt;=0.02,"Croissant (2-10%/an)",IF(ETUDE!B167&gt;=0,"Stable","Dividende en BAISSE")))),"-")</f>
         <v>0</v>
       </c>
@@ -7623,16 +8116,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="B15" s="81">
+        <v>411</v>
+      </c>
+      <c r="B15" s="86">
         <f>IFERROR(IF(AND(ISNUMBER(PROFIL!B48),ISNUMBER(PROFIL!B49),PROFIL!B48&gt;0),(PROFIL!B49-PROFIL!B48)/PROFIL!B48*100,"Non renseigne"),"Non renseigne")</f>
         <v>0</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="D15" s="82">
+        <v>410</v>
+      </c>
+      <c r="D15" s="87">
         <f>IFERROR(IF(OR(NOT(ISNUMBER(PROFIL!B48)),NOT(ISNUMBER(PROFIL!B49))),"Non renseigne — saisir dans PROFIL",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=5,"Accueil tres favorable — marche recompense",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=0,"Accueil positif",IF((PROFIL!B49-PROFIL!B48)/PROFIL!B48*100&gt;=-5,"Reaction mitigee","Punition marche — forte baisse")))),"-")</f>
         <v>0</v>
       </c>
@@ -7643,55 +8136,55 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="84">
+        <v>412</v>
+      </c>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="89">
         <f>SUM(E6:E15)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="5" customHeight="1"/>
     <row r="18" spans="1:5" ht="18" customHeight="1">
-      <c r="A18" s="80" t="s">
-        <v>378</v>
-      </c>
-      <c r="B18" s="80"/>
-      <c r="C18" s="80"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
+      <c r="A18" s="85" t="s">
+        <v>413</v>
+      </c>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="B20" s="85">
+        <v>414</v>
+      </c>
+      <c r="B20" s="90">
         <f>IFERROR(ETUDE!D91,"")</f>
         <v>0</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>380</v>
-      </c>
-      <c r="D20" s="82">
+        <v>415</v>
+      </c>
+      <c r="D20" s="87">
         <f>IFERROR(ETUDE!E91,"-")</f>
         <v>0</v>
       </c>
@@ -7702,16 +8195,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="B21" s="85">
+        <v>416</v>
+      </c>
+      <c r="B21" s="90">
         <f>IFERROR(ETUDE!E95,"")</f>
         <v>0</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>382</v>
-      </c>
-      <c r="D21" s="82">
+        <v>417</v>
+      </c>
+      <c r="D21" s="87">
         <f>IFERROR(ETUDE!E96,"-")</f>
         <v>0</v>
       </c>
@@ -7722,16 +8215,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="B22" s="85">
+        <v>418</v>
+      </c>
+      <c r="B22" s="90">
         <f>IFERROR(ETUDE!B104,"")</f>
         <v>0</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>384</v>
-      </c>
-      <c r="D22" s="82">
+        <v>419</v>
+      </c>
+      <c r="D22" s="87">
         <f>IFERROR(ETUDE!D104,"-")</f>
         <v>0</v>
       </c>
@@ -7742,16 +8235,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="B23" s="85">
+        <v>420</v>
+      </c>
+      <c r="B23" s="90">
         <f>IFERROR(ETUDE!B116,"")</f>
         <v>0</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="D23" s="82">
+        <v>421</v>
+      </c>
+      <c r="D23" s="87">
         <f>IFERROR(ETUDE!B125,"-")</f>
         <v>0</v>
       </c>
@@ -7762,16 +8255,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="B24" s="85">
+        <v>422</v>
+      </c>
+      <c r="B24" s="90">
         <f>IFERROR(ETUDE!B135,"")</f>
         <v>0</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="D24" s="82">
+        <v>423</v>
+      </c>
+      <c r="D24" s="87">
         <f>IFERROR(ETUDE!D135,"-")</f>
         <v>0</v>
       </c>
@@ -7782,161 +8275,161 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="84">
+        <v>424</v>
+      </c>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
+      <c r="D25" s="88"/>
+      <c r="E25" s="89">
         <f>SUM(E20:E24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="5" customHeight="1"/>
     <row r="27" spans="1:5" ht="18" customHeight="1">
-      <c r="A27" s="86" t="s">
-        <v>390</v>
-      </c>
-      <c r="B27" s="86"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
-      <c r="E27" s="86"/>
+      <c r="A27" s="91" t="s">
+        <v>425</v>
+      </c>
+      <c r="B27" s="91"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="22" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>393</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="87">
+        <v>11</v>
+      </c>
+      <c r="B29" s="92">
         <f>E16</f>
         <v>0</v>
       </c>
-      <c r="C29" s="88">
+      <c r="C29" s="93">
         <v>30</v>
       </c>
-      <c r="D29" s="89">
+      <c r="D29" s="94">
         <f>IFERROR(E16/30*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="90">
+      <c r="E29" s="95">
         <f>IFERROR(IF(E16/30&gt;=0.7,"Solide",IF(E16/30&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B30" s="87">
+        <v>12</v>
+      </c>
+      <c r="B30" s="92">
         <f>E25</f>
         <v>0</v>
       </c>
-      <c r="C30" s="88">
+      <c r="C30" s="93">
         <v>15</v>
       </c>
-      <c r="D30" s="89">
+      <c r="D30" s="94">
         <f>IFERROR(E25/15*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="90">
+      <c r="E30" s="95">
         <f>IFERROR(IF(E25/15&gt;=0.7,"Solide",IF(E25/15&gt;=0.5,"Moyen","Faible")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="38" t="s">
-        <v>394</v>
-      </c>
-      <c r="B31" s="91">
+        <v>429</v>
+      </c>
+      <c r="B31" s="96">
         <f>IFERROR(E16+E25,"")</f>
         <v>0</v>
       </c>
-      <c r="C31" s="92">
+      <c r="C31" s="97">
         <v>45</v>
       </c>
-      <c r="D31" s="89">
+      <c r="D31" s="94">
         <f>IFERROR(B31/45*100,"")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="93">
+      <c r="E31" s="98">
         <f>IFERROR(IF(B31/45&gt;=0.7,"ACHETER",IF(B31/45&gt;=0.5,"SURVEILLER","EVITER")),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="5" customHeight="1"/>
     <row r="33" spans="1:5" ht="18" customHeight="1">
-      <c r="A33" s="80" t="s">
-        <v>395</v>
-      </c>
-      <c r="B33" s="80"/>
-      <c r="C33" s="80"/>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
+      <c r="A33" s="85" t="s">
+        <v>430</v>
+      </c>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="85"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="22" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>398</v>
+        <v>433</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" customHeight="1">
-      <c r="A35" s="94">
+      <c r="A35" s="99">
         <f>IFERROR(ETUDE!D178,"")</f>
         <v>0</v>
       </c>
-      <c r="B35" s="95">
+      <c r="B35" s="100">
         <f>IFERROR(ETUDE!E179,"-")</f>
         <v>0</v>
       </c>
-      <c r="C35" s="96">
+      <c r="C35" s="101">
         <f>IFERROR(ETUDE!D153,"")</f>
         <v>0</v>
       </c>
-      <c r="D35" s="96">
+      <c r="D35" s="101">
         <f>IFERROR(ETUDE!D161,"")</f>
         <v>0</v>
       </c>
-      <c r="E35" s="97">
+      <c r="E35" s="102">
         <f>IFERROR(IF(ETUDE!B24&lt;ETUDE!B31,"Prix &lt; VMC","Prix &gt; VMC"),"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="5" customHeight="1"/>
     <row r="37" spans="1:5" ht="18" customHeight="1">
-      <c r="A37" s="80" t="s">
-        <v>399</v>
-      </c>
-      <c r="B37" s="80"/>
-      <c r="C37" s="80"/>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
+      <c r="A37" s="85" t="s">
+        <v>434</v>
+      </c>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
     </row>
     <row r="38" spans="1:5" ht="50" customHeight="1">
       <c r="A38" s="46"/>
@@ -7973,9 +8466,93 @@
       <c r="D42" s="46"/>
       <c r="E42" s="46"/>
     </row>
+    <row r="43" spans="1:5" ht="5" customHeight="1"/>
+    <row r="44" spans="1:5" ht="18" customHeight="1">
+      <c r="A44" s="85" t="s">
+        <v>435</v>
+      </c>
+      <c r="B44" s="85"/>
+      <c r="C44" s="85"/>
+      <c r="D44" s="85"/>
+      <c r="E44" s="85"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="C45" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="46" spans="1:5" ht="20" customHeight="1">
+      <c r="A46" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="103">
+        <f>IFERROR(ETUDE!B298,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="104">
+        <f>IFERROR(ETUDE!D298,"Saisir Amort/CAPEX dans PROFIL")</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+    </row>
+    <row r="47" spans="1:5" ht="20" customHeight="1">
+      <c r="A47" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="B47" s="103">
+        <f>IFERROR(IF(ETUDE!B303="N/A - pas de dividende","N/A",ETUDE!B303),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C47" s="104">
+        <f>IFERROR(ETUDE!D303,"Completer PROFIL — flux de tresorerie")</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+    </row>
+    <row r="48" spans="1:5" ht="20" customHeight="1">
+      <c r="A48" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="B48" s="103">
+        <f>IFERROR(IF(ETUDE!B310="N/A",ETUDE!B310,ETUDE!B310),"")</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="104">
+        <f>IFERROR(ETUDE!D310,"Verifier taux sans risque en ETUDE I3")</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+    </row>
+    <row r="49" spans="1:5" ht="20" customHeight="1">
+      <c r="A49" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="B49" s="103">
+        <f>IFERROR(ETUDE!B311,"")</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="104">
+        <f>IFERROR(ETUDE!D311,"")</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+    </row>
+    <row r="50" spans="1:5" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="8">
+  <mergeCells count="13">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
@@ -7984,7 +8561,38 @@
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A38:E42"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
   </mergeCells>
+  <conditionalFormatting sqref="C46:C49">
+    <cfRule type="containsText" dxfId="3" priority="31" operator="containsText" text="Excellent">
+      <formula>NOT(ISERROR(SEARCH("Excellent",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="32" operator="containsText" text="soutenable">
+      <formula>NOT(ISERROR(SEARCH("soutenable",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="33" operator="containsText" text="TRES REMUNER">
+      <formula>NOT(ISERROR(SEARCH("TRES REMUNER",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="34" operator="containsText" text="remuneratrice">
+      <formula>NOT(ISERROR(SEARCH("remuneratrice",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="35" operator="containsText" text="ALERTE">
+      <formula>NOT(ISERROR(SEARCH("ALERTE",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="36" operator="containsText" text="faible">
+      <formula>NOT(ISERROR(SEARCH("faible",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="37" operator="containsText" text="DANGER">
+      <formula>NOT(ISERROR(SEARCH("DANGER",C46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="38" operator="containsText" text="SOUS-REMUNER">
+      <formula>NOT(ISERROR(SEARCH("SOUS-REMUNER",C46)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D20:D24">
     <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="Bon">
       <formula>NOT(ISERROR(SEARCH("Bon",D20)))</formula>
@@ -8088,7 +8696,7 @@
   <sheetPr>
     <tabColor rgb="FF6B7280"/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.7109375" customWidth="1"/>
@@ -8099,7 +8707,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8107,56 +8715,56 @@
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1">
       <c r="A2" s="21" t="s">
-        <v>401</v>
+        <v>441</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
       <c r="D2" s="21"/>
     </row>
     <row r="3" spans="1:4" ht="22" customHeight="1">
-      <c r="A3" s="98" t="s">
-        <v>402</v>
-      </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
+      <c r="A3" s="105" t="s">
+        <v>442</v>
+      </c>
+      <c r="B3" s="106"/>
+      <c r="C3" s="106"/>
       <c r="D3" s="75" t="s">
-        <v>403</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="22" customHeight="1">
-      <c r="A4" s="98" t="s">
-        <v>404</v>
-      </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
+      <c r="A4" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="75" t="s">
-        <v>405</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1">
-      <c r="A5" s="98" t="s">
-        <v>406</v>
-      </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="99"/>
+      <c r="A5" s="105" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
       <c r="D5" s="75" t="s">
-        <v>407</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="22" customHeight="1">
-      <c r="A6" s="98" t="s">
-        <v>408</v>
-      </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="100"/>
+      <c r="A6" s="105" t="s">
+        <v>448</v>
+      </c>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="75" t="s">
-        <v>409</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="8" customHeight="1"/>
     <row r="8" spans="1:4" ht="20" customHeight="1">
       <c r="A8" s="21" t="s">
-        <v>410</v>
+        <v>450</v>
       </c>
       <c r="B8" s="21"/>
       <c r="C8" s="21"/>
@@ -8164,46 +8772,46 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="23" t="s">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="B9" s="63">
         <f>B3</f>
         <v>0</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="23" t="s">
-        <v>404</v>
+        <v>444</v>
       </c>
       <c r="B10" s="63">
         <f>B4</f>
         <v>0</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="23" t="s">
-        <v>413</v>
+        <v>453</v>
       </c>
       <c r="B11" s="63">
         <f>B5</f>
         <v>0</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>412</v>
+        <v>452</v>
       </c>
       <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="23" t="s">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="B12" s="70"/>
       <c r="C12" s="30"/>
@@ -8211,7 +8819,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="23" t="s">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="B13" s="70"/>
       <c r="C13" s="30"/>
@@ -8220,7 +8828,7 @@
     <row r="14" spans="1:4" ht="5" customHeight="1"/>
     <row r="15" spans="1:4" ht="20" customHeight="1">
       <c r="A15" s="21" t="s">
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -8228,7 +8836,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B16" s="70"/>
       <c r="C16" s="30"/>
@@ -8236,7 +8844,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="23" t="s">
-        <v>417</v>
+        <v>457</v>
       </c>
       <c r="B17" s="70"/>
       <c r="C17" s="30"/>
@@ -8244,7 +8852,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B18" s="70"/>
       <c r="C18" s="30"/>
@@ -8252,7 +8860,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B19" s="70"/>
       <c r="C19" s="30"/>
@@ -8261,7 +8869,7 @@
     <row r="20" spans="1:4" ht="5" customHeight="1"/>
     <row r="21" spans="1:4" ht="20" customHeight="1">
       <c r="A21" s="21" t="s">
-        <v>418</v>
+        <v>458</v>
       </c>
       <c r="B21" s="21"/>
       <c r="C21" s="21"/>
@@ -8269,17 +8877,17 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B22" s="32" t="s">
-        <v>419</v>
+        <v>459</v>
       </c>
       <c r="C22" s="30"/>
       <c r="D22" s="30"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B23" s="70"/>
       <c r="C23" s="30"/>
@@ -8287,20 +8895,20 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>420</v>
+        <v>460</v>
       </c>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c r="C25" s="30"/>
       <c r="D25" s="30"/>
@@ -8308,7 +8916,7 @@
     <row r="26" spans="1:4" ht="5" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>422</v>
+        <v>462</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -8316,7 +8924,7 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" s="70"/>
       <c r="C28" s="30"/>
@@ -8324,7 +8932,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B29" s="70"/>
       <c r="C29" s="30"/>
@@ -8332,7 +8940,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B30" s="70"/>
       <c r="C30" s="30"/>
@@ -8340,10 +8948,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="23" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>423</v>
+        <v>463</v>
       </c>
       <c r="C31" s="30"/>
       <c r="D31" s="30"/>
@@ -8351,7 +8959,7 @@
     <row r="32" spans="1:4" ht="5" customHeight="1"/>
     <row r="33" spans="1:4" ht="20" customHeight="1">
       <c r="A33" s="21" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="B33" s="21"/>
       <c r="C33" s="21"/>
@@ -8359,17 +8967,17 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="23" t="s">
-        <v>425</v>
+        <v>465</v>
       </c>
       <c r="B34" s="32" t="s">
-        <v>426</v>
+        <v>466</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="23" t="s">
-        <v>427</v>
+        <v>467</v>
       </c>
       <c r="B35" s="70"/>
       <c r="C35" s="30"/>
@@ -8377,20 +8985,20 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="23" t="s">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>429</v>
+        <v>469</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="23" t="s">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>431</v>
+        <v>471</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
@@ -8398,7 +9006,7 @@
     <row r="38" spans="1:4" ht="5" customHeight="1"/>
     <row r="39" spans="1:4" ht="20" customHeight="1">
       <c r="A39" s="21" t="s">
-        <v>432</v>
+        <v>472</v>
       </c>
       <c r="B39" s="21"/>
       <c r="C39" s="21"/>
@@ -8406,60 +9014,60 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>433</v>
+        <v>473</v>
       </c>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="23" t="s">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="C42" s="30"/>
       <c r="D42" s="30"/>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>437</v>
+        <v>477</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
       <c r="C45" s="30"/>
       <c r="D45" s="30"/>
@@ -8467,7 +9075,7 @@
     <row r="46" spans="1:4" ht="5" customHeight="1"/>
     <row r="47" spans="1:4" ht="20" customHeight="1">
       <c r="A47" s="21" t="s">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="B47" s="21"/>
       <c r="C47" s="21"/>
@@ -8475,28 +9083,67 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="23" t="s">
-        <v>439</v>
+        <v>479</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>440</v>
+        <v>480</v>
       </c>
       <c r="C48" s="30"/>
       <c r="D48" s="30"/>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="23" t="s">
-        <v>441</v>
+        <v>481</v>
       </c>
       <c r="B49" s="32" t="s">
-        <v>442</v>
+        <v>482</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="30"/>
     </row>
     <row r="50" spans="1:4" ht="5" customHeight="1"/>
+    <row r="51" spans="1:4" ht="20" customHeight="1">
+      <c r="A51" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>485</v>
+      </c>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>487</v>
+      </c>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+    </row>
+    <row r="55" spans="1:4" ht="5" customHeight="1"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B3:C3"/>
@@ -8510,6 +9157,7 @@
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A51:D51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8537,7 +9185,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="26" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>443</v>
+        <v>490</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -8552,491 +9200,491 @@
       <c r="L1" s="19"/>
     </row>
     <row r="2" spans="1:12" ht="16" customHeight="1">
-      <c r="A2" s="101" t="s">
-        <v>444</v>
-      </c>
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
+      <c r="A2" s="108" t="s">
+        <v>491</v>
+      </c>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
     </row>
     <row r="3" spans="1:12" ht="5" customHeight="1"/>
     <row r="4" spans="1:12" ht="32" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>447</v>
+        <v>494</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>449</v>
+        <v>496</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>451</v>
+        <v>498</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>452</v>
+        <v>499</v>
       </c>
       <c r="I4" s="22" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="J4" s="22" t="s">
-        <v>454</v>
+        <v>501</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>455</v>
+        <v>502</v>
       </c>
       <c r="L4" s="22" t="s">
-        <v>456</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="20" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="104">
+      <c r="A5" s="109"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="111">
         <f>IFERROR(IF(A5="","",C5*D5*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I5" s="104">
+      <c r="I5" s="111">
         <f>IFERROR(IF(A5="","",C5*E5),"")</f>
         <v>0</v>
       </c>
-      <c r="J5" s="104">
+      <c r="J5" s="111">
         <f>IFERROR(IF(A5="","",(C5*E5)-(C5*D5*1.014)+(C5*F5)),"")</f>
         <v>0</v>
       </c>
-      <c r="K5" s="105">
+      <c r="K5" s="112">
         <f>IFERROR(IF(A5="","",J5/H5*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L5" s="106">
+      <c r="L5" s="113">
         <f>IFERROR(IF(A5="","—",IF(K5&lt;-10,"VENDRE — Stop-loss",IF(AND(G5&gt;=24,K5&gt;=0),"RENFORCER",IF(AND(G5&gt;=15,K5&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="20" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="103"/>
-      <c r="H6" s="104">
+      <c r="A6" s="109"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="111">
         <f>IFERROR(IF(A6="","",C6*D6*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I6" s="104">
+      <c r="I6" s="111">
         <f>IFERROR(IF(A6="","",C6*E6),"")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="104">
+      <c r="J6" s="111">
         <f>IFERROR(IF(A6="","",(C6*E6)-(C6*D6*1.014)+(C6*F6)),"")</f>
         <v>0</v>
       </c>
-      <c r="K6" s="105">
+      <c r="K6" s="112">
         <f>IFERROR(IF(A6="","",J6/H6*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L6" s="106">
+      <c r="L6" s="113">
         <f>IFERROR(IF(A6="","—",IF(K6&lt;-10,"VENDRE — Stop-loss",IF(AND(G6&gt;=24,K6&gt;=0),"RENFORCER",IF(AND(G6&gt;=15,K6&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="20" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="104">
+      <c r="A7" s="109"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="111">
         <f>IFERROR(IF(A7="","",C7*D7*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I7" s="104">
+      <c r="I7" s="111">
         <f>IFERROR(IF(A7="","",C7*E7),"")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="104">
+      <c r="J7" s="111">
         <f>IFERROR(IF(A7="","",(C7*E7)-(C7*D7*1.014)+(C7*F7)),"")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="105">
+      <c r="K7" s="112">
         <f>IFERROR(IF(A7="","",J7/H7*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="106">
+      <c r="L7" s="113">
         <f>IFERROR(IF(A7="","—",IF(K7&lt;-10,"VENDRE — Stop-loss",IF(AND(G7&gt;=24,K7&gt;=0),"RENFORCER",IF(AND(G7&gt;=15,K7&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="20" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="102"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103"/>
-      <c r="G8" s="103"/>
-      <c r="H8" s="104">
+      <c r="A8" s="109"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="111">
         <f>IFERROR(IF(A8="","",C8*D8*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I8" s="104">
+      <c r="I8" s="111">
         <f>IFERROR(IF(A8="","",C8*E8),"")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="104">
+      <c r="J8" s="111">
         <f>IFERROR(IF(A8="","",(C8*E8)-(C8*D8*1.014)+(C8*F8)),"")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="105">
+      <c r="K8" s="112">
         <f>IFERROR(IF(A8="","",J8/H8*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L8" s="106">
+      <c r="L8" s="113">
         <f>IFERROR(IF(A8="","—",IF(K8&lt;-10,"VENDRE — Stop-loss",IF(AND(G8&gt;=24,K8&gt;=0),"RENFORCER",IF(AND(G8&gt;=15,K8&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="20" customHeight="1">
-      <c r="A9" s="102"/>
-      <c r="B9" s="102"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="104">
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="111">
         <f>IFERROR(IF(A9="","",C9*D9*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="111">
         <f>IFERROR(IF(A9="","",C9*E9),"")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="111">
         <f>IFERROR(IF(A9="","",(C9*E9)-(C9*D9*1.014)+(C9*F9)),"")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="105">
+      <c r="K9" s="112">
         <f>IFERROR(IF(A9="","",J9/H9*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="106">
+      <c r="L9" s="113">
         <f>IFERROR(IF(A9="","—",IF(K9&lt;-10,"VENDRE — Stop-loss",IF(AND(G9&gt;=24,K9&gt;=0),"RENFORCER",IF(AND(G9&gt;=15,K9&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="20" customHeight="1">
-      <c r="A10" s="102"/>
-      <c r="B10" s="102"/>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="104">
+      <c r="A10" s="109"/>
+      <c r="B10" s="109"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="111">
         <f>IFERROR(IF(A10="","",C10*D10*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I10" s="104">
+      <c r="I10" s="111">
         <f>IFERROR(IF(A10="","",C10*E10),"")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="104">
+      <c r="J10" s="111">
         <f>IFERROR(IF(A10="","",(C10*E10)-(C10*D10*1.014)+(C10*F10)),"")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="112">
         <f>IFERROR(IF(A10="","",J10/H10*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="113">
         <f>IFERROR(IF(A10="","—",IF(K10&lt;-10,"VENDRE — Stop-loss",IF(AND(G10&gt;=24,K10&gt;=0),"RENFORCER",IF(AND(G10&gt;=15,K10&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="20" customHeight="1">
-      <c r="A11" s="102"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="104">
+      <c r="A11" s="109"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="110"/>
+      <c r="F11" s="110"/>
+      <c r="G11" s="110"/>
+      <c r="H11" s="111">
         <f>IFERROR(IF(A11="","",C11*D11*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I11" s="104">
+      <c r="I11" s="111">
         <f>IFERROR(IF(A11="","",C11*E11),"")</f>
         <v>0</v>
       </c>
-      <c r="J11" s="104">
+      <c r="J11" s="111">
         <f>IFERROR(IF(A11="","",(C11*E11)-(C11*D11*1.014)+(C11*F11)),"")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="105">
+      <c r="K11" s="112">
         <f>IFERROR(IF(A11="","",J11/H11*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="106">
+      <c r="L11" s="113">
         <f>IFERROR(IF(A11="","—",IF(K11&lt;-10,"VENDRE — Stop-loss",IF(AND(G11&gt;=24,K11&gt;=0),"RENFORCER",IF(AND(G11&gt;=15,K11&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="20" customHeight="1">
-      <c r="A12" s="102"/>
-      <c r="B12" s="102"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
-      <c r="G12" s="103"/>
-      <c r="H12" s="104">
+      <c r="A12" s="109"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="110"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
+      <c r="G12" s="110"/>
+      <c r="H12" s="111">
         <f>IFERROR(IF(A12="","",C12*D12*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I12" s="104">
+      <c r="I12" s="111">
         <f>IFERROR(IF(A12="","",C12*E12),"")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="104">
+      <c r="J12" s="111">
         <f>IFERROR(IF(A12="","",(C12*E12)-(C12*D12*1.014)+(C12*F12)),"")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="105">
+      <c r="K12" s="112">
         <f>IFERROR(IF(A12="","",J12/H12*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="106">
+      <c r="L12" s="113">
         <f>IFERROR(IF(A12="","—",IF(K12&lt;-10,"VENDRE — Stop-loss",IF(AND(G12&gt;=24,K12&gt;=0),"RENFORCER",IF(AND(G12&gt;=15,K12&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="20" customHeight="1">
-      <c r="A13" s="102"/>
-      <c r="B13" s="102"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
-      <c r="G13" s="103"/>
-      <c r="H13" s="104">
+      <c r="A13" s="109"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="111">
         <f>IFERROR(IF(A13="","",C13*D13*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I13" s="104">
+      <c r="I13" s="111">
         <f>IFERROR(IF(A13="","",C13*E13),"")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="104">
+      <c r="J13" s="111">
         <f>IFERROR(IF(A13="","",(C13*E13)-(C13*D13*1.014)+(C13*F13)),"")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="105">
+      <c r="K13" s="112">
         <f>IFERROR(IF(A13="","",J13/H13*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="106">
+      <c r="L13" s="113">
         <f>IFERROR(IF(A13="","—",IF(K13&lt;-10,"VENDRE — Stop-loss",IF(AND(G13&gt;=24,K13&gt;=0),"RENFORCER",IF(AND(G13&gt;=15,K13&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="20" customHeight="1">
-      <c r="A14" s="102"/>
-      <c r="B14" s="102"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103"/>
-      <c r="G14" s="103"/>
-      <c r="H14" s="104">
+      <c r="A14" s="109"/>
+      <c r="B14" s="109"/>
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="111">
         <f>IFERROR(IF(A14="","",C14*D14*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I14" s="104">
+      <c r="I14" s="111">
         <f>IFERROR(IF(A14="","",C14*E14),"")</f>
         <v>0</v>
       </c>
-      <c r="J14" s="104">
+      <c r="J14" s="111">
         <f>IFERROR(IF(A14="","",(C14*E14)-(C14*D14*1.014)+(C14*F14)),"")</f>
         <v>0</v>
       </c>
-      <c r="K14" s="105">
+      <c r="K14" s="112">
         <f>IFERROR(IF(A14="","",J14/H14*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L14" s="106">
+      <c r="L14" s="113">
         <f>IFERROR(IF(A14="","—",IF(K14&lt;-10,"VENDRE — Stop-loss",IF(AND(G14&gt;=24,K14&gt;=0),"RENFORCER",IF(AND(G14&gt;=15,K14&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="20" customHeight="1">
-      <c r="A15" s="102"/>
-      <c r="B15" s="102"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="104">
+      <c r="A15" s="109"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="111">
         <f>IFERROR(IF(A15="","",C15*D15*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="104">
+      <c r="I15" s="111">
         <f>IFERROR(IF(A15="","",C15*E15),"")</f>
         <v>0</v>
       </c>
-      <c r="J15" s="104">
+      <c r="J15" s="111">
         <f>IFERROR(IF(A15="","",(C15*E15)-(C15*D15*1.014)+(C15*F15)),"")</f>
         <v>0</v>
       </c>
-      <c r="K15" s="105">
+      <c r="K15" s="112">
         <f>IFERROR(IF(A15="","",J15/H15*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L15" s="106">
+      <c r="L15" s="113">
         <f>IFERROR(IF(A15="","—",IF(K15&lt;-10,"VENDRE — Stop-loss",IF(AND(G15&gt;=24,K15&gt;=0),"RENFORCER",IF(AND(G15&gt;=15,K15&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="20" customHeight="1">
-      <c r="A16" s="102"/>
-      <c r="B16" s="102"/>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="104">
+      <c r="A16" s="109"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
+      <c r="F16" s="110"/>
+      <c r="G16" s="110"/>
+      <c r="H16" s="111">
         <f>IFERROR(IF(A16="","",C16*D16*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I16" s="104">
+      <c r="I16" s="111">
         <f>IFERROR(IF(A16="","",C16*E16),"")</f>
         <v>0</v>
       </c>
-      <c r="J16" s="104">
+      <c r="J16" s="111">
         <f>IFERROR(IF(A16="","",(C16*E16)-(C16*D16*1.014)+(C16*F16)),"")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="105">
+      <c r="K16" s="112">
         <f>IFERROR(IF(A16="","",J16/H16*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L16" s="106">
+      <c r="L16" s="113">
         <f>IFERROR(IF(A16="","—",IF(K16&lt;-10,"VENDRE — Stop-loss",IF(AND(G16&gt;=24,K16&gt;=0),"RENFORCER",IF(AND(G16&gt;=15,K16&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="20" customHeight="1">
-      <c r="A17" s="102"/>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="104">
+      <c r="A17" s="109"/>
+      <c r="B17" s="109"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="110"/>
+      <c r="F17" s="110"/>
+      <c r="G17" s="110"/>
+      <c r="H17" s="111">
         <f>IFERROR(IF(A17="","",C17*D17*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I17" s="104">
+      <c r="I17" s="111">
         <f>IFERROR(IF(A17="","",C17*E17),"")</f>
         <v>0</v>
       </c>
-      <c r="J17" s="104">
+      <c r="J17" s="111">
         <f>IFERROR(IF(A17="","",(C17*E17)-(C17*D17*1.014)+(C17*F17)),"")</f>
         <v>0</v>
       </c>
-      <c r="K17" s="105">
+      <c r="K17" s="112">
         <f>IFERROR(IF(A17="","",J17/H17*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L17" s="106">
+      <c r="L17" s="113">
         <f>IFERROR(IF(A17="","—",IF(K17&lt;-10,"VENDRE — Stop-loss",IF(AND(G17&gt;=24,K17&gt;=0),"RENFORCER",IF(AND(G17&gt;=15,K17&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="20" customHeight="1">
-      <c r="A18" s="102"/>
-      <c r="B18" s="102"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="104">
+      <c r="A18" s="109"/>
+      <c r="B18" s="109"/>
+      <c r="C18" s="110"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="111">
         <f>IFERROR(IF(A18="","",C18*D18*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I18" s="104">
+      <c r="I18" s="111">
         <f>IFERROR(IF(A18="","",C18*E18),"")</f>
         <v>0</v>
       </c>
-      <c r="J18" s="104">
+      <c r="J18" s="111">
         <f>IFERROR(IF(A18="","",(C18*E18)-(C18*D18*1.014)+(C18*F18)),"")</f>
         <v>0</v>
       </c>
-      <c r="K18" s="105">
+      <c r="K18" s="112">
         <f>IFERROR(IF(A18="","",J18/H18*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L18" s="106">
+      <c r="L18" s="113">
         <f>IFERROR(IF(A18="","—",IF(K18&lt;-10,"VENDRE — Stop-loss",IF(AND(G18&gt;=24,K18&gt;=0),"RENFORCER",IF(AND(G18&gt;=15,K18&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="20" customHeight="1">
-      <c r="A19" s="102"/>
-      <c r="B19" s="102"/>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="104">
+      <c r="A19" s="109"/>
+      <c r="B19" s="109"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="110"/>
+      <c r="E19" s="110"/>
+      <c r="F19" s="110"/>
+      <c r="G19" s="110"/>
+      <c r="H19" s="111">
         <f>IFERROR(IF(A19="","",C19*D19*1.014),"")</f>
         <v>0</v>
       </c>
-      <c r="I19" s="104">
+      <c r="I19" s="111">
         <f>IFERROR(IF(A19="","",C19*E19),"")</f>
         <v>0</v>
       </c>
-      <c r="J19" s="104">
+      <c r="J19" s="111">
         <f>IFERROR(IF(A19="","",(C19*E19)-(C19*D19*1.014)+(C19*F19)),"")</f>
         <v>0</v>
       </c>
-      <c r="K19" s="105">
+      <c r="K19" s="112">
         <f>IFERROR(IF(A19="","",J19/H19*100),"")</f>
         <v>0</v>
       </c>
-      <c r="L19" s="106">
+      <c r="L19" s="113">
         <f>IFERROR(IF(A19="","—",IF(K19&lt;-10,"VENDRE — Stop-loss",IF(AND(G19&gt;=24,K19&gt;=0),"RENFORCER",IF(AND(G19&gt;=15,K19&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
         <v>0</v>
       </c>
@@ -9044,123 +9692,123 @@
     <row r="20" spans="1:12" ht="5" customHeight="1"/>
     <row r="21" spans="1:12" ht="22" customHeight="1">
       <c r="A21" s="38" t="s">
-        <v>457</v>
-      </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="107"/>
-      <c r="H21" s="108">
+        <v>504</v>
+      </c>
+      <c r="B21" s="114"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="114"/>
+      <c r="G21" s="114"/>
+      <c r="H21" s="115">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
         <v>0</v>
       </c>
-      <c r="I21" s="108">
+      <c r="I21" s="115">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
         <v>0</v>
       </c>
-      <c r="J21" s="108">
+      <c r="J21" s="115">
         <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
         <v>0</v>
       </c>
-      <c r="K21" s="109">
+      <c r="K21" s="116">
         <f>IFERROR(J21/H21*100,"")</f>
         <v>0</v>
       </c>
-      <c r="L21" s="106">
+      <c r="L21" s="113">
         <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="8" customHeight="1"/>
     <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="110" t="s">
-        <v>458</v>
-      </c>
-      <c r="B23" s="110"/>
-      <c r="C23" s="110"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="110"/>
+      <c r="A23" s="117" t="s">
+        <v>505</v>
+      </c>
+      <c r="B23" s="117"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
     </row>
     <row r="24" spans="1:12" ht="16" customHeight="1">
-      <c r="A24" s="111" t="s">
-        <v>459</v>
-      </c>
-      <c r="B24" s="112" t="s">
-        <v>460</v>
-      </c>
-      <c r="C24" s="112"/>
-      <c r="D24" s="112"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="112"/>
-      <c r="H24" s="112"/>
-      <c r="I24" s="112"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="112"/>
-      <c r="L24" s="112"/>
+      <c r="A24" s="118" t="s">
+        <v>506</v>
+      </c>
+      <c r="B24" s="119" t="s">
+        <v>507</v>
+      </c>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
     </row>
     <row r="25" spans="1:12" ht="16" customHeight="1">
-      <c r="A25" s="111" t="s">
-        <v>461</v>
-      </c>
-      <c r="B25" s="112" t="s">
-        <v>462</v>
-      </c>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
-      <c r="L25" s="112"/>
+      <c r="A25" s="118" t="s">
+        <v>508</v>
+      </c>
+      <c r="B25" s="119" t="s">
+        <v>509</v>
+      </c>
+      <c r="C25" s="119"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="119"/>
+      <c r="K25" s="119"/>
+      <c r="L25" s="119"/>
     </row>
     <row r="26" spans="1:12" ht="16" customHeight="1">
-      <c r="A26" s="111" t="s">
-        <v>463</v>
-      </c>
-      <c r="B26" s="112" t="s">
-        <v>464</v>
-      </c>
-      <c r="C26" s="112"/>
-      <c r="D26" s="112"/>
-      <c r="E26" s="112"/>
-      <c r="F26" s="112"/>
-      <c r="G26" s="112"/>
-      <c r="H26" s="112"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="112"/>
-      <c r="L26" s="112"/>
+      <c r="A26" s="118" t="s">
+        <v>510</v>
+      </c>
+      <c r="B26" s="119" t="s">
+        <v>511</v>
+      </c>
+      <c r="C26" s="119"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
+      <c r="J26" s="119"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="119"/>
     </row>
     <row r="27" spans="1:12" ht="16" customHeight="1">
-      <c r="A27" s="111" t="s">
-        <v>465</v>
-      </c>
-      <c r="B27" s="112" t="s">
-        <v>466</v>
-      </c>
-      <c r="C27" s="112"/>
-      <c r="D27" s="112"/>
-      <c r="E27" s="112"/>
-      <c r="F27" s="112"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="112"/>
+      <c r="A27" s="118" t="s">
+        <v>512</v>
+      </c>
+      <c r="B27" s="119" t="s">
+        <v>513</v>
+      </c>
+      <c r="C27" s="119"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="119"/>
+      <c r="H27" s="119"/>
+      <c r="I27" s="119"/>
+      <c r="J27" s="119"/>
+      <c r="K27" s="119"/>
+      <c r="L27" s="119"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
@@ -9192,554 +9840,554 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1">
       <c r="A1" s="19" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="113" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="113" t="s">
-        <v>468</v>
-      </c>
-      <c r="C2" s="113" t="s">
-        <v>341</v>
-      </c>
-      <c r="D2" s="113" t="s">
-        <v>469</v>
+      <c r="A2" s="120" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="120" t="s">
+        <v>515</v>
+      </c>
+      <c r="C2" s="120" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="120" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1">
-      <c r="A3" s="80" t="s">
-        <v>470</v>
-      </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
+      <c r="A3" s="85" t="s">
+        <v>517</v>
+      </c>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
     </row>
     <row r="4" spans="1:4" ht="28" customHeight="1">
       <c r="A4" s="38" t="s">
-        <v>471</v>
-      </c>
-      <c r="B4" s="114" t="s">
-        <v>472</v>
-      </c>
-      <c r="C4" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D4" s="115" t="s">
-        <v>473</v>
+        <v>518</v>
+      </c>
+      <c r="B4" s="121" t="s">
+        <v>519</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="122" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28" customHeight="1">
       <c r="A5" s="38" t="s">
-        <v>474</v>
-      </c>
-      <c r="B5" s="114" t="s">
-        <v>475</v>
-      </c>
-      <c r="C5" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D5" s="115" t="s">
-        <v>476</v>
+        <v>521</v>
+      </c>
+      <c r="B5" s="121" t="s">
+        <v>522</v>
+      </c>
+      <c r="C5" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D5" s="122" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28" customHeight="1">
       <c r="A6" s="38" t="s">
-        <v>477</v>
-      </c>
-      <c r="B6" s="114" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="115" t="s">
-        <v>479</v>
+        <v>524</v>
+      </c>
+      <c r="B6" s="121" t="s">
+        <v>525</v>
+      </c>
+      <c r="C6" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="122" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28" customHeight="1">
       <c r="A7" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="114" t="s">
-        <v>480</v>
-      </c>
-      <c r="C7" s="88" t="s">
-        <v>481</v>
-      </c>
-      <c r="D7" s="115" t="s">
-        <v>482</v>
+      <c r="B7" s="121" t="s">
+        <v>527</v>
+      </c>
+      <c r="C7" s="93" t="s">
+        <v>528</v>
+      </c>
+      <c r="D7" s="122" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28" customHeight="1">
       <c r="A8" s="38" t="s">
-        <v>483</v>
-      </c>
-      <c r="B8" s="114" t="s">
-        <v>484</v>
-      </c>
-      <c r="C8" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D8" s="115" t="s">
-        <v>485</v>
+        <v>530</v>
+      </c>
+      <c r="B8" s="121" t="s">
+        <v>531</v>
+      </c>
+      <c r="C8" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="122" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" customHeight="1">
       <c r="A9" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="114" t="s">
-        <v>486</v>
-      </c>
-      <c r="C9" s="88" t="s">
-        <v>481</v>
-      </c>
-      <c r="D9" s="115" t="s">
-        <v>487</v>
+      <c r="B9" s="121" t="s">
+        <v>533</v>
+      </c>
+      <c r="C9" s="93" t="s">
+        <v>528</v>
+      </c>
+      <c r="D9" s="122" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" customHeight="1">
       <c r="A10" s="38" t="s">
-        <v>488</v>
-      </c>
-      <c r="B10" s="114" t="s">
-        <v>489</v>
-      </c>
-      <c r="C10" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D10" s="115" t="s">
-        <v>490</v>
+        <v>535</v>
+      </c>
+      <c r="B10" s="121" t="s">
+        <v>536</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D10" s="122" t="s">
+        <v>537</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="28" customHeight="1">
       <c r="A11" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="B11" s="114" t="s">
-        <v>492</v>
-      </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="115" t="s">
-        <v>493</v>
+        <v>538</v>
+      </c>
+      <c r="B11" s="121" t="s">
+        <v>539</v>
+      </c>
+      <c r="C11" s="93"/>
+      <c r="D11" s="122" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="28" customHeight="1">
       <c r="A12" s="38" t="s">
-        <v>494</v>
-      </c>
-      <c r="B12" s="114" t="s">
-        <v>495</v>
-      </c>
-      <c r="C12" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D12" s="115" t="s">
-        <v>496</v>
+        <v>541</v>
+      </c>
+      <c r="B12" s="121" t="s">
+        <v>542</v>
+      </c>
+      <c r="C12" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D12" s="122" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" customHeight="1">
       <c r="A13" s="38" t="s">
-        <v>497</v>
-      </c>
-      <c r="B13" s="114" t="s">
-        <v>498</v>
-      </c>
-      <c r="C13" s="88" t="s">
-        <v>347</v>
-      </c>
-      <c r="D13" s="115" t="s">
-        <v>499</v>
+        <v>544</v>
+      </c>
+      <c r="B13" s="121" t="s">
+        <v>545</v>
+      </c>
+      <c r="C13" s="93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" s="122" t="s">
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" customHeight="1">
-      <c r="A14" s="80" t="s">
-        <v>500</v>
-      </c>
-      <c r="B14" s="80"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="80"/>
+      <c r="A14" s="85" t="s">
+        <v>547</v>
+      </c>
+      <c r="B14" s="85"/>
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
     </row>
     <row r="15" spans="1:4" ht="28" customHeight="1">
       <c r="A15" s="38" t="s">
-        <v>501</v>
-      </c>
-      <c r="B15" s="114" t="s">
-        <v>502</v>
-      </c>
-      <c r="C15" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D15" s="115" t="s">
-        <v>503</v>
+        <v>548</v>
+      </c>
+      <c r="B15" s="121" t="s">
+        <v>549</v>
+      </c>
+      <c r="C15" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" s="122" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="28" customHeight="1">
       <c r="A16" s="38" t="s">
-        <v>504</v>
-      </c>
-      <c r="B16" s="114" t="s">
-        <v>505</v>
-      </c>
-      <c r="C16" s="88"/>
-      <c r="D16" s="115" t="s">
-        <v>506</v>
+        <v>551</v>
+      </c>
+      <c r="B16" s="121" t="s">
+        <v>552</v>
+      </c>
+      <c r="C16" s="93"/>
+      <c r="D16" s="122" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="28" customHeight="1">
       <c r="A17" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="B17" s="114" t="s">
-        <v>505</v>
-      </c>
-      <c r="C17" s="88"/>
-      <c r="D17" s="115" t="s">
-        <v>507</v>
+        <v>138</v>
+      </c>
+      <c r="B17" s="121" t="s">
+        <v>552</v>
+      </c>
+      <c r="C17" s="93"/>
+      <c r="D17" s="122" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="28" customHeight="1">
       <c r="A18" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="B18" s="114" t="s">
-        <v>508</v>
-      </c>
-      <c r="C18" s="88" t="s">
-        <v>481</v>
-      </c>
-      <c r="D18" s="115" t="s">
-        <v>509</v>
+        <v>162</v>
+      </c>
+      <c r="B18" s="121" t="s">
+        <v>555</v>
+      </c>
+      <c r="C18" s="93" t="s">
+        <v>528</v>
+      </c>
+      <c r="D18" s="122" t="s">
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="28" customHeight="1">
       <c r="A19" s="38" t="s">
-        <v>510</v>
-      </c>
-      <c r="B19" s="114" t="s">
-        <v>511</v>
-      </c>
-      <c r="C19" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D19" s="115" t="s">
-        <v>512</v>
+        <v>557</v>
+      </c>
+      <c r="B19" s="121" t="s">
+        <v>558</v>
+      </c>
+      <c r="C19" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" s="122" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="38" t="s">
-        <v>513</v>
-      </c>
-      <c r="B20" s="114" t="s">
-        <v>514</v>
-      </c>
-      <c r="C20" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D20" s="115" t="s">
-        <v>515</v>
+        <v>560</v>
+      </c>
+      <c r="B20" s="121" t="s">
+        <v>561</v>
+      </c>
+      <c r="C20" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" s="122" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="18" customHeight="1">
-      <c r="A21" s="80" t="s">
-        <v>516</v>
-      </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="80"/>
-      <c r="D21" s="80"/>
+      <c r="A21" s="85" t="s">
+        <v>563</v>
+      </c>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="38" t="s">
-        <v>517</v>
-      </c>
-      <c r="B22" s="114" t="s">
-        <v>518</v>
-      </c>
-      <c r="C22" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D22" s="115" t="s">
-        <v>519</v>
+        <v>564</v>
+      </c>
+      <c r="B22" s="121" t="s">
+        <v>565</v>
+      </c>
+      <c r="C22" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D22" s="122" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="28" customHeight="1">
       <c r="A23" s="38" t="s">
-        <v>520</v>
-      </c>
-      <c r="B23" s="114" t="s">
-        <v>521</v>
-      </c>
-      <c r="C23" s="88" t="s">
-        <v>522</v>
-      </c>
-      <c r="D23" s="115" t="s">
-        <v>523</v>
+        <v>567</v>
+      </c>
+      <c r="B23" s="121" t="s">
+        <v>568</v>
+      </c>
+      <c r="C23" s="93" t="s">
+        <v>383</v>
+      </c>
+      <c r="D23" s="122" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="28" customHeight="1">
       <c r="A24" s="38" t="s">
-        <v>524</v>
-      </c>
-      <c r="B24" s="114" t="s">
-        <v>525</v>
-      </c>
-      <c r="C24" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D24" s="115" t="s">
-        <v>526</v>
+        <v>570</v>
+      </c>
+      <c r="B24" s="121" t="s">
+        <v>571</v>
+      </c>
+      <c r="C24" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="122" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="28" customHeight="1">
       <c r="A25" s="38" t="s">
-        <v>527</v>
-      </c>
-      <c r="B25" s="114" t="s">
-        <v>528</v>
-      </c>
-      <c r="C25" s="88" t="s">
-        <v>343</v>
-      </c>
-      <c r="D25" s="115" t="s">
-        <v>529</v>
+        <v>573</v>
+      </c>
+      <c r="B25" s="121" t="s">
+        <v>574</v>
+      </c>
+      <c r="C25" s="93" t="s">
+        <v>345</v>
+      </c>
+      <c r="D25" s="122" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="8" customHeight="1"/>
     <row r="27" spans="1:4" ht="20" customHeight="1">
-      <c r="A27" s="80" t="s">
-        <v>530</v>
-      </c>
-      <c r="B27" s="80"/>
-      <c r="C27" s="80"/>
-      <c r="D27" s="80"/>
+      <c r="A27" s="85" t="s">
+        <v>576</v>
+      </c>
+      <c r="B27" s="85"/>
+      <c r="C27" s="85"/>
+      <c r="D27" s="85"/>
     </row>
     <row r="28" spans="1:4" ht="16" customHeight="1">
-      <c r="A28" s="110" t="s">
-        <v>531</v>
-      </c>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
+      <c r="A28" s="117" t="s">
+        <v>577</v>
+      </c>
+      <c r="B28" s="117"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
     </row>
     <row r="29" spans="1:4" ht="18" customHeight="1">
-      <c r="A29" s="116" t="s">
-        <v>532</v>
-      </c>
-      <c r="B29" s="117" t="s">
-        <v>533</v>
+      <c r="A29" s="123" t="s">
+        <v>578</v>
+      </c>
+      <c r="B29" s="124" t="s">
+        <v>579</v>
       </c>
       <c r="C29" s="75" t="s">
-        <v>534</v>
+        <v>580</v>
       </c>
       <c r="D29" s="30"/>
     </row>
     <row r="30" spans="1:4" ht="18" customHeight="1">
-      <c r="A30" s="116" t="s">
-        <v>535</v>
-      </c>
-      <c r="B30" s="117" t="s">
-        <v>536</v>
+      <c r="A30" s="123" t="s">
+        <v>581</v>
+      </c>
+      <c r="B30" s="124" t="s">
+        <v>582</v>
       </c>
       <c r="C30" s="75" t="s">
-        <v>537</v>
+        <v>583</v>
       </c>
       <c r="D30" s="30"/>
     </row>
     <row r="31" spans="1:4" ht="18" customHeight="1">
-      <c r="A31" s="116" t="s">
-        <v>538</v>
-      </c>
-      <c r="B31" s="117" t="s">
-        <v>539</v>
+      <c r="A31" s="123" t="s">
+        <v>584</v>
+      </c>
+      <c r="B31" s="124" t="s">
+        <v>585</v>
       </c>
       <c r="C31" s="75" t="s">
-        <v>540</v>
+        <v>586</v>
       </c>
       <c r="D31" s="30"/>
     </row>
     <row r="32" spans="1:4" ht="16" customHeight="1">
-      <c r="A32" s="110" t="s">
-        <v>541</v>
-      </c>
-      <c r="B32" s="110"/>
-      <c r="C32" s="110"/>
-      <c r="D32" s="110"/>
+      <c r="A32" s="117" t="s">
+        <v>587</v>
+      </c>
+      <c r="B32" s="117"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
     </row>
     <row r="33" spans="1:4" ht="18" customHeight="1">
-      <c r="A33" s="116" t="s">
-        <v>542</v>
-      </c>
-      <c r="B33" s="117" t="s">
-        <v>543</v>
+      <c r="A33" s="123" t="s">
+        <v>588</v>
+      </c>
+      <c r="B33" s="124" t="s">
+        <v>589</v>
       </c>
       <c r="C33" s="75" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="D33" s="30"/>
     </row>
     <row r="34" spans="1:4" ht="18" customHeight="1">
-      <c r="A34" s="116" t="s">
-        <v>545</v>
-      </c>
-      <c r="B34" s="117" t="s">
-        <v>546</v>
+      <c r="A34" s="123" t="s">
+        <v>591</v>
+      </c>
+      <c r="B34" s="124" t="s">
+        <v>592</v>
       </c>
       <c r="C34" s="75" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="D34" s="30"/>
     </row>
     <row r="35" spans="1:4" ht="18" customHeight="1">
-      <c r="A35" s="116" t="s">
-        <v>547</v>
-      </c>
-      <c r="B35" s="117" t="s">
-        <v>548</v>
+      <c r="A35" s="123" t="s">
+        <v>593</v>
+      </c>
+      <c r="B35" s="124" t="s">
+        <v>594</v>
       </c>
       <c r="C35" s="75" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="D35" s="30"/>
     </row>
     <row r="36" spans="1:4" ht="18" customHeight="1">
-      <c r="A36" s="116" t="s">
-        <v>549</v>
-      </c>
-      <c r="B36" s="117" t="s">
-        <v>550</v>
+      <c r="A36" s="123" t="s">
+        <v>595</v>
+      </c>
+      <c r="B36" s="124" t="s">
+        <v>596</v>
       </c>
       <c r="C36" s="75" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="D36" s="30"/>
     </row>
     <row r="37" spans="1:4" ht="18" customHeight="1">
-      <c r="A37" s="116" t="s">
-        <v>551</v>
-      </c>
-      <c r="B37" s="117" t="s">
-        <v>552</v>
+      <c r="A37" s="123" t="s">
+        <v>597</v>
+      </c>
+      <c r="B37" s="124" t="s">
+        <v>598</v>
       </c>
       <c r="C37" s="75" t="s">
-        <v>544</v>
+        <v>590</v>
       </c>
       <c r="D37" s="30"/>
     </row>
     <row r="38" spans="1:4" ht="18" customHeight="1">
-      <c r="A38" s="116" t="s">
-        <v>553</v>
-      </c>
-      <c r="B38" s="117" t="s">
-        <v>554</v>
+      <c r="A38" s="123" t="s">
+        <v>599</v>
+      </c>
+      <c r="B38" s="124" t="s">
+        <v>600</v>
       </c>
       <c r="C38" s="75" t="s">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="D38" s="30"/>
     </row>
     <row r="39" spans="1:4" ht="16" customHeight="1">
-      <c r="A39" s="110" t="s">
-        <v>556</v>
-      </c>
-      <c r="B39" s="110"/>
-      <c r="C39" s="110"/>
-      <c r="D39" s="110"/>
+      <c r="A39" s="117" t="s">
+        <v>602</v>
+      </c>
+      <c r="B39" s="117"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="117"/>
     </row>
     <row r="40" spans="1:4" ht="18" customHeight="1">
-      <c r="A40" s="116" t="s">
-        <v>557</v>
-      </c>
-      <c r="B40" s="117" t="s">
-        <v>558</v>
+      <c r="A40" s="123" t="s">
+        <v>603</v>
+      </c>
+      <c r="B40" s="124" t="s">
+        <v>604</v>
       </c>
       <c r="C40" s="75" t="s">
-        <v>559</v>
+        <v>605</v>
       </c>
       <c r="D40" s="30"/>
     </row>
     <row r="41" spans="1:4" ht="18" customHeight="1">
-      <c r="A41" s="116" t="s">
-        <v>560</v>
-      </c>
-      <c r="B41" s="117" t="s">
-        <v>561</v>
+      <c r="A41" s="123" t="s">
+        <v>606</v>
+      </c>
+      <c r="B41" s="124" t="s">
+        <v>607</v>
       </c>
       <c r="C41" s="75" t="s">
-        <v>562</v>
+        <v>608</v>
       </c>
       <c r="D41" s="30"/>
     </row>
     <row r="42" spans="1:4" ht="18" customHeight="1">
-      <c r="A42" s="116" t="s">
-        <v>563</v>
-      </c>
-      <c r="B42" s="117" t="s">
-        <v>564</v>
+      <c r="A42" s="123" t="s">
+        <v>609</v>
+      </c>
+      <c r="B42" s="124" t="s">
+        <v>610</v>
       </c>
       <c r="C42" s="75" t="s">
-        <v>565</v>
+        <v>611</v>
       </c>
       <c r="D42" s="30"/>
     </row>
     <row r="43" spans="1:4" ht="16" customHeight="1">
-      <c r="A43" s="110" t="s">
-        <v>566</v>
-      </c>
-      <c r="B43" s="110"/>
-      <c r="C43" s="110"/>
-      <c r="D43" s="110"/>
+      <c r="A43" s="117" t="s">
+        <v>612</v>
+      </c>
+      <c r="B43" s="117"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
     </row>
     <row r="44" spans="1:4" ht="18" customHeight="1">
-      <c r="A44" s="116" t="s">
-        <v>567</v>
-      </c>
-      <c r="B44" s="117" t="s">
-        <v>568</v>
+      <c r="A44" s="123" t="s">
+        <v>613</v>
+      </c>
+      <c r="B44" s="124" t="s">
+        <v>614</v>
       </c>
       <c r="C44" s="75" t="s">
-        <v>569</v>
+        <v>615</v>
       </c>
       <c r="D44" s="30"/>
     </row>
     <row r="45" spans="1:4" ht="18" customHeight="1">
-      <c r="A45" s="116" t="s">
-        <v>570</v>
-      </c>
-      <c r="B45" s="117" t="s">
-        <v>571</v>
+      <c r="A45" s="123" t="s">
+        <v>616</v>
+      </c>
+      <c r="B45" s="124" t="s">
+        <v>617</v>
       </c>
       <c r="C45" s="75" t="s">
-        <v>569</v>
+        <v>615</v>
       </c>
       <c r="D45" s="30"/>
     </row>
     <row r="46" spans="1:4" ht="18" customHeight="1">
-      <c r="A46" s="116" t="s">
-        <v>572</v>
-      </c>
-      <c r="B46" s="117" t="s">
-        <v>573</v>
+      <c r="A46" s="123" t="s">
+        <v>618</v>
+      </c>
+      <c r="B46" s="124" t="s">
+        <v>619</v>
       </c>
       <c r="C46" s="75" t="s">
-        <v>569</v>
+        <v>615</v>
       </c>
       <c r="D46" s="30"/>
     </row>
     <row r="47" spans="1:4" ht="18" customHeight="1">
-      <c r="A47" s="116" t="s">
-        <v>574</v>
-      </c>
-      <c r="B47" s="117" t="s">
-        <v>575</v>
+      <c r="A47" s="123" t="s">
+        <v>620</v>
+      </c>
+      <c r="B47" s="124" t="s">
+        <v>621</v>
       </c>
       <c r="C47" s="75" t="s">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="D47" s="30"/>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -4285,7 +4285,7 @@
         <v>39</v>
       </c>
       <c r="D5" s="26">
-        <f>IF(=PROFIL!B3&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
+        <f>IF(PROFIL!B3&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E5" s="27" t="s">
@@ -4303,7 +4303,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="26">
-        <f>IF(=PROFIL!B4&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
+        <f>IF(PROFIL!B4&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E6" s="27" t="s">
@@ -4321,7 +4321,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="26">
-        <f>IF(=PROFIL!B5&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
+        <f>IF(PROFIL!B5&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E7" s="27" t="s">
@@ -4339,7 +4339,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="26">
-        <f>IF(=PROFIL!B6&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
+        <f>IF(PROFIL!B6&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E8" s="27" t="s">
@@ -4366,7 +4366,7 @@
         <v>52</v>
       </c>
       <c r="D10" s="26">
-        <f>IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E10" s="27" t="s">
@@ -4384,7 +4384,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="26">
-        <f>IF(=AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E11" s="27" t="s">
@@ -4402,7 +4402,7 @@
         <v>58</v>
       </c>
       <c r="D12" s="26">
-        <f>IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E12" s="27" t="s">
@@ -4429,7 +4429,7 @@
         <v>62</v>
       </c>
       <c r="D14" s="26">
-        <f>IF(=ISNUMBER(ETUDE!B24),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B24),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E14" s="27" t="s">
@@ -4447,7 +4447,7 @@
         <v>65</v>
       </c>
       <c r="D15" s="26">
-        <f>IF(=ISNUMBER(ETUDE!B25),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B25),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E15" s="27" t="s">
@@ -4465,7 +4465,7 @@
         <v>68</v>
       </c>
       <c r="D16" s="26">
-        <f>IF(=ISNUMBER(ETUDE!B26),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B26),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E16" s="27" t="s">
@@ -4483,7 +4483,7 @@
         <v>71</v>
       </c>
       <c r="D17" s="26">
-        <f>IF(=ISNUMBER(ETUDE!B28),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B28),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E17" s="27" t="s">
@@ -4510,7 +4510,7 @@
         <v>75</v>
       </c>
       <c r="D19" s="26">
-        <f>IF(=ISNUMBER(ETUDE!B43),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B43),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E19" s="27" t="s">
@@ -4537,7 +4537,7 @@
         <v>79</v>
       </c>
       <c r="D21" s="26">
-        <f>IF(=AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E21" s="27" t="s">
@@ -4555,7 +4555,7 @@
         <v>82</v>
       </c>
       <c r="D22" s="26">
-        <f>IF(=AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E22" s="27" t="s">
@@ -4582,7 +4582,7 @@
         <v>86</v>
       </c>
       <c r="D24" s="26">
-        <f>IF(=AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E24" s="27" t="s">
@@ -4609,7 +4609,7 @@
         <v>91</v>
       </c>
       <c r="D26" s="28">
-        <f>IF(=ISNUMBER(ETUDE!B307),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B307),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E26" s="27" t="s">
@@ -4627,7 +4627,7 @@
         <v>94</v>
       </c>
       <c r="D27" s="28">
-        <f>IF(=ISNUMBER(ETUDE!B128),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(ETUDE!B128),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E27" s="27" t="s">
@@ -4645,7 +4645,7 @@
         <v>97</v>
       </c>
       <c r="D28" s="28">
-        <f>IF(=ISNUMBER(PROFIL!B48),"✓ Rempli","✗ Manquant")</f>
+        <f>IF(ISNUMBER(PROFIL!B48),"✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E28" s="27" t="s">
@@ -4663,7 +4663,7 @@
         <v>100</v>
       </c>
       <c r="D29" s="28">
-        <f>IF(=ETUDE!A254&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
+        <f>IF(ETUDE!A254&lt;&gt;"","✓ Rempli","✗ Manquant")</f>
         <v>0</v>
       </c>
       <c r="E29" s="27" t="s">
@@ -4678,11 +4678,11 @@
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
       <c r="D31" s="30">
-        <f>IFERROR(IF(=PROFIL!B3&lt;&gt;"",1,0)+IF(=PROFIL!B4&lt;&gt;"",1,0)+IF(=PROFIL!B5&lt;&gt;"",1,0)+IF(=PROFIL!B6&lt;&gt;"",1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(=AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(=ISNUMBER(ETUDE!B24),1,0)+IF(=ISNUMBER(ETUDE!B25),1,0)+IF(=ISNUMBER(ETUDE!B26),1,0)+IF(=ISNUMBER(ETUDE!B28),1,0)+IF(=ISNUMBER(ETUDE!B43),1,0)+IF(=AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(=AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(=AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0)&amp;"/15 etapes remplies","")</f>
+        <f>IFERROR(IF(PROFIL!B3&lt;&gt;"",1,0)+IF(PROFIL!B4&lt;&gt;"",1,0)+IF(PROFIL!B5&lt;&gt;"",1,0)+IF(PROFIL!B6&lt;&gt;"",1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(ISNUMBER(ETUDE!B24),1,0)+IF(ISNUMBER(ETUDE!B25),1,0)+IF(ISNUMBER(ETUDE!B26),1,0)+IF(ISNUMBER(ETUDE!B28),1,0)+IF(ISNUMBER(ETUDE!B43),1,0)+IF(AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0)&amp;"/15 etapes remplies","")</f>
         <v>0</v>
       </c>
       <c r="E31" s="31">
-        <f>IFERROR(IF((IF(=PROFIL!B3&lt;&gt;"",1,0)+IF(=PROFIL!B4&lt;&gt;"",1,0)+IF(=PROFIL!B5&lt;&gt;"",1,0)+IF(=PROFIL!B6&lt;&gt;"",1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(=AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(=ISNUMBER(ETUDE!B24),1,0)+IF(=ISNUMBER(ETUDE!B25),1,0)+IF(=ISNUMBER(ETUDE!B26),1,0)+IF(=ISNUMBER(ETUDE!B28),1,0)+IF(=ISNUMBER(ETUDE!B43),1,0)+IF(=AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(=AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(=AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=1,"Analyse complete — pret pour le RAPPORT",IF((IF(=PROFIL!B3&lt;&gt;"",1,0)+IF(=PROFIL!B4&lt;&gt;"",1,0)+IF(=PROFIL!B5&lt;&gt;"",1,0)+IF(=PROFIL!B6&lt;&gt;"",1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(=AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(=ISNUMBER(ETUDE!B24),1,0)+IF(=ISNUMBER(ETUDE!B25),1,0)+IF(=ISNUMBER(ETUDE!B26),1,0)+IF(=ISNUMBER(ETUDE!B28),1,0)+IF(=ISNUMBER(ETUDE!B43),1,0)+IF(=AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(=AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(=AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=0.8,"Bonne avancee — finaliser les etapes manquantes",IF((IF(=PROFIL!B3&lt;&gt;"",1,0)+IF(=PROFIL!B4&lt;&gt;"",1,0)+IF(=PROFIL!B5&lt;&gt;"",1,0)+IF(=PROFIL!B6&lt;&gt;"",1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(=AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(=AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(=ISNUMBER(ETUDE!B24),1,0)+IF(=ISNUMBER(ETUDE!B25),1,0)+IF(=ISNUMBER(ETUDE!B26),1,0)+IF(=ISNUMBER(ETUDE!B28),1,0)+IF(=ISNUMBER(ETUDE!B43),1,0)+IF(=AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(=AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(=AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=0.5,"En cours — saisir les donnees financieres prioritaires","Demarrer : PROFIL &gt; Nom + Ticker + Secteur"))),"")</f>
+        <f>IFERROR(IF((IF(PROFIL!B3&lt;&gt;"",1,0)+IF(PROFIL!B4&lt;&gt;"",1,0)+IF(PROFIL!B5&lt;&gt;"",1,0)+IF(PROFIL!B6&lt;&gt;"",1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(ISNUMBER(ETUDE!B24),1,0)+IF(ISNUMBER(ETUDE!B25),1,0)+IF(ISNUMBER(ETUDE!B26),1,0)+IF(ISNUMBER(ETUDE!B28),1,0)+IF(ISNUMBER(ETUDE!B43),1,0)+IF(AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=1,"Analyse complete — pret pour le RAPPORT",IF((IF(PROFIL!B3&lt;&gt;"",1,0)+IF(PROFIL!B4&lt;&gt;"",1,0)+IF(PROFIL!B5&lt;&gt;"",1,0)+IF(PROFIL!B6&lt;&gt;"",1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(ISNUMBER(ETUDE!B24),1,0)+IF(ISNUMBER(ETUDE!B25),1,0)+IF(ISNUMBER(ETUDE!B26),1,0)+IF(ISNUMBER(ETUDE!B28),1,0)+IF(ISNUMBER(ETUDE!B43),1,0)+IF(AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=0.8,"Bonne avancee — finaliser les etapes manquantes",IF((IF(PROFIL!B3&lt;&gt;"",1,0)+IF(PROFIL!B4&lt;&gt;"",1,0)+IF(PROFIL!B5&lt;&gt;"",1,0)+IF(PROFIL!B6&lt;&gt;"",1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!F8)),1,0)+IF(AND(ISNUMBER(ETUDE!B12),ISNUMBER(ETUDE!F12)),1,0)+IF(AND(ISNUMBER(ETUDE!B8),ISNUMBER(ETUDE!B12)),1,0)+IF(ISNUMBER(ETUDE!B24),1,0)+IF(ISNUMBER(ETUDE!B25),1,0)+IF(ISNUMBER(ETUDE!B26),1,0)+IF(ISNUMBER(ETUDE!B28),1,0)+IF(ISNUMBER(ETUDE!B43),1,0)+IF(AND(ISNUMBER(PROFIL!B40),ISNUMBER(PROFIL!B42)),1,0)+IF(AND(ISNUMBER(PROFIL!B44),ISNUMBER(PROFIL!B45)),1,0)+IF(AND(ISNUMBER(PROFIL!B52),ISNUMBER(PROFIL!B53)),1,0))/15&gt;=0.5,"En cours — saisir les donnees financieres prioritaires","Demarrer : PROFIL &gt; Nom + Ticker + Secteur"))),"")</f>
         <v>0</v>
       </c>
     </row>

--- a/brvm-analyzer/etudes_actions_v2.xlsx
+++ b/brvm-analyzer/etudes_actions_v2.xlsx
@@ -10037,7 +10037,7 @@
   <sheetPr>
     <tabColor rgb="FF059669"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -10558,137 +10558,427 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="5" customHeight="1"/>
-    <row r="21" spans="1:12" ht="22" customHeight="1">
-      <c r="A21" s="50" t="s">
+    <row r="20" spans="1:12" ht="20" customHeight="1">
+      <c r="A20" s="121"/>
+      <c r="B20" s="121"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="122"/>
+      <c r="F20" s="122"/>
+      <c r="G20" s="122"/>
+      <c r="H20" s="123">
+        <f>IFERROR(IF(A20="","",C20*D20*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="123">
+        <f>IFERROR(IF(A20="","",C20*E20),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="123">
+        <f>IFERROR(IF(A20="","",(C20*E20)-(C20*D20*1.014)+(C20*F20)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="124">
+        <f>IFERROR(IF(A20="","",J20/H20*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="125">
+        <f>IFERROR(IF(A20="","—",IF(K20&lt;-10,"VENDRE — Stop-loss",IF(AND(G20&gt;=24,K20&gt;=0),"RENFORCER",IF(AND(G20&gt;=15,K20&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="20" customHeight="1">
+      <c r="A21" s="121"/>
+      <c r="B21" s="121"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="122"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="123">
+        <f>IFERROR(IF(A21="","",C21*D21*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="123">
+        <f>IFERROR(IF(A21="","",C21*E21),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="123">
+        <f>IFERROR(IF(A21="","",(C21*E21)-(C21*D21*1.014)+(C21*F21)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="124">
+        <f>IFERROR(IF(A21="","",J21/H21*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="125">
+        <f>IFERROR(IF(A21="","—",IF(K21&lt;-10,"VENDRE — Stop-loss",IF(AND(G21&gt;=24,K21&gt;=0),"RENFORCER",IF(AND(G21&gt;=15,K21&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="20" customHeight="1">
+      <c r="A22" s="121"/>
+      <c r="B22" s="121"/>
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="122"/>
+      <c r="G22" s="122"/>
+      <c r="H22" s="123">
+        <f>IFERROR(IF(A22="","",C22*D22*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="123">
+        <f>IFERROR(IF(A22="","",C22*E22),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="123">
+        <f>IFERROR(IF(A22="","",(C22*E22)-(C22*D22*1.014)+(C22*F22)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="124">
+        <f>IFERROR(IF(A22="","",J22/H22*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="125">
+        <f>IFERROR(IF(A22="","—",IF(K22&lt;-10,"VENDRE — Stop-loss",IF(AND(G22&gt;=24,K22&gt;=0),"RENFORCER",IF(AND(G22&gt;=15,K22&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="20" customHeight="1">
+      <c r="A23" s="121"/>
+      <c r="B23" s="121"/>
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="122"/>
+      <c r="G23" s="122"/>
+      <c r="H23" s="123">
+        <f>IFERROR(IF(A23="","",C23*D23*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="123">
+        <f>IFERROR(IF(A23="","",C23*E23),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="123">
+        <f>IFERROR(IF(A23="","",(C23*E23)-(C23*D23*1.014)+(C23*F23)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="124">
+        <f>IFERROR(IF(A23="","",J23/H23*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="125">
+        <f>IFERROR(IF(A23="","—",IF(K23&lt;-10,"VENDRE — Stop-loss",IF(AND(G23&gt;=24,K23&gt;=0),"RENFORCER",IF(AND(G23&gt;=15,K23&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20" customHeight="1">
+      <c r="A24" s="121"/>
+      <c r="B24" s="121"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
+      <c r="H24" s="123">
+        <f>IFERROR(IF(A24="","",C24*D24*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="123">
+        <f>IFERROR(IF(A24="","",C24*E24),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="123">
+        <f>IFERROR(IF(A24="","",(C24*E24)-(C24*D24*1.014)+(C24*F24)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K24" s="124">
+        <f>IFERROR(IF(A24="","",J24/H24*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="125">
+        <f>IFERROR(IF(A24="","—",IF(K24&lt;-10,"VENDRE — Stop-loss",IF(AND(G24&gt;=24,K24&gt;=0),"RENFORCER",IF(AND(G24&gt;=15,K24&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20" customHeight="1">
+      <c r="A25" s="121"/>
+      <c r="B25" s="121"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="122"/>
+      <c r="G25" s="122"/>
+      <c r="H25" s="123">
+        <f>IFERROR(IF(A25="","",C25*D25*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="123">
+        <f>IFERROR(IF(A25="","",C25*E25),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="123">
+        <f>IFERROR(IF(A25="","",(C25*E25)-(C25*D25*1.014)+(C25*F25)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="124">
+        <f>IFERROR(IF(A25="","",J25/H25*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="125">
+        <f>IFERROR(IF(A25="","—",IF(K25&lt;-10,"VENDRE — Stop-loss",IF(AND(G25&gt;=24,K25&gt;=0),"RENFORCER",IF(AND(G25&gt;=15,K25&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="20" customHeight="1">
+      <c r="A26" s="121"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="122"/>
+      <c r="G26" s="122"/>
+      <c r="H26" s="123">
+        <f>IFERROR(IF(A26="","",C26*D26*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="123">
+        <f>IFERROR(IF(A26="","",C26*E26),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="123">
+        <f>IFERROR(IF(A26="","",(C26*E26)-(C26*D26*1.014)+(C26*F26)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="124">
+        <f>IFERROR(IF(A26="","",J26/H26*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="125">
+        <f>IFERROR(IF(A26="","—",IF(K26&lt;-10,"VENDRE — Stop-loss",IF(AND(G26&gt;=24,K26&gt;=0),"RENFORCER",IF(AND(G26&gt;=15,K26&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="20" customHeight="1">
+      <c r="A27" s="121"/>
+      <c r="B27" s="121"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="123">
+        <f>IFERROR(IF(A27="","",C27*D27*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="123">
+        <f>IFERROR(IF(A27="","",C27*E27),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="123">
+        <f>IFERROR(IF(A27="","",(C27*E27)-(C27*D27*1.014)+(C27*F27)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="124">
+        <f>IFERROR(IF(A27="","",J27/H27*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="125">
+        <f>IFERROR(IF(A27="","—",IF(K27&lt;-10,"VENDRE — Stop-loss",IF(AND(G27&gt;=24,K27&gt;=0),"RENFORCER",IF(AND(G27&gt;=15,K27&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="20" customHeight="1">
+      <c r="A28" s="121"/>
+      <c r="B28" s="121"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="122"/>
+      <c r="G28" s="122"/>
+      <c r="H28" s="123">
+        <f>IFERROR(IF(A28="","",C28*D28*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="123">
+        <f>IFERROR(IF(A28="","",C28*E28),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="123">
+        <f>IFERROR(IF(A28="","",(C28*E28)-(C28*D28*1.014)+(C28*F28)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="124">
+        <f>IFERROR(IF(A28="","",J28/H28*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="125">
+        <f>IFERROR(IF(A28="","—",IF(K28&lt;-10,"VENDRE — Stop-loss",IF(AND(G28&gt;=24,K28&gt;=0),"RENFORCER",IF(AND(G28&gt;=15,K28&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="20" customHeight="1">
+      <c r="A29" s="121"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="123">
+        <f>IFERROR(IF(A29="","",C29*D29*1.014),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="123">
+        <f>IFERROR(IF(A29="","",C29*E29),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="123">
+        <f>IFERROR(IF(A29="","",(C29*E29)-(C29*D29*1.014)+(C29*F29)),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="124">
+        <f>IFERROR(IF(A29="","",J29/H29*100),"")</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="125">
+        <f>IFERROR(IF(A29="","—",IF(K29&lt;-10,"VENDRE — Stop-loss",IF(AND(G29&gt;=24,K29&gt;=0),"RENFORCER",IF(AND(G29&gt;=15,K29&gt;=-5),"CONSERVER","SURVEILLER")))),"—")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="5" customHeight="1"/>
+    <row r="31" spans="1:12" ht="22" customHeight="1">
+      <c r="A31" s="50" t="s">
         <v>573</v>
       </c>
-      <c r="B21" s="126"/>
-      <c r="C21" s="126"/>
-      <c r="D21" s="126"/>
-      <c r="E21" s="126"/>
-      <c r="F21" s="126"/>
-      <c r="G21" s="126"/>
-      <c r="H21" s="127">
-        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",H5:H19),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="127">
-        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",I5:I19),"")</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="127">
-        <f>IFERROR(SUMIF(A5:A19,"&lt;&gt;",J5:J19),"")</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="128">
-        <f>IFERROR(J21/H21*100,"")</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="125">
-        <f>IFERROR(IF(J21/H21*100&gt;15,"Portefeuille PERFORMANT",IF(J21/H21*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="8" customHeight="1"/>
-    <row r="23" spans="1:12" ht="18" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="B31" s="126"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="126"/>
+      <c r="H31" s="127">
+        <f>IFERROR(SUMIF(A5:A29,"&lt;&gt;",H5:H29),"")</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="127">
+        <f>IFERROR(SUMIF(A5:A29,"&lt;&gt;",I5:I29),"")</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="127">
+        <f>IFERROR(SUMIF(A5:A29,"&lt;&gt;",J5:J29),"")</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="128">
+        <f>IFERROR(J31/H31*100,"")</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="125">
+        <f>IFERROR(IF(J31/H31*100&gt;15,"Portefeuille PERFORMANT",IF(J31/H31*100&gt;0,"Portefeuille POSITIF","Portefeuille EN PERTE")),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="8" customHeight="1"/>
+    <row r="33" spans="1:12" ht="18" customHeight="1">
+      <c r="A33" s="22" t="s">
         <v>574</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-    </row>
-    <row r="24" spans="1:12" ht="16" customHeight="1">
-      <c r="A24" s="129" t="s">
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+    </row>
+    <row r="34" spans="1:12" ht="16" customHeight="1">
+      <c r="A34" s="129" t="s">
         <v>575</v>
       </c>
-      <c r="B24" s="130" t="s">
+      <c r="B34" s="130" t="s">
         <v>576</v>
       </c>
-      <c r="C24" s="130"/>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="130"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="130"/>
-    </row>
-    <row r="25" spans="1:12" ht="16" customHeight="1">
-      <c r="A25" s="129" t="s">
+      <c r="C34" s="130"/>
+      <c r="D34" s="130"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="130"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
+      <c r="J34" s="130"/>
+      <c r="K34" s="130"/>
+      <c r="L34" s="130"/>
+    </row>
+    <row r="35" spans="1:12" ht="16" customHeight="1">
+      <c r="A35" s="129" t="s">
         <v>577</v>
       </c>
-      <c r="B25" s="130" t="s">
+      <c r="B35" s="130" t="s">
         <v>578</v>
       </c>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="130"/>
-      <c r="I25" s="130"/>
-      <c r="J25" s="130"/>
-      <c r="K25" s="130"/>
-      <c r="L25" s="130"/>
-    </row>
-    <row r="26" spans="1:12" ht="16" customHeight="1">
-      <c r="A26" s="129" t="s">
+      <c r="C35" s="130"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="130"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="130"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="130"/>
+      <c r="L35" s="130"/>
+    </row>
+    <row r="36" spans="1:12" ht="16" customHeight="1">
+      <c r="A36" s="129" t="s">
         <v>579</v>
       </c>
-      <c r="B26" s="130" t="s">
+      <c r="B36" s="130" t="s">
         <v>580</v>
       </c>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="130"/>
-      <c r="L26" s="130"/>
-    </row>
-    <row r="27" spans="1:12" ht="16" customHeight="1">
-      <c r="A27" s="129" t="s">
+      <c r="C36" s="130"/>
+      <c r="D36" s="130"/>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="130"/>
+      <c r="H36" s="130"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="130"/>
+      <c r="K36" s="130"/>
+      <c r="L36" s="130"/>
+    </row>
+    <row r="37" spans="1:12" ht="16" customHeight="1">
+      <c r="A37" s="129" t="s">
         <v>581</v>
       </c>
-      <c r="B27" s="130" t="s">
+      <c r="B37" s="130" t="s">
         <v>582</v>
       </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="130"/>
-      <c r="L27" s="130"/>
+      <c r="C37" s="130"/>
+      <c r="D37" s="130"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="130"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="130"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="130"/>
+      <c r="L37" s="130"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="7">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="B24:L24"/>
-    <mergeCell ref="B25:L25"/>
-    <mergeCell ref="B26:L26"/>
-    <mergeCell ref="B27:L27"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B35:L35"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B37:L37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
